--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -3088,7 +3088,7 @@
         <v/>
       </c>
       <c r="F65" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V1(20.4)</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -3123,7 +3123,7 @@
         <v/>
       </c>
       <c r="F66" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V1(20.4)</v>
       </c>
       <c r="G66" t="str">
         <v/>

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -64,7 +64,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -123,11 +123,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF333333"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFAA1F1"/>
       </patternFill>
     </fill>
@@ -143,6 +138,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFF5AC4"/>
       </patternFill>
     </fill>
@@ -154,6 +154,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF757575"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7F5347"/>
       </patternFill>
     </fill>
     <fill>
@@ -179,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -251,6 +256,9 @@
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -264,7 +272,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -719,7 +727,7 @@
         <v/>
       </c>
       <c r="H4" s="6" t="str">
-        <v>V1(20.4)</v>
+        <v>V1(20.4), V2(4.5)</v>
       </c>
       <c r="I4" s="6" t="str">
         <v>Card vs IBAN MNGT</v>
@@ -1023,7 +1031,7 @@
         <v/>
       </c>
       <c r="F12" s="6" t="str">
-        <v>V1(20.4)</v>
+        <v>V1(20.4), V2(4.5)</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1561,7 +1569,7 @@
         <v/>
       </c>
       <c r="B26" s="4" t="str">
-        <v>Execution pop-up - move funds- Roy- Ilan to check status</v>
+        <v>Execution pop-up  Open &amp; close - move funds- Roy- Ilan to check status</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -1871,8 +1879,8 @@
       <c r="C33" s="6" t="str">
         <v>Noit Hoffman, Joanna Fajga</v>
       </c>
-      <c r="D33" s="17" t="str">
-        <v>Grooming</v>
+      <c r="D33" s="16" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E33" s="6" t="str">
         <v/>
@@ -2221,7 +2229,7 @@
       <c r="C43" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D43" s="18" t="str">
+      <c r="D43" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E43" s="6" t="str">
@@ -2256,7 +2264,7 @@
       <c r="C44" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D44" s="18" t="str">
+      <c r="D44" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E44" s="6" t="str">
@@ -2291,7 +2299,7 @@
       <c r="C45" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D45" s="18" t="str">
+      <c r="D45" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E45" s="6" t="str">
@@ -2361,7 +2369,7 @@
       <c r="C47" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D47" s="19" t="str">
+      <c r="D47" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E47" s="6" t="str">
@@ -2396,7 +2404,7 @@
       <c r="C48" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D48" s="19" t="str">
+      <c r="D48" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E48" s="6" t="str">
@@ -2431,7 +2439,7 @@
       <c r="C49" t="str">
         <v/>
       </c>
-      <c r="D49" s="19" t="str">
+      <c r="D49" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E49" s="6" t="str">
@@ -2566,7 +2574,7 @@
       <c r="C52" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D52" s="19" t="str">
+      <c r="D52" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E52" s="6" t="str">
@@ -2601,7 +2609,7 @@
       <c r="C53" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D53" s="19" t="str">
+      <c r="D53" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E53" s="6" t="str">
@@ -2636,7 +2644,7 @@
       <c r="C54" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D54" s="19" t="str">
+      <c r="D54" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E54" s="6" t="str">
@@ -2671,7 +2679,7 @@
       <c r="C55" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D55" s="19" t="str">
+      <c r="D55" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E55" s="6" t="str">
@@ -2706,7 +2714,7 @@
       <c r="C56" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D56" s="19" t="str">
+      <c r="D56" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E56" s="6" t="str">
@@ -2741,7 +2749,7 @@
       <c r="C57" t="str">
         <v/>
       </c>
-      <c r="D57" s="19" t="str">
+      <c r="D57" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E57" s="6" t="str">
@@ -2773,7 +2781,7 @@
       <c r="B58" t="str">
         <v/>
       </c>
-      <c r="C58" s="19" t="str">
+      <c r="C58" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="D58" s="6" t="str">
@@ -2876,7 +2884,7 @@
       <c r="C60" t="str">
         <v/>
       </c>
-      <c r="D60" s="19" t="str">
+      <c r="D60" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E60" s="6" t="str">
@@ -2911,7 +2919,7 @@
       <c r="C61" t="str">
         <v/>
       </c>
-      <c r="D61" s="19" t="str">
+      <c r="D61" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E61" s="6" t="str">
@@ -2946,7 +2954,7 @@
       <c r="C62" t="str">
         <v/>
       </c>
-      <c r="D62" s="19" t="str">
+      <c r="D62" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E62" s="6" t="str">
@@ -2994,7 +3002,7 @@
         <v>46112</v>
       </c>
       <c r="H63" s="6" t="str">
-        <v>V2(4.5), V3(18.5)</v>
+        <v>V2(4.5), V3(18.5), V1(20.4)</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -3146,7 +3154,7 @@
         <v/>
       </c>
       <c r="B67" s="4" t="str">
-        <v>Custodial wallet crypto - New Wallet creation flow (first time)</v>
+        <v>Custodial wallet crypto - New Wallet creation flow (first time)- IDEA</v>
       </c>
       <c r="C67" s="6" t="str">
         <v>Nikolaus Kulier</v>
@@ -3326,7 +3334,7 @@
       <c r="C72" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D72" s="20" t="str">
+      <c r="D72" s="19" t="str">
         <v>Design</v>
       </c>
       <c r="E72" s="6" t="str">
@@ -3356,12 +3364,12 @@
         <v/>
       </c>
       <c r="B73" s="4" t="str">
-        <v>Custodial wallet crypto - Receive</v>
+        <v>Custodial wallet crypto - Receive -General</v>
       </c>
       <c r="C73" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D73" s="20" t="str">
+      <c r="D73" s="19" t="str">
         <v>Design</v>
       </c>
       <c r="E73" s="6" t="str">
@@ -3466,8 +3474,8 @@
       <c r="C76" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D76" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D76" s="20" t="str">
+        <v>Grooming</v>
       </c>
       <c r="E76" s="6" t="str">
         <v/>
@@ -3485,7 +3493,7 @@
         <v>46160</v>
       </c>
       <c r="J76" s="7">
-        <v>46111</v>
+        <v>46142</v>
       </c>
       <c r="K76" s="6">
         <v>2</v>
@@ -3671,8 +3679,8 @@
       <c r="C81" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D81" s="5" t="str">
-        <v>Dev - WIP</v>
+      <c r="D81" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E81" s="6" t="str">
         <v>https://etoro-jira.atlassian.net/browse/PM-214</v>
@@ -3706,8 +3714,8 @@
       <c r="C82" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D82" s="5" t="str">
-        <v>Dev - WIP</v>
+      <c r="D82" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E82" s="6" t="str">
         <v>https://etoro-jira.atlassian.net/browse/PM-215</v>
@@ -3776,8 +3784,8 @@
       <c r="C84" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D84" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D84" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E84" s="6" t="str">
         <v>https://etoro-jira.atlassian.net/browse/PM-211</v>
@@ -3811,7 +3819,7 @@
       <c r="C85" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D85" s="17" t="str">
+      <c r="D85" s="20" t="str">
         <v>Grooming</v>
       </c>
       <c r="E85" s="6" t="str">
@@ -3881,7 +3889,7 @@
       <c r="C87" t="str">
         <v/>
       </c>
-      <c r="D87" s="19" t="str">
+      <c r="D87" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E87" s="6" t="str">
@@ -3951,7 +3959,7 @@
       <c r="C89" t="str">
         <v/>
       </c>
-      <c r="D89" s="18" t="str">
+      <c r="D89" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E89" s="6" t="str">
@@ -3986,7 +3994,7 @@
       <c r="C90" t="str">
         <v/>
       </c>
-      <c r="D90" s="18" t="str">
+      <c r="D90" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E90" s="6" t="str">
@@ -4021,7 +4029,7 @@
       <c r="C91" t="str">
         <v/>
       </c>
-      <c r="D91" s="18" t="str">
+      <c r="D91" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E91" s="6" t="str">
@@ -4226,7 +4234,7 @@
       <c r="C96" t="str">
         <v/>
       </c>
-      <c r="D96" s="17" t="str">
+      <c r="D96" s="20" t="str">
         <v>Grooming</v>
       </c>
       <c r="E96" s="6" t="str">
@@ -4261,7 +4269,7 @@
       <c r="C97" t="str">
         <v/>
       </c>
-      <c r="D97" s="19" t="str">
+      <c r="D97" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E97" s="6" t="str">
@@ -4391,7 +4399,7 @@
         <v/>
       </c>
       <c r="B100" s="4" t="str">
-        <v>Manage Card - Home</v>
+        <v>Manage Card - Home/Main screen</v>
       </c>
       <c r="C100" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
@@ -4571,7 +4579,7 @@
       <c r="C105" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D105" s="17" t="str">
+      <c r="D105" s="20" t="str">
         <v>Grooming</v>
       </c>
       <c r="E105" s="6" t="str">
@@ -4606,7 +4614,7 @@
       <c r="C106" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D106" s="17" t="str">
+      <c r="D106" s="20" t="str">
         <v>Grooming</v>
       </c>
       <c r="E106" s="6" t="str">
@@ -4641,7 +4649,7 @@
       <c r="C107" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D107" s="17" t="str">
+      <c r="D107" s="20" t="str">
         <v>Grooming</v>
       </c>
       <c r="E107" s="6" t="str">
@@ -4676,7 +4684,7 @@
       <c r="C108" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D108" s="17" t="str">
+      <c r="D108" s="20" t="str">
         <v>Grooming</v>
       </c>
       <c r="E108" s="6" t="str">
@@ -4746,7 +4754,7 @@
       <c r="C110" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D110" s="17" t="str">
+      <c r="D110" s="20" t="str">
         <v>Grooming</v>
       </c>
       <c r="E110" s="6" t="str">
@@ -4781,7 +4789,7 @@
       <c r="C111" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D111" s="18" t="str">
+      <c r="D111" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E111" s="6" t="str">
@@ -4813,8 +4821,8 @@
       <c r="B112" t="str">
         <v/>
       </c>
-      <c r="C112" s="14" t="str">
-        <v>Discovery</v>
+      <c r="C112" s="24" t="str">
+        <v>Dependency</v>
       </c>
       <c r="D112" t="str">
         <v/>
@@ -4981,7 +4989,7 @@
       <c r="C115" t="str">
         <v/>
       </c>
-      <c r="D115" s="19" t="str">
+      <c r="D115" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E115" s="6" t="str">
@@ -5016,7 +5024,7 @@
       <c r="C116" t="str">
         <v/>
       </c>
-      <c r="D116" s="19" t="str">
+      <c r="D116" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E116" s="6" t="str">
@@ -5048,7 +5056,7 @@
       <c r="B117" t="str">
         <v/>
       </c>
-      <c r="C117" s="19" t="str">
+      <c r="C117" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="D117" s="6" t="str">
@@ -5113,8 +5121,8 @@
       <c r="B118" t="str">
         <v/>
       </c>
-      <c r="C118" s="14" t="str">
-        <v>Discovery</v>
+      <c r="C118" s="22" t="str">
+        <v>Managed by other team</v>
       </c>
       <c r="D118" t="str">
         <v/>
@@ -5216,8 +5224,8 @@
       <c r="C120" t="str">
         <v/>
       </c>
-      <c r="D120" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D120" s="14" t="str">
+        <v>Handle by other team</v>
       </c>
       <c r="E120" s="6" t="str">
         <v/>
@@ -5251,8 +5259,8 @@
       <c r="C121" t="str">
         <v/>
       </c>
-      <c r="D121" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D121" s="14" t="str">
+        <v>Handle by other team</v>
       </c>
       <c r="E121" s="6" t="str">
         <v/>
@@ -5286,7 +5294,7 @@
       <c r="C122" t="str">
         <v/>
       </c>
-      <c r="D122" s="18" t="str">
+      <c r="D122" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E122" s="6" t="str">
@@ -5551,8 +5559,8 @@
       <c r="C127" s="6" t="str">
         <v>Hagit Zamir</v>
       </c>
-      <c r="D127" s="24" t="str">
-        <v>deployment</v>
+      <c r="D127" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E127" s="6" t="str">
         <v/>
@@ -5586,7 +5594,7 @@
       <c r="C128" t="str">
         <v/>
       </c>
-      <c r="D128" s="24" t="str">
+      <c r="D128" s="25" t="str">
         <v>deployment</v>
       </c>
       <c r="E128" s="6" t="str">
@@ -5656,7 +5664,7 @@
       <c r="C130" t="str">
         <v/>
       </c>
-      <c r="D130" s="19" t="str">
+      <c r="D130" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E130" s="6" t="str">
@@ -5691,7 +5699,7 @@
       <c r="C131" t="str">
         <v/>
       </c>
-      <c r="D131" s="19" t="str">
+      <c r="D131" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="E131" s="6" t="str">
@@ -5726,7 +5734,7 @@
       <c r="C132" s="6" t="str">
         <v>Eyal Boas</v>
       </c>
-      <c r="D132" s="18" t="str">
+      <c r="D132" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E132" s="6" t="str">
@@ -5761,7 +5769,7 @@
       <c r="C133" t="str">
         <v/>
       </c>
-      <c r="D133" s="18" t="str">
+      <c r="D133" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E133" s="6" t="str">
@@ -5796,7 +5804,7 @@
       <c r="C134" s="6" t="str">
         <v>Eyal Boas</v>
       </c>
-      <c r="D134" s="18" t="str">
+      <c r="D134" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E134" s="6" t="str">
@@ -5831,7 +5839,7 @@
       <c r="C135" t="str">
         <v/>
       </c>
-      <c r="D135" s="18" t="str">
+      <c r="D135" s="17" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E135" s="6" t="str">
@@ -5872,10 +5880,10 @@
       <c r="E136" t="str">
         <v/>
       </c>
-      <c r="F136" s="25">
+      <c r="F136" s="26">
         <v>46061</v>
       </c>
-      <c r="G136" s="25">
+      <c r="G136" s="26">
         <v>46141</v>
       </c>
       <c r="H136" t="str">
@@ -5893,7 +5901,7 @@
       <c r="L136" t="str">
         <v/>
       </c>
-      <c r="M136" s="26">
+      <c r="M136" s="27">
         <v>37</v>
       </c>
       <c r="N136" t="str">
@@ -5905,25 +5913,25 @@
       <c r="P136" t="str">
         <v/>
       </c>
-      <c r="Q136" s="27" t="str">
+      <c r="Q136" s="28" t="str">
         <v>2026-02-02 to 2026-04-15</v>
       </c>
       <c r="R136" t="str">
         <v/>
       </c>
-      <c r="S136" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T136" s="25">
+      <c r="S136" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T136" s="26">
         <v>46058</v>
       </c>
-      <c r="U136" s="25">
+      <c r="U136" s="26">
         <v>46114</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="138" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="29" t="str">
+      <c r="A138" s="30" t="str">
         <v>In Focus</v>
       </c>
     </row>
@@ -6124,7 +6132,7 @@
     </row>
     <row r="142" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="str">
-        <v>Compliance new requirement- to display the entity behind every balance</v>
+        <v>Deleaniation - Compliance new requirement- to display the entity behind every balance</v>
       </c>
       <c r="B142" t="str">
         <v/>
@@ -6194,7 +6202,7 @@
       <c r="B143" t="str">
         <v/>
       </c>
-      <c r="C143" s="30" t="str">
+      <c r="C143" s="31" t="str">
         <v>Risk</v>
       </c>
       <c r="D143" t="str">
@@ -7438,10 +7446,10 @@
       <c r="E162" t="str">
         <v/>
       </c>
-      <c r="F162" s="25">
+      <c r="F162" s="26">
         <v>46054</v>
       </c>
-      <c r="G162" s="25">
+      <c r="G162" s="26">
         <v>46118</v>
       </c>
       <c r="H162" t="str">
@@ -7459,7 +7467,7 @@
       <c r="L162" t="str">
         <v/>
       </c>
-      <c r="M162" s="26">
+      <c r="M162" s="27">
         <v>0</v>
       </c>
       <c r="N162" t="str">
@@ -7471,25 +7479,25 @@
       <c r="P162" t="str">
         <v/>
       </c>
-      <c r="Q162" s="28" t="str">
+      <c r="Q162" s="29" t="str">
         <v/>
       </c>
       <c r="R162" t="str">
         <v/>
       </c>
-      <c r="S162" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T162" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U162" s="28" t="str">
+      <c r="S162" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T162" s="29" t="str">
+        <v/>
+      </c>
+      <c r="U162" s="29" t="str">
         <v/>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="164" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="31" t="str">
+      <c r="A164" s="32" t="str">
         <v>MVP - API /BFF project</v>
       </c>
     </row>
@@ -7565,8 +7573,8 @@
       <c r="B166" t="str">
         <v/>
       </c>
-      <c r="C166" s="16" t="str">
-        <v>Deployment</v>
+      <c r="C166" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D166" s="6" t="str">
         <v>ApiForPlus</v>
@@ -7738,8 +7746,8 @@
       <c r="C170" s="6" t="str">
         <v>Hagit Zamir</v>
       </c>
-      <c r="D170" s="24" t="str">
-        <v>deployment</v>
+      <c r="D170" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E170" s="6" t="str">
         <v/>
@@ -7843,8 +7851,8 @@
       <c r="C173" t="str">
         <v/>
       </c>
-      <c r="D173" s="19" t="str">
-        <v>Not Started</v>
+      <c r="D173" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E173" s="6" t="str">
         <v/>
@@ -7868,80 +7876,50 @@
         <v/>
       </c>
     </row>
-    <row r="174" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A174" s="4" t="str">
-        <v>EOD Balance- Maksym PAYUA-7769</v>
-      </c>
-      <c r="B174" t="str">
-        <v/>
-      </c>
-      <c r="C174" s="16" t="str">
-        <v>Deployment</v>
-      </c>
-      <c r="D174" s="6" t="str">
-        <v>ApiForPlus</v>
-      </c>
-      <c r="E174" t="str">
-        <v/>
-      </c>
-      <c r="F174" s="8">
-        <v>46042</v>
-      </c>
-      <c r="G174" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H174" s="6" t="str">
-        <v>V2(4.5)</v>
-      </c>
-      <c r="I174" s="6" t="str">
-        <v>Need data to expose historical balances</v>
-      </c>
-      <c r="J174" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K174" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L174" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M174" s="6">
-        <v>2</v>
-      </c>
-      <c r="N174" s="6" t="str">
-        <v>XS</v>
-      </c>
-      <c r="O174" t="str">
-        <v/>
-      </c>
-      <c r="P174" t="str">
-        <v/>
-      </c>
-      <c r="Q174" t="str">
-        <v/>
-      </c>
-      <c r="R174" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
-      </c>
-      <c r="S174" t="str">
-        <v/>
-      </c>
-      <c r="T174" t="str">
-        <v/>
-      </c>
-      <c r="U174" t="str">
+    <row r="174" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" t="str">
+        <v/>
+      </c>
+      <c r="B174" s="4" t="str">
+        <v>Communicate with Exp ( Filipe/Renata) to implement it</v>
+      </c>
+      <c r="C174" t="str">
+        <v/>
+      </c>
+      <c r="D174" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="E174" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F174" t="str">
+        <v/>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+      <c r="H174" t="str">
+        <v/>
+      </c>
+      <c r="I174" t="str">
+        <v/>
+      </c>
+      <c r="J174" t="str">
+        <v/>
+      </c>
+      <c r="K174" t="str">
         <v/>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="str">
-        <v>Deposit APIs (using existing) +Payment Eligibility +Funding</v>
+        <v>EOD Balance- Maksym PAYUA-7769</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
-      <c r="C175" s="11" t="str">
-        <v>Done</v>
+      <c r="C175" s="16" t="str">
+        <v>Deployment</v>
       </c>
       <c r="D175" s="6" t="str">
         <v>ApiForPlus</v>
@@ -7950,16 +7928,16 @@
         <v/>
       </c>
       <c r="F175" s="8">
-        <v>46040</v>
+        <v>46042</v>
       </c>
       <c r="G175" s="8">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="H175" s="6" t="str">
-        <v>V1(20.4)</v>
-      </c>
-      <c r="I175" t="str">
-        <v/>
+        <v>V2(4.5)</v>
+      </c>
+      <c r="I175" s="6" t="str">
+        <v>Need data to expose historical balances</v>
       </c>
       <c r="J175" s="6" t="str">
         <v/>
@@ -7968,13 +7946,13 @@
         <v/>
       </c>
       <c r="L175" s="6" t="str">
-        <v>Shuky</v>
+        <v/>
       </c>
       <c r="M175" s="6">
         <v>2</v>
       </c>
       <c r="N175" s="6" t="str">
-        <v>S</v>
+        <v>XS</v>
       </c>
       <c r="O175" t="str">
         <v/>
@@ -7998,74 +7976,104 @@
         <v/>
       </c>
     </row>
-    <row r="176" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A176" s="9" t="str">
+    <row r="176" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="str">
+        <v>Deposit APIs (using existing) +Payment Eligibility +Funding</v>
+      </c>
+      <c r="B176" t="str">
+        <v/>
+      </c>
+      <c r="C176" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="D176" s="6" t="str">
+        <v>ApiForPlus</v>
+      </c>
+      <c r="E176" t="str">
+        <v/>
+      </c>
+      <c r="F176" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G176" s="8">
+        <v>46126</v>
+      </c>
+      <c r="H176" s="6" t="str">
+        <v>V1(20.4)</v>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
+      <c r="J176" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K176" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L176" s="6" t="str">
+        <v>Shuky</v>
+      </c>
+      <c r="M176" s="6">
+        <v>2</v>
+      </c>
+      <c r="N176" s="6" t="str">
+        <v>S</v>
+      </c>
+      <c r="O176" t="str">
+        <v/>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
+      <c r="R176" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+      </c>
+      <c r="S176" t="str">
+        <v/>
+      </c>
+      <c r="T176" t="str">
+        <v/>
+      </c>
+      <c r="U176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B176" s="10" t="str">
+      <c r="B177" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C176" s="10" t="str">
+      <c r="C177" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D176" s="10" t="str">
+      <c r="D177" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E176" s="10" t="str">
+      <c r="E177" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F176" s="10" t="str">
+      <c r="F177" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G176" s="10" t="str">
+      <c r="G177" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H176" s="10" t="str">
+      <c r="H177" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I176" s="10" t="str">
+      <c r="I177" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J176" s="10" t="str">
+      <c r="J177" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K176" s="10" t="str">
+      <c r="K177" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="177" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A177" t="str">
-        <v/>
-      </c>
-      <c r="B177" s="4" t="str">
-        <v>get Eligible funding API (payment-methods/(PaymentMethodTypeId) - Shuky</v>
-      </c>
-      <c r="C177" t="str">
-        <v/>
-      </c>
-      <c r="D177" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="E177" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F177" t="str">
-        <v/>
-      </c>
-      <c r="G177" t="str">
-        <v/>
-      </c>
-      <c r="H177" t="str">
-        <v/>
-      </c>
-      <c r="I177" t="str">
-        <v/>
-      </c>
-      <c r="J177" t="str">
-        <v/>
-      </c>
-      <c r="K177" t="str">
-        <v/>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -8073,7 +8081,7 @@
         <v/>
       </c>
       <c r="B178" s="4" t="str">
-        <v>Mean of Payments (eligible-payment-method-types) API.- PAYIL-10721Shuky</v>
+        <v>get Eligible funding API (payment-methods/(PaymentMethodTypeId) - Shuky</v>
       </c>
       <c r="C178" t="str">
         <v/>
@@ -8090,11 +8098,11 @@
       <c r="G178" t="str">
         <v/>
       </c>
-      <c r="H178" s="8">
-        <v>46064</v>
-      </c>
-      <c r="I178" s="8">
-        <v>46100</v>
+      <c r="H178" t="str">
+        <v/>
+      </c>
+      <c r="I178" t="str">
+        <v/>
       </c>
       <c r="J178" t="str">
         <v/>
@@ -8108,7 +8116,7 @@
         <v/>
       </c>
       <c r="B179" s="4" t="str">
-        <v>Banking deposit MOP API- Maksym</v>
+        <v>Mean of Payments (eligible-payment-method-types) API.- PAYIL-10721Shuky</v>
       </c>
       <c r="C179" t="str">
         <v/>
@@ -8126,10 +8134,10 @@
         <v/>
       </c>
       <c r="H179" s="8">
-        <v>46055</v>
+        <v>46064</v>
       </c>
       <c r="I179" s="8">
-        <v>46125</v>
+        <v>46100</v>
       </c>
       <c r="J179" t="str">
         <v/>
@@ -8143,7 +8151,7 @@
         <v/>
       </c>
       <c r="B180" s="4" t="str">
-        <v>Swagger delivery</v>
+        <v>Banking deposit MOP API- Maksym</v>
       </c>
       <c r="C180" t="str">
         <v/>
@@ -8161,10 +8169,10 @@
         <v/>
       </c>
       <c r="H180" s="8">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="I180" s="8">
-        <v>46064</v>
+        <v>46125</v>
       </c>
       <c r="J180" t="str">
         <v/>
@@ -8178,7 +8186,7 @@
         <v/>
       </c>
       <c r="B181" s="4" t="str">
-        <v>Dictionary API- Shuky</v>
+        <v>Swagger delivery</v>
       </c>
       <c r="C181" t="str">
         <v/>
@@ -8195,11 +8203,11 @@
       <c r="G181" t="str">
         <v/>
       </c>
-      <c r="H181" t="str">
-        <v/>
-      </c>
-      <c r="I181" t="str">
-        <v/>
+      <c r="H181" s="8">
+        <v>46056</v>
+      </c>
+      <c r="I181" s="8">
+        <v>46064</v>
       </c>
       <c r="J181" t="str">
         <v/>
@@ -8213,7 +8221,7 @@
         <v/>
       </c>
       <c r="B182" s="4" t="str">
-        <v>Dictionary API- Maksym-</v>
+        <v>Dictionary API- Shuky</v>
       </c>
       <c r="C182" t="str">
         <v/>
@@ -8243,20 +8251,20 @@
         <v/>
       </c>
     </row>
-    <row r="183" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A183" s="4" t="str">
-        <v>cashflow bff - Zipi is working on it for one task</v>
-      </c>
-      <c r="B183" t="str">
-        <v/>
-      </c>
-      <c r="C183" s="5" t="str">
-        <v>FE DEV WIP</v>
-      </c>
-      <c r="D183" t="str">
-        <v/>
-      </c>
-      <c r="E183" t="str">
+    <row r="183" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A183" t="str">
+        <v/>
+      </c>
+      <c r="B183" s="4" t="str">
+        <v>Dictionary API- Maksym-</v>
+      </c>
+      <c r="C183" t="str">
+        <v/>
+      </c>
+      <c r="D183" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="E183" s="6" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
@@ -8271,52 +8279,22 @@
       <c r="I183" t="str">
         <v/>
       </c>
-      <c r="J183" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K183" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L183" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M183" s="6">
-        <v>1</v>
-      </c>
-      <c r="N183" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O183" t="str">
-        <v/>
-      </c>
-      <c r="P183" t="str">
-        <v/>
-      </c>
-      <c r="Q183" t="str">
-        <v/>
-      </c>
-      <c r="R183" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
-      </c>
-      <c r="S183" t="str">
-        <v/>
-      </c>
-      <c r="T183" t="str">
-        <v/>
-      </c>
-      <c r="U183" t="str">
+      <c r="J183" t="str">
+        <v/>
+      </c>
+      <c r="K183" t="str">
         <v/>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="str">
-        <v>deposit bff - we will start working on it soon. We are now preparing the contract</v>
+        <v>cashflow bff - Zipi is working on it for one task</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
-      <c r="C184" s="19" t="str">
-        <v>Not Started</v>
+      <c r="C184" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D184" t="str">
         <v/>
@@ -8346,7 +8324,7 @@
         <v/>
       </c>
       <c r="M184" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N184" s="6" t="str">
         <v/>
@@ -8361,7 +8339,7 @@
         <v/>
       </c>
       <c r="R184" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:17 PM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
       </c>
       <c r="S184" t="str">
         <v/>
@@ -8375,13 +8353,13 @@
     </row>
     <row r="185" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="str">
-        <v>banking bff - Amichai is working on it (for couple of tasks)</v>
+        <v>deposit bff - we will start working on it soon. We are now preparing the contract</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
-      <c r="C185" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C185" s="18" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D185" t="str">
         <v/>
@@ -8411,7 +8389,7 @@
         <v/>
       </c>
       <c r="M185" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N185" s="6" t="str">
         <v/>
@@ -8426,7 +8404,7 @@
         <v/>
       </c>
       <c r="R185" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:17 PM</v>
       </c>
       <c r="S185" t="str">
         <v/>
@@ -8440,31 +8418,31 @@
     </row>
     <row r="186" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="str">
-        <v>Financial History M&amp;A</v>
+        <v>banking bff - Amichai is working on it (for couple of tasks)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
-      <c r="C186" s="19" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="D186" s="6" t="str">
-        <v>ApiForM&amp;A</v>
+      <c r="C186" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="D186" t="str">
+        <v/>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
-      <c r="F186" s="8">
-        <v>46040</v>
-      </c>
-      <c r="G186" s="8">
-        <v>46040</v>
+      <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186" t="str">
+        <v/>
       </c>
       <c r="H186" t="str">
         <v/>
       </c>
-      <c r="I186" s="6" t="str">
-        <v>add iban mimo &amp; card trx</v>
+      <c r="I186" t="str">
+        <v/>
       </c>
       <c r="J186" s="6" t="str">
         <v/>
@@ -8475,11 +8453,11 @@
       <c r="L186" s="6" t="str">
         <v/>
       </c>
-      <c r="M186" t="str">
-        <v/>
+      <c r="M186" s="6">
+        <v>1</v>
       </c>
       <c r="N186" s="6" t="str">
-        <v>S</v>
+        <v/>
       </c>
       <c r="O186" t="str">
         <v/>
@@ -8491,7 +8469,7 @@
         <v/>
       </c>
       <c r="R186" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 10:49 AM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
       </c>
       <c r="S186" t="str">
         <v/>
@@ -8505,12 +8483,12 @@
     </row>
     <row r="187" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="str">
-        <v>IBAN (balance, account, transactions, eligibility)</v>
+        <v>Financial History M&amp;A</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
-      <c r="C187" s="19" t="str">
+      <c r="C187" s="18" t="str">
         <v>Not Started</v>
       </c>
       <c r="D187" s="6" t="str">
@@ -8519,17 +8497,17 @@
       <c r="E187" t="str">
         <v/>
       </c>
-      <c r="F187" t="str">
-        <v/>
-      </c>
-      <c r="G187" t="str">
-        <v/>
+      <c r="F187" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G187" s="8">
+        <v>46040</v>
       </c>
       <c r="H187" t="str">
         <v/>
       </c>
-      <c r="I187" t="str">
-        <v/>
+      <c r="I187" s="6" t="str">
+        <v>add iban mimo &amp; card trx</v>
       </c>
       <c r="J187" s="6" t="str">
         <v/>
@@ -8556,7 +8534,7 @@
         <v/>
       </c>
       <c r="R187" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
+        <v>Ilan Tatar Jan 28, 2026 10:49 AM</v>
       </c>
       <c r="S187" t="str">
         <v/>
@@ -8570,13 +8548,13 @@
     </row>
     <row r="188" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="str">
-        <v>Transfer (money bus)</v>
+        <v>IBAN (balance, account, transactions, eligibility)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
-      <c r="C188" s="19" t="str">
-        <v>Not Started</v>
+      <c r="C188" s="12" t="str">
+        <v>Stuck</v>
       </c>
       <c r="D188" s="6" t="str">
         <v>ApiForM&amp;A</v>
@@ -8609,7 +8587,7 @@
         <v/>
       </c>
       <c r="N188" s="6" t="str">
-        <v>XS</v>
+        <v>S</v>
       </c>
       <c r="O188" t="str">
         <v/>
@@ -8633,85 +8611,55 @@
         <v/>
       </c>
     </row>
-    <row r="189" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A189" s="4" t="str">
-        <v>Global FTD</v>
-      </c>
-      <c r="B189" t="str">
-        <v/>
-      </c>
-      <c r="C189" s="19" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="D189" s="6" t="str">
-        <v>ApiForM&amp;A</v>
-      </c>
-      <c r="E189" t="str">
-        <v/>
-      </c>
-      <c r="F189" t="str">
-        <v/>
-      </c>
-      <c r="G189" t="str">
-        <v/>
-      </c>
-      <c r="H189" t="str">
-        <v/>
-      </c>
-      <c r="I189" t="str">
-        <v/>
-      </c>
-      <c r="J189" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K189" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L189" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M189" t="str">
-        <v/>
-      </c>
-      <c r="N189" s="6" t="str">
-        <v>XS</v>
-      </c>
-      <c r="O189" t="str">
-        <v/>
-      </c>
-      <c r="P189" t="str">
-        <v/>
-      </c>
-      <c r="Q189" t="str">
-        <v/>
-      </c>
-      <c r="R189" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
-      </c>
-      <c r="S189" t="str">
-        <v/>
-      </c>
-      <c r="T189" t="str">
-        <v/>
-      </c>
-      <c r="U189" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="190" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A190" s="4" t="str">
-        <v>Customer Finance</v>
-      </c>
-      <c r="B190" t="str">
-        <v/>
-      </c>
-      <c r="C190" s="19" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="D190" s="6" t="str">
-        <v>ApiForM&amp;A</v>
-      </c>
-      <c r="E190" t="str">
+    <row r="189" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" s="9" t="str">
+        <v>Subitems</v>
+      </c>
+      <c r="B189" s="10" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C189" s="10" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="D189" s="10" t="str">
+        <v>Status</v>
+      </c>
+      <c r="E189" s="10" t="str">
+        <v>JIRA</v>
+      </c>
+      <c r="F189" s="10" t="str">
+        <v>Drop</v>
+      </c>
+      <c r="G189" s="10" t="str">
+        <v>Team</v>
+      </c>
+      <c r="H189" s="10" t="str">
+        <v>Timeline - Start</v>
+      </c>
+      <c r="I189" s="10" t="str">
+        <v>Timeline - End</v>
+      </c>
+      <c r="J189" s="10" t="str">
+        <v>Groom Readiness Date</v>
+      </c>
+      <c r="K189" s="10" t="str">
+        <v>Priority</v>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A190" t="str">
+        <v/>
+      </c>
+      <c r="B190" s="4" t="str">
+        <v>getAccounts</v>
+      </c>
+      <c r="C190" t="str">
+        <v/>
+      </c>
+      <c r="D190" s="12" t="str">
+        <v>Stuck</v>
+      </c>
+      <c r="E190" s="6" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
@@ -8726,52 +8674,22 @@
       <c r="I190" t="str">
         <v/>
       </c>
-      <c r="J190" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K190" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L190" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M190" t="str">
-        <v/>
-      </c>
-      <c r="N190" s="6" t="str">
-        <v>XS</v>
-      </c>
-      <c r="O190" t="str">
-        <v/>
-      </c>
-      <c r="P190" t="str">
-        <v/>
-      </c>
-      <c r="Q190" t="str">
-        <v/>
-      </c>
-      <c r="R190" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
-      </c>
-      <c r="S190" t="str">
-        <v/>
-      </c>
-      <c r="T190" t="str">
-        <v/>
-      </c>
-      <c r="U190" t="str">
+      <c r="J190" t="str">
+        <v/>
+      </c>
+      <c r="K190" t="str">
         <v/>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="str">
-        <v>Banking (Payee, Withdraw)</v>
+        <v>Transfer (money bus)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
-      <c r="C191" s="19" t="str">
-        <v>Not Started</v>
+      <c r="C191" s="12" t="str">
+        <v>Stuck</v>
       </c>
       <c r="D191" s="6" t="str">
         <v>ApiForM&amp;A</v>
@@ -8779,11 +8697,11 @@
       <c r="E191" t="str">
         <v/>
       </c>
-      <c r="F191" t="str">
-        <v/>
-      </c>
-      <c r="G191" t="str">
-        <v/>
+      <c r="F191" s="8">
+        <v>46091</v>
+      </c>
+      <c r="G191" s="8">
+        <v>46134</v>
       </c>
       <c r="H191" t="str">
         <v/>
@@ -8804,7 +8722,7 @@
         <v/>
       </c>
       <c r="N191" s="6" t="str">
-        <v/>
+        <v>XS</v>
       </c>
       <c r="O191" t="str">
         <v/>
@@ -8830,16 +8748,16 @@
     </row>
     <row r="192" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="str">
-        <v>CashFlow BFF- Hagit</v>
+        <v>Global FTD</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
-      <c r="C192" s="14" t="str">
-        <v>Discovery</v>
-      </c>
-      <c r="D192" t="str">
-        <v/>
+      <c r="C192" s="12" t="str">
+        <v>Stuck</v>
+      </c>
+      <c r="D192" s="6" t="str">
+        <v>ApiForM&amp;A</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -8869,7 +8787,7 @@
         <v/>
       </c>
       <c r="N192" s="6" t="str">
-        <v/>
+        <v>XS</v>
       </c>
       <c r="O192" t="str">
         <v/>
@@ -8881,7 +8799,7 @@
         <v/>
       </c>
       <c r="R192" s="6" t="str">
-        <v>Ilan Tatar Feb 12, 2026 1:19 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
       </c>
       <c r="S192" t="str">
         <v/>
@@ -8895,16 +8813,16 @@
     </row>
     <row r="193" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="str">
-        <v>Cash Account BFF- Hagit</v>
+        <v>Customer Finance</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
-      <c r="C193" s="14" t="str">
-        <v>Discovery</v>
-      </c>
-      <c r="D193" t="str">
-        <v/>
+      <c r="C193" s="18" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="D193" s="6" t="str">
+        <v>ApiForM&amp;A</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -8934,7 +8852,7 @@
         <v/>
       </c>
       <c r="N193" s="6" t="str">
-        <v/>
+        <v>XS</v>
       </c>
       <c r="O193" t="str">
         <v/>
@@ -8946,7 +8864,7 @@
         <v/>
       </c>
       <c r="R193" s="6" t="str">
-        <v>Ilan Tatar Feb 12, 2026 1:19 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
       </c>
       <c r="S193" t="str">
         <v/>
@@ -8960,19 +8878,19 @@
     </row>
     <row r="194" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="str">
-        <v>Buy from IBAN</v>
+        <v>Banking (Payee, Withdraw)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
-      <c r="C194" s="20" t="str">
-        <v>Cancelled</v>
+      <c r="C194" s="18" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D194" s="6" t="str">
-        <v>ApiForPlus</v>
-      </c>
-      <c r="E194" s="6" t="str">
-        <v>trading BE orch</v>
+        <v>ApiForM&amp;A</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
       </c>
       <c r="F194" t="str">
         <v/>
@@ -8999,7 +8917,7 @@
         <v/>
       </c>
       <c r="N194" s="6" t="str">
-        <v>XS</v>
+        <v/>
       </c>
       <c r="O194" t="str">
         <v/>
@@ -9011,7 +8929,7 @@
         <v/>
       </c>
       <c r="R194" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
       </c>
       <c r="S194" t="str">
         <v/>
@@ -9025,37 +8943,37 @@
     </row>
     <row r="195" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="str">
-        <v>Withdraw +Payment Eligibility</v>
+        <v>CashFlow BFF- Hagit</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
-      <c r="C195" s="20" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="D195" s="6" t="str">
-        <v>ApiForPlus</v>
+      <c r="C195" s="14" t="str">
+        <v>Discovery</v>
+      </c>
+      <c r="D195" t="str">
+        <v/>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
-      <c r="F195" s="8">
-        <v>46040</v>
-      </c>
-      <c r="G195" s="8">
-        <v>46065</v>
+      <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195" t="str">
+        <v/>
       </c>
       <c r="H195" t="str">
         <v/>
       </c>
-      <c r="I195" s="6" t="str">
-        <v>Using new money bus withdraw orch.</v>
+      <c r="I195" t="str">
+        <v/>
       </c>
       <c r="J195" s="6" t="str">
         <v/>
       </c>
       <c r="K195" s="6" t="str">
-        <v>IRena Plotkin</v>
+        <v/>
       </c>
       <c r="L195" s="6" t="str">
         <v/>
@@ -9064,7 +8982,7 @@
         <v/>
       </c>
       <c r="N195" s="6" t="str">
-        <v>S-M</v>
+        <v/>
       </c>
       <c r="O195" t="str">
         <v/>
@@ -9076,7 +8994,7 @@
         <v/>
       </c>
       <c r="R195" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+        <v>Ilan Tatar Feb 12, 2026 1:19 PM</v>
       </c>
       <c r="S195" t="str">
         <v/>
@@ -9090,403 +9008,403 @@
     </row>
     <row r="196" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="str">
+        <v>Cash Account BFF- Hagit</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" s="14" t="str">
+        <v>Discovery</v>
+      </c>
+      <c r="D196" t="str">
+        <v/>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v/>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+      <c r="H196" t="str">
+        <v/>
+      </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
+      <c r="J196" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K196" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L196" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M196" t="str">
+        <v/>
+      </c>
+      <c r="N196" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
+        <v/>
+      </c>
+      <c r="P196" t="str">
+        <v/>
+      </c>
+      <c r="Q196" t="str">
+        <v/>
+      </c>
+      <c r="R196" s="6" t="str">
+        <v>Ilan Tatar Feb 12, 2026 1:19 PM</v>
+      </c>
+      <c r="S196" t="str">
+        <v/>
+      </c>
+      <c r="T196" t="str">
+        <v/>
+      </c>
+      <c r="U196" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="str">
+        <v>Buy from IBAN</v>
+      </c>
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" s="19" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D197" s="6" t="str">
+        <v>ApiForPlus</v>
+      </c>
+      <c r="E197" s="6" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="F197" t="str">
+        <v/>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+      <c r="H197" t="str">
+        <v/>
+      </c>
+      <c r="I197" t="str">
+        <v/>
+      </c>
+      <c r="J197" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K197" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L197" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M197" t="str">
+        <v/>
+      </c>
+      <c r="N197" s="6" t="str">
+        <v>XS</v>
+      </c>
+      <c r="O197" t="str">
+        <v/>
+      </c>
+      <c r="P197" t="str">
+        <v/>
+      </c>
+      <c r="Q197" t="str">
+        <v/>
+      </c>
+      <c r="R197" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+      </c>
+      <c r="S197" t="str">
+        <v/>
+      </c>
+      <c r="T197" t="str">
+        <v/>
+      </c>
+      <c r="U197" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="str">
+        <v>Withdraw +Payment Eligibility</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" s="19" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D198" s="6" t="str">
+        <v>ApiForPlus</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G198" s="8">
+        <v>46065</v>
+      </c>
+      <c r="H198" t="str">
+        <v/>
+      </c>
+      <c r="I198" s="6" t="str">
+        <v>Using new money bus withdraw orch.</v>
+      </c>
+      <c r="J198" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K198" s="6" t="str">
+        <v>IRena Plotkin</v>
+      </c>
+      <c r="L198" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M198" t="str">
+        <v/>
+      </c>
+      <c r="N198" s="6" t="str">
+        <v>S-M</v>
+      </c>
+      <c r="O198" t="str">
+        <v/>
+      </c>
+      <c r="P198" t="str">
+        <v/>
+      </c>
+      <c r="Q198" t="str">
+        <v/>
+      </c>
+      <c r="R198" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+      </c>
+      <c r="S198" t="str">
+        <v/>
+      </c>
+      <c r="T198" t="str">
+        <v/>
+      </c>
+      <c r="U198" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="str">
         <v>Financial History- Hagit</v>
       </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" s="22" t="str">
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" s="22" t="str">
         <v>Managed by other team</v>
       </c>
-      <c r="D196" s="6" t="str">
+      <c r="D199" s="6" t="str">
         <v>ApiForPlus</v>
       </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" s="8">
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" s="8">
         <v>46040</v>
       </c>
-      <c r="G196" s="8">
+      <c r="G199" s="8">
         <v>46040</v>
       </c>
-      <c r="H196" t="str">
-        <v/>
-      </c>
-      <c r="I196" s="6" t="str">
+      <c r="H199" t="str">
+        <v/>
+      </c>
+      <c r="I199" s="6" t="str">
         <v>add iban mimo &amp; card trx</v>
       </c>
-      <c r="J196" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K196" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L196" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M196" t="str">
-        <v/>
-      </c>
-      <c r="N196" s="6" t="str">
+      <c r="J199" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K199" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L199" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M199" t="str">
+        <v/>
+      </c>
+      <c r="N199" s="6" t="str">
         <v>S</v>
       </c>
-      <c r="O196" t="str">
-        <v/>
-      </c>
-      <c r="P196" t="str">
-        <v/>
-      </c>
-      <c r="Q196" t="str">
-        <v/>
-      </c>
-      <c r="R196" s="6" t="str">
+      <c r="O199" t="str">
+        <v/>
+      </c>
+      <c r="P199" t="str">
+        <v/>
+      </c>
+      <c r="Q199" t="str">
+        <v/>
+      </c>
+      <c r="R199" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
       </c>
-      <c r="S196" t="str">
-        <v/>
-      </c>
-      <c r="T196" t="str">
-        <v/>
-      </c>
-      <c r="U196" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="197" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A197" t="str">
-        <v/>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v/>
-      </c>
-      <c r="D197" t="str">
-        <v/>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" s="25">
+      <c r="S199" t="str">
+        <v/>
+      </c>
+      <c r="T199" t="str">
+        <v/>
+      </c>
+      <c r="U199" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A200" t="str">
+        <v/>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v/>
+      </c>
+      <c r="D200" t="str">
+        <v/>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" s="26">
         <v>46036</v>
       </c>
-      <c r="G197" s="25">
-        <v>46127</v>
-      </c>
-      <c r="H197" t="str">
-        <v/>
-      </c>
-      <c r="I197" t="str">
-        <v/>
-      </c>
-      <c r="J197" t="str">
-        <v/>
-      </c>
-      <c r="K197" t="str">
-        <v/>
-      </c>
-      <c r="L197" t="str">
-        <v/>
-      </c>
-      <c r="M197" s="26">
+      <c r="G200" s="26">
+        <v>46134</v>
+      </c>
+      <c r="H200" t="str">
+        <v/>
+      </c>
+      <c r="I200" t="str">
+        <v/>
+      </c>
+      <c r="J200" t="str">
+        <v/>
+      </c>
+      <c r="K200" t="str">
+        <v/>
+      </c>
+      <c r="L200" t="str">
+        <v/>
+      </c>
+      <c r="M200" s="27">
         <v>9</v>
       </c>
-      <c r="N197" t="str">
-        <v/>
-      </c>
-      <c r="O197" t="str">
-        <v/>
-      </c>
-      <c r="P197" t="str">
-        <v/>
-      </c>
-      <c r="Q197" s="28" t="str">
-        <v/>
-      </c>
-      <c r="R197" t="str">
-        <v/>
-      </c>
-      <c r="S197" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T197" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U197" s="28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="198" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" s="32" t="str">
+      <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+      <c r="P200" t="str">
+        <v/>
+      </c>
+      <c r="Q200" s="29" t="str">
+        <v/>
+      </c>
+      <c r="R200" t="str">
+        <v/>
+      </c>
+      <c r="S200" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T200" s="29" t="str">
+        <v/>
+      </c>
+      <c r="U200" s="29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="33" t="str">
         <v>Not in Money scope/Future versions</v>
       </c>
     </row>
-    <row r="200" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A200" s="3" t="str">
+    <row r="203" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B200" s="3" t="str">
+      <c r="B203" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C200" s="3" t="str">
+      <c r="C203" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D200" s="3" t="str">
+      <c r="D203" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E200" s="3" t="str">
+      <c r="E203" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F200" s="3" t="str">
+      <c r="F203" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G200" s="3" t="str">
+      <c r="G203" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H200" s="3" t="str">
+      <c r="H203" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I200" s="3" t="str">
+      <c r="I203" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J200" s="3" t="str">
+      <c r="J203" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K200" s="3" t="str">
+      <c r="K203" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L200" s="3" t="str">
+      <c r="L203" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M200" s="3" t="str">
+      <c r="M203" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N200" s="3" t="str">
+      <c r="N203" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O200" s="3" t="str">
+      <c r="O203" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P200" s="3" t="str">
+      <c r="P203" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q200" s="3" t="str">
+      <c r="Q203" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R200" s="3" t="str">
+      <c r="R203" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S200" s="3" t="str">
+      <c r="S203" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T200" s="3" t="str">
+      <c r="T203" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U200" s="3" t="str">
+      <c r="U203" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="201" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A201" s="4" t="str">
-        <v>Portfolio: Balance breakdown display</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" s="22" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D201" s="6" t="str">
-        <v>Home:Balances&amp; Graph</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" s="8">
-        <v>46076</v>
-      </c>
-      <c r="G201" s="8">
-        <v>46076</v>
-      </c>
-      <c r="H201" t="str">
-        <v/>
-      </c>
-      <c r="I201" t="str">
-        <v/>
-      </c>
-      <c r="J201" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K201" s="6" t="str">
-        <v>Inbal Escholi</v>
-      </c>
-      <c r="L201" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M201" s="6">
-        <v>99</v>
-      </c>
-      <c r="N201" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O201" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1mnu7wyyW4vQQQTn1fJ2Uz4OAAqlZYDXQ</v>
-      </c>
-      <c r="P201" s="6" t="str">
-        <v>Balance</v>
-      </c>
-      <c r="Q201" t="str">
-        <v/>
-      </c>
-      <c r="R201" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
-      </c>
-      <c r="S201" t="str">
-        <v/>
-      </c>
-      <c r="T201" t="str">
-        <v/>
-      </c>
-      <c r="U201" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="202" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A202" s="4" t="str">
-        <v>Close to IBAN</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" s="22" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D202" s="6" t="str">
-        <v>tradeIBAN</v>
-      </c>
-      <c r="E202" s="6" t="str">
-        <v>trading BE orch</v>
-      </c>
-      <c r="F202" t="str">
-        <v/>
-      </c>
-      <c r="G202" t="str">
-        <v/>
-      </c>
-      <c r="H202" t="str">
-        <v/>
-      </c>
-      <c r="I202" s="6" t="str">
-        <v>Dependency with Trading- TBD</v>
-      </c>
-      <c r="J202" s="6" t="str">
-        <v>Joanna</v>
-      </c>
-      <c r="K202" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L202" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M202" s="6">
-        <v>99</v>
-      </c>
-      <c r="N202" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O202" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1ddNvCALwf6FEU0B0IL99tpwkLeoal_W_</v>
-      </c>
-      <c r="P202" s="6" t="str">
-        <v>Local currency, Trading</v>
-      </c>
-      <c r="Q202" t="str">
-        <v/>
-      </c>
-      <c r="R202" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S202" t="str">
-        <v/>
-      </c>
-      <c r="T202" t="str">
-        <v/>
-      </c>
-      <c r="U202" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="203" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A203" s="4" t="str">
-        <v>Trade from IBAN (local currency)</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" s="22" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D203" s="6" t="str">
-        <v>tradeIBAN</v>
-      </c>
-      <c r="E203" s="6" t="str">
-        <v>trading BE orch</v>
-      </c>
-      <c r="F203" t="str">
-        <v/>
-      </c>
-      <c r="G203" t="str">
-        <v/>
-      </c>
-      <c r="H203" t="str">
-        <v/>
-      </c>
-      <c r="I203" s="6" t="str">
-        <v>Dependency with Trading- TBD</v>
-      </c>
-      <c r="J203" s="6" t="str">
-        <v>Joanna</v>
-      </c>
-      <c r="K203" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L203" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M203" s="6">
-        <v>99</v>
-      </c>
-      <c r="N203" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O203" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1coMCsTt9H1FUbALyki0_k30a77Ff3Hou</v>
-      </c>
-      <c r="P203" s="6" t="str">
-        <v>Local currency, Trading</v>
-      </c>
-      <c r="Q203" t="str">
-        <v/>
-      </c>
-      <c r="R203" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S203" t="str">
-        <v/>
-      </c>
-      <c r="T203" t="str">
-        <v/>
-      </c>
-      <c r="U203" t="str">
-        <v/>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="str">
-        <v>Exectuion popup - balance drawer</v>
+        <v>Portfolio: Balance breakdown display</v>
       </c>
       <c r="B204" t="str">
         <v/>
@@ -9495,28 +9413,28 @@
         <v>Managed by other team</v>
       </c>
       <c r="D204" s="6" t="str">
-        <v>tradeIBAN</v>
-      </c>
-      <c r="E204" s="6" t="str">
-        <v>trading BE orch</v>
-      </c>
-      <c r="F204" t="str">
-        <v/>
-      </c>
-      <c r="G204" t="str">
-        <v/>
+        <v>Home:Balances&amp; Graph</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" s="8">
+        <v>46076</v>
+      </c>
+      <c r="G204" s="8">
+        <v>46076</v>
       </c>
       <c r="H204" t="str">
         <v/>
       </c>
-      <c r="I204" s="6" t="str">
-        <v>Using the SDK + API. Need execution popup BFF</v>
+      <c r="I204" t="str">
+        <v/>
       </c>
       <c r="J204" s="6" t="str">
-        <v>Joanna</v>
+        <v/>
       </c>
       <c r="K204" s="6" t="str">
-        <v/>
+        <v>Inbal Escholi</v>
       </c>
       <c r="L204" s="6" t="str">
         <v/>
@@ -9528,16 +9446,16 @@
         <v/>
       </c>
       <c r="O204" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1uRBpFFz5LHbz_kS_QTlKAjAysLDykQKF</v>
+        <v>https://drive.google.com/drive/u/0/folders/1mnu7wyyW4vQQQTn1fJ2Uz4OAAqlZYDXQ</v>
       </c>
       <c r="P204" s="6" t="str">
-        <v>Local currency, Payments</v>
+        <v>Balance</v>
       </c>
       <c r="Q204" t="str">
         <v/>
       </c>
       <c r="R204" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
       </c>
       <c r="S204" t="str">
         <v/>
@@ -9551,7 +9469,7 @@
     </row>
     <row r="205" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="str">
-        <v>Home Page- Balance Display</v>
+        <v>Close to IBAN</v>
       </c>
       <c r="B205" t="str">
         <v/>
@@ -9560,675 +9478,705 @@
         <v>Managed by other team</v>
       </c>
       <c r="D205" s="6" t="str">
+        <v>tradeIBAN</v>
+      </c>
+      <c r="E205" s="6" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+      <c r="H205" t="str">
+        <v/>
+      </c>
+      <c r="I205" s="6" t="str">
+        <v>Dependency with Trading- TBD</v>
+      </c>
+      <c r="J205" s="6" t="str">
+        <v>Joanna</v>
+      </c>
+      <c r="K205" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L205" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M205" s="6">
+        <v>99</v>
+      </c>
+      <c r="N205" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O205" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1ddNvCALwf6FEU0B0IL99tpwkLeoal_W_</v>
+      </c>
+      <c r="P205" s="6" t="str">
+        <v>Local currency, Trading</v>
+      </c>
+      <c r="Q205" t="str">
+        <v/>
+      </c>
+      <c r="R205" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S205" t="str">
+        <v/>
+      </c>
+      <c r="T205" t="str">
+        <v/>
+      </c>
+      <c r="U205" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="str">
+        <v>Trade from IBAN (local currency)</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" s="22" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D206" s="6" t="str">
+        <v>tradeIBAN</v>
+      </c>
+      <c r="E206" s="6" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+      <c r="H206" t="str">
+        <v/>
+      </c>
+      <c r="I206" s="6" t="str">
+        <v>Dependency with Trading- TBD</v>
+      </c>
+      <c r="J206" s="6" t="str">
+        <v>Joanna</v>
+      </c>
+      <c r="K206" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L206" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M206" s="6">
+        <v>99</v>
+      </c>
+      <c r="N206" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O206" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1coMCsTt9H1FUbALyki0_k30a77Ff3Hou</v>
+      </c>
+      <c r="P206" s="6" t="str">
+        <v>Local currency, Trading</v>
+      </c>
+      <c r="Q206" t="str">
+        <v/>
+      </c>
+      <c r="R206" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S206" t="str">
+        <v/>
+      </c>
+      <c r="T206" t="str">
+        <v/>
+      </c>
+      <c r="U206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="str">
+        <v>Exectuion popup - balance drawer</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" s="22" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D207" s="6" t="str">
+        <v>tradeIBAN</v>
+      </c>
+      <c r="E207" s="6" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+      <c r="H207" t="str">
+        <v/>
+      </c>
+      <c r="I207" s="6" t="str">
+        <v>Using the SDK + API. Need execution popup BFF</v>
+      </c>
+      <c r="J207" s="6" t="str">
+        <v>Joanna</v>
+      </c>
+      <c r="K207" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L207" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M207" s="6">
+        <v>99</v>
+      </c>
+      <c r="N207" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O207" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1uRBpFFz5LHbz_kS_QTlKAjAysLDykQKF</v>
+      </c>
+      <c r="P207" s="6" t="str">
+        <v>Local currency, Payments</v>
+      </c>
+      <c r="Q207" t="str">
+        <v/>
+      </c>
+      <c r="R207" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S207" t="str">
+        <v/>
+      </c>
+      <c r="T207" t="str">
+        <v/>
+      </c>
+      <c r="U207" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="208" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="str">
+        <v>Home Page- Balance Display</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" s="22" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D208" s="6" t="str">
         <v>Home:Balances&amp; Graph</v>
       </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" s="8">
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" s="8">
         <v>46076</v>
       </c>
-      <c r="G205" s="8">
+      <c r="G208" s="8">
         <v>46076</v>
       </c>
-      <c r="H205" t="str">
-        <v/>
-      </c>
-      <c r="I205" s="6" t="str">
+      <c r="H208" t="str">
+        <v/>
+      </c>
+      <c r="I208" s="6" t="str">
         <v>Require effort to expose the data from the lake
 Meeting 20/1 - home page redesign</v>
       </c>
-      <c r="J205" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K205" s="6" t="str">
+      <c r="J208" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K208" s="6" t="str">
         <v>Inbal Escholi</v>
       </c>
-      <c r="L205" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M205" s="6">
+      <c r="L208" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M208" s="6">
         <v>99</v>
       </c>
-      <c r="N205" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O205" s="6" t="str">
+      <c r="N208" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O208" s="6" t="str">
         <v>https://drive.google.com/drive/u/0/folders/1ajgQLvU3kxLq70yAZZBcFppbac3M02Jm</v>
       </c>
-      <c r="P205" s="6" t="str">
+      <c r="P208" s="6" t="str">
         <v>Balance</v>
       </c>
-      <c r="Q205" s="7">
+      <c r="Q208" s="7">
         <v>46083</v>
       </c>
-      <c r="R205" s="6" t="str">
+      <c r="R208" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
-      <c r="S205" t="str">
-        <v/>
-      </c>
-      <c r="T205" t="str">
-        <v/>
-      </c>
-      <c r="U205" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="206" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A206" s="4" t="str">
+      <c r="S208" t="str">
+        <v/>
+      </c>
+      <c r="T208" t="str">
+        <v/>
+      </c>
+      <c r="U208" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="str">
         <v>Recurring Investment</v>
       </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" s="22" t="str">
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" s="22" t="str">
         <v>Managed by other team</v>
       </c>
-      <c r="D206" s="6" t="str">
+      <c r="D209" s="6" t="str">
         <v>recurInvestment</v>
       </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" s="8">
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" s="8">
         <v>46105</v>
       </c>
-      <c r="G206" s="8">
+      <c r="G209" s="8">
         <v>46132</v>
       </c>
-      <c r="H206" t="str">
-        <v/>
-      </c>
-      <c r="I206" t="str">
-        <v/>
-      </c>
-      <c r="J206" s="6" t="str">
+      <c r="H209" t="str">
+        <v/>
+      </c>
+      <c r="I209" t="str">
+        <v/>
+      </c>
+      <c r="J209" s="6" t="str">
         <v>Noit</v>
       </c>
-      <c r="K206" s="6" t="str">
+      <c r="K209" s="6" t="str">
         <v>Inbal Escholi</v>
       </c>
-      <c r="L206" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M206" s="6">
+      <c r="L209" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M209" s="6">
         <v>99</v>
       </c>
-      <c r="N206" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O206" t="str">
-        <v/>
-      </c>
-      <c r="P206" s="6" t="str">
+      <c r="N209" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O209" t="str">
+        <v/>
+      </c>
+      <c r="P209" s="6" t="str">
         <v>Payments, Recurring Investment</v>
       </c>
-      <c r="Q206" t="str">
-        <v/>
-      </c>
-      <c r="R206" s="6" t="str">
+      <c r="Q209" t="str">
+        <v/>
+      </c>
+      <c r="R209" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
-      <c r="S206" t="str">
-        <v/>
-      </c>
-      <c r="T206" t="str">
-        <v/>
-      </c>
-      <c r="U206" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="207" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A207" s="9" t="str">
+      <c r="S209" t="str">
+        <v/>
+      </c>
+      <c r="T209" t="str">
+        <v/>
+      </c>
+      <c r="U209" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="210" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A210" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B207" s="10" t="str">
+      <c r="B210" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C207" s="10" t="str">
+      <c r="C210" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D207" s="10" t="str">
+      <c r="D210" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E207" s="10" t="str">
+      <c r="E210" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F207" s="10" t="str">
+      <c r="F210" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G207" s="10" t="str">
+      <c r="G210" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H207" s="10" t="str">
+      <c r="H210" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I207" s="10" t="str">
+      <c r="I210" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J207" s="10" t="str">
+      <c r="J210" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K207" s="10" t="str">
+      <c r="K210" s="10" t="str">
         <v>Priority</v>
       </c>
     </row>
-    <row r="208" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A208" t="str">
-        <v/>
-      </c>
-      <c r="B208" s="4" t="str">
+    <row r="211" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A211" t="str">
+        <v/>
+      </c>
+      <c r="B211" s="4" t="str">
         <v>Recurring investment - card details</v>
       </c>
-      <c r="C208" t="str">
-        <v/>
-      </c>
-      <c r="D208" s="19" t="str">
+      <c r="C211" t="str">
+        <v/>
+      </c>
+      <c r="D211" s="18" t="str">
         <v>Not Started</v>
       </c>
-      <c r="E208" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v/>
-      </c>
-      <c r="G208" s="6" t="str">
+      <c r="E211" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" s="6" t="str">
         <v>Payments</v>
       </c>
-      <c r="H208" t="str">
-        <v/>
-      </c>
-      <c r="I208" t="str">
-        <v/>
-      </c>
-      <c r="J208" t="str">
-        <v/>
-      </c>
-      <c r="K208" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="209" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A209" t="str">
-        <v/>
-      </c>
-      <c r="B209" s="4" t="str">
+      <c r="H211" t="str">
+        <v/>
+      </c>
+      <c r="I211" t="str">
+        <v/>
+      </c>
+      <c r="J211" t="str">
+        <v/>
+      </c>
+      <c r="K211" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A212" t="str">
+        <v/>
+      </c>
+      <c r="B212" s="4" t="str">
         <v>Recurring investment feature</v>
       </c>
-      <c r="C209" t="str">
-        <v/>
-      </c>
-      <c r="D209" s="19" t="str">
+      <c r="C212" t="str">
+        <v/>
+      </c>
+      <c r="D212" s="18" t="str">
         <v>Not Started</v>
       </c>
-      <c r="E209" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v/>
-      </c>
-      <c r="G209" t="str">
-        <v/>
-      </c>
-      <c r="H209" t="str">
-        <v/>
-      </c>
-      <c r="I209" t="str">
-        <v/>
-      </c>
-      <c r="J209" t="str">
-        <v/>
-      </c>
-      <c r="K209" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="210" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A210" s="4" t="str">
+      <c r="E212" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v/>
+      </c>
+      <c r="G212" t="str">
+        <v/>
+      </c>
+      <c r="H212" t="str">
+        <v/>
+      </c>
+      <c r="I212" t="str">
+        <v/>
+      </c>
+      <c r="J212" t="str">
+        <v/>
+      </c>
+      <c r="K212" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="213" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="str">
         <v>IBAN - Club Upgrades for Account Programs</v>
       </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" s="21" t="str">
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" s="21" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D210" s="6" t="str">
+      <c r="D213" s="6" t="str">
         <v>Banking</v>
       </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v/>
-      </c>
-      <c r="G210" t="str">
-        <v/>
-      </c>
-      <c r="H210" t="str">
-        <v/>
-      </c>
-      <c r="I210" t="str">
-        <v/>
-      </c>
-      <c r="J210" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K210" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L210" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M210" s="6">
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v/>
+      </c>
+      <c r="G213" t="str">
+        <v/>
+      </c>
+      <c r="H213" t="str">
+        <v/>
+      </c>
+      <c r="I213" t="str">
+        <v/>
+      </c>
+      <c r="J213" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K213" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L213" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M213" s="6">
         <v>100</v>
       </c>
-      <c r="N210" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O210" t="str">
-        <v/>
-      </c>
-      <c r="P210" s="6" t="str">
+      <c r="N213" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O213" t="str">
+        <v/>
+      </c>
+      <c r="P213" s="6" t="str">
         <v>Banking</v>
       </c>
-      <c r="Q210" t="str">
-        <v/>
-      </c>
-      <c r="R210" s="6" t="str">
+      <c r="Q213" t="str">
+        <v/>
+      </c>
+      <c r="R213" s="6" t="str">
         <v>Hagit Zamir Feb 3, 2026 3:42 PM</v>
       </c>
-      <c r="S210" t="str">
-        <v/>
-      </c>
-      <c r="T210" t="str">
-        <v/>
-      </c>
-      <c r="U210" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="211" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A211" s="4" t="str">
+      <c r="S213" t="str">
+        <v/>
+      </c>
+      <c r="T213" t="str">
+        <v/>
+      </c>
+      <c r="U213" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="214" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="str">
         <v>Wallet tab - IBAN - Direct Debit</v>
       </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" s="21" t="str">
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" s="21" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D211" s="6" t="str">
+      <c r="D214" s="6" t="str">
         <v>ManageDirectDebit</v>
       </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v/>
-      </c>
-      <c r="G211" t="str">
-        <v/>
-      </c>
-      <c r="H211" t="str">
-        <v/>
-      </c>
-      <c r="I211" s="6" t="str">
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v/>
+      </c>
+      <c r="G214" t="str">
+        <v/>
+      </c>
+      <c r="H214" t="str">
+        <v/>
+      </c>
+      <c r="I214" s="6" t="str">
         <v>Web only (mobile web is optional)</v>
       </c>
-      <c r="J211" s="6" t="str">
+      <c r="J214" s="6" t="str">
         <v>Adi</v>
       </c>
-      <c r="K211" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L211" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M211" s="6">
+      <c r="K214" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L214" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M214" s="6">
         <v>100</v>
       </c>
-      <c r="N211" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O211" s="6" t="str">
+      <c r="N214" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O214" s="6" t="str">
         <v>https://drive.google.com/drive/u/0/folders/1ckH93ib0CmcIINKUzOdZWWhqNbnIAiZi</v>
       </c>
-      <c r="P211" s="6" t="str">
+      <c r="P214" s="6" t="str">
         <v>Banking</v>
       </c>
-      <c r="Q211" t="str">
-        <v/>
-      </c>
-      <c r="R211" s="6" t="str">
+      <c r="Q214" t="str">
+        <v/>
+      </c>
+      <c r="R214" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
-      <c r="S211" t="str">
-        <v/>
-      </c>
-      <c r="T211" t="str">
-        <v/>
-      </c>
-      <c r="U211" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="212" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A212" s="4" t="str">
+      <c r="S214" t="str">
+        <v/>
+      </c>
+      <c r="T214" t="str">
+        <v/>
+      </c>
+      <c r="U214" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="215" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="str">
         <v>Crypto-in/out - New Flow</v>
       </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" s="21" t="str">
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" s="21" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D212" t="str">
-        <v/>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" s="8">
+      <c r="D215" t="str">
+        <v/>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" s="8">
         <v>46061</v>
       </c>
-      <c r="G212" s="8">
+      <c r="G215" s="8">
         <v>46075</v>
       </c>
-      <c r="H212" t="str">
-        <v/>
-      </c>
-      <c r="I212" t="str">
-        <v/>
-      </c>
-      <c r="J212" s="6" t="str">
+      <c r="H215" t="str">
+        <v/>
+      </c>
+      <c r="I215" t="str">
+        <v/>
+      </c>
+      <c r="J215" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="K212" s="6" t="str">
+      <c r="K215" s="6" t="str">
         <v>Inbal Escholi</v>
       </c>
-      <c r="L212" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M212" s="6">
+      <c r="L215" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M215" s="6">
         <v>100</v>
       </c>
-      <c r="N212" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O212" s="6" t="str">
+      <c r="N215" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O215" s="6" t="str">
         <v>https://drive.google.com/drive/u/0/folders/1T9bzCpQdskwwMHl_F_RF-WzMtTOtaaem</v>
       </c>
-      <c r="P212" s="6" t="str">
+      <c r="P215" s="6" t="str">
         <v>Crypto</v>
       </c>
-      <c r="Q212" t="str">
-        <v/>
-      </c>
-      <c r="R212" s="6" t="str">
+      <c r="Q215" t="str">
+        <v/>
+      </c>
+      <c r="R215" s="6" t="str">
         <v>Hagit Zamir Feb 3, 2026 11:58 AM</v>
       </c>
-      <c r="S212" t="str">
-        <v/>
-      </c>
-      <c r="T212" t="str">
-        <v/>
-      </c>
-      <c r="U212" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="213" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A213" s="9" t="str">
+      <c r="S215" t="str">
+        <v/>
+      </c>
+      <c r="T215" t="str">
+        <v/>
+      </c>
+      <c r="U215" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="216" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B213" s="10" t="str">
+      <c r="B216" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C213" s="10" t="str">
+      <c r="C216" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D213" s="10" t="str">
+      <c r="D216" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E213" s="10" t="str">
+      <c r="E216" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F213" s="10" t="str">
+      <c r="F216" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G213" s="10" t="str">
+      <c r="G216" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H213" s="10" t="str">
+      <c r="H216" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I213" s="10" t="str">
+      <c r="I216" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J213" s="10" t="str">
+      <c r="J216" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K213" s="10" t="str">
+      <c r="K216" s="10" t="str">
         <v>Priority</v>
       </c>
     </row>
-    <row r="214" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A214" t="str">
-        <v/>
-      </c>
-      <c r="B214" s="4" t="str">
+    <row r="217" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A217" t="str">
+        <v/>
+      </c>
+      <c r="B217" s="4" t="str">
         <v>New Crypto in flow</v>
       </c>
-      <c r="C214" t="str">
-        <v/>
-      </c>
-      <c r="D214" s="19" t="str">
+      <c r="C217" t="str">
+        <v/>
+      </c>
+      <c r="D217" s="18" t="str">
         <v>Not Started</v>
       </c>
-      <c r="E214" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v/>
-      </c>
-      <c r="G214" t="str">
-        <v/>
-      </c>
-      <c r="H214" t="str">
-        <v/>
-      </c>
-      <c r="I214" t="str">
-        <v/>
-      </c>
-      <c r="J214" t="str">
-        <v/>
-      </c>
-      <c r="K214" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="215" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A215" t="str">
-        <v/>
-      </c>
-      <c r="B215" s="4" t="str">
+      <c r="E217" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
+        <v/>
+      </c>
+      <c r="G217" t="str">
+        <v/>
+      </c>
+      <c r="H217" t="str">
+        <v/>
+      </c>
+      <c r="I217" t="str">
+        <v/>
+      </c>
+      <c r="J217" t="str">
+        <v/>
+      </c>
+      <c r="K217" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="218" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A218" t="str">
+        <v/>
+      </c>
+      <c r="B218" s="4" t="str">
         <v>New Crypto out flow</v>
       </c>
-      <c r="C215" t="str">
-        <v/>
-      </c>
-      <c r="D215" s="19" t="str">
+      <c r="C218" t="str">
+        <v/>
+      </c>
+      <c r="D218" s="18" t="str">
         <v>Not Started</v>
       </c>
-      <c r="E215" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v/>
-      </c>
-      <c r="G215" t="str">
-        <v/>
-      </c>
-      <c r="H215" t="str">
-        <v/>
-      </c>
-      <c r="I215" t="str">
-        <v/>
-      </c>
-      <c r="J215" t="str">
-        <v/>
-      </c>
-      <c r="K215" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="216" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A216" s="4" t="str">
-        <v>Account statement - IBAN</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" s="21" t="str">
-        <v>Future Version</v>
-      </c>
-      <c r="D216" s="6" t="str">
-        <v>acctStatement</v>
-      </c>
-      <c r="E216" t="str">
-        <v/>
-      </c>
-      <c r="F216" t="str">
-        <v/>
-      </c>
-      <c r="G216" t="str">
-        <v/>
-      </c>
-      <c r="H216" t="str">
-        <v/>
-      </c>
-      <c r="I216" t="str">
-        <v/>
-      </c>
-      <c r="J216" s="6" t="str">
-        <v>Richard</v>
-      </c>
-      <c r="K216" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L216" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M216" s="6">
-        <v>100</v>
-      </c>
-      <c r="N216" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O216" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1YGwoAq790Wb8Iudfx3nh276XbPp4uDF1</v>
-      </c>
-      <c r="P216" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="Q216" t="str">
-        <v/>
-      </c>
-      <c r="R216" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S216" t="str">
-        <v/>
-      </c>
-      <c r="T216" t="str">
-        <v/>
-      </c>
-      <c r="U216" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="217" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A217" s="4" t="str">
-        <v>Wallet tab - Global banners- Transactional Banners</v>
-      </c>
-      <c r="B217" t="str">
-        <v/>
-      </c>
-      <c r="C217" s="21" t="str">
-        <v>Future Version</v>
-      </c>
-      <c r="D217" s="6" t="str">
-        <v>WalletTab</v>
-      </c>
-      <c r="E217" t="str">
-        <v/>
-      </c>
-      <c r="F217" t="str">
-        <v/>
-      </c>
-      <c r="G217" t="str">
-        <v/>
-      </c>
-      <c r="H217" t="str">
-        <v/>
-      </c>
-      <c r="I217" s="6" t="str">
-        <v>Meeting 20/1 - home page redesign</v>
-      </c>
-      <c r="J217" s="6" t="str">
-        <v>Adi</v>
-      </c>
-      <c r="K217" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L217" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M217" s="6">
-        <v>100</v>
-      </c>
-      <c r="N217" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O217" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1lvshcV8HLj_Iyu76ode34g2d_JhKBOze</v>
-      </c>
-      <c r="P217" s="6" t="str">
-        <v>Banking, Card Mng.</v>
-      </c>
-      <c r="Q217" t="str">
-        <v/>
-      </c>
-      <c r="R217" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S217" t="str">
-        <v/>
-      </c>
-      <c r="T217" t="str">
-        <v/>
-      </c>
-      <c r="U217" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="218" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A218" s="4" t="str">
-        <v>Long term solution for Trade button between Money and Trading</v>
-      </c>
-      <c r="B218" t="str">
-        <v/>
-      </c>
-      <c r="C218" s="21" t="str">
-        <v>Future Version</v>
-      </c>
-      <c r="D218" t="str">
-        <v/>
-      </c>
-      <c r="E218" t="str">
+      <c r="E218" s="6" t="str">
         <v/>
       </c>
       <c r="F218" t="str">
@@ -10243,46 +10191,16 @@
       <c r="I218" t="str">
         <v/>
       </c>
-      <c r="J218" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K218" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L218" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M218" s="6">
-        <v>100</v>
-      </c>
-      <c r="N218" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O218" t="str">
-        <v/>
-      </c>
-      <c r="P218" t="str">
-        <v/>
-      </c>
-      <c r="Q218" t="str">
-        <v/>
-      </c>
-      <c r="R218" s="6" t="str">
-        <v>Ilan Tatar Mar 9, 2026 2:46 PM</v>
-      </c>
-      <c r="S218" t="str">
-        <v/>
-      </c>
-      <c r="T218" t="str">
-        <v/>
-      </c>
-      <c r="U218" t="str">
+      <c r="J218" t="str">
+        <v/>
+      </c>
+      <c r="K218" t="str">
         <v/>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="str">
-        <v>NCW in eToro Plus</v>
+        <v>Account statement - IBAN</v>
       </c>
       <c r="B219" t="str">
         <v/>
@@ -10290,8 +10208,8 @@
       <c r="C219" s="21" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D219" t="str">
-        <v/>
+      <c r="D219" s="6" t="str">
+        <v>acctStatement</v>
       </c>
       <c r="E219" t="str">
         <v/>
@@ -10305,11 +10223,11 @@
       <c r="H219" t="str">
         <v/>
       </c>
-      <c r="I219" s="6" t="str">
-        <v>Dependency with Compliance</v>
+      <c r="I219" t="str">
+        <v/>
       </c>
       <c r="J219" s="6" t="str">
-        <v>Nikolaus Kulier</v>
+        <v>Richard</v>
       </c>
       <c r="K219" s="6" t="str">
         <v/>
@@ -10324,10 +10242,10 @@
         <v/>
       </c>
       <c r="O219" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1pmEz5faaG4dEEUBCP93uCA8HuUcY4q5r</v>
+        <v>https://drive.google.com/drive/u/0/folders/1YGwoAq790Wb8Iudfx3nh276XbPp4uDF1</v>
       </c>
       <c r="P219" s="6" t="str">
-        <v>Crypto</v>
+        <v>Banking</v>
       </c>
       <c r="Q219" t="str">
         <v/>
@@ -10347,7 +10265,7 @@
     </row>
     <row r="220" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="str">
-        <v>Wallet Tab - Product Promotions (all products - Local Accounts / ISA / Crypto etc etc)</v>
+        <v>Wallet tab - Global banners- Transactional Banners</v>
       </c>
       <c r="B220" t="str">
         <v/>
@@ -10356,7 +10274,7 @@
         <v>Future Version</v>
       </c>
       <c r="D220" s="6" t="str">
-        <v>WalletTabTotalValueGraph</v>
+        <v>WalletTab</v>
       </c>
       <c r="E220" t="str">
         <v/>
@@ -10370,8 +10288,8 @@
       <c r="H220" t="str">
         <v/>
       </c>
-      <c r="I220" t="str">
-        <v/>
+      <c r="I220" s="6" t="str">
+        <v>Meeting 20/1 - home page redesign</v>
       </c>
       <c r="J220" s="6" t="str">
         <v>Adi</v>
@@ -10383,22 +10301,22 @@
         <v/>
       </c>
       <c r="M220" s="6">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="N220" s="6" t="str">
         <v/>
       </c>
       <c r="O220" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1lu17LS1984RvIkY8iqJEjH6fS-wJvZta</v>
+        <v>https://drive.google.com/drive/u/0/folders/1lvshcV8HLj_Iyu76ode34g2d_JhKBOze</v>
       </c>
       <c r="P220" s="6" t="str">
-        <v>Wallet Tab</v>
+        <v>Banking, Card Mng.</v>
       </c>
       <c r="Q220" t="str">
         <v/>
       </c>
       <c r="R220" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:28 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
       <c r="S220" t="str">
         <v/>
@@ -10412,13 +10330,13 @@
     </row>
     <row r="221" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="str">
-        <v>Trigger Web Deposit workaround for 20.4- Inbal</v>
+        <v>Long term solution for Trade button between Money and Trading</v>
       </c>
       <c r="B221" t="str">
         <v/>
       </c>
-      <c r="C221" s="20" t="str">
-        <v>Cancelled</v>
+      <c r="C221" s="21" t="str">
+        <v>Future Version</v>
       </c>
       <c r="D221" t="str">
         <v/>
@@ -10439,7 +10357,7 @@
         <v/>
       </c>
       <c r="J221" s="6" t="str">
-        <v>Richard</v>
+        <v/>
       </c>
       <c r="K221" s="6" t="str">
         <v/>
@@ -10448,7 +10366,7 @@
         <v/>
       </c>
       <c r="M221" s="6">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N221" s="6" t="str">
         <v/>
@@ -10463,7 +10381,7 @@
         <v/>
       </c>
       <c r="R221" s="6" t="str">
-        <v>Ilan Tatar Mar 4, 2026 2:45 PM</v>
+        <v>Ilan Tatar Mar 9, 2026 2:46 PM</v>
       </c>
       <c r="S221" t="str">
         <v/>
@@ -10477,16 +10395,16 @@
     </row>
     <row r="222" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="str">
-        <v>Wallet Tab - Balances list</v>
+        <v>NCW in eToro Plus</v>
       </c>
       <c r="B222" t="str">
         <v/>
       </c>
-      <c r="C222" s="20" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="D222" s="6" t="str">
-        <v>WalletTabTotalValueGraph</v>
+      <c r="C222" s="21" t="str">
+        <v>Future Version</v>
+      </c>
+      <c r="D222" t="str">
+        <v/>
       </c>
       <c r="E222" t="str">
         <v/>
@@ -10500,11 +10418,11 @@
       <c r="H222" t="str">
         <v/>
       </c>
-      <c r="I222" t="str">
-        <v/>
+      <c r="I222" s="6" t="str">
+        <v>Dependency with Compliance</v>
       </c>
       <c r="J222" s="6" t="str">
-        <v>Adi</v>
+        <v>Nikolaus Kulier</v>
       </c>
       <c r="K222" s="6" t="str">
         <v/>
@@ -10513,22 +10431,22 @@
         <v/>
       </c>
       <c r="M222" s="6">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="N222" s="6" t="str">
         <v/>
       </c>
       <c r="O222" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/10j0uo11-TGKBFj82pUueB78g_uihED_F</v>
+        <v>https://drive.google.com/drive/u/0/folders/1pmEz5faaG4dEEUBCP93uCA8HuUcY4q5r</v>
       </c>
       <c r="P222" s="6" t="str">
-        <v>Balance</v>
+        <v>Crypto</v>
       </c>
       <c r="Q222" t="str">
         <v/>
       </c>
       <c r="R222" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:16 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
       <c r="S222" t="str">
         <v/>
@@ -10542,25 +10460,25 @@
     </row>
     <row r="223" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="str">
-        <v>Watchlist: Balance breakdown display</v>
+        <v>Wallet Tab - Product Promotions (all products - Local Accounts / ISA / Crypto etc etc)</v>
       </c>
       <c r="B223" t="str">
         <v/>
       </c>
-      <c r="C223" s="20" t="str">
-        <v>Cancelled</v>
+      <c r="C223" s="21" t="str">
+        <v>Future Version</v>
       </c>
       <c r="D223" s="6" t="str">
-        <v>Home:Balances&amp; Graph</v>
+        <v>WalletTabTotalValueGraph</v>
       </c>
       <c r="E223" t="str">
         <v/>
       </c>
-      <c r="F223" s="8">
-        <v>46076</v>
-      </c>
-      <c r="G223" s="8">
-        <v>46076</v>
+      <c r="F223" t="str">
+        <v/>
+      </c>
+      <c r="G223" t="str">
+        <v/>
       </c>
       <c r="H223" t="str">
         <v/>
@@ -10569,10 +10487,10 @@
         <v/>
       </c>
       <c r="J223" s="6" t="str">
-        <v/>
+        <v>Adi</v>
       </c>
       <c r="K223" s="6" t="str">
-        <v>Inbal Escholi</v>
+        <v/>
       </c>
       <c r="L223" s="6" t="str">
         <v/>
@@ -10584,16 +10502,16 @@
         <v/>
       </c>
       <c r="O223" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1zjptd0Ar2VSiDWkXRLTOFCR4pUHOZSJH</v>
+        <v>https://drive.google.com/drive/u/0/folders/1lu17LS1984RvIkY8iqJEjH6fS-wJvZta</v>
       </c>
       <c r="P223" s="6" t="str">
-        <v>Balance</v>
+        <v>Wallet Tab</v>
       </c>
       <c r="Q223" t="str">
         <v/>
       </c>
       <c r="R223" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
+        <v>Ilan Tatar Jan 28, 2026 6:28 PM</v>
       </c>
       <c r="S223" t="str">
         <v/>
@@ -10607,409 +10525,409 @@
     </row>
     <row r="224" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="str">
+        <v>Trigger Web Deposit workaround for 20.4- Inbal</v>
+      </c>
+      <c r="B224" t="str">
+        <v/>
+      </c>
+      <c r="C224" s="19" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D224" t="str">
+        <v/>
+      </c>
+      <c r="E224" t="str">
+        <v/>
+      </c>
+      <c r="F224" t="str">
+        <v/>
+      </c>
+      <c r="G224" t="str">
+        <v/>
+      </c>
+      <c r="H224" t="str">
+        <v/>
+      </c>
+      <c r="I224" t="str">
+        <v/>
+      </c>
+      <c r="J224" s="6" t="str">
+        <v>Richard</v>
+      </c>
+      <c r="K224" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L224" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M224" s="6">
+        <v>1</v>
+      </c>
+      <c r="N224" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O224" t="str">
+        <v/>
+      </c>
+      <c r="P224" t="str">
+        <v/>
+      </c>
+      <c r="Q224" t="str">
+        <v/>
+      </c>
+      <c r="R224" s="6" t="str">
+        <v>Ilan Tatar Mar 4, 2026 2:45 PM</v>
+      </c>
+      <c r="S224" t="str">
+        <v/>
+      </c>
+      <c r="T224" t="str">
+        <v/>
+      </c>
+      <c r="U224" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="225" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="str">
+        <v>Wallet Tab - Balances list</v>
+      </c>
+      <c r="B225" t="str">
+        <v/>
+      </c>
+      <c r="C225" s="19" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D225" s="6" t="str">
+        <v>WalletTabTotalValueGraph</v>
+      </c>
+      <c r="E225" t="str">
+        <v/>
+      </c>
+      <c r="F225" t="str">
+        <v/>
+      </c>
+      <c r="G225" t="str">
+        <v/>
+      </c>
+      <c r="H225" t="str">
+        <v/>
+      </c>
+      <c r="I225" t="str">
+        <v/>
+      </c>
+      <c r="J225" s="6" t="str">
+        <v>Adi</v>
+      </c>
+      <c r="K225" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L225" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M225" s="6">
+        <v>-1</v>
+      </c>
+      <c r="N225" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O225" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/10j0uo11-TGKBFj82pUueB78g_uihED_F</v>
+      </c>
+      <c r="P225" s="6" t="str">
+        <v>Balance</v>
+      </c>
+      <c r="Q225" t="str">
+        <v/>
+      </c>
+      <c r="R225" s="6" t="str">
+        <v>Ilan Tatar Jan 28, 2026 6:16 PM</v>
+      </c>
+      <c r="S225" t="str">
+        <v/>
+      </c>
+      <c r="T225" t="str">
+        <v/>
+      </c>
+      <c r="U225" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="226" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="str">
+        <v>Watchlist: Balance breakdown display</v>
+      </c>
+      <c r="B226" t="str">
+        <v/>
+      </c>
+      <c r="C226" s="19" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D226" s="6" t="str">
+        <v>Home:Balances&amp; Graph</v>
+      </c>
+      <c r="E226" t="str">
+        <v/>
+      </c>
+      <c r="F226" s="8">
+        <v>46076</v>
+      </c>
+      <c r="G226" s="8">
+        <v>46076</v>
+      </c>
+      <c r="H226" t="str">
+        <v/>
+      </c>
+      <c r="I226" t="str">
+        <v/>
+      </c>
+      <c r="J226" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K226" s="6" t="str">
+        <v>Inbal Escholi</v>
+      </c>
+      <c r="L226" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M226" s="6">
+        <v>-1</v>
+      </c>
+      <c r="N226" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O226" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1zjptd0Ar2VSiDWkXRLTOFCR4pUHOZSJH</v>
+      </c>
+      <c r="P226" s="6" t="str">
+        <v>Balance</v>
+      </c>
+      <c r="Q226" t="str">
+        <v/>
+      </c>
+      <c r="R226" s="6" t="str">
+        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
+      </c>
+      <c r="S226" t="str">
+        <v/>
+      </c>
+      <c r="T226" t="str">
+        <v/>
+      </c>
+      <c r="U226" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="227" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="str">
         <v>Payment Client Technical gaps for aftr launch</v>
       </c>
-      <c r="B224" t="str">
-        <v/>
-      </c>
-      <c r="C224" s="21" t="str">
+      <c r="B227" t="str">
+        <v/>
+      </c>
+      <c r="C227" s="21" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D224" t="str">
-        <v/>
-      </c>
-      <c r="E224" t="str">
-        <v/>
-      </c>
-      <c r="F224" t="str">
-        <v/>
-      </c>
-      <c r="G224" t="str">
-        <v/>
-      </c>
-      <c r="H224" t="str">
-        <v/>
-      </c>
-      <c r="I224" t="str">
-        <v/>
-      </c>
-      <c r="J224" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K224" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L224" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M224" t="str">
-        <v/>
-      </c>
-      <c r="N224" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O224" t="str">
-        <v/>
-      </c>
-      <c r="P224" t="str">
-        <v/>
-      </c>
-      <c r="Q224" t="str">
-        <v/>
-      </c>
-      <c r="R224" s="6" t="str">
+      <c r="D227" t="str">
+        <v/>
+      </c>
+      <c r="E227" t="str">
+        <v/>
+      </c>
+      <c r="F227" t="str">
+        <v/>
+      </c>
+      <c r="G227" t="str">
+        <v/>
+      </c>
+      <c r="H227" t="str">
+        <v/>
+      </c>
+      <c r="I227" t="str">
+        <v/>
+      </c>
+      <c r="J227" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K227" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L227" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M227" t="str">
+        <v/>
+      </c>
+      <c r="N227" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O227" t="str">
+        <v/>
+      </c>
+      <c r="P227" t="str">
+        <v/>
+      </c>
+      <c r="Q227" t="str">
+        <v/>
+      </c>
+      <c r="R227" s="6" t="str">
         <v>Ilan Tatar Apr 12, 2026 12:56 PM</v>
       </c>
-      <c r="S224" t="str">
-        <v/>
-      </c>
-      <c r="T224" t="str">
-        <v/>
-      </c>
-      <c r="U224" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="225" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A225" t="str">
-        <v/>
-      </c>
-      <c r="B225" t="str">
-        <v/>
-      </c>
-      <c r="C225" t="str">
-        <v/>
-      </c>
-      <c r="D225" t="str">
-        <v/>
-      </c>
-      <c r="E225" t="str">
-        <v/>
-      </c>
-      <c r="F225" s="25">
+      <c r="S227" t="str">
+        <v/>
+      </c>
+      <c r="T227" t="str">
+        <v/>
+      </c>
+      <c r="U227" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="228" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A228" t="str">
+        <v/>
+      </c>
+      <c r="B228" t="str">
+        <v/>
+      </c>
+      <c r="C228" t="str">
+        <v/>
+      </c>
+      <c r="D228" t="str">
+        <v/>
+      </c>
+      <c r="E228" t="str">
+        <v/>
+      </c>
+      <c r="F228" s="26">
         <v>46061</v>
       </c>
-      <c r="G225" s="25">
+      <c r="G228" s="26">
         <v>46132</v>
       </c>
-      <c r="H225" t="str">
-        <v/>
-      </c>
-      <c r="I225" t="str">
-        <v/>
-      </c>
-      <c r="J225" t="str">
-        <v/>
-      </c>
-      <c r="K225" t="str">
-        <v/>
-      </c>
-      <c r="L225" t="str">
-        <v/>
-      </c>
-      <c r="M225" s="26">
+      <c r="H228" t="str">
+        <v/>
+      </c>
+      <c r="I228" t="str">
+        <v/>
+      </c>
+      <c r="J228" t="str">
+        <v/>
+      </c>
+      <c r="K228" t="str">
+        <v/>
+      </c>
+      <c r="L228" t="str">
+        <v/>
+      </c>
+      <c r="M228" s="27">
         <v>1292</v>
       </c>
-      <c r="N225" t="str">
-        <v/>
-      </c>
-      <c r="O225" t="str">
-        <v/>
-      </c>
-      <c r="P225" t="str">
-        <v/>
-      </c>
-      <c r="Q225" s="27" t="str">
+      <c r="N228" t="str">
+        <v/>
+      </c>
+      <c r="O228" t="str">
+        <v/>
+      </c>
+      <c r="P228" t="str">
+        <v/>
+      </c>
+      <c r="Q228" s="28" t="str">
         <v>2026-03-02</v>
       </c>
-      <c r="R225" t="str">
-        <v/>
-      </c>
-      <c r="S225" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T225" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U225" s="28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="226" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A227" s="33" t="str">
+      <c r="R228" t="str">
+        <v/>
+      </c>
+      <c r="S228" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T228" s="29" t="str">
+        <v/>
+      </c>
+      <c r="U228" s="29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="229" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="34" t="str">
         <v>Program Milestones</v>
       </c>
     </row>
-    <row r="228" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A228" s="3" t="str">
+    <row r="231" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A231" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B228" s="3" t="str">
+      <c r="B231" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C228" s="3" t="str">
+      <c r="C231" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D228" s="3" t="str">
+      <c r="D231" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E228" s="3" t="str">
+      <c r="E231" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F228" s="3" t="str">
+      <c r="F231" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G228" s="3" t="str">
+      <c r="G231" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H228" s="3" t="str">
+      <c r="H231" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I228" s="3" t="str">
+      <c r="I231" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J228" s="3" t="str">
+      <c r="J231" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K228" s="3" t="str">
+      <c r="K231" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L228" s="3" t="str">
+      <c r="L231" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M228" s="3" t="str">
+      <c r="M231" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N228" s="3" t="str">
+      <c r="N231" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O228" s="3" t="str">
+      <c r="O231" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P228" s="3" t="str">
+      <c r="P231" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q228" s="3" t="str">
+      <c r="Q231" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R228" s="3" t="str">
+      <c r="R231" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S228" s="3" t="str">
+      <c r="S231" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T228" s="3" t="str">
+      <c r="T231" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U228" s="3" t="str">
+      <c r="U231" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="229" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A229" s="4" t="str">
-        <v>STD + Swaggers</v>
-      </c>
-      <c r="B229" t="str">
-        <v/>
-      </c>
-      <c r="C229" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="D229" t="str">
-        <v/>
-      </c>
-      <c r="E229" t="str">
-        <v/>
-      </c>
-      <c r="F229" s="8">
-        <v>46048</v>
-      </c>
-      <c r="G229" s="8">
-        <v>46048</v>
-      </c>
-      <c r="H229" t="str">
-        <v/>
-      </c>
-      <c r="I229" t="str">
-        <v/>
-      </c>
-      <c r="J229" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K229" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L229" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M229" t="str">
-        <v/>
-      </c>
-      <c r="N229" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O229" t="str">
-        <v/>
-      </c>
-      <c r="P229" t="str">
-        <v/>
-      </c>
-      <c r="Q229" t="str">
-        <v/>
-      </c>
-      <c r="R229" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:19 PM</v>
-      </c>
-      <c r="S229" t="str">
-        <v/>
-      </c>
-      <c r="T229" t="str">
-        <v/>
-      </c>
-      <c r="U229" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="230" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A230" s="4" t="str">
-        <v>Critical APIs in production</v>
-      </c>
-      <c r="B230" t="str">
-        <v/>
-      </c>
-      <c r="C230" s="5" t="str">
-        <v>FE DEV WIP</v>
-      </c>
-      <c r="D230" t="str">
-        <v/>
-      </c>
-      <c r="E230" t="str">
-        <v/>
-      </c>
-      <c r="F230" s="8">
-        <v>46112</v>
-      </c>
-      <c r="G230" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H230" t="str">
-        <v/>
-      </c>
-      <c r="I230" t="str">
-        <v/>
-      </c>
-      <c r="J230" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K230" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L230" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M230" t="str">
-        <v/>
-      </c>
-      <c r="N230" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O230" t="str">
-        <v/>
-      </c>
-      <c r="P230" t="str">
-        <v/>
-      </c>
-      <c r="Q230" t="str">
-        <v/>
-      </c>
-      <c r="R230" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:15 PM</v>
-      </c>
-      <c r="S230" t="str">
-        <v/>
-      </c>
-      <c r="T230" t="str">
-        <v/>
-      </c>
-      <c r="U230" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="231" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A231" s="4" t="str">
-        <v>Non critical APIs in prodcution</v>
-      </c>
-      <c r="B231" t="str">
-        <v/>
-      </c>
-      <c r="C231" s="5" t="str">
-        <v>FE DEV WIP</v>
-      </c>
-      <c r="D231" t="str">
-        <v/>
-      </c>
-      <c r="E231" t="str">
-        <v/>
-      </c>
-      <c r="F231" s="8">
-        <v>46127</v>
-      </c>
-      <c r="G231" s="8">
-        <v>46142</v>
-      </c>
-      <c r="H231" t="str">
-        <v/>
-      </c>
-      <c r="I231" t="str">
-        <v/>
-      </c>
-      <c r="J231" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K231" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L231" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M231" t="str">
-        <v/>
-      </c>
-      <c r="N231" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O231" t="str">
-        <v/>
-      </c>
-      <c r="P231" t="str">
-        <v/>
-      </c>
-      <c r="Q231" t="str">
-        <v/>
-      </c>
-      <c r="R231" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
-      </c>
-      <c r="S231" t="str">
-        <v/>
-      </c>
-      <c r="T231" t="str">
-        <v/>
-      </c>
-      <c r="U231" t="str">
-        <v/>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="str">
-        <v>E2E readiness</v>
+        <v>STD + Swaggers</v>
       </c>
       <c r="B232" t="str">
         <v/>
       </c>
-      <c r="C232" s="19" t="str">
-        <v>Not Started</v>
+      <c r="C232" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D232" t="str">
         <v/>
@@ -11018,16 +10936,16 @@
         <v/>
       </c>
       <c r="F232" s="8">
-        <v>46145</v>
+        <v>46048</v>
       </c>
       <c r="G232" s="8">
-        <v>46145</v>
+        <v>46048</v>
       </c>
       <c r="H232" t="str">
         <v/>
       </c>
-      <c r="I232" s="6" t="str">
-        <v>E2E to start in Mid May + 1.5 weeks buffer</v>
+      <c r="I232" t="str">
+        <v/>
       </c>
       <c r="J232" s="6" t="str">
         <v/>
@@ -11054,7 +10972,7 @@
         <v/>
       </c>
       <c r="R232" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:19 PM</v>
       </c>
       <c r="S232" t="str">
         <v/>
@@ -11068,13 +10986,13 @@
     </row>
     <row r="233" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="str">
-        <v>Drop 1 Super- 20.4</v>
+        <v>Critical APIs in production</v>
       </c>
       <c r="B233" t="str">
         <v/>
       </c>
-      <c r="C233" s="16" t="str">
-        <v>Deployment</v>
+      <c r="C233" s="5" t="str">
+        <v>FE DEV WIP</v>
       </c>
       <c r="D233" t="str">
         <v/>
@@ -11082,11 +11000,11 @@
       <c r="E233" t="str">
         <v/>
       </c>
-      <c r="F233" t="str">
-        <v/>
-      </c>
-      <c r="G233" t="str">
-        <v/>
+      <c r="F233" s="8">
+        <v>46112</v>
+      </c>
+      <c r="G233" s="8">
+        <v>46127</v>
       </c>
       <c r="H233" t="str">
         <v/>
@@ -11119,7 +11037,7 @@
         <v/>
       </c>
       <c r="R233" s="6" t="str">
-        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:15 PM</v>
       </c>
       <c r="S233" t="str">
         <v/>
@@ -11133,7 +11051,7 @@
     </row>
     <row r="234" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="str">
-        <v>Drop 2 - Super 4.5</v>
+        <v>Non critical APIs in prodcution</v>
       </c>
       <c r="B234" t="str">
         <v/>
@@ -11147,11 +11065,11 @@
       <c r="E234" t="str">
         <v/>
       </c>
-      <c r="F234" t="str">
-        <v/>
-      </c>
-      <c r="G234" t="str">
-        <v/>
+      <c r="F234" s="8">
+        <v>46127</v>
+      </c>
+      <c r="G234" s="8">
+        <v>46142</v>
       </c>
       <c r="H234" t="str">
         <v/>
@@ -11184,7 +11102,7 @@
         <v/>
       </c>
       <c r="R234" s="6" t="str">
-        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
       </c>
       <c r="S234" t="str">
         <v/>
@@ -11198,13 +11116,13 @@
     </row>
     <row r="235" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="str">
-        <v>Drop 3 Super - 18.5</v>
+        <v>E2E readiness</v>
       </c>
       <c r="B235" t="str">
         <v/>
       </c>
-      <c r="C235" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C235" s="18" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D235" t="str">
         <v/>
@@ -11212,17 +11130,17 @@
       <c r="E235" t="str">
         <v/>
       </c>
-      <c r="F235" t="str">
-        <v/>
-      </c>
-      <c r="G235" t="str">
-        <v/>
+      <c r="F235" s="8">
+        <v>46145</v>
+      </c>
+      <c r="G235" s="8">
+        <v>46145</v>
       </c>
       <c r="H235" t="str">
         <v/>
       </c>
-      <c r="I235" t="str">
-        <v/>
+      <c r="I235" s="6" t="str">
+        <v>E2E to start in Mid May + 1.5 weeks buffer</v>
       </c>
       <c r="J235" s="6" t="str">
         <v/>
@@ -11249,7 +11167,7 @@
         <v/>
       </c>
       <c r="R235" s="6" t="str">
-        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
       </c>
       <c r="S235" t="str">
         <v/>
@@ -11263,13 +11181,13 @@
     </row>
     <row r="236" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="str">
-        <v>Drop 4- Super - 1.6</v>
+        <v>Drop 1 Super- 20.4</v>
       </c>
       <c r="B236" t="str">
         <v/>
       </c>
-      <c r="C236" s="14" t="str">
-        <v>Discovery</v>
+      <c r="C236" s="16" t="str">
+        <v>Deployment</v>
       </c>
       <c r="D236" t="str">
         <v/>
@@ -11327,14 +11245,14 @@
       </c>
     </row>
     <row r="237" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A237" t="str">
-        <v/>
+      <c r="A237" s="4" t="str">
+        <v>Drop 2 - Super 4.5</v>
       </c>
       <c r="B237" t="str">
         <v/>
       </c>
-      <c r="C237" t="str">
-        <v/>
+      <c r="C237" s="5" t="str">
+        <v>FE DEV WIP</v>
       </c>
       <c r="D237" t="str">
         <v/>
@@ -11342,387 +11260,582 @@
       <c r="E237" t="str">
         <v/>
       </c>
-      <c r="F237" s="25">
+      <c r="F237" t="str">
+        <v/>
+      </c>
+      <c r="G237" t="str">
+        <v/>
+      </c>
+      <c r="H237" t="str">
+        <v/>
+      </c>
+      <c r="I237" t="str">
+        <v/>
+      </c>
+      <c r="J237" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K237" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L237" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M237" t="str">
+        <v/>
+      </c>
+      <c r="N237" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O237" t="str">
+        <v/>
+      </c>
+      <c r="P237" t="str">
+        <v/>
+      </c>
+      <c r="Q237" t="str">
+        <v/>
+      </c>
+      <c r="R237" s="6" t="str">
+        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+      </c>
+      <c r="S237" t="str">
+        <v/>
+      </c>
+      <c r="T237" t="str">
+        <v/>
+      </c>
+      <c r="U237" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="238" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="str">
+        <v>Drop 3 Super - 18.5</v>
+      </c>
+      <c r="B238" t="str">
+        <v/>
+      </c>
+      <c r="C238" s="5" t="str">
+        <v>FE DEV WIP</v>
+      </c>
+      <c r="D238" t="str">
+        <v/>
+      </c>
+      <c r="E238" t="str">
+        <v/>
+      </c>
+      <c r="F238" t="str">
+        <v/>
+      </c>
+      <c r="G238" t="str">
+        <v/>
+      </c>
+      <c r="H238" t="str">
+        <v/>
+      </c>
+      <c r="I238" t="str">
+        <v/>
+      </c>
+      <c r="J238" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K238" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L238" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M238" t="str">
+        <v/>
+      </c>
+      <c r="N238" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O238" t="str">
+        <v/>
+      </c>
+      <c r="P238" t="str">
+        <v/>
+      </c>
+      <c r="Q238" t="str">
+        <v/>
+      </c>
+      <c r="R238" s="6" t="str">
+        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+      </c>
+      <c r="S238" t="str">
+        <v/>
+      </c>
+      <c r="T238" t="str">
+        <v/>
+      </c>
+      <c r="U238" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="239" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="str">
+        <v>Drop 4- Super - 1.6</v>
+      </c>
+      <c r="B239" t="str">
+        <v/>
+      </c>
+      <c r="C239" s="14" t="str">
+        <v>Discovery</v>
+      </c>
+      <c r="D239" t="str">
+        <v/>
+      </c>
+      <c r="E239" t="str">
+        <v/>
+      </c>
+      <c r="F239" t="str">
+        <v/>
+      </c>
+      <c r="G239" t="str">
+        <v/>
+      </c>
+      <c r="H239" t="str">
+        <v/>
+      </c>
+      <c r="I239" t="str">
+        <v/>
+      </c>
+      <c r="J239" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K239" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L239" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M239" t="str">
+        <v/>
+      </c>
+      <c r="N239" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O239" t="str">
+        <v/>
+      </c>
+      <c r="P239" t="str">
+        <v/>
+      </c>
+      <c r="Q239" t="str">
+        <v/>
+      </c>
+      <c r="R239" s="6" t="str">
+        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+      </c>
+      <c r="S239" t="str">
+        <v/>
+      </c>
+      <c r="T239" t="str">
+        <v/>
+      </c>
+      <c r="U239" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="240" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A240" t="str">
+        <v/>
+      </c>
+      <c r="B240" t="str">
+        <v/>
+      </c>
+      <c r="C240" t="str">
+        <v/>
+      </c>
+      <c r="D240" t="str">
+        <v/>
+      </c>
+      <c r="E240" t="str">
+        <v/>
+      </c>
+      <c r="F240" s="26">
         <v>46048</v>
       </c>
-      <c r="G237" s="25">
+      <c r="G240" s="26">
         <v>46145</v>
       </c>
-      <c r="H237" t="str">
-        <v/>
-      </c>
-      <c r="I237" t="str">
-        <v/>
-      </c>
-      <c r="J237" t="str">
-        <v/>
-      </c>
-      <c r="K237" t="str">
-        <v/>
-      </c>
-      <c r="L237" t="str">
-        <v/>
-      </c>
-      <c r="M237" s="26">
+      <c r="H240" t="str">
+        <v/>
+      </c>
+      <c r="I240" t="str">
+        <v/>
+      </c>
+      <c r="J240" t="str">
+        <v/>
+      </c>
+      <c r="K240" t="str">
+        <v/>
+      </c>
+      <c r="L240" t="str">
+        <v/>
+      </c>
+      <c r="M240" s="27">
         <v>0</v>
       </c>
-      <c r="N237" t="str">
-        <v/>
-      </c>
-      <c r="O237" t="str">
-        <v/>
-      </c>
-      <c r="P237" t="str">
-        <v/>
-      </c>
-      <c r="Q237" s="28" t="str">
-        <v/>
-      </c>
-      <c r="R237" t="str">
-        <v/>
-      </c>
-      <c r="S237" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T237" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U237" s="28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="238" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A239" s="29" t="str">
+      <c r="N240" t="str">
+        <v/>
+      </c>
+      <c r="O240" t="str">
+        <v/>
+      </c>
+      <c r="P240" t="str">
+        <v/>
+      </c>
+      <c r="Q240" s="29" t="str">
+        <v/>
+      </c>
+      <c r="R240" t="str">
+        <v/>
+      </c>
+      <c r="S240" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T240" s="29" t="str">
+        <v/>
+      </c>
+      <c r="U240" s="29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="241" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" s="30" t="str">
         <v>Dependencies</v>
       </c>
     </row>
-    <row r="240" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A240" s="3" t="str">
+    <row r="243" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A243" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B240" s="3" t="str">
+      <c r="B243" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C240" s="3" t="str">
+      <c r="C243" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D240" s="3" t="str">
+      <c r="D243" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E240" s="3" t="str">
+      <c r="E243" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F240" s="3" t="str">
+      <c r="F243" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G240" s="3" t="str">
+      <c r="G243" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H240" s="3" t="str">
+      <c r="H243" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I240" s="3" t="str">
+      <c r="I243" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J240" s="3" t="str">
+      <c r="J243" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K240" s="3" t="str">
+      <c r="K243" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L240" s="3" t="str">
+      <c r="L243" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M240" s="3" t="str">
+      <c r="M243" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N240" s="3" t="str">
+      <c r="N243" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O240" s="3" t="str">
+      <c r="O243" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P240" s="3" t="str">
+      <c r="P243" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q240" s="3" t="str">
+      <c r="Q243" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R240" s="3" t="str">
+      <c r="R243" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S240" s="3" t="str">
+      <c r="S243" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T240" s="3" t="str">
+      <c r="T243" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U240" s="3" t="str">
+      <c r="U243" s="3" t="str">
         <v>Product ETA - End</v>
       </c>
     </row>
-    <row r="241" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A241" s="4" t="str">
+    <row r="244" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="str">
         <v>trading real time equity API</v>
       </c>
-      <c r="B241" t="str">
-        <v/>
-      </c>
-      <c r="C241" s="11" t="str">
+      <c r="B244" t="str">
+        <v/>
+      </c>
+      <c r="C244" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D241" t="str">
-        <v/>
-      </c>
-      <c r="E241" t="str">
-        <v/>
-      </c>
-      <c r="F241" t="str">
-        <v/>
-      </c>
-      <c r="G241" t="str">
-        <v/>
-      </c>
-      <c r="H241" t="str">
-        <v/>
-      </c>
-      <c r="I241" t="str">
-        <v/>
-      </c>
-      <c r="J241" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K241" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L241" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M241" t="str">
-        <v/>
-      </c>
-      <c r="N241" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O241" t="str">
-        <v/>
-      </c>
-      <c r="P241" t="str">
-        <v/>
-      </c>
-      <c r="Q241" t="str">
-        <v/>
-      </c>
-      <c r="R241" s="6" t="str">
+      <c r="D244" t="str">
+        <v/>
+      </c>
+      <c r="E244" t="str">
+        <v/>
+      </c>
+      <c r="F244" t="str">
+        <v/>
+      </c>
+      <c r="G244" t="str">
+        <v/>
+      </c>
+      <c r="H244" t="str">
+        <v/>
+      </c>
+      <c r="I244" t="str">
+        <v/>
+      </c>
+      <c r="J244" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K244" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L244" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M244" t="str">
+        <v/>
+      </c>
+      <c r="N244" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O244" t="str">
+        <v/>
+      </c>
+      <c r="P244" t="str">
+        <v/>
+      </c>
+      <c r="Q244" t="str">
+        <v/>
+      </c>
+      <c r="R244" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 11:31 AM</v>
       </c>
-      <c r="S241" t="str">
-        <v/>
-      </c>
-      <c r="T241" t="str">
-        <v/>
-      </c>
-      <c r="U241" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="242" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A242" s="4" t="str">
+      <c r="S244" t="str">
+        <v/>
+      </c>
+      <c r="T244" t="str">
+        <v/>
+      </c>
+      <c r="U244" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="245" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A245" s="4" t="str">
         <v>trading BE orch</v>
       </c>
-      <c r="B242" t="str">
-        <v/>
-      </c>
-      <c r="C242" s="20" t="str">
+      <c r="B245" t="str">
+        <v/>
+      </c>
+      <c r="C245" s="19" t="str">
         <v>Cancelled</v>
       </c>
-      <c r="D242" t="str">
-        <v/>
-      </c>
-      <c r="E242" t="str">
-        <v/>
-      </c>
-      <c r="F242" t="str">
-        <v/>
-      </c>
-      <c r="G242" t="str">
-        <v/>
-      </c>
-      <c r="H242" t="str">
-        <v/>
-      </c>
-      <c r="I242" t="str">
-        <v/>
-      </c>
-      <c r="J242" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K242" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L242" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M242" t="str">
-        <v/>
-      </c>
-      <c r="N242" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O242" t="str">
-        <v/>
-      </c>
-      <c r="P242" t="str">
-        <v/>
-      </c>
-      <c r="Q242" t="str">
-        <v/>
-      </c>
-      <c r="R242" s="6" t="str">
+      <c r="D245" t="str">
+        <v/>
+      </c>
+      <c r="E245" t="str">
+        <v/>
+      </c>
+      <c r="F245" t="str">
+        <v/>
+      </c>
+      <c r="G245" t="str">
+        <v/>
+      </c>
+      <c r="H245" t="str">
+        <v/>
+      </c>
+      <c r="I245" t="str">
+        <v/>
+      </c>
+      <c r="J245" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K245" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L245" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M245" t="str">
+        <v/>
+      </c>
+      <c r="N245" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O245" t="str">
+        <v/>
+      </c>
+      <c r="P245" t="str">
+        <v/>
+      </c>
+      <c r="Q245" t="str">
+        <v/>
+      </c>
+      <c r="R245" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 11:50 AM</v>
       </c>
-      <c r="S242" t="str">
-        <v/>
-      </c>
-      <c r="T242" t="str">
-        <v/>
-      </c>
-      <c r="U242" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="243" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A243" s="4" t="str">
+      <c r="S245" t="str">
+        <v/>
+      </c>
+      <c r="T245" t="str">
+        <v/>
+      </c>
+      <c r="U245" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="246" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A246" s="4" t="str">
         <v>Banking deposit MOP</v>
       </c>
-      <c r="B243" t="str">
-        <v/>
-      </c>
-      <c r="C243" s="11" t="str">
+      <c r="B246" t="str">
+        <v/>
+      </c>
+      <c r="C246" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D243" t="str">
-        <v/>
-      </c>
-      <c r="E243" t="str">
-        <v/>
-      </c>
-      <c r="F243" t="str">
-        <v/>
-      </c>
-      <c r="G243" t="str">
-        <v/>
-      </c>
-      <c r="H243" t="str">
-        <v/>
-      </c>
-      <c r="I243" t="str">
-        <v/>
-      </c>
-      <c r="J243" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K243" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L243" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M243" t="str">
-        <v/>
-      </c>
-      <c r="N243" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O243" t="str">
-        <v/>
-      </c>
-      <c r="P243" t="str">
-        <v/>
-      </c>
-      <c r="Q243" t="str">
-        <v/>
-      </c>
-      <c r="R243" s="6" t="str">
+      <c r="D246" t="str">
+        <v/>
+      </c>
+      <c r="E246" t="str">
+        <v/>
+      </c>
+      <c r="F246" t="str">
+        <v/>
+      </c>
+      <c r="G246" t="str">
+        <v/>
+      </c>
+      <c r="H246" t="str">
+        <v/>
+      </c>
+      <c r="I246" t="str">
+        <v/>
+      </c>
+      <c r="J246" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K246" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L246" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M246" t="str">
+        <v/>
+      </c>
+      <c r="N246" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O246" t="str">
+        <v/>
+      </c>
+      <c r="P246" t="str">
+        <v/>
+      </c>
+      <c r="Q246" t="str">
+        <v/>
+      </c>
+      <c r="R246" s="6" t="str">
         <v>Hagit Zamir Feb 5, 2026 4:03 PM</v>
       </c>
-      <c r="S243" t="str">
-        <v/>
-      </c>
-      <c r="T243" t="str">
-        <v/>
-      </c>
-      <c r="U243" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="244" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A244" t="str">
-        <v/>
-      </c>
-      <c r="B244" t="str">
-        <v/>
-      </c>
-      <c r="C244" t="str">
-        <v/>
-      </c>
-      <c r="D244" t="str">
-        <v/>
-      </c>
-      <c r="E244" t="str">
-        <v/>
-      </c>
-      <c r="F244" s="28" t="str">
-        <v/>
-      </c>
-      <c r="G244" s="28" t="str">
-        <v/>
-      </c>
-      <c r="H244" t="str">
-        <v/>
-      </c>
-      <c r="I244" t="str">
-        <v/>
-      </c>
-      <c r="J244" t="str">
-        <v/>
-      </c>
-      <c r="K244" t="str">
-        <v/>
-      </c>
-      <c r="L244" t="str">
-        <v/>
-      </c>
-      <c r="M244" s="26">
+      <c r="S246" t="str">
+        <v/>
+      </c>
+      <c r="T246" t="str">
+        <v/>
+      </c>
+      <c r="U246" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="247" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A247" t="str">
+        <v/>
+      </c>
+      <c r="B247" t="str">
+        <v/>
+      </c>
+      <c r="C247" t="str">
+        <v/>
+      </c>
+      <c r="D247" t="str">
+        <v/>
+      </c>
+      <c r="E247" t="str">
+        <v/>
+      </c>
+      <c r="F247" s="29" t="str">
+        <v/>
+      </c>
+      <c r="G247" s="29" t="str">
+        <v/>
+      </c>
+      <c r="H247" t="str">
+        <v/>
+      </c>
+      <c r="I247" t="str">
+        <v/>
+      </c>
+      <c r="J247" t="str">
+        <v/>
+      </c>
+      <c r="K247" t="str">
+        <v/>
+      </c>
+      <c r="L247" t="str">
+        <v/>
+      </c>
+      <c r="M247" s="27">
         <v>0</v>
       </c>
-      <c r="N244" t="str">
-        <v/>
-      </c>
-      <c r="O244" t="str">
-        <v/>
-      </c>
-      <c r="P244" t="str">
-        <v/>
-      </c>
-      <c r="Q244" s="28" t="str">
-        <v/>
-      </c>
-      <c r="R244" t="str">
-        <v/>
-      </c>
-      <c r="S244" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T244" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U244" s="28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="245" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="N247" t="str">
+        <v/>
+      </c>
+      <c r="O247" t="str">
+        <v/>
+      </c>
+      <c r="P247" t="str">
+        <v/>
+      </c>
+      <c r="Q247" s="29" t="str">
+        <v/>
+      </c>
+      <c r="R247" t="str">
+        <v/>
+      </c>
+      <c r="S247" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T247" s="29" t="str">
+        <v/>
+      </c>
+      <c r="U247" s="29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="248" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -1601,7 +1601,7 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="str">
-        <v>Money Core- - Inbal</v>
+        <v>Money Core- Inbal</v>
       </c>
       <c r="B27" t="str">
         <v/>
@@ -3159,8 +3159,8 @@
       <c r="C67" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D67" s="5" t="str">
-        <v>Dev - WIP</v>
+      <c r="D67" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E67" s="6" t="str">
         <v/>
@@ -6007,8 +6007,8 @@
       <c r="B140" t="str">
         <v/>
       </c>
-      <c r="C140" s="14" t="str">
-        <v>Discovery</v>
+      <c r="C140" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D140" t="str">
         <v/>

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -108,17 +108,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF007F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF579BFC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCAB641"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF007F"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,7 +133,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBB3354"/>
+        <fgColor rgb="FF784BD1"/>
       </patternFill>
     </fill>
     <fill>
@@ -143,12 +143,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF5AC4"/>
+        <fgColor rgb="FFBB3354"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF784BD1"/>
+        <fgColor rgb="FFFF5AC4"/>
       </patternFill>
     </fill>
     <fill>
@@ -1161,8 +1161,8 @@
       <c r="B16" t="str">
         <v/>
       </c>
-      <c r="C16" s="13" t="str">
-        <v>In QA</v>
+      <c r="C16" s="14" t="str">
+        <v>Deployment</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -1539,7 +1539,7 @@
       <c r="C25" t="str">
         <v/>
       </c>
-      <c r="D25" s="14" t="str">
+      <c r="D25" s="15" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E25" s="6" t="str">
@@ -1574,7 +1574,7 @@
       <c r="C26" t="str">
         <v/>
       </c>
-      <c r="D26" s="14" t="str">
+      <c r="D26" s="15" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E26" s="6" t="str">
@@ -1606,8 +1606,8 @@
       <c r="B27" t="str">
         <v/>
       </c>
-      <c r="C27" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C27" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -1736,7 +1736,7 @@
       <c r="B29" t="str">
         <v/>
       </c>
-      <c r="C29" s="14" t="str">
+      <c r="C29" s="15" t="str">
         <v>Discovery</v>
       </c>
       <c r="D29" s="6" t="str">
@@ -1839,7 +1839,7 @@
       <c r="C31" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D31" s="15" t="str">
+      <c r="D31" s="16" t="str">
         <v>QA</v>
       </c>
       <c r="E31" s="6" t="str">
@@ -1874,7 +1874,7 @@
       <c r="C32" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D32" s="16" t="str">
+      <c r="D32" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E32" s="6" t="str">
@@ -1909,7 +1909,7 @@
       <c r="C33" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D33" s="16" t="str">
+      <c r="D33" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E33" s="6" t="str">
@@ -1944,7 +1944,7 @@
       <c r="C34" s="6" t="str">
         <v>Noit Hoffman, Joanna Fajga</v>
       </c>
-      <c r="D34" s="16" t="str">
+      <c r="D34" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E34" s="6" t="str">
@@ -2536,7 +2536,7 @@
       <c r="B51" t="str">
         <v/>
       </c>
-      <c r="C51" s="14" t="str">
+      <c r="C51" s="15" t="str">
         <v>Discovery</v>
       </c>
       <c r="D51" t="str">
@@ -2639,8 +2639,8 @@
       <c r="C53" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D53" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D53" s="13" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E53" s="6" t="str">
         <v/>
@@ -2674,8 +2674,8 @@
       <c r="C54" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D54" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D54" s="13" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E54" s="6" t="str">
         <v/>
@@ -2709,8 +2709,8 @@
       <c r="C55" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D55" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D55" s="13" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E55" s="6" t="str">
         <v/>
@@ -2839,139 +2839,139 @@
         <v/>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="str">
+    <row r="59" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="str">
+        <v/>
+      </c>
+      <c r="B59" s="4" t="str">
+        <v>Deposit flow for Desktop - Joanna is teh product</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" s="19" t="str">
+        <v>futureVersion</v>
+      </c>
+      <c r="E59" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="str">
         <v>IBAN Creation-</v>
       </c>
-      <c r="B59" t="str">
-        <v/>
-      </c>
-      <c r="C59" s="18" t="str">
+      <c r="B60" t="str">
+        <v/>
+      </c>
+      <c r="C60" s="18" t="str">
         <v>Not Started</v>
       </c>
-      <c r="D59" s="6" t="str">
+      <c r="D60" s="6" t="str">
         <v>depositOpenBanking, Banking</v>
       </c>
-      <c r="E59" t="str">
-        <v/>
-      </c>
-      <c r="F59" t="str">
-        <v/>
-      </c>
-      <c r="G59" t="str">
-        <v/>
-      </c>
-      <c r="H59" s="6" t="str">
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" s="6" t="str">
         <v>V3(18.5)</v>
       </c>
-      <c r="I59" t="str">
-        <v/>
-      </c>
-      <c r="J59" s="6" t="str">
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" s="6" t="str">
         <v>Richard</v>
       </c>
-      <c r="K59" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L59" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M59" s="6">
+      <c r="K60" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L60" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M60" s="6">
         <v>2</v>
       </c>
-      <c r="N59" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O59" s="6" t="str">
+      <c r="N60" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O60" s="6" t="str">
         <v>https://drive.google.com/drive/u/0/folders/1FWXRnhi0O2SFFPPtZkGZJ0lrDmfD8ElO</v>
       </c>
-      <c r="P59" s="6" t="str">
+      <c r="P60" s="6" t="str">
         <v>Banking</v>
       </c>
-      <c r="Q59" s="7">
+      <c r="Q60" s="7">
         <v>46127</v>
       </c>
-      <c r="R59" s="6" t="str">
+      <c r="R60" s="6" t="str">
         <v>Hagit Zamir Feb 3, 2026 12:32 PM</v>
       </c>
-      <c r="S59" t="str">
-        <v/>
-      </c>
-      <c r="T59" t="str">
-        <v/>
-      </c>
-      <c r="U59" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="str">
+      <c r="S60" t="str">
+        <v/>
+      </c>
+      <c r="T60" t="str">
+        <v/>
+      </c>
+      <c r="U60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B60" s="10" t="str">
+      <c r="B61" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C60" s="10" t="str">
+      <c r="C61" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D60" s="10" t="str">
+      <c r="D61" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E60" s="10" t="str">
+      <c r="E61" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F60" s="10" t="str">
+      <c r="F61" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G60" s="10" t="str">
+      <c r="G61" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H60" s="10" t="str">
+      <c r="H61" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I60" s="10" t="str">
+      <c r="I61" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J60" s="10" t="str">
+      <c r="J61" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K60" s="10" t="str">
+      <c r="K61" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" t="str">
-        <v/>
-      </c>
-      <c r="B61" s="4" t="str">
-        <v>IBAN creation without card (touchpoints from Deposit, Wallet Tab, Withdrawal) - 1</v>
-      </c>
-      <c r="C61" t="str">
-        <v/>
-      </c>
-      <c r="D61" s="18" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="E61" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F61" t="str">
-        <v/>
-      </c>
-      <c r="G61" t="str">
-        <v/>
-      </c>
-      <c r="H61" t="str">
-        <v/>
-      </c>
-      <c r="I61" t="str">
-        <v/>
-      </c>
-      <c r="J61" t="str">
-        <v/>
-      </c>
-      <c r="K61" t="str">
-        <v/>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2979,7 +2979,7 @@
         <v/>
       </c>
       <c r="B62" s="4" t="str">
-        <v>IBAN creation for Card Programs - confirm address and set PIN (touchpoints from Deposit, Wallet Tab, Withdrawal) - 2</v>
+        <v>IBAN creation without card (touchpoints from Deposit, Wallet Tab, Withdrawal) - 1</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -3014,7 +3014,7 @@
         <v/>
       </c>
       <c r="B63" s="4" t="str">
-        <v>IBAN creation Terms &amp; Conditions (All Programs) -2</v>
+        <v>IBAN creation for Card Programs - confirm address and set PIN (touchpoints from Deposit, Wallet Tab, Withdrawal) - 2</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -3044,139 +3044,139 @@
         <v/>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="str">
+    <row r="64" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="str">
+        <v/>
+      </c>
+      <c r="B64" s="4" t="str">
+        <v>IBAN creation Terms &amp; Conditions (All Programs) -2</v>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" s="18" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="E64" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="str">
         <v>Custodial wallet crypto</v>
       </c>
-      <c r="B64" t="str">
-        <v/>
-      </c>
-      <c r="C64" s="5" t="str">
+      <c r="B65" t="str">
+        <v/>
+      </c>
+      <c r="C65" s="5" t="str">
         <v>FE DEV WIP</v>
       </c>
-      <c r="D64" s="6" t="str">
-        <v/>
-      </c>
-      <c r="E64" t="str">
-        <v/>
-      </c>
-      <c r="F64" s="8">
+      <c r="D65" s="6" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" s="8">
         <v>46061</v>
       </c>
-      <c r="G64" s="8">
+      <c r="G65" s="8">
         <v>46112</v>
       </c>
-      <c r="H64" s="6" t="str">
-        <v>V2(4.5), V3(18.5), V1(20.4)</v>
-      </c>
-      <c r="I64" t="str">
-        <v/>
-      </c>
-      <c r="J64" s="6" t="str">
+      <c r="H65" s="6" t="str">
+        <v>V2(4.5), V3(18.5), V1(20.4), V5(15.6)</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="K64" s="6" t="str">
+      <c r="K65" s="6" t="str">
         <v>Ofir Shwartz</v>
       </c>
-      <c r="L64" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M64" s="6">
+      <c r="L65" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M65" s="6">
         <v>2</v>
       </c>
-      <c r="N64" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O64" s="6" t="str">
+      <c r="N65" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O65" s="6" t="str">
         <v>https://drive.google.com/drive/u/0/folders/1TUMyoZElqh662CF76uU0K3UJY0bomFzx</v>
       </c>
-      <c r="P64" s="6" t="str">
+      <c r="P65" s="6" t="str">
         <v>Crypto</v>
       </c>
-      <c r="Q64" s="7">
+      <c r="Q65" s="7">
         <v>46100</v>
       </c>
-      <c r="R64" s="6" t="str">
+      <c r="R65" s="6" t="str">
         <v>Hagit Zamir Feb 3, 2026 12:24 PM</v>
       </c>
-      <c r="S64" t="str">
-        <v/>
-      </c>
-      <c r="T64" s="8">
+      <c r="S65" t="str">
+        <v/>
+      </c>
+      <c r="T65" s="8">
         <v>46094</v>
       </c>
-      <c r="U64" s="8">
+      <c r="U65" s="8">
         <v>46094</v>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="str">
+    <row r="66" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B65" s="10" t="str">
+      <c r="B66" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C65" s="10" t="str">
+      <c r="C66" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D65" s="10" t="str">
+      <c r="D66" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E65" s="10" t="str">
+      <c r="E66" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F65" s="10" t="str">
+      <c r="F66" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G65" s="10" t="str">
+      <c r="G66" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H65" s="10" t="str">
+      <c r="H66" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I65" s="10" t="str">
+      <c r="I66" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J65" s="10" t="str">
+      <c r="J66" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K65" s="10" t="str">
+      <c r="K66" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" t="str">
-        <v/>
-      </c>
-      <c r="B66" s="4" t="str">
-        <v>Custodial wallet crypto - Wallet page overview &amp; activities</v>
-      </c>
-      <c r="C66" s="6" t="str">
-        <v>Nikolaus Kulier</v>
-      </c>
-      <c r="D66" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="E66" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F66" s="6" t="str">
-        <v>V1(20.4)</v>
-      </c>
-      <c r="G66" t="str">
-        <v/>
-      </c>
-      <c r="H66" s="8">
-        <v>46082</v>
-      </c>
-      <c r="I66" s="8">
-        <v>46132</v>
-      </c>
-      <c r="J66" s="7">
-        <v>46079</v>
-      </c>
-      <c r="K66" s="6">
-        <v>2</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3184,7 +3184,7 @@
         <v/>
       </c>
       <c r="B67" s="4" t="str">
-        <v>Custodial wallet crypto - Wallet Drawer</v>
+        <v>Custodial wallet crypto - Wallet page overview &amp; activities</v>
       </c>
       <c r="C67" s="6" t="str">
         <v>Nikolaus Kulier</v>
@@ -3202,7 +3202,7 @@
         <v/>
       </c>
       <c r="H67" s="8">
-        <v>46105</v>
+        <v>46082</v>
       </c>
       <c r="I67" s="8">
         <v>46132</v>
@@ -3219,7 +3219,7 @@
         <v/>
       </c>
       <c r="B68" s="4" t="str">
-        <v>Custodial wallet crypto - New Wallet creation flow (first time)- IDEA</v>
+        <v>Custodial wallet crypto - Wallet Drawer</v>
       </c>
       <c r="C68" s="6" t="str">
         <v>Nikolaus Kulier</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="F68" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V1(20.4)</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3240,10 +3240,10 @@
         <v>46105</v>
       </c>
       <c r="I68" s="8">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="J68" s="7">
-        <v>46105</v>
+        <v>46079</v>
       </c>
       <c r="K68" s="6">
         <v>2</v>
@@ -3254,13 +3254,13 @@
         <v/>
       </c>
       <c r="B69" s="4" t="str">
-        <v>Custodial wallet crypto - NotaBene Widget</v>
+        <v>Custodial wallet crypto - New Wallet creation flow (first time)- IDEA</v>
       </c>
       <c r="C69" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D69" s="16" t="str">
-        <v>Groomed</v>
+      <c r="D69" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E69" s="6" t="str">
         <v/>
@@ -3275,7 +3275,7 @@
         <v>46105</v>
       </c>
       <c r="I69" s="8">
-        <v>46132</v>
+        <v>46126</v>
       </c>
       <c r="J69" s="7">
         <v>46105</v>
@@ -3289,13 +3289,13 @@
         <v/>
       </c>
       <c r="B70" s="4" t="str">
-        <v>Custodial wallet crypto - Gaps infrastructure- Not travel rule</v>
+        <v>Custodial wallet crypto - NotaBene Widget</v>
       </c>
       <c r="C70" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D70" s="16" t="str">
-        <v>Groomed</v>
+      <c r="D70" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E70" s="6" t="str">
         <v/>
@@ -3307,10 +3307,10 @@
         <v/>
       </c>
       <c r="H70" s="8">
+        <v>46105</v>
+      </c>
+      <c r="I70" s="8">
         <v>46132</v>
-      </c>
-      <c r="I70" s="8">
-        <v>46146</v>
       </c>
       <c r="J70" s="7">
         <v>46105</v>
@@ -3324,28 +3324,28 @@
         <v/>
       </c>
       <c r="B71" s="4" t="str">
-        <v>Custodial wallet crypto - Gaps - travel Rule recieve</v>
+        <v>Custodial wallet crypto - Gaps infrastructure- Not travel rule</v>
       </c>
       <c r="C71" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D71" s="16" t="str">
+      <c r="D71" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E71" s="6" t="str">
         <v/>
       </c>
       <c r="F71" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V3(18.5)</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" s="8">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="I71" s="8">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="J71" s="7">
         <v>46105</v>
@@ -3359,31 +3359,31 @@
         <v/>
       </c>
       <c r="B72" s="4" t="str">
-        <v>Custodial wallet crypto - Send (with travel rule) CASP/Self Hosted</v>
+        <v>Custodial wallet crypto - Gaps - travel Rule recieve</v>
       </c>
       <c r="C72" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D72" s="16" t="str">
+      <c r="D72" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E72" s="6" t="str">
         <v/>
       </c>
       <c r="F72" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V2(4.5)</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" s="8">
+        <v>46132</v>
+      </c>
+      <c r="I72" s="8">
         <v>46146</v>
       </c>
-      <c r="I72" s="8">
-        <v>46160</v>
-      </c>
       <c r="J72" s="7">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="K72" s="6">
         <v>2</v>
@@ -3399,8 +3399,8 @@
       <c r="C73" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D73" s="19" t="str">
-        <v>Design</v>
+      <c r="D73" s="14" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E73" s="6" t="str">
         <v/>
@@ -3434,14 +3434,14 @@
       <c r="C74" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D74" s="19" t="str">
-        <v>Design</v>
+      <c r="D74" s="20" t="str">
+        <v>Grooming</v>
       </c>
       <c r="E74" s="6" t="str">
         <v/>
       </c>
       <c r="F74" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V4(1.6)</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3469,14 +3469,14 @@
       <c r="C75" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D75" s="16" t="str">
+      <c r="D75" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E75" s="6" t="str">
         <v/>
       </c>
       <c r="F75" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V4(1.6)</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3504,14 +3504,14 @@
       <c r="C76" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D76" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D76" s="21" t="str">
+        <v>Design</v>
       </c>
       <c r="E76" s="6" t="str">
         <v/>
       </c>
       <c r="F76" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V5(15.6)</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3534,19 +3534,19 @@
         <v/>
       </c>
       <c r="B77" s="4" t="str">
-        <v>Portfolio - Crypto redeem</v>
+        <v>Custodial wallet crypto - Send (with travel rule) CASP/Self Hosted</v>
       </c>
       <c r="C77" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D77" s="20" t="str">
-        <v>Grooming</v>
+      <c r="D77" s="14" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E77" s="6" t="str">
         <v/>
       </c>
       <c r="F77" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V5(15.6)</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3558,145 +3558,145 @@
         <v>46160</v>
       </c>
       <c r="J77" s="7">
-        <v>46142</v>
+        <v>46106</v>
       </c>
       <c r="K77" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="str">
+    <row r="78" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" t="str">
+        <v/>
+      </c>
+      <c r="B78" s="4" t="str">
+        <v>Portfolio - Crypto redeem</v>
+      </c>
+      <c r="C78" s="6" t="str">
+        <v>Nikolaus Kulier</v>
+      </c>
+      <c r="D78" s="21" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E78" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F78" s="6" t="str">
+        <v>V3(18.5)</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" s="8">
+        <v>46146</v>
+      </c>
+      <c r="I78" s="8">
+        <v>46160</v>
+      </c>
+      <c r="J78" s="7">
+        <v>46142</v>
+      </c>
+      <c r="K78" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="str">
         <v>IBAN - Send Payment- Withdraw from IBAN</v>
       </c>
-      <c r="B78" t="str">
-        <v/>
-      </c>
-      <c r="C78" s="5" t="str">
+      <c r="B79" t="str">
+        <v/>
+      </c>
+      <c r="C79" s="5" t="str">
         <v>FE DEV WIP</v>
       </c>
-      <c r="D78" s="6" t="str">
+      <c r="D79" s="6" t="str">
         <v>sendPayment</v>
       </c>
-      <c r="E78" t="str">
-        <v/>
-      </c>
-      <c r="F78" s="8">
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" s="8">
         <v>46117</v>
       </c>
-      <c r="G78" s="8">
+      <c r="G79" s="8">
         <v>46132</v>
       </c>
-      <c r="H78" s="6" t="str">
+      <c r="H79" s="6" t="str">
         <v>V3(18.5)</v>
       </c>
-      <c r="I78" s="6" t="str">
+      <c r="I79" s="6" t="str">
         <v>Send Payment - GBP / EUR / AUD / DKK Payment Schemes</v>
       </c>
-      <c r="J78" s="6" t="str">
+      <c r="J79" s="6" t="str">
         <v>Adi</v>
       </c>
-      <c r="K78" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L78" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M78" s="6">
+      <c r="K79" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L79" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M79" s="6">
         <v>2</v>
       </c>
-      <c r="N78" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O78" s="6" t="str">
+      <c r="N79" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O79" s="6" t="str">
         <v>https://drive.google.com/drive/u/0/folders/1cqLfzkkJdYpR8bVF73xOU89anuVCub81</v>
       </c>
-      <c r="P78" s="6" t="str">
+      <c r="P79" s="6" t="str">
         <v>Banking, Deposit</v>
       </c>
-      <c r="Q78" s="7">
+      <c r="Q79" s="7">
         <v>46086</v>
       </c>
-      <c r="R78" s="6" t="str">
+      <c r="R79" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
-      <c r="S78" t="str">
-        <v/>
-      </c>
-      <c r="T78" t="str">
-        <v/>
-      </c>
-      <c r="U78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="str">
+      <c r="S79" t="str">
+        <v/>
+      </c>
+      <c r="T79" t="str">
+        <v/>
+      </c>
+      <c r="U79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B79" s="10" t="str">
+      <c r="B80" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C79" s="10" t="str">
+      <c r="C80" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D79" s="10" t="str">
+      <c r="D80" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E79" s="10" t="str">
+      <c r="E80" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F79" s="10" t="str">
+      <c r="F80" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G79" s="10" t="str">
+      <c r="G80" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H79" s="10" t="str">
+      <c r="H80" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I79" s="10" t="str">
+      <c r="I80" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J79" s="10" t="str">
+      <c r="J80" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K79" s="10" t="str">
+      <c r="K80" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" t="str">
-        <v/>
-      </c>
-      <c r="B80" s="4" t="str">
-        <v>Payee List and empty state</v>
-      </c>
-      <c r="C80" s="6" t="str">
-        <v>Joanna Fajga</v>
-      </c>
-      <c r="D80" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="E80" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-207</v>
-      </c>
-      <c r="F80" t="str">
-        <v/>
-      </c>
-      <c r="G80" t="str">
-        <v/>
-      </c>
-      <c r="H80" t="str">
-        <v/>
-      </c>
-      <c r="I80" t="str">
-        <v/>
-      </c>
-      <c r="J80" t="str">
-        <v/>
-      </c>
-      <c r="K80" t="str">
-        <v/>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3704,7 +3704,7 @@
         <v/>
       </c>
       <c r="B81" s="4" t="str">
-        <v>Payee Details View/Delete</v>
+        <v>Payee List and empty state</v>
       </c>
       <c r="C81" s="6" t="str">
         <v>Joanna Fajga</v>
@@ -3713,7 +3713,7 @@
         <v>Done</v>
       </c>
       <c r="E81" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-209</v>
+        <v>https://etoro-jira.atlassian.net/browse/PM-207</v>
       </c>
       <c r="F81" t="str">
         <v/>
@@ -3739,7 +3739,7 @@
         <v/>
       </c>
       <c r="B82" s="4" t="str">
-        <v>Amend / Create a Payee</v>
+        <v>Payee Details View/Delete</v>
       </c>
       <c r="C82" s="6" t="str">
         <v>Joanna Fajga</v>
@@ -3748,7 +3748,7 @@
         <v>Done</v>
       </c>
       <c r="E82" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-214</v>
+        <v>https://etoro-jira.atlassian.net/browse/PM-209</v>
       </c>
       <c r="F82" t="str">
         <v/>
@@ -3756,11 +3756,11 @@
       <c r="G82" t="str">
         <v/>
       </c>
-      <c r="H82" s="8">
-        <v>46117</v>
-      </c>
-      <c r="I82" s="8">
-        <v>46132</v>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
       </c>
       <c r="J82" t="str">
         <v/>
@@ -3774,7 +3774,7 @@
         <v/>
       </c>
       <c r="B83" s="4" t="str">
-        <v>Verification of Payees - Error state / Mismatch</v>
+        <v>Amend / Create a Payee</v>
       </c>
       <c r="C83" s="6" t="str">
         <v>Joanna Fajga</v>
@@ -3783,7 +3783,7 @@
         <v>Done</v>
       </c>
       <c r="E83" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-215</v>
+        <v>https://etoro-jira.atlassian.net/browse/PM-214</v>
       </c>
       <c r="F83" t="str">
         <v/>
@@ -3800,8 +3800,8 @@
       <c r="J83" t="str">
         <v/>
       </c>
-      <c r="K83" s="6">
-        <v>1</v>
+      <c r="K83" t="str">
+        <v/>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3809,16 +3809,16 @@
         <v/>
       </c>
       <c r="B84" s="4" t="str">
-        <v>IBAN Restricted State</v>
+        <v>Verification of Payees - Error state / Mismatch</v>
       </c>
       <c r="C84" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D84" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D84" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E84" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-226</v>
+        <v>https://etoro-jira.atlassian.net/browse/PM-215</v>
       </c>
       <c r="F84" t="str">
         <v/>
@@ -3826,17 +3826,17 @@
       <c r="G84" t="str">
         <v/>
       </c>
-      <c r="H84" t="str">
-        <v/>
-      </c>
-      <c r="I84" t="str">
-        <v/>
+      <c r="H84" s="8">
+        <v>46117</v>
+      </c>
+      <c r="I84" s="8">
+        <v>46132</v>
       </c>
       <c r="J84" t="str">
         <v/>
       </c>
-      <c r="K84" t="str">
-        <v/>
+      <c r="K84" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3844,16 +3844,16 @@
         <v/>
       </c>
       <c r="B85" s="4" t="str">
-        <v>Send Payment - GBP / EUR / AUD / DKK Payment Schemes</v>
+        <v>IBAN Restricted State</v>
       </c>
       <c r="C85" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D85" s="11" t="str">
-        <v>Done</v>
+      <c r="D85" s="13" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E85" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-211</v>
+        <v>https://etoro-jira.atlassian.net/browse/PM-226</v>
       </c>
       <c r="F85" t="str">
         <v/>
@@ -3870,8 +3870,8 @@
       <c r="J85" t="str">
         <v/>
       </c>
-      <c r="K85" s="6">
-        <v>1</v>
+      <c r="K85" t="str">
+        <v/>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3879,16 +3879,16 @@
         <v/>
       </c>
       <c r="B86" s="4" t="str">
-        <v>Send Payment - Error Handling / Mapping</v>
+        <v>Send Payment - GBP / EUR / AUD / DKK Payment Schemes</v>
       </c>
       <c r="C86" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D86" s="20" t="str">
-        <v>Grooming</v>
+      <c r="D86" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E86" s="6" t="str">
-        <v/>
+        <v>https://etoro-jira.atlassian.net/browse/PM-211</v>
       </c>
       <c r="F86" t="str">
         <v/>
@@ -3914,13 +3914,13 @@
         <v/>
       </c>
       <c r="B87" s="4" t="str">
-        <v>Send Payment - Hold &amp; Release</v>
-      </c>
-      <c r="C87" t="str">
-        <v/>
-      </c>
-      <c r="D87" s="21" t="str">
-        <v>OnHold</v>
+        <v>Send Payment - Error Handling / Mapping</v>
+      </c>
+      <c r="C87" s="6" t="str">
+        <v>Joanna Fajga</v>
+      </c>
+      <c r="D87" s="20" t="str">
+        <v>Grooming</v>
       </c>
       <c r="E87" s="6" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v/>
       </c>
       <c r="K87" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3949,13 +3949,13 @@
         <v/>
       </c>
       <c r="B88" s="4" t="str">
-        <v>QA - E2E</v>
+        <v>Send Payment - Hold &amp; Release</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
-      <c r="D88" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D88" s="22" t="str">
+        <v>OnHold</v>
       </c>
       <c r="E88" s="6" t="str">
         <v/>
@@ -3975,8 +3975,8 @@
       <c r="J88" t="str">
         <v/>
       </c>
-      <c r="K88" t="str">
-        <v/>
+      <c r="K88" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3984,13 +3984,13 @@
         <v/>
       </c>
       <c r="B89" s="4" t="str">
-        <v>IBAN- Send Payment- BFF for WD from IBAN- Ron/Amichay Kafka</v>
+        <v>QA - E2E</v>
       </c>
       <c r="C89" t="str">
         <v/>
       </c>
-      <c r="D89" s="22" t="str">
-        <v>futureVersion</v>
+      <c r="D89" s="18" t="str">
+        <v>Not Started</v>
       </c>
       <c r="E89" s="6" t="str">
         <v/>
@@ -4010,8 +4010,8 @@
       <c r="J89" t="str">
         <v/>
       </c>
-      <c r="K89" s="6">
-        <v>1</v>
+      <c r="K89" t="str">
+        <v/>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -4019,13 +4019,13 @@
         <v/>
       </c>
       <c r="B90" s="4" t="str">
-        <v>Send Payment - Confirmation of Payee UK-</v>
+        <v>IBAN- Send Payment- BFF for WD from IBAN- Ron/Amichay Kafka</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
-      <c r="D90" s="17" t="str">
-        <v>Cancelled</v>
+      <c r="D90" s="19" t="str">
+        <v>futureVersion</v>
       </c>
       <c r="E90" s="6" t="str">
         <v/>
@@ -4046,7 +4046,7 @@
         <v/>
       </c>
       <c r="K90" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -4054,7 +4054,7 @@
         <v/>
       </c>
       <c r="B91" s="4" t="str">
-        <v>Send Payment - Verification of Payee EU</v>
+        <v>Send Payment - Confirmation of Payee UK-</v>
       </c>
       <c r="C91" t="str">
         <v/>
@@ -4089,7 +4089,7 @@
         <v/>
       </c>
       <c r="B92" s="4" t="str">
-        <v>Send Payment - Confirmation of Payee AU</v>
+        <v>Send Payment - Verification of Payee EU</v>
       </c>
       <c r="C92" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
         <v/>
       </c>
       <c r="B93" s="4" t="str">
-        <v>Send Payment- 2FA</v>
+        <v>Send Payment - Confirmation of Payee AU</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
-      <c r="D93" s="14" t="str">
-        <v>Handle by other team</v>
+      <c r="D93" s="17" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="E93" s="6" t="str">
         <v/>
@@ -4154,139 +4154,139 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="str">
+    <row r="94" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="str">
+        <v/>
+      </c>
+      <c r="B94" s="4" t="str">
+        <v>Send Payment- 2FA</v>
+      </c>
+      <c r="C94" t="str">
+        <v/>
+      </c>
+      <c r="D94" s="15" t="str">
+        <v>Handle by other team</v>
+      </c>
+      <c r="E94" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="str">
         <v>Withdraw USD</v>
       </c>
-      <c r="B94" t="str">
-        <v/>
-      </c>
-      <c r="C94" s="5" t="str">
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" s="5" t="str">
         <v>FE DEV WIP</v>
       </c>
-      <c r="D94" s="6" t="str">
+      <c r="D95" s="6" t="str">
         <v>withdrawWizard</v>
       </c>
-      <c r="E94" t="str">
-        <v/>
-      </c>
-      <c r="F94" s="8">
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" s="8">
         <v>46070</v>
       </c>
-      <c r="G94" s="8">
+      <c r="G95" s="8">
         <v>46134</v>
       </c>
-      <c r="H94" s="6" t="str">
+      <c r="H95" s="6" t="str">
         <v>V3(18.5)</v>
       </c>
-      <c r="I94" s="6" t="str">
+      <c r="I95" s="6" t="str">
         <v>BFF</v>
       </c>
-      <c r="J94" s="6" t="str">
+      <c r="J95" s="6" t="str">
         <v>Shimi</v>
       </c>
-      <c r="K94" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L94" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M94" s="6">
+      <c r="K95" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L95" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M95" s="6">
         <v>2</v>
       </c>
-      <c r="N94" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O94" s="6" t="str">
+      <c r="N95" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O95" s="6" t="str">
         <v>https://drive.google.com/drive/u/0/folders/13rvXTFCTXPLR9rSBFXqDGB5Jldv5kH6m</v>
       </c>
-      <c r="P94" s="6" t="str">
+      <c r="P95" s="6" t="str">
         <v>Withdraw</v>
       </c>
-      <c r="Q94" s="7">
+      <c r="Q95" s="7">
         <v>46098</v>
       </c>
-      <c r="R94" s="6" t="str">
+      <c r="R95" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
-      <c r="S94" t="str">
-        <v/>
-      </c>
-      <c r="T94" s="8">
+      <c r="S95" t="str">
+        <v/>
+      </c>
+      <c r="T95" s="8">
         <v>46089</v>
       </c>
-      <c r="U94" s="8">
+      <c r="U95" s="8">
         <v>46089</v>
       </c>
     </row>
-    <row r="95" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="9" t="str">
+    <row r="96" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B95" s="10" t="str">
+      <c r="B96" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C95" s="10" t="str">
+      <c r="C96" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D95" s="10" t="str">
+      <c r="D96" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E95" s="10" t="str">
+      <c r="E96" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F95" s="10" t="str">
+      <c r="F96" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G95" s="10" t="str">
+      <c r="G96" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H95" s="10" t="str">
+      <c r="H96" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I95" s="10" t="str">
+      <c r="I96" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J95" s="10" t="str">
+      <c r="J96" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K95" s="10" t="str">
+      <c r="K96" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" t="str">
-        <v/>
-      </c>
-      <c r="B96" s="4" t="str">
-        <v>BFF for WD to USD- Merab</v>
-      </c>
-      <c r="C96" t="str">
-        <v/>
-      </c>
-      <c r="D96" s="13" t="str">
-        <v>Discovery</v>
-      </c>
-      <c r="E96" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
-        <v/>
-      </c>
-      <c r="G96" t="str">
-        <v/>
-      </c>
-      <c r="H96" t="str">
-        <v/>
-      </c>
-      <c r="I96" t="str">
-        <v/>
-      </c>
-      <c r="J96" t="str">
-        <v/>
-      </c>
-      <c r="K96" t="str">
-        <v/>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -4294,13 +4294,13 @@
         <v/>
       </c>
       <c r="B97" s="4" t="str">
-        <v>Product requirements readiness- Shimi</v>
+        <v>BFF for WD to USD- Merab</v>
       </c>
       <c r="C97" t="str">
         <v/>
       </c>
-      <c r="D97" s="20" t="str">
-        <v>Grooming</v>
+      <c r="D97" s="13" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E97" s="6" t="str">
         <v/>
@@ -4311,11 +4311,11 @@
       <c r="G97" t="str">
         <v/>
       </c>
-      <c r="H97" s="8">
-        <v>46071</v>
-      </c>
-      <c r="I97" s="8">
-        <v>46089</v>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v/>
       </c>
       <c r="J97" t="str">
         <v/>
@@ -4329,169 +4329,169 @@
         <v/>
       </c>
       <c r="B98" s="4" t="str">
+        <v>Product requirements readiness- Shimi</v>
+      </c>
+      <c r="C98" t="str">
+        <v/>
+      </c>
+      <c r="D98" s="20" t="str">
+        <v>Grooming</v>
+      </c>
+      <c r="E98" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" s="8">
+        <v>46071</v>
+      </c>
+      <c r="I98" s="8">
+        <v>46089</v>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="str">
+        <v/>
+      </c>
+      <c r="B99" s="4" t="str">
         <v>Withdraw Blocked- Generic solution for Dep/WD</v>
       </c>
-      <c r="C98" t="str">
-        <v/>
-      </c>
-      <c r="D98" s="18" t="str">
+      <c r="C99" t="str">
+        <v/>
+      </c>
+      <c r="D99" s="18" t="str">
         <v>Not Started</v>
       </c>
-      <c r="E98" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F98" t="str">
-        <v/>
-      </c>
-      <c r="G98" t="str">
-        <v/>
-      </c>
-      <c r="H98" t="str">
-        <v/>
-      </c>
-      <c r="I98" t="str">
-        <v/>
-      </c>
-      <c r="J98" t="str">
-        <v/>
-      </c>
-      <c r="K98" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="str">
+      <c r="E99" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="str">
         <v>Card Management (Manage Card IBAN)</v>
       </c>
-      <c r="B99" t="str">
-        <v/>
-      </c>
-      <c r="C99" s="23" t="str">
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" s="23" t="str">
         <v>Groomed</v>
       </c>
-      <c r="D99" s="6" t="str">
+      <c r="D100" s="6" t="str">
         <v>iBanManageCard</v>
       </c>
-      <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" s="8">
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" s="8">
         <v>46061</v>
       </c>
-      <c r="G99" s="8">
+      <c r="G100" s="8">
         <v>46075</v>
       </c>
-      <c r="H99" s="6" t="str">
+      <c r="H100" s="6" t="str">
         <v>V2(4.5)</v>
       </c>
-      <c r="I99" s="6" t="str">
+      <c r="I100" s="6" t="str">
         <v>Freeze Card and Card Status mgmt still requires Design</v>
       </c>
-      <c r="J99" s="6" t="str">
+      <c r="J100" s="6" t="str">
         <v>Richard</v>
       </c>
-      <c r="K99" s="6" t="str">
+      <c r="K100" s="6" t="str">
         <v>Inbal Escholi</v>
       </c>
-      <c r="L99" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M99" s="6">
+      <c r="L100" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M100" s="6">
         <v>3</v>
       </c>
-      <c r="N99" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O99" s="6" t="str">
+      <c r="N100" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O100" s="6" t="str">
         <v>https://drive.google.com/drive/u/0/folders/1mLvTPp1jkHGRDPftaLG6VX3L6-KSChBM</v>
       </c>
-      <c r="P99" s="6" t="str">
+      <c r="P100" s="6" t="str">
         <v>Banking, Card Mng.</v>
       </c>
-      <c r="Q99" s="7">
+      <c r="Q100" s="7">
         <v>46090</v>
       </c>
-      <c r="R99" s="6" t="str">
+      <c r="R100" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
-      <c r="S99" t="str">
-        <v/>
-      </c>
-      <c r="T99" s="8">
+      <c r="S100" t="str">
+        <v/>
+      </c>
+      <c r="T100" s="8">
         <v>46090</v>
       </c>
-      <c r="U99" s="8">
+      <c r="U100" s="8">
         <v>46090</v>
       </c>
     </row>
-    <row r="100" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="9" t="str">
+    <row r="101" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B100" s="10" t="str">
+      <c r="B101" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C100" s="10" t="str">
+      <c r="C101" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D100" s="10" t="str">
+      <c r="D101" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E100" s="10" t="str">
+      <c r="E101" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F100" s="10" t="str">
+      <c r="F101" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G100" s="10" t="str">
+      <c r="G101" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H100" s="10" t="str">
+      <c r="H101" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I100" s="10" t="str">
+      <c r="I101" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J100" s="10" t="str">
+      <c r="J101" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K100" s="10" t="str">
+      <c r="K101" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" t="str">
-        <v/>
-      </c>
-      <c r="B101" s="4" t="str">
-        <v>Manage Card - Home/Main screen</v>
-      </c>
-      <c r="C101" s="6" t="str">
-        <v>Richard Whitehouse, Inbal Escholi</v>
-      </c>
-      <c r="D101" s="5" t="str">
-        <v>Dev - WIP</v>
-      </c>
-      <c r="E101" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
-        <v/>
-      </c>
-      <c r="G101" t="str">
-        <v/>
-      </c>
-      <c r="H101" s="8">
-        <v>46118</v>
-      </c>
-      <c r="I101" s="8">
-        <v>46127</v>
-      </c>
-      <c r="J101" t="str">
-        <v/>
-      </c>
-      <c r="K101" t="str">
-        <v/>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -4499,28 +4499,28 @@
         <v/>
       </c>
       <c r="B102" s="4" t="str">
-        <v>Manage Card - Card Status Management</v>
+        <v>Manage Card - Home/Main screen</v>
       </c>
       <c r="C102" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D102" s="16" t="str">
-        <v>Groomed</v>
+      <c r="D102" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E102" s="6" t="str">
         <v/>
       </c>
-      <c r="F102" s="6" t="str">
+      <c r="F102" t="str">
         <v/>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
-      <c r="H102" t="str">
-        <v/>
-      </c>
-      <c r="I102" t="str">
-        <v/>
+      <c r="H102" s="8">
+        <v>46118</v>
+      </c>
+      <c r="I102" s="8">
+        <v>46127</v>
       </c>
       <c r="J102" t="str">
         <v/>
@@ -4534,18 +4534,18 @@
         <v/>
       </c>
       <c r="B103" s="4" t="str">
-        <v>Manage Card - Activate Card</v>
+        <v>Manage Card - Card Status Management</v>
       </c>
       <c r="C103" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D103" s="16" t="str">
+      <c r="D103" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E103" s="6" t="str">
         <v/>
       </c>
-      <c r="F103" t="str">
+      <c r="F103" s="6" t="str">
         <v/>
       </c>
       <c r="G103" t="str">
@@ -4569,12 +4569,12 @@
         <v/>
       </c>
       <c r="B104" s="4" t="str">
-        <v>Manage Card - View Card Details</v>
+        <v>Manage Card - Activate Card</v>
       </c>
       <c r="C104" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D104" s="16" t="str">
+      <c r="D104" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E104" s="6" t="str">
@@ -4604,12 +4604,12 @@
         <v/>
       </c>
       <c r="B105" s="4" t="str">
-        <v>Manage Card - PIN Reminder</v>
+        <v>Manage Card - View Card Details</v>
       </c>
       <c r="C105" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D105" s="16" t="str">
+      <c r="D105" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E105" s="6" t="str">
@@ -4639,13 +4639,13 @@
         <v/>
       </c>
       <c r="B106" s="4" t="str">
-        <v>Manage Card - Freeze Card</v>
+        <v>Manage Card - PIN Reminder</v>
       </c>
       <c r="C106" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D106" s="20" t="str">
-        <v>Grooming</v>
+      <c r="D106" s="14" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E106" s="6" t="str">
         <v/>
@@ -4674,7 +4674,7 @@
         <v/>
       </c>
       <c r="B107" s="4" t="str">
-        <v>Manage Card - Mark Lost / Stolen</v>
+        <v>Manage Card - Freeze Card</v>
       </c>
       <c r="C107" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
@@ -4709,7 +4709,7 @@
         <v/>
       </c>
       <c r="B108" s="4" t="str">
-        <v>Manage Card - Reissue Flow</v>
+        <v>Manage Card - Mark Lost / Stolen</v>
       </c>
       <c r="C108" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
@@ -4744,7 +4744,7 @@
         <v/>
       </c>
       <c r="B109" s="4" t="str">
-        <v>Manage Card - Expiry Flow</v>
+        <v>Manage Card - Reissue Flow</v>
       </c>
       <c r="C109" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
@@ -4779,13 +4779,13 @@
         <v/>
       </c>
       <c r="B110" s="4" t="str">
-        <v>Manage Card - Club Upgrades for Card Program</v>
+        <v>Manage Card - Expiry Flow</v>
       </c>
       <c r="C110" s="6" t="str">
-        <v>Richard Whitehouse</v>
-      </c>
-      <c r="D110" s="13" t="str">
-        <v>Discovery</v>
+        <v>Richard Whitehouse, Inbal Escholi</v>
+      </c>
+      <c r="D110" s="20" t="str">
+        <v>Grooming</v>
       </c>
       <c r="E110" s="6" t="str">
         <v/>
@@ -4814,13 +4814,13 @@
         <v/>
       </c>
       <c r="B111" s="4" t="str">
-        <v>Manage Card - Apple Wallet touchpoint- The button to trigger the addition</v>
+        <v>Manage Card - Club Upgrades for Card Program</v>
       </c>
       <c r="C111" s="6" t="str">
-        <v>Richard Whitehouse, Inbal Escholi</v>
-      </c>
-      <c r="D111" s="20" t="str">
-        <v>Grooming</v>
+        <v>Richard Whitehouse</v>
+      </c>
+      <c r="D111" s="13" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E111" s="6" t="str">
         <v/>
@@ -4849,50 +4849,50 @@
         <v/>
       </c>
       <c r="B112" s="4" t="str">
-        <v>Manage Card - Google Wallet Manual Provision</v>
+        <v>Manage Card - Apple Wallet touchpoint- The button to trigger the addition</v>
       </c>
       <c r="C112" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D112" s="17" t="str">
+      <c r="D112" s="20" t="str">
+        <v>Grooming</v>
+      </c>
+      <c r="E112" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" t="str">
+        <v/>
+      </c>
+      <c r="B113" s="4" t="str">
+        <v>Manage Card - Google Wallet Manual Provision</v>
+      </c>
+      <c r="C113" s="6" t="str">
+        <v>Richard Whitehouse, Inbal Escholi</v>
+      </c>
+      <c r="D113" s="17" t="str">
         <v>Cancelled</v>
       </c>
-      <c r="E112" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F112" t="str">
-        <v/>
-      </c>
-      <c r="G112" t="str">
-        <v/>
-      </c>
-      <c r="H112" t="str">
-        <v/>
-      </c>
-      <c r="I112" t="str">
-        <v/>
-      </c>
-      <c r="J112" t="str">
-        <v/>
-      </c>
-      <c r="K112" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="str">
-        <v>Card Management 3DS Flow</v>
-      </c>
-      <c r="B113" t="str">
-        <v/>
-      </c>
-      <c r="C113" s="24" t="str">
-        <v>Dependency</v>
-      </c>
-      <c r="D113" t="str">
-        <v/>
-      </c>
-      <c r="E113" t="str">
+      <c r="E113" s="6" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
@@ -4901,58 +4901,28 @@
       <c r="G113" t="str">
         <v/>
       </c>
-      <c r="H113" s="6" t="str">
-        <v>V3(18.5)</v>
+      <c r="H113" t="str">
+        <v/>
       </c>
       <c r="I113" t="str">
         <v/>
       </c>
-      <c r="J113" s="6" t="str">
-        <v>Richard</v>
-      </c>
-      <c r="K113" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L113" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M113" s="6">
-        <v>3</v>
-      </c>
-      <c r="N113" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O113" t="str">
-        <v/>
-      </c>
-      <c r="P113" t="str">
-        <v/>
-      </c>
-      <c r="Q113" s="7">
-        <v>46127</v>
-      </c>
-      <c r="R113" s="6" t="str">
-        <v>Richard Whitehouse Mar 4, 2026 2:30 PM</v>
-      </c>
-      <c r="S113" t="str">
-        <v/>
-      </c>
-      <c r="T113" s="8">
-        <v>46114</v>
-      </c>
-      <c r="U113" s="8">
-        <v>46114</v>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v/>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="str">
-        <v>Card Management - Add To Apple Wallet- SDK</v>
+        <v>Card Management 3DS Flow</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
-      <c r="C114" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C114" s="24" t="str">
+        <v>Dependency</v>
       </c>
       <c r="D114" t="str">
         <v/>
@@ -4969,8 +4939,8 @@
       <c r="H114" s="6" t="str">
         <v>V3(18.5)</v>
       </c>
-      <c r="I114" s="6" t="str">
-        <v>Awaiting some feedback from Apple</v>
+      <c r="I114" t="str">
+        <v/>
       </c>
       <c r="J114" s="6" t="str">
         <v>Richard</v>
@@ -4982,7 +4952,7 @@
         <v/>
       </c>
       <c r="M114" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N114" s="6" t="str">
         <v/>
@@ -4997,86 +4967,116 @@
         <v>46127</v>
       </c>
       <c r="R114" s="6" t="str">
+        <v>Richard Whitehouse Mar 4, 2026 2:30 PM</v>
+      </c>
+      <c r="S114" t="str">
+        <v/>
+      </c>
+      <c r="T114" s="8">
+        <v>46114</v>
+      </c>
+      <c r="U114" s="8">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="str">
+        <v>Card Management - Add To Apple Wallet- SDK</v>
+      </c>
+      <c r="B115" t="str">
+        <v/>
+      </c>
+      <c r="C115" s="5" t="str">
+        <v>FE DEV WIP</v>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" s="6" t="str">
+        <v>V3(18.5)</v>
+      </c>
+      <c r="I115" s="6" t="str">
+        <v>Awaiting some feedback from Apple</v>
+      </c>
+      <c r="J115" s="6" t="str">
+        <v>Richard</v>
+      </c>
+      <c r="K115" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L115" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M115" s="6">
+        <v>2</v>
+      </c>
+      <c r="N115" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115" s="7">
+        <v>46127</v>
+      </c>
+      <c r="R115" s="6" t="str">
         <v>Richard Whitehouse Mar 4, 2026 2:31 PM</v>
       </c>
-      <c r="S114" t="str">
-        <v/>
-      </c>
-      <c r="T114" s="8">
+      <c r="S115" t="str">
+        <v/>
+      </c>
+      <c r="T115" s="8">
         <v>46093</v>
       </c>
-      <c r="U114" s="8">
+      <c r="U115" s="8">
         <v>46093</v>
       </c>
     </row>
-    <row r="115" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="9" t="str">
+    <row r="116" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B115" s="10" t="str">
+      <c r="B116" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C115" s="10" t="str">
+      <c r="C116" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D115" s="10" t="str">
+      <c r="D116" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E115" s="10" t="str">
+      <c r="E116" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F115" s="10" t="str">
+      <c r="F116" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G115" s="10" t="str">
+      <c r="G116" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H115" s="10" t="str">
+      <c r="H116" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I115" s="10" t="str">
+      <c r="I116" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J115" s="10" t="str">
+      <c r="J116" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K115" s="10" t="str">
+      <c r="K116" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" t="str">
-        <v/>
-      </c>
-      <c r="B116" s="4" t="str">
-        <v>SDK Implimentation</v>
-      </c>
-      <c r="C116" t="str">
-        <v/>
-      </c>
-      <c r="D116" s="18" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="E116" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F116" t="str">
-        <v/>
-      </c>
-      <c r="G116" t="str">
-        <v/>
-      </c>
-      <c r="H116" t="str">
-        <v/>
-      </c>
-      <c r="I116" t="str">
-        <v/>
-      </c>
-      <c r="J116" t="str">
-        <v/>
-      </c>
-      <c r="K116" t="str">
-        <v/>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5084,7 +5084,7 @@
         <v/>
       </c>
       <c r="B117" s="4" t="str">
-        <v>Apple Pay Status -  State Management ABCDE</v>
+        <v>SDK Implimentation</v>
       </c>
       <c r="C117" t="str">
         <v/>
@@ -5114,20 +5114,20 @@
         <v/>
       </c>
     </row>
-    <row r="118" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="str">
-        <v>Wallet tab - total value graph- Total Value Rolloup- Desktop</v>
-      </c>
-      <c r="B118" t="str">
-        <v/>
-      </c>
-      <c r="C118" s="18" t="str">
+    <row r="118" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" t="str">
+        <v/>
+      </c>
+      <c r="B118" s="4" t="str">
+        <v>Apple Pay Status -  State Management ABCDE</v>
+      </c>
+      <c r="C118" t="str">
+        <v/>
+      </c>
+      <c r="D118" s="18" t="str">
         <v>Not Started</v>
       </c>
-      <c r="D118" s="6" t="str">
-        <v>WalletTabTotalValueGraph</v>
-      </c>
-      <c r="E118" t="str">
+      <c r="E118" s="6" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
@@ -5136,61 +5136,31 @@
       <c r="G118" t="str">
         <v/>
       </c>
-      <c r="H118" s="6" t="str">
-        <v>V4(1.6)</v>
-      </c>
-      <c r="I118" s="6" t="str">
-        <v>OOS - Wallet Tab - Balance Display - Total Value Rollup-</v>
-      </c>
-      <c r="J118" s="6" t="str">
-        <v>Adi</v>
-      </c>
-      <c r="K118" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L118" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M118" s="6">
-        <v>3</v>
-      </c>
-      <c r="N118" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O118" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1FWMl54Cw95y4XBFRvgY-5TTl0MXk8IbT</v>
-      </c>
-      <c r="P118" s="6" t="str">
-        <v>Balance</v>
-      </c>
-      <c r="Q118" s="7">
-        <v>46127</v>
-      </c>
-      <c r="R118" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S118" t="str">
-        <v/>
-      </c>
-      <c r="T118" t="str">
-        <v/>
-      </c>
-      <c r="U118" t="str">
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
         <v/>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="str">
-        <v>Settings</v>
+        <v>Wallet tab - total value graph- Total Value Rolloup- Desktop</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
-      <c r="C119" s="22" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D119" t="str">
-        <v/>
+      <c r="C119" s="18" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="D119" s="6" t="str">
+        <v>WalletTabTotalValueGraph</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -5202,13 +5172,13 @@
         <v/>
       </c>
       <c r="H119" s="6" t="str">
-        <v>V3(18.5)</v>
-      </c>
-      <c r="I119" t="str">
-        <v/>
+        <v>V4(1.6)</v>
+      </c>
+      <c r="I119" s="6" t="str">
+        <v>OOS - Wallet Tab - Balance Display - Total Value Rollup-</v>
       </c>
       <c r="J119" s="6" t="str">
-        <v>Noit</v>
+        <v>Adi</v>
       </c>
       <c r="K119" s="6" t="str">
         <v/>
@@ -5222,96 +5192,126 @@
       <c r="N119" s="6" t="str">
         <v/>
       </c>
-      <c r="O119" t="str">
-        <v/>
+      <c r="O119" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1FWMl54Cw95y4XBFRvgY-5TTl0MXk8IbT</v>
       </c>
       <c r="P119" s="6" t="str">
-        <v>Payments, Settings</v>
+        <v>Balance</v>
       </c>
       <c r="Q119" s="7">
         <v>46127</v>
       </c>
       <c r="R119" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S119" t="str">
+        <v/>
+      </c>
+      <c r="T119" t="str">
+        <v/>
+      </c>
+      <c r="U119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="B120" t="str">
+        <v/>
+      </c>
+      <c r="C120" s="19" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" s="6" t="str">
+        <v>V3(18.5)</v>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" s="6" t="str">
+        <v>Noit</v>
+      </c>
+      <c r="K120" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L120" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M120" s="6">
+        <v>3</v>
+      </c>
+      <c r="N120" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" s="6" t="str">
+        <v>Payments, Settings</v>
+      </c>
+      <c r="Q120" s="7">
+        <v>46127</v>
+      </c>
+      <c r="R120" s="6" t="str">
         <v>Hagit Zamir Feb 5, 2026 4:10 PM</v>
       </c>
-      <c r="S119" t="str">
-        <v/>
-      </c>
-      <c r="T119" t="str">
-        <v/>
-      </c>
-      <c r="U119" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="9" t="str">
+      <c r="S120" t="str">
+        <v/>
+      </c>
+      <c r="T120" t="str">
+        <v/>
+      </c>
+      <c r="U120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B120" s="10" t="str">
+      <c r="B121" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C120" s="10" t="str">
+      <c r="C121" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D120" s="10" t="str">
+      <c r="D121" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E120" s="10" t="str">
+      <c r="E121" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F120" s="10" t="str">
+      <c r="F121" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G120" s="10" t="str">
+      <c r="G121" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H120" s="10" t="str">
+      <c r="H121" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I120" s="10" t="str">
+      <c r="I121" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J120" s="10" t="str">
+      <c r="J121" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K120" s="10" t="str">
+      <c r="K121" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" t="str">
-        <v/>
-      </c>
-      <c r="B121" s="4" t="str">
-        <v>Settings: Default currency for LC</v>
-      </c>
-      <c r="C121" t="str">
-        <v/>
-      </c>
-      <c r="D121" s="14" t="str">
-        <v>Handle by other team</v>
-      </c>
-      <c r="E121" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F121" t="str">
-        <v/>
-      </c>
-      <c r="G121" t="str">
-        <v/>
-      </c>
-      <c r="H121" t="str">
-        <v/>
-      </c>
-      <c r="I121" t="str">
-        <v/>
-      </c>
-      <c r="J121" t="str">
-        <v/>
-      </c>
-      <c r="K121" t="str">
-        <v/>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5319,12 +5319,12 @@
         <v/>
       </c>
       <c r="B122" s="4" t="str">
-        <v>Settings: Recurring Order, recurring deposit will be supported via link to web</v>
+        <v>Settings: Default currency for LC</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
-      <c r="D122" s="14" t="str">
+      <c r="D122" s="15" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E122" s="6" t="str">
@@ -5333,8 +5333,8 @@
       <c r="F122" t="str">
         <v/>
       </c>
-      <c r="G122" s="6" t="str">
-        <v>Payments</v>
+      <c r="G122" t="str">
+        <v/>
       </c>
       <c r="H122" t="str">
         <v/>
@@ -5354,50 +5354,50 @@
         <v/>
       </c>
       <c r="B123" s="4" t="str">
+        <v>Settings: Recurring Order, recurring deposit will be supported via link to web</v>
+      </c>
+      <c r="C123" t="str">
+        <v/>
+      </c>
+      <c r="D123" s="15" t="str">
+        <v>Handle by other team</v>
+      </c>
+      <c r="E123" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" s="6" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" t="str">
+        <v/>
+      </c>
+      <c r="B124" s="4" t="str">
         <v>Settings: Recurring Deposit flow - plan creation</v>
       </c>
-      <c r="C123" t="str">
-        <v/>
-      </c>
-      <c r="D123" s="17" t="str">
+      <c r="C124" t="str">
+        <v/>
+      </c>
+      <c r="D124" s="17" t="str">
         <v>Cancelled</v>
       </c>
-      <c r="E123" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F123" t="str">
-        <v/>
-      </c>
-      <c r="G123" t="str">
-        <v/>
-      </c>
-      <c r="H123" t="str">
-        <v/>
-      </c>
-      <c r="I123" t="str">
-        <v/>
-      </c>
-      <c r="J123" t="str">
-        <v/>
-      </c>
-      <c r="K123" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="str">
-        <v>Account statement - Fees statement</v>
-      </c>
-      <c r="B124" t="str">
-        <v/>
-      </c>
-      <c r="C124" s="14" t="str">
-        <v>Discovery</v>
-      </c>
-      <c r="D124" s="6" t="str">
-        <v>acctStatement</v>
-      </c>
-      <c r="E124" t="str">
+      <c r="E124" s="6" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
@@ -5406,79 +5406,49 @@
       <c r="G124" t="str">
         <v/>
       </c>
-      <c r="H124" s="6" t="str">
-        <v>V4(1.6)</v>
+      <c r="H124" t="str">
+        <v/>
       </c>
       <c r="I124" t="str">
         <v/>
       </c>
-      <c r="J124" s="6" t="str">
-        <v>Richard</v>
-      </c>
-      <c r="K124" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L124" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M124" s="6">
-        <v>5</v>
-      </c>
-      <c r="N124" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O124" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1e0om-xgw9NsChJPHa1NS2-VjxGJdDyH0</v>
-      </c>
-      <c r="P124" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="Q124" s="7">
-        <v>46104</v>
-      </c>
-      <c r="R124" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S124" t="str">
-        <v/>
-      </c>
-      <c r="T124" s="8">
-        <v>46104</v>
-      </c>
-      <c r="U124" s="8">
-        <v>46104</v>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v/>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="str">
-        <v>Crypto staking</v>
+        <v>Account statement - Fees statement</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
-      <c r="C125" s="5" t="str">
-        <v>FE DEV WIP</v>
-      </c>
-      <c r="D125" t="str">
-        <v/>
+      <c r="C125" s="15" t="str">
+        <v>Discovery</v>
+      </c>
+      <c r="D125" s="6" t="str">
+        <v>acctStatement</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
-      <c r="F125" s="8">
-        <v>46062</v>
-      </c>
-      <c r="G125" s="8">
-        <v>46141</v>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v/>
       </c>
       <c r="H125" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V4(1.6)</v>
       </c>
       <c r="I125" t="str">
         <v/>
       </c>
       <c r="J125" s="6" t="str">
-        <v>Nikolaus Kulier</v>
+        <v>Richard</v>
       </c>
       <c r="K125" s="6" t="str">
         <v/>
@@ -5486,43 +5456,43 @@
       <c r="L125" s="6" t="str">
         <v/>
       </c>
-      <c r="M125" t="str">
-        <v/>
+      <c r="M125" s="6">
+        <v>5</v>
       </c>
       <c r="N125" s="6" t="str">
         <v/>
       </c>
-      <c r="O125" t="str">
-        <v/>
-      </c>
-      <c r="P125" t="str">
-        <v/>
+      <c r="O125" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1e0om-xgw9NsChJPHa1NS2-VjxGJdDyH0</v>
+      </c>
+      <c r="P125" s="6" t="str">
+        <v>Banking</v>
       </c>
       <c r="Q125" s="7">
-        <v>46127</v>
+        <v>46104</v>
       </c>
       <c r="R125" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 7:18 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
       <c r="S125" t="str">
         <v/>
       </c>
-      <c r="T125" t="str">
-        <v/>
-      </c>
-      <c r="U125" t="str">
-        <v/>
+      <c r="T125" s="8">
+        <v>46104</v>
+      </c>
+      <c r="U125" s="8">
+        <v>46104</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="str">
-        <v>Home Page Graph FE\BE</v>
+        <v>Crypto staking</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
-      <c r="C126" s="16" t="str">
-        <v>Deployment</v>
+      <c r="C126" s="5" t="str">
+        <v>FE DEV WIP</v>
       </c>
       <c r="D126" t="str">
         <v/>
@@ -5531,10 +5501,10 @@
         <v/>
       </c>
       <c r="F126" s="8">
-        <v>46082</v>
+        <v>46062</v>
       </c>
       <c r="G126" s="8">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="H126" s="6" t="str">
         <v>V2(4.5)</v>
@@ -5543,110 +5513,140 @@
         <v/>
       </c>
       <c r="J126" s="6" t="str">
-        <v/>
+        <v>Nikolaus Kulier</v>
       </c>
       <c r="K126" s="6" t="str">
         <v/>
       </c>
       <c r="L126" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126" s="7">
+        <v>46127</v>
+      </c>
+      <c r="R126" s="6" t="str">
+        <v>Ilan Tatar Jan 28, 2026 7:18 PM</v>
+      </c>
+      <c r="S126" t="str">
+        <v/>
+      </c>
+      <c r="T126" t="str">
+        <v/>
+      </c>
+      <c r="U126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="str">
+        <v>Home Page Graph FE\BE</v>
+      </c>
+      <c r="B127" t="str">
+        <v/>
+      </c>
+      <c r="C127" s="14" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="D127" t="str">
+        <v/>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" s="8">
+        <v>46082</v>
+      </c>
+      <c r="G127" s="8">
+        <v>46127</v>
+      </c>
+      <c r="H127" s="6" t="str">
+        <v>V2(4.5)</v>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K127" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L127" s="6" t="str">
         <v>Eyal Boas+ Ron Lukovitsky</v>
       </c>
-      <c r="M126" s="6">
+      <c r="M127" s="6">
         <v>2</v>
       </c>
-      <c r="N126" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O126" s="6" t="str">
+      <c r="N127" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O127" s="6" t="str">
         <v>https://drive.google.com/drive/u/0/folders/1MmbR5lAYBNObxfbjaAaR0IyHvrI5RpD1</v>
       </c>
-      <c r="P126" s="6" t="str">
+      <c r="P127" s="6" t="str">
         <v>Balance</v>
       </c>
-      <c r="Q126" t="str">
-        <v/>
-      </c>
-      <c r="R126" s="6" t="str">
+      <c r="Q127" t="str">
+        <v/>
+      </c>
+      <c r="R127" s="6" t="str">
         <v>Ilan Tatar Feb 2, 2026 10:23 AM</v>
       </c>
-      <c r="S126" t="str">
-        <v/>
-      </c>
-      <c r="T126" t="str">
-        <v/>
-      </c>
-      <c r="U126" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127" s="9" t="str">
+      <c r="S127" t="str">
+        <v/>
+      </c>
+      <c r="T127" t="str">
+        <v/>
+      </c>
+      <c r="U127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B127" s="10" t="str">
+      <c r="B128" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C127" s="10" t="str">
+      <c r="C128" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D127" s="10" t="str">
+      <c r="D128" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E127" s="10" t="str">
+      <c r="E128" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F127" s="10" t="str">
+      <c r="F128" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G127" s="10" t="str">
+      <c r="G128" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H127" s="10" t="str">
+      <c r="H128" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I127" s="10" t="str">
+      <c r="I128" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J127" s="10" t="str">
+      <c r="J128" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K127" s="10" t="str">
+      <c r="K128" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" t="str">
-        <v/>
-      </c>
-      <c r="B128" s="4" t="str">
-        <v>prod-dbrcks-money-we - Anton</v>
-      </c>
-      <c r="C128" s="6" t="str">
-        <v>Hagit Zamir</v>
-      </c>
-      <c r="D128" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="E128" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F128" t="str">
-        <v/>
-      </c>
-      <c r="G128" t="str">
-        <v/>
-      </c>
-      <c r="H128" s="8">
-        <v>46068</v>
-      </c>
-      <c r="I128" s="8">
-        <v>46078</v>
-      </c>
-      <c r="J128" t="str">
-        <v/>
-      </c>
-      <c r="K128" t="str">
-        <v/>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5654,13 +5654,13 @@
         <v/>
       </c>
       <c r="B129" s="4" t="str">
-        <v>Gold table data verification- Yosi Elias/Lior Ben Tzur</v>
-      </c>
-      <c r="C129" t="str">
-        <v/>
-      </c>
-      <c r="D129" s="25" t="str">
-        <v>deployment</v>
+        <v>prod-dbrcks-money-we - Anton</v>
+      </c>
+      <c r="C129" s="6" t="str">
+        <v>Hagit Zamir</v>
+      </c>
+      <c r="D129" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E129" s="6" t="str">
         <v/>
@@ -5672,10 +5672,10 @@
         <v/>
       </c>
       <c r="H129" s="8">
-        <v>46070</v>
+        <v>46068</v>
       </c>
       <c r="I129" s="8">
-        <v>46128</v>
+        <v>46078</v>
       </c>
       <c r="J129" t="str">
         <v/>
@@ -5689,13 +5689,13 @@
         <v/>
       </c>
       <c r="B130" s="4" t="str">
-        <v>Home page for Plus- Filipe- Luka T</v>
+        <v>Gold table data verification- Yosi Elias/Lior Ben Tzur</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
-      <c r="D130" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D130" s="25" t="str">
+        <v>deployment</v>
       </c>
       <c r="E130" s="6" t="str">
         <v/>
@@ -5706,11 +5706,11 @@
       <c r="G130" t="str">
         <v/>
       </c>
-      <c r="H130" t="str">
-        <v/>
-      </c>
-      <c r="I130" t="str">
-        <v/>
+      <c r="H130" s="8">
+        <v>46070</v>
+      </c>
+      <c r="I130" s="8">
+        <v>46128</v>
       </c>
       <c r="J130" t="str">
         <v/>
@@ -5724,13 +5724,13 @@
         <v/>
       </c>
       <c r="B131" s="4" t="str">
-        <v>Home page Graph for Desktop/Existing App- Hila/Oleg</v>
+        <v>Home page for Plus- Filipe- Luka T</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
-      <c r="D131" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D131" s="13" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E131" s="6" t="str">
         <v/>
@@ -5741,11 +5741,11 @@
       <c r="G131" t="str">
         <v/>
       </c>
-      <c r="H131" s="8">
-        <v>46082</v>
-      </c>
-      <c r="I131" s="8">
-        <v>46112</v>
+      <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <v/>
       </c>
       <c r="J131" t="str">
         <v/>
@@ -5759,7 +5759,7 @@
         <v/>
       </c>
       <c r="B132" s="4" t="str">
-        <v>BFF for Home Page Graph- Filipe &amp; Luka</v>
+        <v>Home page Graph for Desktop/Existing App- Hila/Oleg</v>
       </c>
       <c r="C132" t="str">
         <v/>
@@ -5776,11 +5776,11 @@
       <c r="G132" t="str">
         <v/>
       </c>
-      <c r="H132" t="str">
-        <v/>
-      </c>
-      <c r="I132" t="str">
-        <v/>
+      <c r="H132" s="8">
+        <v>46082</v>
+      </c>
+      <c r="I132" s="8">
+        <v>46112</v>
       </c>
       <c r="J132" t="str">
         <v/>
@@ -5794,13 +5794,13 @@
         <v/>
       </c>
       <c r="B133" s="4" t="str">
-        <v>Lake to SQL server daily extract- Inbal</v>
-      </c>
-      <c r="C133" s="6" t="str">
-        <v>Eyal Boas</v>
-      </c>
-      <c r="D133" s="17" t="str">
-        <v>Cancelled</v>
+        <v>BFF for Home Page Graph- Filipe &amp; Luka</v>
+      </c>
+      <c r="C133" t="str">
+        <v/>
+      </c>
+      <c r="D133" s="18" t="str">
+        <v>Not Started</v>
       </c>
       <c r="E133" s="6" t="str">
         <v/>
@@ -5811,11 +5811,11 @@
       <c r="G133" t="str">
         <v/>
       </c>
-      <c r="H133" s="8">
-        <v>46070</v>
-      </c>
-      <c r="I133" s="8">
-        <v>46096</v>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v/>
       </c>
       <c r="J133" t="str">
         <v/>
@@ -5829,10 +5829,10 @@
         <v/>
       </c>
       <c r="B134" s="4" t="str">
-        <v>Balance API for Graph- Maksym Shpanovsky</v>
-      </c>
-      <c r="C134" t="str">
-        <v/>
+        <v>Lake to SQL server daily extract- Inbal</v>
+      </c>
+      <c r="C134" s="6" t="str">
+        <v>Eyal Boas</v>
       </c>
       <c r="D134" s="17" t="str">
         <v>Cancelled</v>
@@ -5846,11 +5846,11 @@
       <c r="G134" t="str">
         <v/>
       </c>
-      <c r="H134" t="str">
-        <v/>
-      </c>
-      <c r="I134" t="str">
-        <v/>
+      <c r="H134" s="8">
+        <v>46070</v>
+      </c>
+      <c r="I134" s="8">
+        <v>46096</v>
       </c>
       <c r="J134" t="str">
         <v/>
@@ -5864,10 +5864,10 @@
         <v/>
       </c>
       <c r="B135" s="4" t="str">
-        <v>dldataplatformprodwe- Eyal- Monitoring</v>
-      </c>
-      <c r="C135" s="6" t="str">
-        <v>Eyal Boas</v>
+        <v>Balance API for Graph- Maksym Shpanovsky</v>
+      </c>
+      <c r="C135" t="str">
+        <v/>
       </c>
       <c r="D135" s="17" t="str">
         <v>Cancelled</v>
@@ -5899,10 +5899,10 @@
         <v/>
       </c>
       <c r="B136" s="4" t="str">
-        <v>EOD Balance API handshake- Table readiness- Anton</v>
-      </c>
-      <c r="C136" t="str">
-        <v/>
+        <v>dldataplatformprodwe- Eyal- Monitoring</v>
+      </c>
+      <c r="C136" s="6" t="str">
+        <v>Eyal Boas</v>
       </c>
       <c r="D136" s="17" t="str">
         <v>Cancelled</v>
@@ -5916,229 +5916,199 @@
       <c r="G136" t="str">
         <v/>
       </c>
-      <c r="H136" s="8">
+      <c r="H136" t="str">
+        <v/>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" t="str">
+        <v/>
+      </c>
+      <c r="B137" s="4" t="str">
+        <v>EOD Balance API handshake- Table readiness- Anton</v>
+      </c>
+      <c r="C137" t="str">
+        <v/>
+      </c>
+      <c r="D137" s="17" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="E137" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+      <c r="H137" s="8">
         <v>46076</v>
       </c>
-      <c r="I136" s="8">
+      <c r="I137" s="8">
         <v>46078</v>
       </c>
-      <c r="J136" t="str">
-        <v/>
-      </c>
-      <c r="K136" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A137" t="str">
-        <v/>
-      </c>
-      <c r="B137" t="str">
-        <v/>
-      </c>
-      <c r="C137" t="str">
-        <v/>
-      </c>
-      <c r="D137" t="str">
-        <v/>
-      </c>
-      <c r="E137" t="str">
-        <v/>
-      </c>
-      <c r="F137" s="26">
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A138" t="str">
+        <v/>
+      </c>
+      <c r="B138" t="str">
+        <v/>
+      </c>
+      <c r="C138" t="str">
+        <v/>
+      </c>
+      <c r="D138" t="str">
+        <v/>
+      </c>
+      <c r="E138" t="str">
+        <v/>
+      </c>
+      <c r="F138" s="26">
         <v>46061</v>
       </c>
-      <c r="G137" s="26">
+      <c r="G138" s="26">
         <v>46141</v>
       </c>
-      <c r="H137" t="str">
-        <v/>
-      </c>
-      <c r="I137" t="str">
-        <v/>
-      </c>
-      <c r="J137" t="str">
-        <v/>
-      </c>
-      <c r="K137" t="str">
-        <v/>
-      </c>
-      <c r="L137" t="str">
-        <v/>
-      </c>
-      <c r="M137" s="27">
+      <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
+        <v/>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" s="27">
         <v>38</v>
       </c>
-      <c r="N137" t="str">
-        <v/>
-      </c>
-      <c r="O137" t="str">
-        <v/>
-      </c>
-      <c r="P137" t="str">
-        <v/>
-      </c>
-      <c r="Q137" s="28" t="str">
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138" s="28" t="str">
         <v>2026-02-02 to 2026-04-15</v>
       </c>
-      <c r="R137" t="str">
-        <v/>
-      </c>
-      <c r="S137" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T137" s="26">
+      <c r="R138" t="str">
+        <v/>
+      </c>
+      <c r="S138" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T138" s="26">
         <v>46058</v>
       </c>
-      <c r="U137" s="26">
+      <c r="U138" s="26">
         <v>46114</v>
       </c>
     </row>
-    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="30" t="str">
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="30" t="str">
         <v>In Focus</v>
       </c>
     </row>
-    <row r="140" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A140" s="3" t="str">
+    <row r="141" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B140" s="3" t="str">
+      <c r="B141" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C140" s="3" t="str">
+      <c r="C141" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D140" s="3" t="str">
+      <c r="D141" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E140" s="3" t="str">
+      <c r="E141" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F140" s="3" t="str">
+      <c r="F141" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G140" s="3" t="str">
+      <c r="G141" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H140" s="3" t="str">
+      <c r="H141" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I140" s="3" t="str">
+      <c r="I141" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J140" s="3" t="str">
+      <c r="J141" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K140" s="3" t="str">
+      <c r="K141" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L140" s="3" t="str">
+      <c r="L141" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M140" s="3" t="str">
+      <c r="M141" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N140" s="3" t="str">
+      <c r="N141" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O140" s="3" t="str">
+      <c r="O141" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P140" s="3" t="str">
+      <c r="P141" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q140" s="3" t="str">
+      <c r="Q141" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R140" s="3" t="str">
+      <c r="R141" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S140" s="3" t="str">
+      <c r="S141" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T140" s="3" t="str">
+      <c r="T141" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U140" s="3" t="str">
+      <c r="U141" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="str">
-        <v>Risk - PCI Audit for credit card deposit- Hagit to deliver details</v>
-      </c>
-      <c r="B141" t="str">
-        <v/>
-      </c>
-      <c r="C141" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="D141" t="str">
-        <v/>
-      </c>
-      <c r="E141" t="str">
-        <v/>
-      </c>
-      <c r="F141" t="str">
-        <v/>
-      </c>
-      <c r="G141" t="str">
-        <v/>
-      </c>
-      <c r="H141" t="str">
-        <v/>
-      </c>
-      <c r="I141" t="str">
-        <v/>
-      </c>
-      <c r="J141" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K141" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L141" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M141" t="str">
-        <v/>
-      </c>
-      <c r="N141" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O141" t="str">
-        <v/>
-      </c>
-      <c r="P141" t="str">
-        <v/>
-      </c>
-      <c r="Q141" t="str">
-        <v/>
-      </c>
-      <c r="R141" s="6" t="str">
-        <v>Ilan Tatar Mar 29, 2026 1:16 PM</v>
-      </c>
-      <c r="S141" t="str">
-        <v/>
-      </c>
-      <c r="T141" t="str">
-        <v/>
-      </c>
-      <c r="U141" t="str">
-        <v/>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="str">
-        <v>Sagiv- Deposit apporval rate check- in order to prioritize/remove other MOPs from scope</v>
+        <v>Risk - PCI Audit for credit card deposit- Hagit to deliver details</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
-      <c r="C142" s="14" t="str">
-        <v>Discovery</v>
+      <c r="C142" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D142" t="str">
         <v/>
@@ -6183,7 +6153,7 @@
         <v/>
       </c>
       <c r="R142" s="6" t="str">
-        <v>Ilan Tatar Mar 26, 2026 6:04 PM</v>
+        <v>Ilan Tatar Mar 29, 2026 1:16 PM</v>
       </c>
       <c r="S142" t="str">
         <v/>
@@ -6197,12 +6167,12 @@
     </row>
     <row r="143" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="str">
-        <v>Deleaniation - Compliance new requirement- to display the entity behind every balance</v>
+        <v>Sagiv- Deposit apporval rate check- in order to prioritize/remove other MOPs from scope</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
-      <c r="C143" s="14" t="str">
+      <c r="C143" s="15" t="str">
         <v>Discovery</v>
       </c>
       <c r="D143" t="str">
@@ -6248,7 +6218,7 @@
         <v/>
       </c>
       <c r="R143" s="6" t="str">
-        <v>Ilan Tatar Mar 8, 2026 2:13 PM</v>
+        <v>Ilan Tatar Mar 26, 2026 6:04 PM</v>
       </c>
       <c r="S143" t="str">
         <v/>
@@ -6262,13 +6232,13 @@
     </row>
     <row r="144" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="str">
-        <v>Withdraw risk- Work on MOP - or Deposit work is enough</v>
+        <v>Deleaniation - Compliance new requirement- to display the entity behind every balance</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
-      <c r="C144" s="31" t="str">
-        <v>Risk</v>
+      <c r="C144" s="15" t="str">
+        <v>Discovery</v>
       </c>
       <c r="D144" t="str">
         <v/>
@@ -6313,7 +6283,7 @@
         <v/>
       </c>
       <c r="R144" s="6" t="str">
-        <v>Ilan Tatar Mar 12, 2026 5:47 PM</v>
+        <v>Ilan Tatar Mar 8, 2026 2:13 PM</v>
       </c>
       <c r="S144" t="str">
         <v/>
@@ -6327,13 +6297,13 @@
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="str">
-        <v>Recurring Investment- Who will handle it in PLUS- Hodaya BE &amp; Hagit &amp; to advice</v>
+        <v>Withdraw risk- Work on MOP - or Deposit work is enough</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
-      <c r="C145" s="11" t="str">
-        <v>Done</v>
+      <c r="C145" s="31" t="str">
+        <v>Risk</v>
       </c>
       <c r="D145" t="str">
         <v/>
@@ -6378,7 +6348,7 @@
         <v/>
       </c>
       <c r="R145" s="6" t="str">
-        <v>Ilan Tatar Mar 8, 2026 2:06 PM</v>
+        <v>Ilan Tatar Mar 12, 2026 5:47 PM</v>
       </c>
       <c r="S145" t="str">
         <v/>
@@ -6392,7 +6362,7 @@
     </row>
     <row r="146" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="str">
-        <v>Main Risk : Deposit flow are waiting for ABC test for solution, develop will start Mid MArch only</v>
+        <v>Recurring Investment- Who will handle it in PLUS- Hodaya BE &amp; Hagit &amp; to advice</v>
       </c>
       <c r="B146" t="str">
         <v/>
@@ -6406,11 +6376,11 @@
       <c r="E146" t="str">
         <v/>
       </c>
-      <c r="F146" s="8">
-        <v>46082</v>
-      </c>
-      <c r="G146" s="8">
-        <v>46118</v>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v/>
       </c>
       <c r="H146" t="str">
         <v/>
@@ -6443,7 +6413,7 @@
         <v/>
       </c>
       <c r="R146" s="6" t="str">
-        <v>Ilan Tatar Feb 15, 2026 1:06 PM</v>
+        <v>Ilan Tatar Mar 8, 2026 2:06 PM</v>
       </c>
       <c r="S146" t="str">
         <v/>
@@ -6457,7 +6427,7 @@
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="str">
-        <v>Send Payment- issues with readiness to develop/Adi absence</v>
+        <v>Main Risk : Deposit flow are waiting for ABC test for solution, develop will start Mid MArch only</v>
       </c>
       <c r="B147" t="str">
         <v/>
@@ -6471,11 +6441,11 @@
       <c r="E147" t="str">
         <v/>
       </c>
-      <c r="F147" t="str">
-        <v/>
-      </c>
-      <c r="G147" t="str">
-        <v/>
+      <c r="F147" s="8">
+        <v>46082</v>
+      </c>
+      <c r="G147" s="8">
+        <v>46118</v>
       </c>
       <c r="H147" t="str">
         <v/>
@@ -6508,7 +6478,7 @@
         <v/>
       </c>
       <c r="R147" s="6" t="str">
-        <v>Ilan Tatar Mar 22, 2026 11:45 AM</v>
+        <v>Ilan Tatar Feb 15, 2026 1:06 PM</v>
       </c>
       <c r="S147" t="str">
         <v/>
@@ -6522,7 +6492,7 @@
     </row>
     <row r="148" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="str">
-        <v>Where we launch the cashflow on April 20 version? Sagiv to update 8.3</v>
+        <v>Send Payment- issues with readiness to develop/Adi absence</v>
       </c>
       <c r="B148" t="str">
         <v/>
@@ -6573,7 +6543,7 @@
         <v/>
       </c>
       <c r="R148" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:48 PM</v>
+        <v>Ilan Tatar Mar 22, 2026 11:45 AM</v>
       </c>
       <c r="S148" t="str">
         <v/>
@@ -6587,7 +6557,7 @@
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="str">
-        <v>Filipe- 1.4 get the 2 cards working + be- Ilan to coordinate</v>
+        <v>Where we launch the cashflow on April 20 version? Sagiv to update 8.3</v>
       </c>
       <c r="B149" t="str">
         <v/>
@@ -6638,7 +6608,7 @@
         <v/>
       </c>
       <c r="R149" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:50 PM</v>
+        <v>Ilan Tatar Mar 5, 2026 12:48 PM</v>
       </c>
       <c r="S149" t="str">
         <v/>
@@ -6652,7 +6622,7 @@
     </row>
     <row r="150" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="str">
-        <v>FTD ABC</v>
+        <v>Filipe- 1.4 get the 2 cards working + be- Ilan to coordinate</v>
       </c>
       <c r="B150" t="str">
         <v/>
@@ -6666,11 +6636,11 @@
       <c r="E150" t="str">
         <v/>
       </c>
-      <c r="F150" s="8">
-        <v>46057</v>
-      </c>
-      <c r="G150" s="8">
-        <v>46083</v>
+      <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150" t="str">
+        <v/>
       </c>
       <c r="H150" t="str">
         <v/>
@@ -6703,7 +6673,7 @@
         <v/>
       </c>
       <c r="R150" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:17 PM</v>
+        <v>Ilan Tatar Mar 5, 2026 12:50 PM</v>
       </c>
       <c r="S150" t="str">
         <v/>
@@ -6717,7 +6687,7 @@
     </row>
     <row r="151" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="str">
-        <v>Cash flow- Decision where to locate it in the new Website</v>
+        <v>FTD ABC</v>
       </c>
       <c r="B151" t="str">
         <v/>
@@ -6732,19 +6702,19 @@
         <v/>
       </c>
       <c r="F151" s="8">
-        <v>46054</v>
+        <v>46057</v>
       </c>
       <c r="G151" s="8">
-        <v>46062</v>
+        <v>46083</v>
       </c>
       <c r="H151" t="str">
         <v/>
       </c>
-      <c r="I151" s="6" t="str">
-        <v>Meeting 9.2- Sagiv</v>
+      <c r="I151" t="str">
+        <v/>
       </c>
       <c r="J151" s="6" t="str">
-        <v>Sagiv</v>
+        <v/>
       </c>
       <c r="K151" s="6" t="str">
         <v/>
@@ -6768,7 +6738,7 @@
         <v/>
       </c>
       <c r="R151" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:06 PM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:17 PM</v>
       </c>
       <c r="S151" t="str">
         <v/>
@@ -6782,7 +6752,7 @@
     </row>
     <row r="152" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="str">
-        <v>DOD for 20.4 to Inbal? Ilan with Tal/Igor</v>
+        <v>Cash flow- Decision where to locate it in the new Website</v>
       </c>
       <c r="B152" t="str">
         <v/>
@@ -6796,20 +6766,20 @@
       <c r="E152" t="str">
         <v/>
       </c>
-      <c r="F152" t="str">
-        <v/>
-      </c>
-      <c r="G152" t="str">
-        <v/>
+      <c r="F152" s="8">
+        <v>46054</v>
+      </c>
+      <c r="G152" s="8">
+        <v>46062</v>
       </c>
       <c r="H152" t="str">
         <v/>
       </c>
-      <c r="I152" t="str">
-        <v/>
+      <c r="I152" s="6" t="str">
+        <v>Meeting 9.2- Sagiv</v>
       </c>
       <c r="J152" s="6" t="str">
-        <v/>
+        <v>Sagiv</v>
       </c>
       <c r="K152" s="6" t="str">
         <v/>
@@ -6833,7 +6803,7 @@
         <v/>
       </c>
       <c r="R152" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:49 PM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:06 PM</v>
       </c>
       <c r="S152" t="str">
         <v/>
@@ -6847,7 +6817,7 @@
     </row>
     <row r="153" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="str">
-        <v>Cash info access in the new Application</v>
+        <v>DOD for 20.4 to Inbal? Ilan with Tal/Igor</v>
       </c>
       <c r="B153" t="str">
         <v/>
@@ -6870,8 +6840,8 @@
       <c r="H153" t="str">
         <v/>
       </c>
-      <c r="I153" s="6" t="str">
-        <v>Decision about Crypto and custodial wallet. Gili and Tuval are taking this. ETA? Update ? Sagiv?</v>
+      <c r="I153" t="str">
+        <v/>
       </c>
       <c r="J153" s="6" t="str">
         <v/>
@@ -6898,7 +6868,7 @@
         <v/>
       </c>
       <c r="R153" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:15 PM</v>
+        <v>Ilan Tatar Mar 5, 2026 12:49 PM</v>
       </c>
       <c r="S153" t="str">
         <v/>
@@ -6912,7 +6882,7 @@
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="str">
-        <v>Financial History API - Understanding and plans</v>
+        <v>Cash info access in the new Application</v>
       </c>
       <c r="B154" t="str">
         <v/>
@@ -6936,7 +6906,7 @@
         <v/>
       </c>
       <c r="I154" s="6" t="str">
-        <v>Itis the list of Dep/WD from Trading account  and IBAN</v>
+        <v>Decision about Crypto and custodial wallet. Gili and Tuval are taking this. ETA? Update ? Sagiv?</v>
       </c>
       <c r="J154" s="6" t="str">
         <v/>
@@ -6963,7 +6933,7 @@
         <v/>
       </c>
       <c r="R154" s="6" t="str">
-        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:15 PM</v>
       </c>
       <c r="S154" t="str">
         <v/>
@@ -6977,7 +6947,7 @@
     </row>
     <row r="155" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="str">
-        <v>Wallet  Custodial and Non Custodial</v>
+        <v>Financial History API - Understanding and plans</v>
       </c>
       <c r="B155" t="str">
         <v/>
@@ -6985,26 +6955,26 @@
       <c r="C155" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D155" s="6" t="str">
-        <v>plusDev</v>
+      <c r="D155" t="str">
+        <v/>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
-      <c r="F155" s="8">
-        <v>46054</v>
-      </c>
-      <c r="G155" s="8">
-        <v>46058</v>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v/>
       </c>
       <c r="H155" t="str">
         <v/>
       </c>
       <c r="I155" s="6" t="str">
-        <v>What is the solution to the Wallet tab functionality in the Plus app? Sagiv is taking this and should finalize by 5.2 the requirements</v>
+        <v>Itis the list of Dep/WD from Trading account  and IBAN</v>
       </c>
       <c r="J155" s="6" t="str">
-        <v>sagiv</v>
+        <v/>
       </c>
       <c r="K155" s="6" t="str">
         <v/>
@@ -7028,7 +6998,7 @@
         <v/>
       </c>
       <c r="R155" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 11:52 AM</v>
+        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
       </c>
       <c r="S155" t="str">
         <v/>
@@ -7042,7 +7012,7 @@
     </row>
     <row r="156" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="str">
-        <v>HP Graph - Gaps to launch on production</v>
+        <v>Wallet  Custodial and Non Custodial</v>
       </c>
       <c r="B156" t="str">
         <v/>
@@ -7050,26 +7020,26 @@
       <c r="C156" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D156" t="str">
-        <v/>
+      <c r="D156" s="6" t="str">
+        <v>plusDev</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" s="8">
-        <v>46056</v>
+        <v>46054</v>
       </c>
       <c r="G156" s="8">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="H156" t="str">
         <v/>
       </c>
       <c r="I156" s="6" t="str">
-        <v>Meeting 10.2 with Ofer and his team to plan the delivery</v>
+        <v>What is the solution to the Wallet tab functionality in the Plus app? Sagiv is taking this and should finalize by 5.2 the requirements</v>
       </c>
       <c r="J156" s="6" t="str">
-        <v/>
+        <v>sagiv</v>
       </c>
       <c r="K156" s="6" t="str">
         <v/>
@@ -7093,7 +7063,7 @@
         <v/>
       </c>
       <c r="R156" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:05 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 11:52 AM</v>
       </c>
       <c r="S156" t="str">
         <v/>
@@ -7107,7 +7077,7 @@
     </row>
     <row r="157" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="str">
-        <v>BFF- Who deliver what is the scope?</v>
+        <v>HP Graph - Gaps to launch on production</v>
       </c>
       <c r="B157" t="str">
         <v/>
@@ -7121,17 +7091,17 @@
       <c r="E157" t="str">
         <v/>
       </c>
-      <c r="F157" t="str">
-        <v/>
-      </c>
-      <c r="G157" t="str">
-        <v/>
+      <c r="F157" s="8">
+        <v>46056</v>
+      </c>
+      <c r="G157" s="8">
+        <v>46056</v>
       </c>
       <c r="H157" t="str">
         <v/>
       </c>
-      <c r="I157" t="str">
-        <v/>
+      <c r="I157" s="6" t="str">
+        <v>Meeting 10.2 with Ofer and his team to plan the delivery</v>
       </c>
       <c r="J157" s="6" t="str">
         <v/>
@@ -7158,7 +7128,7 @@
         <v/>
       </c>
       <c r="R157" s="6" t="str">
-        <v>Ilan Tatar Feb 12, 2026 12:19 PM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:05 PM</v>
       </c>
       <c r="S157" t="str">
         <v/>
@@ -7172,7 +7142,7 @@
     </row>
     <row r="158" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="str">
-        <v>Withdraw - R&amp;R between Elior/Hodaya</v>
+        <v>BFF- Who deliver what is the scope?</v>
       </c>
       <c r="B158" t="str">
         <v/>
@@ -7195,8 +7165,8 @@
       <c r="H158" t="str">
         <v/>
       </c>
-      <c r="I158" s="6" t="str">
-        <v>Elisheva said that it is not clear where it reside in RND?</v>
+      <c r="I158" t="str">
+        <v/>
       </c>
       <c r="J158" s="6" t="str">
         <v/>
@@ -7223,7 +7193,7 @@
         <v/>
       </c>
       <c r="R158" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:09 PM</v>
+        <v>Ilan Tatar Feb 12, 2026 12:19 PM</v>
       </c>
       <c r="S158" t="str">
         <v/>
@@ -7237,7 +7207,7 @@
     </row>
     <row r="159" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="str">
-        <v>EOD Balance depend on HP Graph data solution? Hagit to advise</v>
+        <v>Withdraw - R&amp;R between Elior/Hodaya</v>
       </c>
       <c r="B159" t="str">
         <v/>
@@ -7260,8 +7230,8 @@
       <c r="H159" t="str">
         <v/>
       </c>
-      <c r="I159" t="str">
-        <v/>
+      <c r="I159" s="6" t="str">
+        <v>Elisheva said that it is not clear where it reside in RND?</v>
       </c>
       <c r="J159" s="6" t="str">
         <v/>
@@ -7288,7 +7258,7 @@
         <v/>
       </c>
       <c r="R159" s="6" t="str">
-        <v>Ilan Tatar Feb 4, 2026 11:39 AM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:09 PM</v>
       </c>
       <c r="S159" t="str">
         <v/>
@@ -7302,7 +7272,7 @@
     </row>
     <row r="160" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="str">
-        <v>Work For Inbal next week?</v>
+        <v>EOD Balance depend on HP Graph data solution? Hagit to advise</v>
       </c>
       <c r="B160" t="str">
         <v/>
@@ -7353,7 +7323,7 @@
         <v/>
       </c>
       <c r="R160" s="6" t="str">
-        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
+        <v>Ilan Tatar Feb 4, 2026 11:39 AM</v>
       </c>
       <c r="S160" t="str">
         <v/>
@@ -7367,7 +7337,7 @@
     </row>
     <row r="161" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="str">
-        <v>Sagiv- open task for AB deposit wizard in Monday</v>
+        <v>Work For Inbal next week?</v>
       </c>
       <c r="B161" t="str">
         <v/>
@@ -7418,7 +7388,7 @@
         <v/>
       </c>
       <c r="R161" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:56 PM</v>
+        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
       </c>
       <c r="S161" t="str">
         <v/>
@@ -7432,7 +7402,7 @@
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="str">
-        <v>Inbal- There is nothing new in BE side delivery needed for 20.4 version</v>
+        <v>Sagiv- open task for AB deposit wizard in Monday</v>
       </c>
       <c r="B162" t="str">
         <v/>
@@ -7483,287 +7453,317 @@
         <v/>
       </c>
       <c r="R162" s="6" t="str">
+        <v>Ilan Tatar Mar 5, 2026 12:56 PM</v>
+      </c>
+      <c r="S162" t="str">
+        <v/>
+      </c>
+      <c r="T162" t="str">
+        <v/>
+      </c>
+      <c r="U162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="str">
+        <v>Inbal- There is nothing new in BE side delivery needed for 20.4 version</v>
+      </c>
+      <c r="B163" t="str">
+        <v/>
+      </c>
+      <c r="C163" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="D163" t="str">
+        <v/>
+      </c>
+      <c r="E163" t="str">
+        <v/>
+      </c>
+      <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v/>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K163" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L163" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
+      <c r="R163" s="6" t="str">
         <v>Ilan Tatar Mar 11, 2026 7:41 PM</v>
       </c>
-      <c r="S162" t="str">
-        <v/>
-      </c>
-      <c r="T162" t="str">
-        <v/>
-      </c>
-      <c r="U162" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="163" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A163" t="str">
-        <v/>
-      </c>
-      <c r="B163" t="str">
-        <v/>
-      </c>
-      <c r="C163" t="str">
-        <v/>
-      </c>
-      <c r="D163" t="str">
-        <v/>
-      </c>
-      <c r="E163" t="str">
-        <v/>
-      </c>
-      <c r="F163" s="26">
+      <c r="S163" t="str">
+        <v/>
+      </c>
+      <c r="T163" t="str">
+        <v/>
+      </c>
+      <c r="U163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A164" t="str">
+        <v/>
+      </c>
+      <c r="B164" t="str">
+        <v/>
+      </c>
+      <c r="C164" t="str">
+        <v/>
+      </c>
+      <c r="D164" t="str">
+        <v/>
+      </c>
+      <c r="E164" t="str">
+        <v/>
+      </c>
+      <c r="F164" s="26">
         <v>46054</v>
       </c>
-      <c r="G163" s="26">
+      <c r="G164" s="26">
         <v>46118</v>
       </c>
-      <c r="H163" t="str">
-        <v/>
-      </c>
-      <c r="I163" t="str">
-        <v/>
-      </c>
-      <c r="J163" t="str">
-        <v/>
-      </c>
-      <c r="K163" t="str">
-        <v/>
-      </c>
-      <c r="L163" t="str">
-        <v/>
-      </c>
-      <c r="M163" s="27">
+      <c r="H164" t="str">
+        <v/>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
+      <c r="J164" t="str">
+        <v/>
+      </c>
+      <c r="K164" t="str">
+        <v/>
+      </c>
+      <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" s="27">
         <v>0</v>
       </c>
-      <c r="N163" t="str">
-        <v/>
-      </c>
-      <c r="O163" t="str">
-        <v/>
-      </c>
-      <c r="P163" t="str">
-        <v/>
-      </c>
-      <c r="Q163" s="29" t="str">
-        <v/>
-      </c>
-      <c r="R163" t="str">
-        <v/>
-      </c>
-      <c r="S163" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T163" s="29" t="str">
-        <v/>
-      </c>
-      <c r="U163" s="29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="32" t="str">
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164" s="29" t="str">
+        <v/>
+      </c>
+      <c r="R164" t="str">
+        <v/>
+      </c>
+      <c r="S164" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T164" s="29" t="str">
+        <v/>
+      </c>
+      <c r="U164" s="29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="32" t="str">
         <v>MVP - API /BFF project</v>
       </c>
     </row>
-    <row r="166" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A166" s="3" t="str">
+    <row r="167" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B166" s="3" t="str">
+      <c r="B167" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C166" s="3" t="str">
+      <c r="C167" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D166" s="3" t="str">
+      <c r="D167" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E166" s="3" t="str">
+      <c r="E167" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F166" s="3" t="str">
+      <c r="F167" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G166" s="3" t="str">
+      <c r="G167" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H166" s="3" t="str">
+      <c r="H167" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I166" s="3" t="str">
+      <c r="I167" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J166" s="3" t="str">
+      <c r="J167" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K166" s="3" t="str">
+      <c r="K167" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L166" s="3" t="str">
+      <c r="L167" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M166" s="3" t="str">
+      <c r="M167" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N166" s="3" t="str">
+      <c r="N167" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O166" s="3" t="str">
+      <c r="O167" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P166" s="3" t="str">
+      <c r="P167" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q166" s="3" t="str">
+      <c r="Q167" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R166" s="3" t="str">
+      <c r="R167" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S166" s="3" t="str">
+      <c r="S167" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T166" s="3" t="str">
+      <c r="T167" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U166" s="3" t="str">
+      <c r="U167" s="3" t="str">
         <v>Product ETA - End</v>
       </c>
     </row>
-    <row r="167" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A167" s="4" t="str">
+    <row r="168" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="str">
         <v>Real time Balance &amp; Equity APIs- Hagit</v>
       </c>
-      <c r="B167" t="str">
-        <v/>
-      </c>
-      <c r="C167" s="11" t="str">
+      <c r="B168" t="str">
+        <v/>
+      </c>
+      <c r="C168" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D167" s="6" t="str">
+      <c r="D168" s="6" t="str">
         <v>ApiForPlus</v>
       </c>
-      <c r="E167" s="6" t="str">
+      <c r="E168" s="6" t="str">
         <v>trading real time equity API</v>
       </c>
-      <c r="F167" s="8">
+      <c r="F168" s="8">
         <v>46036</v>
       </c>
-      <c r="G167" s="8">
+      <c r="G168" s="8">
         <v>46126</v>
       </c>
-      <c r="H167" s="6" t="str">
+      <c r="H168" s="6" t="str">
         <v>V1(20.4)</v>
       </c>
-      <c r="I167" t="str">
-        <v/>
-      </c>
-      <c r="J167" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K167" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L167" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M167" s="6">
+      <c r="I168" t="str">
+        <v/>
+      </c>
+      <c r="J168" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K168" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L168" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M168" s="6">
         <v>1</v>
       </c>
-      <c r="N167" s="6" t="str">
+      <c r="N168" s="6" t="str">
         <v>S</v>
       </c>
-      <c r="O167" t="str">
-        <v/>
-      </c>
-      <c r="P167" t="str">
-        <v/>
-      </c>
-      <c r="Q167" t="str">
-        <v/>
-      </c>
-      <c r="R167" s="6" t="str">
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
+      <c r="R168" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
       </c>
-      <c r="S167" t="str">
-        <v/>
-      </c>
-      <c r="T167" t="str">
-        <v/>
-      </c>
-      <c r="U167" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="168" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A168" s="9" t="str">
+      <c r="S168" t="str">
+        <v/>
+      </c>
+      <c r="T168" t="str">
+        <v/>
+      </c>
+      <c r="U168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B168" s="10" t="str">
+      <c r="B169" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C168" s="10" t="str">
+      <c r="C169" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D168" s="10" t="str">
+      <c r="D169" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E168" s="10" t="str">
+      <c r="E169" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F168" s="10" t="str">
+      <c r="F169" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G168" s="10" t="str">
+      <c r="G169" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H168" s="10" t="str">
+      <c r="H169" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I168" s="10" t="str">
+      <c r="I169" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J168" s="10" t="str">
+      <c r="J169" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K168" s="10" t="str">
+      <c r="K169" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="169" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A169" t="str">
-        <v/>
-      </c>
-      <c r="B169" s="4" t="str">
-        <v>Swaggers for 2 APIS- Maksym</v>
-      </c>
-      <c r="C169" t="str">
-        <v/>
-      </c>
-      <c r="D169" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="E169" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F169" t="str">
-        <v/>
-      </c>
-      <c r="G169" t="str">
-        <v/>
-      </c>
-      <c r="H169" s="8">
-        <v>46049</v>
-      </c>
-      <c r="I169" s="8">
-        <v>46052</v>
-      </c>
-      <c r="J169" t="str">
-        <v/>
-      </c>
-      <c r="K169" t="str">
-        <v/>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -7771,7 +7771,7 @@
         <v/>
       </c>
       <c r="B170" s="4" t="str">
-        <v>Accessibility of balances from the various accounts - Elisheva</v>
+        <v>Swaggers for 2 APIS- Maksym</v>
       </c>
       <c r="C170" t="str">
         <v/>
@@ -7792,7 +7792,7 @@
         <v>46049</v>
       </c>
       <c r="I170" s="8">
-        <v>46055</v>
+        <v>46052</v>
       </c>
       <c r="J170" t="str">
         <v/>
@@ -7806,10 +7806,10 @@
         <v/>
       </c>
       <c r="B171" s="4" t="str">
-        <v>Dev - PAYUA-7623.- Maksym</v>
-      </c>
-      <c r="C171" s="6" t="str">
-        <v>Hagit Zamir</v>
+        <v>Accessibility of balances from the various accounts - Elisheva</v>
+      </c>
+      <c r="C171" t="str">
+        <v/>
       </c>
       <c r="D171" s="11" t="str">
         <v>Done</v>
@@ -7824,10 +7824,10 @@
         <v/>
       </c>
       <c r="H171" s="8">
-        <v>46075</v>
+        <v>46049</v>
       </c>
       <c r="I171" s="8">
-        <v>46119</v>
+        <v>46055</v>
       </c>
       <c r="J171" t="str">
         <v/>
@@ -7841,10 +7841,10 @@
         <v/>
       </c>
       <c r="B172" s="4" t="str">
-        <v>Dev Admin TAPI- Amit Glazer</v>
-      </c>
-      <c r="C172" t="str">
-        <v/>
+        <v>Dev - PAYUA-7623.- Maksym</v>
+      </c>
+      <c r="C172" s="6" t="str">
+        <v>Hagit Zamir</v>
       </c>
       <c r="D172" s="11" t="str">
         <v>Done</v>
@@ -7859,10 +7859,10 @@
         <v/>
       </c>
       <c r="H172" s="8">
-        <v>46098</v>
+        <v>46075</v>
       </c>
       <c r="I172" s="8">
-        <v>46124</v>
+        <v>46119</v>
       </c>
       <c r="J172" t="str">
         <v/>
@@ -7876,7 +7876,7 @@
         <v/>
       </c>
       <c r="B173" s="4" t="str">
-        <v>Dev- Crypto- Ofir Schwartz- CRYP-7716</v>
+        <v>Dev Admin TAPI- Amit Glazer</v>
       </c>
       <c r="C173" t="str">
         <v/>
@@ -7894,10 +7894,10 @@
         <v/>
       </c>
       <c r="H173" s="8">
-        <v>46110</v>
+        <v>46098</v>
       </c>
       <c r="I173" s="8">
-        <v>46119</v>
+        <v>46124</v>
       </c>
       <c r="J173" t="str">
         <v/>
@@ -7911,7 +7911,7 @@
         <v/>
       </c>
       <c r="B174" s="4" t="str">
-        <v>Production test with users- Anton</v>
+        <v>Dev- Crypto- Ofir Schwartz- CRYP-7716</v>
       </c>
       <c r="C174" t="str">
         <v/>
@@ -7928,11 +7928,11 @@
       <c r="G174" t="str">
         <v/>
       </c>
-      <c r="H174" t="str">
-        <v/>
-      </c>
-      <c r="I174" t="str">
-        <v/>
+      <c r="H174" s="8">
+        <v>46110</v>
+      </c>
+      <c r="I174" s="8">
+        <v>46119</v>
       </c>
       <c r="J174" t="str">
         <v/>
@@ -7946,7 +7946,7 @@
         <v/>
       </c>
       <c r="B175" s="4" t="str">
-        <v>Communicate with Exp ( Filipe/Renata) to implement it</v>
+        <v>Production test with users- Anton</v>
       </c>
       <c r="C175" t="str">
         <v/>
@@ -7976,74 +7976,44 @@
         <v/>
       </c>
     </row>
-    <row r="176" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A176" s="4" t="str">
-        <v>EOD Balance- Maksym PAYUA-7769</v>
-      </c>
-      <c r="B176" t="str">
-        <v/>
-      </c>
-      <c r="C176" s="16" t="str">
-        <v>Deployment</v>
-      </c>
-      <c r="D176" s="6" t="str">
-        <v>ApiForPlus</v>
-      </c>
-      <c r="E176" t="str">
-        <v/>
-      </c>
-      <c r="F176" s="8">
-        <v>46042</v>
-      </c>
-      <c r="G176" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H176" s="6" t="str">
-        <v>V2(4.5)</v>
-      </c>
-      <c r="I176" s="6" t="str">
-        <v>Need data to expose historical balances</v>
-      </c>
-      <c r="J176" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K176" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L176" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M176" s="6">
-        <v>2</v>
-      </c>
-      <c r="N176" s="6" t="str">
-        <v>XS</v>
-      </c>
-      <c r="O176" t="str">
-        <v/>
-      </c>
-      <c r="P176" t="str">
-        <v/>
-      </c>
-      <c r="Q176" t="str">
-        <v/>
-      </c>
-      <c r="R176" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
-      </c>
-      <c r="S176" t="str">
-        <v/>
-      </c>
-      <c r="T176" t="str">
-        <v/>
-      </c>
-      <c r="U176" t="str">
+    <row r="176" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" t="str">
+        <v/>
+      </c>
+      <c r="B176" s="4" t="str">
+        <v>Communicate with Exp ( Filipe/Renata) to implement it</v>
+      </c>
+      <c r="C176" t="str">
+        <v/>
+      </c>
+      <c r="D176" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="E176" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F176" t="str">
+        <v/>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+      <c r="H176" t="str">
+        <v/>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
+      <c r="J176" t="str">
+        <v/>
+      </c>
+      <c r="K176" t="str">
         <v/>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="str">
-        <v>Deposit APIs (using existing) +Payment Eligibility +Funding</v>
+        <v>EOD Balance- Maksym PAYUA-7769</v>
       </c>
       <c r="B177" t="str">
         <v/>
@@ -8058,16 +8028,16 @@
         <v/>
       </c>
       <c r="F177" s="8">
-        <v>46040</v>
+        <v>46042</v>
       </c>
       <c r="G177" s="8">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="H177" s="6" t="str">
-        <v>V1(20.4)</v>
-      </c>
-      <c r="I177" t="str">
-        <v/>
+        <v>V2(4.5)</v>
+      </c>
+      <c r="I177" s="6" t="str">
+        <v>Need data to expose historical balances</v>
       </c>
       <c r="J177" s="6" t="str">
         <v/>
@@ -8076,13 +8046,13 @@
         <v/>
       </c>
       <c r="L177" s="6" t="str">
-        <v>Shuky</v>
+        <v/>
       </c>
       <c r="M177" s="6">
         <v>2</v>
       </c>
       <c r="N177" s="6" t="str">
-        <v>S</v>
+        <v>XS</v>
       </c>
       <c r="O177" t="str">
         <v/>
@@ -8106,74 +8076,104 @@
         <v/>
       </c>
     </row>
-    <row r="178" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A178" s="9" t="str">
+    <row r="178" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="str">
+        <v>Deposit APIs (using existing) +Payment Eligibility +Funding</v>
+      </c>
+      <c r="B178" t="str">
+        <v/>
+      </c>
+      <c r="C178" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="D178" s="6" t="str">
+        <v>ApiForPlus</v>
+      </c>
+      <c r="E178" t="str">
+        <v/>
+      </c>
+      <c r="F178" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G178" s="8">
+        <v>46126</v>
+      </c>
+      <c r="H178" s="6" t="str">
+        <v>V1(20.4)</v>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K178" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L178" s="6" t="str">
+        <v>Shuky</v>
+      </c>
+      <c r="M178" s="6">
+        <v>2</v>
+      </c>
+      <c r="N178" s="6" t="str">
+        <v>S</v>
+      </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
+      <c r="R178" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+      </c>
+      <c r="S178" t="str">
+        <v/>
+      </c>
+      <c r="T178" t="str">
+        <v/>
+      </c>
+      <c r="U178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B178" s="10" t="str">
+      <c r="B179" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C178" s="10" t="str">
+      <c r="C179" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D178" s="10" t="str">
+      <c r="D179" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E178" s="10" t="str">
+      <c r="E179" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F178" s="10" t="str">
+      <c r="F179" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G178" s="10" t="str">
+      <c r="G179" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H178" s="10" t="str">
+      <c r="H179" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I178" s="10" t="str">
+      <c r="I179" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J178" s="10" t="str">
+      <c r="J179" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K178" s="10" t="str">
+      <c r="K179" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="179" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A179" t="str">
-        <v/>
-      </c>
-      <c r="B179" s="4" t="str">
-        <v>get Eligible funding API (payment-methods/(PaymentMethodTypeId) - Shuky</v>
-      </c>
-      <c r="C179" t="str">
-        <v/>
-      </c>
-      <c r="D179" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="E179" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F179" t="str">
-        <v/>
-      </c>
-      <c r="G179" t="str">
-        <v/>
-      </c>
-      <c r="H179" t="str">
-        <v/>
-      </c>
-      <c r="I179" t="str">
-        <v/>
-      </c>
-      <c r="J179" t="str">
-        <v/>
-      </c>
-      <c r="K179" t="str">
-        <v/>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -8181,7 +8181,7 @@
         <v/>
       </c>
       <c r="B180" s="4" t="str">
-        <v>Mean of Payments (eligible-payment-method-types) API.- PAYIL-10721Shuky</v>
+        <v>get Eligible funding API (payment-methods/(PaymentMethodTypeId) - Shuky</v>
       </c>
       <c r="C180" t="str">
         <v/>
@@ -8198,11 +8198,11 @@
       <c r="G180" t="str">
         <v/>
       </c>
-      <c r="H180" s="8">
-        <v>46064</v>
-      </c>
-      <c r="I180" s="8">
-        <v>46100</v>
+      <c r="H180" t="str">
+        <v/>
+      </c>
+      <c r="I180" t="str">
+        <v/>
       </c>
       <c r="J180" t="str">
         <v/>
@@ -8216,7 +8216,7 @@
         <v/>
       </c>
       <c r="B181" s="4" t="str">
-        <v>Banking deposit MOP API- Maksym</v>
+        <v>Mean of Payments (eligible-payment-method-types) API.- PAYIL-10721Shuky</v>
       </c>
       <c r="C181" t="str">
         <v/>
@@ -8234,10 +8234,10 @@
         <v/>
       </c>
       <c r="H181" s="8">
-        <v>46055</v>
+        <v>46064</v>
       </c>
       <c r="I181" s="8">
-        <v>46125</v>
+        <v>46100</v>
       </c>
       <c r="J181" t="str">
         <v/>
@@ -8251,7 +8251,7 @@
         <v/>
       </c>
       <c r="B182" s="4" t="str">
-        <v>Swagger delivery</v>
+        <v>Banking deposit MOP API- Maksym</v>
       </c>
       <c r="C182" t="str">
         <v/>
@@ -8269,10 +8269,10 @@
         <v/>
       </c>
       <c r="H182" s="8">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="I182" s="8">
-        <v>46064</v>
+        <v>46125</v>
       </c>
       <c r="J182" t="str">
         <v/>
@@ -8286,7 +8286,7 @@
         <v/>
       </c>
       <c r="B183" s="4" t="str">
-        <v>Dictionary API- Shuky</v>
+        <v>Swagger delivery</v>
       </c>
       <c r="C183" t="str">
         <v/>
@@ -8303,11 +8303,11 @@
       <c r="G183" t="str">
         <v/>
       </c>
-      <c r="H183" t="str">
-        <v/>
-      </c>
-      <c r="I183" t="str">
-        <v/>
+      <c r="H183" s="8">
+        <v>46056</v>
+      </c>
+      <c r="I183" s="8">
+        <v>46064</v>
       </c>
       <c r="J183" t="str">
         <v/>
@@ -8321,7 +8321,7 @@
         <v/>
       </c>
       <c r="B184" s="4" t="str">
-        <v>Dictionary API- Maksym-</v>
+        <v>Dictionary API- Shuky</v>
       </c>
       <c r="C184" t="str">
         <v/>
@@ -8351,20 +8351,20 @@
         <v/>
       </c>
     </row>
-    <row r="185" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A185" s="4" t="str">
-        <v>cashflow bff - Zipi is working on it for one task</v>
-      </c>
-      <c r="B185" t="str">
-        <v/>
-      </c>
-      <c r="C185" s="11" t="str">
+    <row r="185" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" t="str">
+        <v/>
+      </c>
+      <c r="B185" s="4" t="str">
+        <v>Dictionary API- Maksym-</v>
+      </c>
+      <c r="C185" t="str">
+        <v/>
+      </c>
+      <c r="D185" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D185" t="str">
-        <v/>
-      </c>
-      <c r="E185" t="str">
+      <c r="E185" s="6" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
@@ -8379,52 +8379,22 @@
       <c r="I185" t="str">
         <v/>
       </c>
-      <c r="J185" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K185" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L185" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M185" s="6">
-        <v>1</v>
-      </c>
-      <c r="N185" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O185" t="str">
-        <v/>
-      </c>
-      <c r="P185" t="str">
-        <v/>
-      </c>
-      <c r="Q185" t="str">
-        <v/>
-      </c>
-      <c r="R185" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
-      </c>
-      <c r="S185" t="str">
-        <v/>
-      </c>
-      <c r="T185" t="str">
-        <v/>
-      </c>
-      <c r="U185" t="str">
+      <c r="J185" t="str">
+        <v/>
+      </c>
+      <c r="K185" t="str">
         <v/>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="str">
-        <v>deposit bff - we will start working on it soon. We are now preparing the contract</v>
+        <v>cashflow bff - Zipi is working on it for one task</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
-      <c r="C186" s="18" t="str">
-        <v>Not Started</v>
+      <c r="C186" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D186" t="str">
         <v/>
@@ -8454,7 +8424,7 @@
         <v/>
       </c>
       <c r="M186" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N186" s="6" t="str">
         <v/>
@@ -8469,7 +8439,7 @@
         <v/>
       </c>
       <c r="R186" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:17 PM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
       </c>
       <c r="S186" t="str">
         <v/>
@@ -8483,13 +8453,13 @@
     </row>
     <row r="187" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="str">
-        <v>banking bff - Amichai is working on it (for couple of tasks)</v>
+        <v>deposit bff - we will start working on it soon. We are now preparing the contract</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
-      <c r="C187" s="11" t="str">
-        <v>Done</v>
+      <c r="C187" s="18" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D187" t="str">
         <v/>
@@ -8519,7 +8489,7 @@
         <v/>
       </c>
       <c r="M187" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N187" s="6" t="str">
         <v/>
@@ -8534,7 +8504,7 @@
         <v/>
       </c>
       <c r="R187" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:17 PM</v>
       </c>
       <c r="S187" t="str">
         <v/>
@@ -8548,31 +8518,31 @@
     </row>
     <row r="188" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="str">
-        <v>Financial History M&amp;A</v>
+        <v>banking bff - Amichai is working on it (for couple of tasks)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
-      <c r="C188" s="18" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="D188" s="6" t="str">
-        <v>ApiForM&amp;A</v>
+      <c r="C188" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="D188" t="str">
+        <v/>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
-      <c r="F188" s="8">
-        <v>46040</v>
-      </c>
-      <c r="G188" s="8">
-        <v>46040</v>
+      <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188" t="str">
+        <v/>
       </c>
       <c r="H188" t="str">
         <v/>
       </c>
-      <c r="I188" s="6" t="str">
-        <v>add iban mimo &amp; card trx</v>
+      <c r="I188" t="str">
+        <v/>
       </c>
       <c r="J188" s="6" t="str">
         <v/>
@@ -8583,11 +8553,11 @@
       <c r="L188" s="6" t="str">
         <v/>
       </c>
-      <c r="M188" t="str">
-        <v/>
+      <c r="M188" s="6">
+        <v>1</v>
       </c>
       <c r="N188" s="6" t="str">
-        <v>S</v>
+        <v/>
       </c>
       <c r="O188" t="str">
         <v/>
@@ -8599,7 +8569,7 @@
         <v/>
       </c>
       <c r="R188" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 10:49 AM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
       </c>
       <c r="S188" t="str">
         <v/>
@@ -8613,13 +8583,13 @@
     </row>
     <row r="189" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="str">
-        <v>IBAN (balance, account, transactions, eligibility)</v>
+        <v>Financial History M&amp;A</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
-      <c r="C189" s="12" t="str">
-        <v>Stuck</v>
+      <c r="C189" s="18" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D189" s="6" t="str">
         <v>ApiForM&amp;A</v>
@@ -8627,17 +8597,17 @@
       <c r="E189" t="str">
         <v/>
       </c>
-      <c r="F189" t="str">
-        <v/>
-      </c>
-      <c r="G189" t="str">
-        <v/>
+      <c r="F189" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G189" s="8">
+        <v>46040</v>
       </c>
       <c r="H189" t="str">
         <v/>
       </c>
-      <c r="I189" t="str">
-        <v/>
+      <c r="I189" s="6" t="str">
+        <v>add iban mimo &amp; card trx</v>
       </c>
       <c r="J189" s="6" t="str">
         <v/>
@@ -8664,109 +8634,139 @@
         <v/>
       </c>
       <c r="R189" s="6" t="str">
+        <v>Ilan Tatar Jan 28, 2026 10:49 AM</v>
+      </c>
+      <c r="S189" t="str">
+        <v/>
+      </c>
+      <c r="T189" t="str">
+        <v/>
+      </c>
+      <c r="U189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="str">
+        <v>IBAN (balance, account, transactions, eligibility)</v>
+      </c>
+      <c r="B190" t="str">
+        <v/>
+      </c>
+      <c r="C190" s="12" t="str">
+        <v>Stuck</v>
+      </c>
+      <c r="D190" s="6" t="str">
+        <v>ApiForM&amp;A</v>
+      </c>
+      <c r="E190" t="str">
+        <v/>
+      </c>
+      <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v/>
+      </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
+      <c r="J190" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K190" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L190" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M190" t="str">
+        <v/>
+      </c>
+      <c r="N190" s="6" t="str">
+        <v>S</v>
+      </c>
+      <c r="O190" t="str">
+        <v/>
+      </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
+      <c r="Q190" t="str">
+        <v/>
+      </c>
+      <c r="R190" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
       </c>
-      <c r="S189" t="str">
-        <v/>
-      </c>
-      <c r="T189" t="str">
-        <v/>
-      </c>
-      <c r="U189" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="190" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A190" s="9" t="str">
+      <c r="S190" t="str">
+        <v/>
+      </c>
+      <c r="T190" t="str">
+        <v/>
+      </c>
+      <c r="U190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A191" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B190" s="10" t="str">
+      <c r="B191" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C190" s="10" t="str">
+      <c r="C191" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D190" s="10" t="str">
+      <c r="D191" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E190" s="10" t="str">
+      <c r="E191" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F190" s="10" t="str">
+      <c r="F191" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G190" s="10" t="str">
+      <c r="G191" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H190" s="10" t="str">
+      <c r="H191" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I190" s="10" t="str">
+      <c r="I191" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J190" s="10" t="str">
+      <c r="J191" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K190" s="10" t="str">
+      <c r="K191" s="10" t="str">
         <v>Priority</v>
       </c>
     </row>
-    <row r="191" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A191" t="str">
-        <v/>
-      </c>
-      <c r="B191" s="4" t="str">
+    <row r="192" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" t="str">
+        <v/>
+      </c>
+      <c r="B192" s="4" t="str">
         <v>getAccounts</v>
       </c>
-      <c r="C191" t="str">
-        <v/>
-      </c>
-      <c r="D191" s="12" t="str">
+      <c r="C192" t="str">
+        <v/>
+      </c>
+      <c r="D192" s="12" t="str">
         <v>Stuck</v>
       </c>
-      <c r="E191" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F191" t="str">
-        <v/>
-      </c>
-      <c r="G191" t="str">
-        <v/>
-      </c>
-      <c r="H191" t="str">
-        <v/>
-      </c>
-      <c r="I191" t="str">
-        <v/>
-      </c>
-      <c r="J191" t="str">
-        <v/>
-      </c>
-      <c r="K191" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="192" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A192" s="4" t="str">
-        <v>Transfer (money bus)</v>
-      </c>
-      <c r="B192" t="str">
-        <v/>
-      </c>
-      <c r="C192" s="12" t="str">
-        <v>Stuck</v>
-      </c>
-      <c r="D192" s="6" t="str">
-        <v>ApiForM&amp;A</v>
-      </c>
-      <c r="E192" t="str">
-        <v/>
-      </c>
-      <c r="F192" s="8">
-        <v>46091</v>
-      </c>
-      <c r="G192" s="8">
-        <v>46134</v>
+      <c r="E192" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192" t="str">
+        <v/>
       </c>
       <c r="H192" t="str">
         <v/>
@@ -8774,46 +8774,16 @@
       <c r="I192" t="str">
         <v/>
       </c>
-      <c r="J192" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K192" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L192" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M192" t="str">
-        <v/>
-      </c>
-      <c r="N192" s="6" t="str">
-        <v>XS</v>
-      </c>
-      <c r="O192" t="str">
-        <v/>
-      </c>
-      <c r="P192" t="str">
-        <v/>
-      </c>
-      <c r="Q192" t="str">
-        <v/>
-      </c>
-      <c r="R192" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
-      </c>
-      <c r="S192" t="str">
-        <v/>
-      </c>
-      <c r="T192" t="str">
-        <v/>
-      </c>
-      <c r="U192" t="str">
+      <c r="J192" t="str">
+        <v/>
+      </c>
+      <c r="K192" t="str">
         <v/>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="str">
-        <v>Global FTD</v>
+        <v>Transfer (money bus)</v>
       </c>
       <c r="B193" t="str">
         <v/>
@@ -8827,11 +8797,11 @@
       <c r="E193" t="str">
         <v/>
       </c>
-      <c r="F193" t="str">
-        <v/>
-      </c>
-      <c r="G193" t="str">
-        <v/>
+      <c r="F193" s="8">
+        <v>46091</v>
+      </c>
+      <c r="G193" s="8">
+        <v>46134</v>
       </c>
       <c r="H193" t="str">
         <v/>
@@ -8878,13 +8848,13 @@
     </row>
     <row r="194" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="str">
-        <v>Customer Finance</v>
+        <v>Global FTD</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
-      <c r="C194" s="18" t="str">
-        <v>Not Started</v>
+      <c r="C194" s="12" t="str">
+        <v>Stuck</v>
       </c>
       <c r="D194" s="6" t="str">
         <v>ApiForM&amp;A</v>
@@ -8943,7 +8913,7 @@
     </row>
     <row r="195" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="str">
-        <v>Banking (Payee, Withdraw)</v>
+        <v>Customer Finance</v>
       </c>
       <c r="B195" t="str">
         <v/>
@@ -8982,7 +8952,7 @@
         <v/>
       </c>
       <c r="N195" s="6" t="str">
-        <v/>
+        <v>XS</v>
       </c>
       <c r="O195" t="str">
         <v/>
@@ -9008,16 +8978,16 @@
     </row>
     <row r="196" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="str">
-        <v>CashFlow BFF- Hagit</v>
+        <v>Banking (Payee, Withdraw)</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
-      <c r="C196" s="14" t="str">
-        <v>Discovery</v>
-      </c>
-      <c r="D196" t="str">
-        <v/>
+      <c r="C196" s="18" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="D196" s="6" t="str">
+        <v>ApiForM&amp;A</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -9059,7 +9029,7 @@
         <v/>
       </c>
       <c r="R196" s="6" t="str">
-        <v>Ilan Tatar Feb 12, 2026 1:19 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
       </c>
       <c r="S196" t="str">
         <v/>
@@ -9073,12 +9043,12 @@
     </row>
     <row r="197" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="str">
-        <v>Cash Account BFF- Hagit</v>
+        <v>CashFlow BFF- Hagit</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
-      <c r="C197" s="14" t="str">
+      <c r="C197" s="15" t="str">
         <v>Discovery</v>
       </c>
       <c r="D197" t="str">
@@ -9138,19 +9108,19 @@
     </row>
     <row r="198" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="str">
-        <v>Buy from IBAN</v>
+        <v>Cash Account BFF- Hagit</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
-      <c r="C198" s="19" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="D198" s="6" t="str">
-        <v>ApiForPlus</v>
-      </c>
-      <c r="E198" s="6" t="str">
-        <v>trading BE orch</v>
+      <c r="C198" s="15" t="str">
+        <v>Discovery</v>
+      </c>
+      <c r="D198" t="str">
+        <v/>
+      </c>
+      <c r="E198" t="str">
+        <v/>
       </c>
       <c r="F198" t="str">
         <v/>
@@ -9177,7 +9147,7 @@
         <v/>
       </c>
       <c r="N198" s="6" t="str">
-        <v>XS</v>
+        <v/>
       </c>
       <c r="O198" t="str">
         <v/>
@@ -9189,7 +9159,7 @@
         <v/>
       </c>
       <c r="R198" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+        <v>Ilan Tatar Feb 12, 2026 1:19 PM</v>
       </c>
       <c r="S198" t="str">
         <v/>
@@ -9203,37 +9173,37 @@
     </row>
     <row r="199" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="str">
-        <v>Withdraw +Payment Eligibility</v>
+        <v>Buy from IBAN</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
-      <c r="C199" s="19" t="str">
+      <c r="C199" s="21" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D199" s="6" t="str">
         <v>ApiForPlus</v>
       </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" s="8">
-        <v>46040</v>
-      </c>
-      <c r="G199" s="8">
-        <v>46065</v>
+      <c r="E199" s="6" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199" t="str">
+        <v/>
       </c>
       <c r="H199" t="str">
         <v/>
       </c>
-      <c r="I199" s="6" t="str">
-        <v>Using new money bus withdraw orch.</v>
+      <c r="I199" t="str">
+        <v/>
       </c>
       <c r="J199" s="6" t="str">
         <v/>
       </c>
       <c r="K199" s="6" t="str">
-        <v>IRena Plotkin</v>
+        <v/>
       </c>
       <c r="L199" s="6" t="str">
         <v/>
@@ -9242,7 +9212,7 @@
         <v/>
       </c>
       <c r="N199" s="6" t="str">
-        <v>S-M</v>
+        <v>XS</v>
       </c>
       <c r="O199" t="str">
         <v/>
@@ -9268,13 +9238,13 @@
     </row>
     <row r="200" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="str">
-        <v>Financial History- Hagit</v>
+        <v>Withdraw +Payment Eligibility</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
-      <c r="C200" s="22" t="str">
-        <v>Managed by other team</v>
+      <c r="C200" s="21" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="D200" s="6" t="str">
         <v>ApiForPlus</v>
@@ -9286,19 +9256,19 @@
         <v>46040</v>
       </c>
       <c r="G200" s="8">
-        <v>46040</v>
+        <v>46065</v>
       </c>
       <c r="H200" t="str">
         <v/>
       </c>
       <c r="I200" s="6" t="str">
-        <v>add iban mimo &amp; card trx</v>
+        <v>Using new money bus withdraw orch.</v>
       </c>
       <c r="J200" s="6" t="str">
         <v/>
       </c>
       <c r="K200" s="6" t="str">
-        <v/>
+        <v>IRena Plotkin</v>
       </c>
       <c r="L200" s="6" t="str">
         <v/>
@@ -9307,7 +9277,7 @@
         <v/>
       </c>
       <c r="N200" s="6" t="str">
-        <v>S</v>
+        <v>S-M</v>
       </c>
       <c r="O200" t="str">
         <v/>
@@ -9332,239 +9302,239 @@
       </c>
     </row>
     <row r="201" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A201" t="str">
-        <v/>
+      <c r="A201" s="4" t="str">
+        <v>Financial History- Hagit</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
-      <c r="C201" t="str">
-        <v/>
-      </c>
-      <c r="D201" t="str">
-        <v/>
+      <c r="C201" s="19" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D201" s="6" t="str">
+        <v>ApiForPlus</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
-      <c r="F201" s="26">
+      <c r="F201" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G201" s="8">
+        <v>46040</v>
+      </c>
+      <c r="H201" t="str">
+        <v/>
+      </c>
+      <c r="I201" s="6" t="str">
+        <v>add iban mimo &amp; card trx</v>
+      </c>
+      <c r="J201" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K201" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L201" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M201" t="str">
+        <v/>
+      </c>
+      <c r="N201" s="6" t="str">
+        <v>S</v>
+      </c>
+      <c r="O201" t="str">
+        <v/>
+      </c>
+      <c r="P201" t="str">
+        <v/>
+      </c>
+      <c r="Q201" t="str">
+        <v/>
+      </c>
+      <c r="R201" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+      </c>
+      <c r="S201" t="str">
+        <v/>
+      </c>
+      <c r="T201" t="str">
+        <v/>
+      </c>
+      <c r="U201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A202" t="str">
+        <v/>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v/>
+      </c>
+      <c r="D202" t="str">
+        <v/>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" s="26">
         <v>46036</v>
       </c>
-      <c r="G201" s="26">
+      <c r="G202" s="26">
         <v>46134</v>
       </c>
-      <c r="H201" t="str">
-        <v/>
-      </c>
-      <c r="I201" t="str">
-        <v/>
-      </c>
-      <c r="J201" t="str">
-        <v/>
-      </c>
-      <c r="K201" t="str">
-        <v/>
-      </c>
-      <c r="L201" t="str">
-        <v/>
-      </c>
-      <c r="M201" s="27">
+      <c r="H202" t="str">
+        <v/>
+      </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
+      <c r="J202" t="str">
+        <v/>
+      </c>
+      <c r="K202" t="str">
+        <v/>
+      </c>
+      <c r="L202" t="str">
+        <v/>
+      </c>
+      <c r="M202" s="27">
         <v>9</v>
       </c>
-      <c r="N201" t="str">
-        <v/>
-      </c>
-      <c r="O201" t="str">
-        <v/>
-      </c>
-      <c r="P201" t="str">
-        <v/>
-      </c>
-      <c r="Q201" s="29" t="str">
-        <v/>
-      </c>
-      <c r="R201" t="str">
-        <v/>
-      </c>
-      <c r="S201" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T201" s="29" t="str">
-        <v/>
-      </c>
-      <c r="U201" s="29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="202" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A203" s="33" t="str">
+      <c r="N202" t="str">
+        <v/>
+      </c>
+      <c r="O202" t="str">
+        <v/>
+      </c>
+      <c r="P202" t="str">
+        <v/>
+      </c>
+      <c r="Q202" s="29" t="str">
+        <v/>
+      </c>
+      <c r="R202" t="str">
+        <v/>
+      </c>
+      <c r="S202" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T202" s="29" t="str">
+        <v/>
+      </c>
+      <c r="U202" s="29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="33" t="str">
         <v>Not in Money scope/Future versions</v>
       </c>
     </row>
-    <row r="204" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A204" s="3" t="str">
+    <row r="205" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B204" s="3" t="str">
+      <c r="B205" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C204" s="3" t="str">
+      <c r="C205" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D204" s="3" t="str">
+      <c r="D205" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E204" s="3" t="str">
+      <c r="E205" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F204" s="3" t="str">
+      <c r="F205" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G204" s="3" t="str">
+      <c r="G205" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H204" s="3" t="str">
+      <c r="H205" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I204" s="3" t="str">
+      <c r="I205" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J204" s="3" t="str">
+      <c r="J205" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K204" s="3" t="str">
+      <c r="K205" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L204" s="3" t="str">
+      <c r="L205" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M204" s="3" t="str">
+      <c r="M205" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N204" s="3" t="str">
+      <c r="N205" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O204" s="3" t="str">
+      <c r="O205" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P204" s="3" t="str">
+      <c r="P205" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q204" s="3" t="str">
+      <c r="Q205" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R204" s="3" t="str">
+      <c r="R205" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S204" s="3" t="str">
+      <c r="S205" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T204" s="3" t="str">
+      <c r="T205" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U204" s="3" t="str">
+      <c r="U205" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="205" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A205" s="4" t="str">
-        <v>Portfolio: Balance breakdown display</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" s="22" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D205" s="6" t="str">
-        <v>Home:Balances&amp; Graph</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" s="8">
-        <v>46076</v>
-      </c>
-      <c r="G205" s="8">
-        <v>46076</v>
-      </c>
-      <c r="H205" t="str">
-        <v/>
-      </c>
-      <c r="I205" t="str">
-        <v/>
-      </c>
-      <c r="J205" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K205" s="6" t="str">
-        <v>Inbal Escholi</v>
-      </c>
-      <c r="L205" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M205" s="6">
-        <v>99</v>
-      </c>
-      <c r="N205" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O205" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1mnu7wyyW4vQQQTn1fJ2Uz4OAAqlZYDXQ</v>
-      </c>
-      <c r="P205" s="6" t="str">
-        <v>Balance</v>
-      </c>
-      <c r="Q205" t="str">
-        <v/>
-      </c>
-      <c r="R205" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
-      </c>
-      <c r="S205" t="str">
-        <v/>
-      </c>
-      <c r="T205" t="str">
-        <v/>
-      </c>
-      <c r="U205" t="str">
-        <v/>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="str">
-        <v>Close to IBAN</v>
+        <v>Portfolio: Balance breakdown display</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
-      <c r="C206" s="22" t="str">
+      <c r="C206" s="19" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D206" s="6" t="str">
-        <v>tradeIBAN</v>
-      </c>
-      <c r="E206" s="6" t="str">
-        <v>trading BE orch</v>
-      </c>
-      <c r="F206" t="str">
-        <v/>
-      </c>
-      <c r="G206" t="str">
-        <v/>
+        <v>Home:Balances&amp; Graph</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" s="8">
+        <v>46076</v>
+      </c>
+      <c r="G206" s="8">
+        <v>46076</v>
       </c>
       <c r="H206" t="str">
         <v/>
       </c>
-      <c r="I206" s="6" t="str">
-        <v>Dependency with Trading- TBD</v>
+      <c r="I206" t="str">
+        <v/>
       </c>
       <c r="J206" s="6" t="str">
-        <v>Joanna</v>
+        <v/>
       </c>
       <c r="K206" s="6" t="str">
-        <v/>
+        <v>Inbal Escholi</v>
       </c>
       <c r="L206" s="6" t="str">
         <v/>
@@ -9576,16 +9546,16 @@
         <v/>
       </c>
       <c r="O206" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1ddNvCALwf6FEU0B0IL99tpwkLeoal_W_</v>
+        <v>https://drive.google.com/drive/u/0/folders/1mnu7wyyW4vQQQTn1fJ2Uz4OAAqlZYDXQ</v>
       </c>
       <c r="P206" s="6" t="str">
-        <v>Local currency, Trading</v>
+        <v>Balance</v>
       </c>
       <c r="Q206" t="str">
         <v/>
       </c>
       <c r="R206" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
       </c>
       <c r="S206" t="str">
         <v/>
@@ -9599,12 +9569,12 @@
     </row>
     <row r="207" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="str">
-        <v>Trade from IBAN (local currency)</v>
+        <v>Close to IBAN</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
-      <c r="C207" s="22" t="str">
+      <c r="C207" s="19" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D207" s="6" t="str">
@@ -9641,7 +9611,7 @@
         <v/>
       </c>
       <c r="O207" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1coMCsTt9H1FUbALyki0_k30a77Ff3Hou</v>
+        <v>https://drive.google.com/drive/u/0/folders/1ddNvCALwf6FEU0B0IL99tpwkLeoal_W_</v>
       </c>
       <c r="P207" s="6" t="str">
         <v>Local currency, Trading</v>
@@ -9664,12 +9634,12 @@
     </row>
     <row r="208" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="str">
-        <v>Exectuion popup - balance drawer</v>
+        <v>Trade from IBAN (local currency)</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
-      <c r="C208" s="22" t="str">
+      <c r="C208" s="19" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D208" s="6" t="str">
@@ -9688,7 +9658,7 @@
         <v/>
       </c>
       <c r="I208" s="6" t="str">
-        <v>Using the SDK + API. Need execution popup BFF</v>
+        <v>Dependency with Trading- TBD</v>
       </c>
       <c r="J208" s="6" t="str">
         <v>Joanna</v>
@@ -9706,10 +9676,10 @@
         <v/>
       </c>
       <c r="O208" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1uRBpFFz5LHbz_kS_QTlKAjAysLDykQKF</v>
+        <v>https://drive.google.com/drive/u/0/folders/1coMCsTt9H1FUbALyki0_k30a77Ff3Hou</v>
       </c>
       <c r="P208" s="6" t="str">
-        <v>Local currency, Payments</v>
+        <v>Local currency, Trading</v>
       </c>
       <c r="Q208" t="str">
         <v/>
@@ -9729,100 +9699,100 @@
     </row>
     <row r="209" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="str">
+        <v>Exectuion popup - balance drawer</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" s="19" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D209" s="6" t="str">
+        <v>tradeIBAN</v>
+      </c>
+      <c r="E209" s="6" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="F209" t="str">
+        <v/>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+      <c r="H209" t="str">
+        <v/>
+      </c>
+      <c r="I209" s="6" t="str">
+        <v>Using the SDK + API. Need execution popup BFF</v>
+      </c>
+      <c r="J209" s="6" t="str">
+        <v>Joanna</v>
+      </c>
+      <c r="K209" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L209" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M209" s="6">
+        <v>99</v>
+      </c>
+      <c r="N209" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O209" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1uRBpFFz5LHbz_kS_QTlKAjAysLDykQKF</v>
+      </c>
+      <c r="P209" s="6" t="str">
+        <v>Local currency, Payments</v>
+      </c>
+      <c r="Q209" t="str">
+        <v/>
+      </c>
+      <c r="R209" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S209" t="str">
+        <v/>
+      </c>
+      <c r="T209" t="str">
+        <v/>
+      </c>
+      <c r="U209" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="210" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="str">
         <v>Home Page- Balance Display</v>
       </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" s="22" t="str">
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" s="19" t="str">
         <v>Managed by other team</v>
       </c>
-      <c r="D209" s="6" t="str">
+      <c r="D210" s="6" t="str">
         <v>Home:Balances&amp; Graph</v>
       </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" s="8">
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" s="8">
         <v>46076</v>
       </c>
-      <c r="G209" s="8">
+      <c r="G210" s="8">
         <v>46076</v>
       </c>
-      <c r="H209" t="str">
-        <v/>
-      </c>
-      <c r="I209" s="6" t="str">
+      <c r="H210" t="str">
+        <v/>
+      </c>
+      <c r="I210" s="6" t="str">
         <v>Require effort to expose the data from the lake
 Meeting 20/1 - home page redesign</v>
       </c>
-      <c r="J209" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K209" s="6" t="str">
-        <v>Inbal Escholi</v>
-      </c>
-      <c r="L209" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M209" s="6">
-        <v>99</v>
-      </c>
-      <c r="N209" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O209" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1ajgQLvU3kxLq70yAZZBcFppbac3M02Jm</v>
-      </c>
-      <c r="P209" s="6" t="str">
-        <v>Balance</v>
-      </c>
-      <c r="Q209" s="7">
-        <v>46083</v>
-      </c>
-      <c r="R209" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S209" t="str">
-        <v/>
-      </c>
-      <c r="T209" t="str">
-        <v/>
-      </c>
-      <c r="U209" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="210" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A210" s="4" t="str">
-        <v>Recurring Investment</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" s="22" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D210" s="6" t="str">
-        <v>recurInvestment</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" s="8">
-        <v>46105</v>
-      </c>
-      <c r="G210" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H210" t="str">
-        <v/>
-      </c>
-      <c r="I210" t="str">
-        <v/>
-      </c>
       <c r="J210" s="6" t="str">
-        <v>Noit</v>
+        <v/>
       </c>
       <c r="K210" s="6" t="str">
         <v>Inbal Escholi</v>
@@ -9836,14 +9806,14 @@
       <c r="N210" s="6" t="str">
         <v/>
       </c>
-      <c r="O210" t="str">
-        <v/>
+      <c r="O210" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1ajgQLvU3kxLq70yAZZBcFppbac3M02Jm</v>
       </c>
       <c r="P210" s="6" t="str">
-        <v>Payments, Recurring Investment</v>
-      </c>
-      <c r="Q210" t="str">
-        <v/>
+        <v>Balance</v>
+      </c>
+      <c r="Q210" s="7">
+        <v>46083</v>
       </c>
       <c r="R210" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
@@ -9858,74 +9828,104 @@
         <v/>
       </c>
     </row>
-    <row r="211" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A211" s="9" t="str">
+    <row r="211" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="str">
+        <v>Recurring Investment</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" s="19" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D211" s="6" t="str">
+        <v>recurInvestment</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" s="8">
+        <v>46105</v>
+      </c>
+      <c r="G211" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H211" t="str">
+        <v/>
+      </c>
+      <c r="I211" t="str">
+        <v/>
+      </c>
+      <c r="J211" s="6" t="str">
+        <v>Noit</v>
+      </c>
+      <c r="K211" s="6" t="str">
+        <v>Inbal Escholi</v>
+      </c>
+      <c r="L211" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M211" s="6">
+        <v>99</v>
+      </c>
+      <c r="N211" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O211" t="str">
+        <v/>
+      </c>
+      <c r="P211" s="6" t="str">
+        <v>Payments, Recurring Investment</v>
+      </c>
+      <c r="Q211" t="str">
+        <v/>
+      </c>
+      <c r="R211" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S211" t="str">
+        <v/>
+      </c>
+      <c r="T211" t="str">
+        <v/>
+      </c>
+      <c r="U211" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A212" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B211" s="10" t="str">
+      <c r="B212" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C211" s="10" t="str">
+      <c r="C212" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D211" s="10" t="str">
+      <c r="D212" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E211" s="10" t="str">
+      <c r="E212" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F211" s="10" t="str">
+      <c r="F212" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G211" s="10" t="str">
+      <c r="G212" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H211" s="10" t="str">
+      <c r="H212" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I211" s="10" t="str">
+      <c r="I212" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J211" s="10" t="str">
+      <c r="J212" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K211" s="10" t="str">
+      <c r="K212" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="212" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A212" t="str">
-        <v/>
-      </c>
-      <c r="B212" s="4" t="str">
-        <v>Recurring investment - card details</v>
-      </c>
-      <c r="C212" t="str">
-        <v/>
-      </c>
-      <c r="D212" s="18" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="E212" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v/>
-      </c>
-      <c r="G212" s="6" t="str">
-        <v>Payments</v>
-      </c>
-      <c r="H212" t="str">
-        <v/>
-      </c>
-      <c r="I212" t="str">
-        <v/>
-      </c>
-      <c r="J212" t="str">
-        <v/>
-      </c>
-      <c r="K212" t="str">
-        <v/>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -9933,7 +9933,7 @@
         <v/>
       </c>
       <c r="B213" s="4" t="str">
-        <v>Recurring investment feature</v>
+        <v>Recurring investment - card details</v>
       </c>
       <c r="C213" t="str">
         <v/>
@@ -9947,8 +9947,8 @@
       <c r="F213" t="str">
         <v/>
       </c>
-      <c r="G213" t="str">
-        <v/>
+      <c r="G213" s="6" t="str">
+        <v>Payments</v>
       </c>
       <c r="H213" t="str">
         <v/>
@@ -9963,20 +9963,20 @@
         <v/>
       </c>
     </row>
-    <row r="214" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A214" s="4" t="str">
-        <v>IBAN - Club Upgrades for Account Programs</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" s="21" t="str">
-        <v>Future Version</v>
-      </c>
-      <c r="D214" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="E214" t="str">
+    <row r="214" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A214" t="str">
+        <v/>
+      </c>
+      <c r="B214" s="4" t="str">
+        <v>Recurring investment feature</v>
+      </c>
+      <c r="C214" t="str">
+        <v/>
+      </c>
+      <c r="D214" s="18" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="E214" s="6" t="str">
         <v/>
       </c>
       <c r="F214" t="str">
@@ -9991,55 +9991,25 @@
       <c r="I214" t="str">
         <v/>
       </c>
-      <c r="J214" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K214" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L214" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M214" s="6">
-        <v>100</v>
-      </c>
-      <c r="N214" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O214" t="str">
-        <v/>
-      </c>
-      <c r="P214" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="Q214" t="str">
-        <v/>
-      </c>
-      <c r="R214" s="6" t="str">
-        <v>Hagit Zamir Feb 3, 2026 3:42 PM</v>
-      </c>
-      <c r="S214" t="str">
-        <v/>
-      </c>
-      <c r="T214" t="str">
-        <v/>
-      </c>
-      <c r="U214" t="str">
+      <c r="J214" t="str">
+        <v/>
+      </c>
+      <c r="K214" t="str">
         <v/>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="str">
-        <v>Wallet tab - IBAN - Direct Debit</v>
+        <v>IBAN - Club Upgrades for Account Programs</v>
       </c>
       <c r="B215" t="str">
         <v/>
       </c>
-      <c r="C215" s="21" t="str">
+      <c r="C215" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D215" s="6" t="str">
-        <v>ManageDirectDebit</v>
+        <v>Banking</v>
       </c>
       <c r="E215" t="str">
         <v/>
@@ -10053,11 +10023,11 @@
       <c r="H215" t="str">
         <v/>
       </c>
-      <c r="I215" s="6" t="str">
-        <v>Web only (mobile web is optional)</v>
+      <c r="I215" t="str">
+        <v/>
       </c>
       <c r="J215" s="6" t="str">
-        <v>Adi</v>
+        <v/>
       </c>
       <c r="K215" s="6" t="str">
         <v/>
@@ -10071,8 +10041,8 @@
       <c r="N215" s="6" t="str">
         <v/>
       </c>
-      <c r="O215" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1ckH93ib0CmcIINKUzOdZWWhqNbnIAiZi</v>
+      <c r="O215" t="str">
+        <v/>
       </c>
       <c r="P215" s="6" t="str">
         <v>Banking</v>
@@ -10081,7 +10051,7 @@
         <v/>
       </c>
       <c r="R215" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+        <v>Hagit Zamir Feb 3, 2026 3:42 PM</v>
       </c>
       <c r="S215" t="str">
         <v/>
@@ -10095,37 +10065,37 @@
     </row>
     <row r="216" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="str">
-        <v>Crypto-in/out - New Flow</v>
+        <v>Wallet tab - IBAN - Direct Debit</v>
       </c>
       <c r="B216" t="str">
         <v/>
       </c>
-      <c r="C216" s="21" t="str">
+      <c r="C216" s="22" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D216" t="str">
-        <v/>
+      <c r="D216" s="6" t="str">
+        <v>ManageDirectDebit</v>
       </c>
       <c r="E216" t="str">
         <v/>
       </c>
-      <c r="F216" s="8">
-        <v>46061</v>
-      </c>
-      <c r="G216" s="8">
-        <v>46075</v>
+      <c r="F216" t="str">
+        <v/>
+      </c>
+      <c r="G216" t="str">
+        <v/>
       </c>
       <c r="H216" t="str">
         <v/>
       </c>
-      <c r="I216" t="str">
-        <v/>
+      <c r="I216" s="6" t="str">
+        <v>Web only (mobile web is optional)</v>
       </c>
       <c r="J216" s="6" t="str">
-        <v>Nikolaus Kulier</v>
+        <v>Adi</v>
       </c>
       <c r="K216" s="6" t="str">
-        <v>Inbal Escholi</v>
+        <v/>
       </c>
       <c r="L216" s="6" t="str">
         <v/>
@@ -10137,95 +10107,125 @@
         <v/>
       </c>
       <c r="O216" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1ckH93ib0CmcIINKUzOdZWWhqNbnIAiZi</v>
+      </c>
+      <c r="P216" s="6" t="str">
+        <v>Banking</v>
+      </c>
+      <c r="Q216" t="str">
+        <v/>
+      </c>
+      <c r="R216" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S216" t="str">
+        <v/>
+      </c>
+      <c r="T216" t="str">
+        <v/>
+      </c>
+      <c r="U216" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="217" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="str">
+        <v>Crypto-in/out - New Flow</v>
+      </c>
+      <c r="B217" t="str">
+        <v/>
+      </c>
+      <c r="C217" s="22" t="str">
+        <v>Future Version</v>
+      </c>
+      <c r="D217" t="str">
+        <v/>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" s="8">
+        <v>46061</v>
+      </c>
+      <c r="G217" s="8">
+        <v>46075</v>
+      </c>
+      <c r="H217" t="str">
+        <v/>
+      </c>
+      <c r="I217" t="str">
+        <v/>
+      </c>
+      <c r="J217" s="6" t="str">
+        <v>Nikolaus Kulier</v>
+      </c>
+      <c r="K217" s="6" t="str">
+        <v>Inbal Escholi</v>
+      </c>
+      <c r="L217" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M217" s="6">
+        <v>100</v>
+      </c>
+      <c r="N217" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O217" s="6" t="str">
         <v>https://drive.google.com/drive/u/0/folders/1T9bzCpQdskwwMHl_F_RF-WzMtTOtaaem</v>
       </c>
-      <c r="P216" s="6" t="str">
+      <c r="P217" s="6" t="str">
         <v>Crypto</v>
       </c>
-      <c r="Q216" t="str">
-        <v/>
-      </c>
-      <c r="R216" s="6" t="str">
+      <c r="Q217" t="str">
+        <v/>
+      </c>
+      <c r="R217" s="6" t="str">
         <v>Hagit Zamir Feb 3, 2026 11:58 AM</v>
       </c>
-      <c r="S216" t="str">
-        <v/>
-      </c>
-      <c r="T216" t="str">
-        <v/>
-      </c>
-      <c r="U216" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="217" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A217" s="9" t="str">
+      <c r="S217" t="str">
+        <v/>
+      </c>
+      <c r="T217" t="str">
+        <v/>
+      </c>
+      <c r="U217" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="218" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A218" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B217" s="10" t="str">
+      <c r="B218" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C217" s="10" t="str">
+      <c r="C218" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D217" s="10" t="str">
+      <c r="D218" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E217" s="10" t="str">
+      <c r="E218" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F217" s="10" t="str">
+      <c r="F218" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G217" s="10" t="str">
+      <c r="G218" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H217" s="10" t="str">
+      <c r="H218" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I217" s="10" t="str">
+      <c r="I218" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J217" s="10" t="str">
+      <c r="J218" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K217" s="10" t="str">
+      <c r="K218" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="218" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A218" t="str">
-        <v/>
-      </c>
-      <c r="B218" s="4" t="str">
-        <v>New Crypto in flow</v>
-      </c>
-      <c r="C218" t="str">
-        <v/>
-      </c>
-      <c r="D218" s="18" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="E218" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F218" t="str">
-        <v/>
-      </c>
-      <c r="G218" t="str">
-        <v/>
-      </c>
-      <c r="H218" t="str">
-        <v/>
-      </c>
-      <c r="I218" t="str">
-        <v/>
-      </c>
-      <c r="J218" t="str">
-        <v/>
-      </c>
-      <c r="K218" t="str">
-        <v/>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -10233,7 +10233,7 @@
         <v/>
       </c>
       <c r="B219" s="4" t="str">
-        <v>New Crypto out flow</v>
+        <v>New Crypto in flow</v>
       </c>
       <c r="C219" t="str">
         <v/>
@@ -10263,20 +10263,20 @@
         <v/>
       </c>
     </row>
-    <row r="220" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A220" s="4" t="str">
-        <v>Account statement - IBAN</v>
-      </c>
-      <c r="B220" t="str">
-        <v/>
-      </c>
-      <c r="C220" s="21" t="str">
-        <v>Future Version</v>
-      </c>
-      <c r="D220" s="6" t="str">
-        <v>acctStatement</v>
-      </c>
-      <c r="E220" t="str">
+    <row r="220" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A220" t="str">
+        <v/>
+      </c>
+      <c r="B220" s="4" t="str">
+        <v>New Crypto out flow</v>
+      </c>
+      <c r="C220" t="str">
+        <v/>
+      </c>
+      <c r="D220" s="18" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="E220" s="6" t="str">
         <v/>
       </c>
       <c r="F220" t="str">
@@ -10291,55 +10291,25 @@
       <c r="I220" t="str">
         <v/>
       </c>
-      <c r="J220" s="6" t="str">
-        <v>Richard</v>
-      </c>
-      <c r="K220" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L220" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M220" s="6">
-        <v>100</v>
-      </c>
-      <c r="N220" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O220" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1YGwoAq790Wb8Iudfx3nh276XbPp4uDF1</v>
-      </c>
-      <c r="P220" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="Q220" t="str">
-        <v/>
-      </c>
-      <c r="R220" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S220" t="str">
-        <v/>
-      </c>
-      <c r="T220" t="str">
-        <v/>
-      </c>
-      <c r="U220" t="str">
+      <c r="J220" t="str">
+        <v/>
+      </c>
+      <c r="K220" t="str">
         <v/>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="str">
-        <v>Wallet tab - Global banners- Transactional Banners</v>
+        <v>Account statement - IBAN</v>
       </c>
       <c r="B221" t="str">
         <v/>
       </c>
-      <c r="C221" s="21" t="str">
+      <c r="C221" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D221" s="6" t="str">
-        <v>WalletTab</v>
+        <v>acctStatement</v>
       </c>
       <c r="E221" t="str">
         <v/>
@@ -10353,11 +10323,11 @@
       <c r="H221" t="str">
         <v/>
       </c>
-      <c r="I221" s="6" t="str">
-        <v>Meeting 20/1 - home page redesign</v>
+      <c r="I221" t="str">
+        <v/>
       </c>
       <c r="J221" s="6" t="str">
-        <v>Adi</v>
+        <v>Richard</v>
       </c>
       <c r="K221" s="6" t="str">
         <v/>
@@ -10372,10 +10342,10 @@
         <v/>
       </c>
       <c r="O221" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1lvshcV8HLj_Iyu76ode34g2d_JhKBOze</v>
+        <v>https://drive.google.com/drive/u/0/folders/1YGwoAq790Wb8Iudfx3nh276XbPp4uDF1</v>
       </c>
       <c r="P221" s="6" t="str">
-        <v>Banking, Card Mng.</v>
+        <v>Banking</v>
       </c>
       <c r="Q221" t="str">
         <v/>
@@ -10395,16 +10365,16 @@
     </row>
     <row r="222" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="str">
-        <v>Long term solution for Trade button between Money and Trading</v>
+        <v>Wallet tab - Global banners- Transactional Banners</v>
       </c>
       <c r="B222" t="str">
         <v/>
       </c>
-      <c r="C222" s="21" t="str">
+      <c r="C222" s="22" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D222" t="str">
-        <v/>
+      <c r="D222" s="6" t="str">
+        <v>WalletTab</v>
       </c>
       <c r="E222" t="str">
         <v/>
@@ -10418,11 +10388,11 @@
       <c r="H222" t="str">
         <v/>
       </c>
-      <c r="I222" t="str">
-        <v/>
+      <c r="I222" s="6" t="str">
+        <v>Meeting 20/1 - home page redesign</v>
       </c>
       <c r="J222" s="6" t="str">
-        <v/>
+        <v>Adi</v>
       </c>
       <c r="K222" s="6" t="str">
         <v/>
@@ -10436,17 +10406,17 @@
       <c r="N222" s="6" t="str">
         <v/>
       </c>
-      <c r="O222" t="str">
-        <v/>
-      </c>
-      <c r="P222" t="str">
-        <v/>
+      <c r="O222" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1lvshcV8HLj_Iyu76ode34g2d_JhKBOze</v>
+      </c>
+      <c r="P222" s="6" t="str">
+        <v>Banking, Card Mng.</v>
       </c>
       <c r="Q222" t="str">
         <v/>
       </c>
       <c r="R222" s="6" t="str">
-        <v>Ilan Tatar Mar 9, 2026 2:46 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
       <c r="S222" t="str">
         <v/>
@@ -10460,12 +10430,12 @@
     </row>
     <row r="223" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="str">
-        <v>NCW in eToro Plus</v>
+        <v>Long term solution for Trade button between Money and Trading</v>
       </c>
       <c r="B223" t="str">
         <v/>
       </c>
-      <c r="C223" s="21" t="str">
+      <c r="C223" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D223" t="str">
@@ -10483,11 +10453,11 @@
       <c r="H223" t="str">
         <v/>
       </c>
-      <c r="I223" s="6" t="str">
-        <v>Dependency with Compliance</v>
+      <c r="I223" t="str">
+        <v/>
       </c>
       <c r="J223" s="6" t="str">
-        <v>Nikolaus Kulier</v>
+        <v/>
       </c>
       <c r="K223" s="6" t="str">
         <v/>
@@ -10501,17 +10471,17 @@
       <c r="N223" s="6" t="str">
         <v/>
       </c>
-      <c r="O223" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1pmEz5faaG4dEEUBCP93uCA8HuUcY4q5r</v>
-      </c>
-      <c r="P223" s="6" t="str">
-        <v>Crypto</v>
+      <c r="O223" t="str">
+        <v/>
+      </c>
+      <c r="P223" t="str">
+        <v/>
       </c>
       <c r="Q223" t="str">
         <v/>
       </c>
       <c r="R223" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+        <v>Ilan Tatar Mar 9, 2026 2:46 PM</v>
       </c>
       <c r="S223" t="str">
         <v/>
@@ -10525,16 +10495,16 @@
     </row>
     <row r="224" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="str">
-        <v>Wallet Tab - Product Promotions (all products - Local Accounts / ISA / Crypto etc etc)</v>
+        <v>NCW in eToro Plus</v>
       </c>
       <c r="B224" t="str">
         <v/>
       </c>
-      <c r="C224" s="21" t="str">
+      <c r="C224" s="22" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D224" s="6" t="str">
-        <v>WalletTabTotalValueGraph</v>
+      <c r="D224" t="str">
+        <v/>
       </c>
       <c r="E224" t="str">
         <v/>
@@ -10548,11 +10518,11 @@
       <c r="H224" t="str">
         <v/>
       </c>
-      <c r="I224" t="str">
-        <v/>
+      <c r="I224" s="6" t="str">
+        <v>Dependency with Compliance</v>
       </c>
       <c r="J224" s="6" t="str">
-        <v>Adi</v>
+        <v>Nikolaus Kulier</v>
       </c>
       <c r="K224" s="6" t="str">
         <v/>
@@ -10561,22 +10531,22 @@
         <v/>
       </c>
       <c r="M224" s="6">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="N224" s="6" t="str">
         <v/>
       </c>
       <c r="O224" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1lu17LS1984RvIkY8iqJEjH6fS-wJvZta</v>
+        <v>https://drive.google.com/drive/u/0/folders/1pmEz5faaG4dEEUBCP93uCA8HuUcY4q5r</v>
       </c>
       <c r="P224" s="6" t="str">
-        <v>Wallet Tab</v>
+        <v>Crypto</v>
       </c>
       <c r="Q224" t="str">
         <v/>
       </c>
       <c r="R224" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:28 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
       <c r="S224" t="str">
         <v/>
@@ -10590,16 +10560,16 @@
     </row>
     <row r="225" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="str">
-        <v>Trigger Web Deposit workaround for 20.4- Inbal</v>
+        <v>Wallet Tab - Product Promotions (all products - Local Accounts / ISA / Crypto etc etc)</v>
       </c>
       <c r="B225" t="str">
         <v/>
       </c>
-      <c r="C225" s="19" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="D225" t="str">
-        <v/>
+      <c r="C225" s="22" t="str">
+        <v>Future Version</v>
+      </c>
+      <c r="D225" s="6" t="str">
+        <v>WalletTabTotalValueGraph</v>
       </c>
       <c r="E225" t="str">
         <v/>
@@ -10617,7 +10587,7 @@
         <v/>
       </c>
       <c r="J225" s="6" t="str">
-        <v>Richard</v>
+        <v>Adi</v>
       </c>
       <c r="K225" s="6" t="str">
         <v/>
@@ -10626,22 +10596,22 @@
         <v/>
       </c>
       <c r="M225" s="6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N225" s="6" t="str">
         <v/>
       </c>
-      <c r="O225" t="str">
-        <v/>
-      </c>
-      <c r="P225" t="str">
-        <v/>
+      <c r="O225" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1lu17LS1984RvIkY8iqJEjH6fS-wJvZta</v>
+      </c>
+      <c r="P225" s="6" t="str">
+        <v>Wallet Tab</v>
       </c>
       <c r="Q225" t="str">
         <v/>
       </c>
       <c r="R225" s="6" t="str">
-        <v>Ilan Tatar Mar 4, 2026 2:45 PM</v>
+        <v>Ilan Tatar Jan 28, 2026 6:28 PM</v>
       </c>
       <c r="S225" t="str">
         <v/>
@@ -10655,16 +10625,16 @@
     </row>
     <row r="226" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="str">
-        <v>Wallet Tab - Balances list</v>
+        <v>Trigger Web Deposit workaround for 20.4- Inbal</v>
       </c>
       <c r="B226" t="str">
         <v/>
       </c>
-      <c r="C226" s="19" t="str">
+      <c r="C226" s="21" t="str">
         <v>Cancelled</v>
       </c>
-      <c r="D226" s="6" t="str">
-        <v>WalletTabTotalValueGraph</v>
+      <c r="D226" t="str">
+        <v/>
       </c>
       <c r="E226" t="str">
         <v/>
@@ -10682,7 +10652,7 @@
         <v/>
       </c>
       <c r="J226" s="6" t="str">
-        <v>Adi</v>
+        <v>Richard</v>
       </c>
       <c r="K226" s="6" t="str">
         <v/>
@@ -10691,22 +10661,22 @@
         <v/>
       </c>
       <c r="M226" s="6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N226" s="6" t="str">
         <v/>
       </c>
-      <c r="O226" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/10j0uo11-TGKBFj82pUueB78g_uihED_F</v>
-      </c>
-      <c r="P226" s="6" t="str">
-        <v>Balance</v>
+      <c r="O226" t="str">
+        <v/>
+      </c>
+      <c r="P226" t="str">
+        <v/>
       </c>
       <c r="Q226" t="str">
         <v/>
       </c>
       <c r="R226" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:16 PM</v>
+        <v>Ilan Tatar Mar 4, 2026 2:45 PM</v>
       </c>
       <c r="S226" t="str">
         <v/>
@@ -10720,25 +10690,25 @@
     </row>
     <row r="227" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="str">
-        <v>Watchlist: Balance breakdown display</v>
+        <v>Wallet Tab - Balances list</v>
       </c>
       <c r="B227" t="str">
         <v/>
       </c>
-      <c r="C227" s="19" t="str">
+      <c r="C227" s="21" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D227" s="6" t="str">
-        <v>Home:Balances&amp; Graph</v>
+        <v>WalletTabTotalValueGraph</v>
       </c>
       <c r="E227" t="str">
         <v/>
       </c>
-      <c r="F227" s="8">
-        <v>46076</v>
-      </c>
-      <c r="G227" s="8">
-        <v>46076</v>
+      <c r="F227" t="str">
+        <v/>
+      </c>
+      <c r="G227" t="str">
+        <v/>
       </c>
       <c r="H227" t="str">
         <v/>
@@ -10747,10 +10717,10 @@
         <v/>
       </c>
       <c r="J227" s="6" t="str">
-        <v/>
+        <v>Adi</v>
       </c>
       <c r="K227" s="6" t="str">
-        <v>Inbal Escholi</v>
+        <v/>
       </c>
       <c r="L227" s="6" t="str">
         <v/>
@@ -10762,7 +10732,7 @@
         <v/>
       </c>
       <c r="O227" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1zjptd0Ar2VSiDWkXRLTOFCR4pUHOZSJH</v>
+        <v>https://drive.google.com/drive/u/0/folders/10j0uo11-TGKBFj82pUueB78g_uihED_F</v>
       </c>
       <c r="P227" s="6" t="str">
         <v>Balance</v>
@@ -10771,7 +10741,7 @@
         <v/>
       </c>
       <c r="R227" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
+        <v>Ilan Tatar Jan 28, 2026 6:16 PM</v>
       </c>
       <c r="S227" t="str">
         <v/>
@@ -10785,279 +10755,279 @@
     </row>
     <row r="228" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="str">
+        <v>Watchlist: Balance breakdown display</v>
+      </c>
+      <c r="B228" t="str">
+        <v/>
+      </c>
+      <c r="C228" s="21" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D228" s="6" t="str">
+        <v>Home:Balances&amp; Graph</v>
+      </c>
+      <c r="E228" t="str">
+        <v/>
+      </c>
+      <c r="F228" s="8">
+        <v>46076</v>
+      </c>
+      <c r="G228" s="8">
+        <v>46076</v>
+      </c>
+      <c r="H228" t="str">
+        <v/>
+      </c>
+      <c r="I228" t="str">
+        <v/>
+      </c>
+      <c r="J228" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K228" s="6" t="str">
+        <v>Inbal Escholi</v>
+      </c>
+      <c r="L228" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M228" s="6">
+        <v>-1</v>
+      </c>
+      <c r="N228" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O228" s="6" t="str">
+        <v>https://drive.google.com/drive/u/0/folders/1zjptd0Ar2VSiDWkXRLTOFCR4pUHOZSJH</v>
+      </c>
+      <c r="P228" s="6" t="str">
+        <v>Balance</v>
+      </c>
+      <c r="Q228" t="str">
+        <v/>
+      </c>
+      <c r="R228" s="6" t="str">
+        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
+      </c>
+      <c r="S228" t="str">
+        <v/>
+      </c>
+      <c r="T228" t="str">
+        <v/>
+      </c>
+      <c r="U228" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="229" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="str">
         <v>Payment Client Technical gaps for aftr launch</v>
       </c>
-      <c r="B228" t="str">
-        <v/>
-      </c>
-      <c r="C228" s="21" t="str">
+      <c r="B229" t="str">
+        <v/>
+      </c>
+      <c r="C229" s="22" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D228" t="str">
-        <v/>
-      </c>
-      <c r="E228" t="str">
-        <v/>
-      </c>
-      <c r="F228" t="str">
-        <v/>
-      </c>
-      <c r="G228" t="str">
-        <v/>
-      </c>
-      <c r="H228" t="str">
-        <v/>
-      </c>
-      <c r="I228" t="str">
-        <v/>
-      </c>
-      <c r="J228" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K228" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L228" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M228" t="str">
-        <v/>
-      </c>
-      <c r="N228" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O228" t="str">
-        <v/>
-      </c>
-      <c r="P228" t="str">
-        <v/>
-      </c>
-      <c r="Q228" t="str">
-        <v/>
-      </c>
-      <c r="R228" s="6" t="str">
+      <c r="D229" t="str">
+        <v/>
+      </c>
+      <c r="E229" t="str">
+        <v/>
+      </c>
+      <c r="F229" t="str">
+        <v/>
+      </c>
+      <c r="G229" t="str">
+        <v/>
+      </c>
+      <c r="H229" t="str">
+        <v/>
+      </c>
+      <c r="I229" t="str">
+        <v/>
+      </c>
+      <c r="J229" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K229" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L229" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M229" t="str">
+        <v/>
+      </c>
+      <c r="N229" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O229" t="str">
+        <v/>
+      </c>
+      <c r="P229" t="str">
+        <v/>
+      </c>
+      <c r="Q229" t="str">
+        <v/>
+      </c>
+      <c r="R229" s="6" t="str">
         <v>Ilan Tatar Apr 12, 2026 12:56 PM</v>
       </c>
-      <c r="S228" t="str">
-        <v/>
-      </c>
-      <c r="T228" t="str">
-        <v/>
-      </c>
-      <c r="U228" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="229" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A229" t="str">
-        <v/>
-      </c>
-      <c r="B229" t="str">
-        <v/>
-      </c>
-      <c r="C229" t="str">
-        <v/>
-      </c>
-      <c r="D229" t="str">
-        <v/>
-      </c>
-      <c r="E229" t="str">
-        <v/>
-      </c>
-      <c r="F229" s="26">
+      <c r="S229" t="str">
+        <v/>
+      </c>
+      <c r="T229" t="str">
+        <v/>
+      </c>
+      <c r="U229" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="230" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A230" t="str">
+        <v/>
+      </c>
+      <c r="B230" t="str">
+        <v/>
+      </c>
+      <c r="C230" t="str">
+        <v/>
+      </c>
+      <c r="D230" t="str">
+        <v/>
+      </c>
+      <c r="E230" t="str">
+        <v/>
+      </c>
+      <c r="F230" s="26">
         <v>46061</v>
       </c>
-      <c r="G229" s="26">
+      <c r="G230" s="26">
         <v>46132</v>
       </c>
-      <c r="H229" t="str">
-        <v/>
-      </c>
-      <c r="I229" t="str">
-        <v/>
-      </c>
-      <c r="J229" t="str">
-        <v/>
-      </c>
-      <c r="K229" t="str">
-        <v/>
-      </c>
-      <c r="L229" t="str">
-        <v/>
-      </c>
-      <c r="M229" s="27">
+      <c r="H230" t="str">
+        <v/>
+      </c>
+      <c r="I230" t="str">
+        <v/>
+      </c>
+      <c r="J230" t="str">
+        <v/>
+      </c>
+      <c r="K230" t="str">
+        <v/>
+      </c>
+      <c r="L230" t="str">
+        <v/>
+      </c>
+      <c r="M230" s="27">
         <v>1292</v>
       </c>
-      <c r="N229" t="str">
-        <v/>
-      </c>
-      <c r="O229" t="str">
-        <v/>
-      </c>
-      <c r="P229" t="str">
-        <v/>
-      </c>
-      <c r="Q229" s="28" t="str">
+      <c r="N230" t="str">
+        <v/>
+      </c>
+      <c r="O230" t="str">
+        <v/>
+      </c>
+      <c r="P230" t="str">
+        <v/>
+      </c>
+      <c r="Q230" s="28" t="str">
         <v>2026-03-02</v>
       </c>
-      <c r="R229" t="str">
-        <v/>
-      </c>
-      <c r="S229" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T229" s="29" t="str">
-        <v/>
-      </c>
-      <c r="U229" s="29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="230" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A231" s="34" t="str">
+      <c r="R230" t="str">
+        <v/>
+      </c>
+      <c r="S230" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T230" s="29" t="str">
+        <v/>
+      </c>
+      <c r="U230" s="29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="34" t="str">
         <v>Program Milestones</v>
       </c>
     </row>
-    <row r="232" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A232" s="3" t="str">
+    <row r="233" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A233" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B232" s="3" t="str">
+      <c r="B233" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C232" s="3" t="str">
+      <c r="C233" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D232" s="3" t="str">
+      <c r="D233" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E232" s="3" t="str">
+      <c r="E233" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F232" s="3" t="str">
+      <c r="F233" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G232" s="3" t="str">
+      <c r="G233" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H232" s="3" t="str">
+      <c r="H233" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I232" s="3" t="str">
+      <c r="I233" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J232" s="3" t="str">
+      <c r="J233" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K232" s="3" t="str">
+      <c r="K233" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L232" s="3" t="str">
+      <c r="L233" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M232" s="3" t="str">
+      <c r="M233" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N232" s="3" t="str">
+      <c r="N233" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O232" s="3" t="str">
+      <c r="O233" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P232" s="3" t="str">
+      <c r="P233" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q232" s="3" t="str">
+      <c r="Q233" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R232" s="3" t="str">
+      <c r="R233" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S232" s="3" t="str">
+      <c r="S233" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T232" s="3" t="str">
+      <c r="T233" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U232" s="3" t="str">
+      <c r="U233" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="233" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A233" s="4" t="str">
-        <v>STD + Swaggers</v>
-      </c>
-      <c r="B233" t="str">
-        <v/>
-      </c>
-      <c r="C233" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="D233" t="str">
-        <v/>
-      </c>
-      <c r="E233" t="str">
-        <v/>
-      </c>
-      <c r="F233" s="8">
-        <v>46048</v>
-      </c>
-      <c r="G233" s="8">
-        <v>46048</v>
-      </c>
-      <c r="H233" t="str">
-        <v/>
-      </c>
-      <c r="I233" t="str">
-        <v/>
-      </c>
-      <c r="J233" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K233" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L233" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M233" t="str">
-        <v/>
-      </c>
-      <c r="N233" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O233" t="str">
-        <v/>
-      </c>
-      <c r="P233" t="str">
-        <v/>
-      </c>
-      <c r="Q233" t="str">
-        <v/>
-      </c>
-      <c r="R233" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:19 PM</v>
-      </c>
-      <c r="S233" t="str">
-        <v/>
-      </c>
-      <c r="T233" t="str">
-        <v/>
-      </c>
-      <c r="U233" t="str">
-        <v/>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="str">
-        <v>Critical APIs in production</v>
+        <v>STD + Swaggers</v>
       </c>
       <c r="B234" t="str">
         <v/>
       </c>
-      <c r="C234" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C234" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D234" t="str">
         <v/>
@@ -11066,10 +11036,10 @@
         <v/>
       </c>
       <c r="F234" s="8">
-        <v>46112</v>
+        <v>46048</v>
       </c>
       <c r="G234" s="8">
-        <v>46127</v>
+        <v>46048</v>
       </c>
       <c r="H234" t="str">
         <v/>
@@ -11102,7 +11072,7 @@
         <v/>
       </c>
       <c r="R234" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:15 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:19 PM</v>
       </c>
       <c r="S234" t="str">
         <v/>
@@ -11116,7 +11086,7 @@
     </row>
     <row r="235" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="str">
-        <v>Non critical APIs in prodcution</v>
+        <v>Critical APIs in production</v>
       </c>
       <c r="B235" t="str">
         <v/>
@@ -11131,11 +11101,11 @@
         <v/>
       </c>
       <c r="F235" s="8">
+        <v>46112</v>
+      </c>
+      <c r="G235" s="8">
         <v>46127</v>
       </c>
-      <c r="G235" s="8">
-        <v>46142</v>
-      </c>
       <c r="H235" t="str">
         <v/>
       </c>
@@ -11167,7 +11137,7 @@
         <v/>
       </c>
       <c r="R235" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:15 PM</v>
       </c>
       <c r="S235" t="str">
         <v/>
@@ -11181,13 +11151,13 @@
     </row>
     <row r="236" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="str">
-        <v>E2E readiness</v>
+        <v>Non critical APIs in prodcution</v>
       </c>
       <c r="B236" t="str">
         <v/>
       </c>
-      <c r="C236" s="18" t="str">
-        <v>Not Started</v>
+      <c r="C236" s="5" t="str">
+        <v>FE DEV WIP</v>
       </c>
       <c r="D236" t="str">
         <v/>
@@ -11196,16 +11166,16 @@
         <v/>
       </c>
       <c r="F236" s="8">
-        <v>46145</v>
+        <v>46127</v>
       </c>
       <c r="G236" s="8">
-        <v>46145</v>
+        <v>46142</v>
       </c>
       <c r="H236" t="str">
         <v/>
       </c>
-      <c r="I236" s="6" t="str">
-        <v>E2E to start in Mid May + 1.5 weeks buffer</v>
+      <c r="I236" t="str">
+        <v/>
       </c>
       <c r="J236" s="6" t="str">
         <v/>
@@ -11246,13 +11216,13 @@
     </row>
     <row r="237" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="str">
-        <v>Drop 1 Super- 20.4</v>
+        <v>E2E readiness</v>
       </c>
       <c r="B237" t="str">
         <v/>
       </c>
-      <c r="C237" s="16" t="str">
-        <v>Deployment</v>
+      <c r="C237" s="18" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D237" t="str">
         <v/>
@@ -11260,17 +11230,17 @@
       <c r="E237" t="str">
         <v/>
       </c>
-      <c r="F237" t="str">
-        <v/>
-      </c>
-      <c r="G237" t="str">
-        <v/>
+      <c r="F237" s="8">
+        <v>46145</v>
+      </c>
+      <c r="G237" s="8">
+        <v>46145</v>
       </c>
       <c r="H237" t="str">
         <v/>
       </c>
-      <c r="I237" t="str">
-        <v/>
+      <c r="I237" s="6" t="str">
+        <v>E2E to start in Mid May + 1.5 weeks buffer</v>
       </c>
       <c r="J237" s="6" t="str">
         <v/>
@@ -11297,7 +11267,7 @@
         <v/>
       </c>
       <c r="R237" s="6" t="str">
-        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
       </c>
       <c r="S237" t="str">
         <v/>
@@ -11311,13 +11281,13 @@
     </row>
     <row r="238" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="str">
-        <v>Drop 2 - Super 4.5</v>
+        <v>Drop 1 Super- 20.4</v>
       </c>
       <c r="B238" t="str">
         <v/>
       </c>
-      <c r="C238" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C238" s="14" t="str">
+        <v>Deployment</v>
       </c>
       <c r="D238" t="str">
         <v/>
@@ -11376,7 +11346,7 @@
     </row>
     <row r="239" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="str">
-        <v>Drop 3 Super - 18.5</v>
+        <v>Drop 2 - Super 4.5</v>
       </c>
       <c r="B239" t="str">
         <v/>
@@ -11441,13 +11411,13 @@
     </row>
     <row r="240" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="str">
-        <v>Drop 4- Super - 1.6</v>
+        <v>Drop 3 Super - 18.5</v>
       </c>
       <c r="B240" t="str">
         <v/>
       </c>
-      <c r="C240" s="14" t="str">
-        <v>Discovery</v>
+      <c r="C240" s="5" t="str">
+        <v>FE DEV WIP</v>
       </c>
       <c r="D240" t="str">
         <v/>
@@ -11505,14 +11475,14 @@
       </c>
     </row>
     <row r="241" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A241" t="str">
-        <v/>
+      <c r="A241" s="4" t="str">
+        <v>Drop 4- Super - 1.6</v>
       </c>
       <c r="B241" t="str">
         <v/>
       </c>
-      <c r="C241" t="str">
-        <v/>
+      <c r="C241" s="15" t="str">
+        <v>Discovery</v>
       </c>
       <c r="D241" t="str">
         <v/>
@@ -11520,200 +11490,200 @@
       <c r="E241" t="str">
         <v/>
       </c>
-      <c r="F241" s="26">
+      <c r="F241" t="str">
+        <v/>
+      </c>
+      <c r="G241" t="str">
+        <v/>
+      </c>
+      <c r="H241" t="str">
+        <v/>
+      </c>
+      <c r="I241" t="str">
+        <v/>
+      </c>
+      <c r="J241" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K241" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L241" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M241" t="str">
+        <v/>
+      </c>
+      <c r="N241" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O241" t="str">
+        <v/>
+      </c>
+      <c r="P241" t="str">
+        <v/>
+      </c>
+      <c r="Q241" t="str">
+        <v/>
+      </c>
+      <c r="R241" s="6" t="str">
+        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+      </c>
+      <c r="S241" t="str">
+        <v/>
+      </c>
+      <c r="T241" t="str">
+        <v/>
+      </c>
+      <c r="U241" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="242" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A242" t="str">
+        <v/>
+      </c>
+      <c r="B242" t="str">
+        <v/>
+      </c>
+      <c r="C242" t="str">
+        <v/>
+      </c>
+      <c r="D242" t="str">
+        <v/>
+      </c>
+      <c r="E242" t="str">
+        <v/>
+      </c>
+      <c r="F242" s="26">
         <v>46048</v>
       </c>
-      <c r="G241" s="26">
+      <c r="G242" s="26">
         <v>46145</v>
       </c>
-      <c r="H241" t="str">
-        <v/>
-      </c>
-      <c r="I241" t="str">
-        <v/>
-      </c>
-      <c r="J241" t="str">
-        <v/>
-      </c>
-      <c r="K241" t="str">
-        <v/>
-      </c>
-      <c r="L241" t="str">
-        <v/>
-      </c>
-      <c r="M241" s="27">
+      <c r="H242" t="str">
+        <v/>
+      </c>
+      <c r="I242" t="str">
+        <v/>
+      </c>
+      <c r="J242" t="str">
+        <v/>
+      </c>
+      <c r="K242" t="str">
+        <v/>
+      </c>
+      <c r="L242" t="str">
+        <v/>
+      </c>
+      <c r="M242" s="27">
         <v>0</v>
       </c>
-      <c r="N241" t="str">
-        <v/>
-      </c>
-      <c r="O241" t="str">
-        <v/>
-      </c>
-      <c r="P241" t="str">
-        <v/>
-      </c>
-      <c r="Q241" s="29" t="str">
-        <v/>
-      </c>
-      <c r="R241" t="str">
-        <v/>
-      </c>
-      <c r="S241" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T241" s="29" t="str">
-        <v/>
-      </c>
-      <c r="U241" s="29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="242" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A243" s="30" t="str">
+      <c r="N242" t="str">
+        <v/>
+      </c>
+      <c r="O242" t="str">
+        <v/>
+      </c>
+      <c r="P242" t="str">
+        <v/>
+      </c>
+      <c r="Q242" s="29" t="str">
+        <v/>
+      </c>
+      <c r="R242" t="str">
+        <v/>
+      </c>
+      <c r="S242" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T242" s="29" t="str">
+        <v/>
+      </c>
+      <c r="U242" s="29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="243" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" s="30" t="str">
         <v>Dependencies</v>
       </c>
     </row>
-    <row r="244" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A244" s="3" t="str">
+    <row r="245" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A245" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B244" s="3" t="str">
+      <c r="B245" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C244" s="3" t="str">
+      <c r="C245" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D244" s="3" t="str">
+      <c r="D245" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E244" s="3" t="str">
+      <c r="E245" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F244" s="3" t="str">
+      <c r="F245" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G244" s="3" t="str">
+      <c r="G245" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H244" s="3" t="str">
+      <c r="H245" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I244" s="3" t="str">
+      <c r="I245" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J244" s="3" t="str">
+      <c r="J245" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K244" s="3" t="str">
+      <c r="K245" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L244" s="3" t="str">
+      <c r="L245" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M244" s="3" t="str">
+      <c r="M245" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N244" s="3" t="str">
+      <c r="N245" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O244" s="3" t="str">
+      <c r="O245" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P244" s="3" t="str">
+      <c r="P245" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q244" s="3" t="str">
+      <c r="Q245" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R244" s="3" t="str">
+      <c r="R245" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S244" s="3" t="str">
+      <c r="S245" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T244" s="3" t="str">
+      <c r="T245" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U244" s="3" t="str">
+      <c r="U245" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="245" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A245" s="4" t="str">
-        <v>trading real time equity API</v>
-      </c>
-      <c r="B245" t="str">
-        <v/>
-      </c>
-      <c r="C245" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="D245" t="str">
-        <v/>
-      </c>
-      <c r="E245" t="str">
-        <v/>
-      </c>
-      <c r="F245" t="str">
-        <v/>
-      </c>
-      <c r="G245" t="str">
-        <v/>
-      </c>
-      <c r="H245" t="str">
-        <v/>
-      </c>
-      <c r="I245" t="str">
-        <v/>
-      </c>
-      <c r="J245" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K245" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L245" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M245" t="str">
-        <v/>
-      </c>
-      <c r="N245" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O245" t="str">
-        <v/>
-      </c>
-      <c r="P245" t="str">
-        <v/>
-      </c>
-      <c r="Q245" t="str">
-        <v/>
-      </c>
-      <c r="R245" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 11:31 AM</v>
-      </c>
-      <c r="S245" t="str">
-        <v/>
-      </c>
-      <c r="T245" t="str">
-        <v/>
-      </c>
-      <c r="U245" t="str">
-        <v/>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="str">
-        <v>trading BE orch</v>
+        <v>trading real time equity API</v>
       </c>
       <c r="B246" t="str">
         <v/>
       </c>
-      <c r="C246" s="19" t="str">
-        <v>Cancelled</v>
+      <c r="C246" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D246" t="str">
         <v/>
@@ -11758,7 +11728,7 @@
         <v/>
       </c>
       <c r="R246" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 11:50 AM</v>
+        <v>Ilan Tatar Jan 25, 2026 11:31 AM</v>
       </c>
       <c r="S246" t="str">
         <v/>
@@ -11772,135 +11742,200 @@
     </row>
     <row r="247" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="B247" t="str">
+        <v/>
+      </c>
+      <c r="C247" s="21" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D247" t="str">
+        <v/>
+      </c>
+      <c r="E247" t="str">
+        <v/>
+      </c>
+      <c r="F247" t="str">
+        <v/>
+      </c>
+      <c r="G247" t="str">
+        <v/>
+      </c>
+      <c r="H247" t="str">
+        <v/>
+      </c>
+      <c r="I247" t="str">
+        <v/>
+      </c>
+      <c r="J247" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K247" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L247" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M247" t="str">
+        <v/>
+      </c>
+      <c r="N247" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O247" t="str">
+        <v/>
+      </c>
+      <c r="P247" t="str">
+        <v/>
+      </c>
+      <c r="Q247" t="str">
+        <v/>
+      </c>
+      <c r="R247" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 11:50 AM</v>
+      </c>
+      <c r="S247" t="str">
+        <v/>
+      </c>
+      <c r="T247" t="str">
+        <v/>
+      </c>
+      <c r="U247" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="248" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A248" s="4" t="str">
         <v>Banking deposit MOP</v>
       </c>
-      <c r="B247" t="str">
-        <v/>
-      </c>
-      <c r="C247" s="11" t="str">
+      <c r="B248" t="str">
+        <v/>
+      </c>
+      <c r="C248" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D247" t="str">
-        <v/>
-      </c>
-      <c r="E247" t="str">
-        <v/>
-      </c>
-      <c r="F247" t="str">
-        <v/>
-      </c>
-      <c r="G247" t="str">
-        <v/>
-      </c>
-      <c r="H247" t="str">
-        <v/>
-      </c>
-      <c r="I247" t="str">
-        <v/>
-      </c>
-      <c r="J247" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K247" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L247" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M247" t="str">
-        <v/>
-      </c>
-      <c r="N247" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O247" t="str">
-        <v/>
-      </c>
-      <c r="P247" t="str">
-        <v/>
-      </c>
-      <c r="Q247" t="str">
-        <v/>
-      </c>
-      <c r="R247" s="6" t="str">
+      <c r="D248" t="str">
+        <v/>
+      </c>
+      <c r="E248" t="str">
+        <v/>
+      </c>
+      <c r="F248" t="str">
+        <v/>
+      </c>
+      <c r="G248" t="str">
+        <v/>
+      </c>
+      <c r="H248" t="str">
+        <v/>
+      </c>
+      <c r="I248" t="str">
+        <v/>
+      </c>
+      <c r="J248" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K248" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L248" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M248" t="str">
+        <v/>
+      </c>
+      <c r="N248" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O248" t="str">
+        <v/>
+      </c>
+      <c r="P248" t="str">
+        <v/>
+      </c>
+      <c r="Q248" t="str">
+        <v/>
+      </c>
+      <c r="R248" s="6" t="str">
         <v>Hagit Zamir Feb 5, 2026 4:03 PM</v>
       </c>
-      <c r="S247" t="str">
-        <v/>
-      </c>
-      <c r="T247" t="str">
-        <v/>
-      </c>
-      <c r="U247" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="248" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A248" t="str">
-        <v/>
-      </c>
-      <c r="B248" t="str">
-        <v/>
-      </c>
-      <c r="C248" t="str">
-        <v/>
-      </c>
-      <c r="D248" t="str">
-        <v/>
-      </c>
-      <c r="E248" t="str">
-        <v/>
-      </c>
-      <c r="F248" s="29" t="str">
-        <v/>
-      </c>
-      <c r="G248" s="29" t="str">
-        <v/>
-      </c>
-      <c r="H248" t="str">
-        <v/>
-      </c>
-      <c r="I248" t="str">
-        <v/>
-      </c>
-      <c r="J248" t="str">
-        <v/>
-      </c>
-      <c r="K248" t="str">
-        <v/>
-      </c>
-      <c r="L248" t="str">
-        <v/>
-      </c>
-      <c r="M248" s="27">
+      <c r="S248" t="str">
+        <v/>
+      </c>
+      <c r="T248" t="str">
+        <v/>
+      </c>
+      <c r="U248" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="249" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A249" t="str">
+        <v/>
+      </c>
+      <c r="B249" t="str">
+        <v/>
+      </c>
+      <c r="C249" t="str">
+        <v/>
+      </c>
+      <c r="D249" t="str">
+        <v/>
+      </c>
+      <c r="E249" t="str">
+        <v/>
+      </c>
+      <c r="F249" s="29" t="str">
+        <v/>
+      </c>
+      <c r="G249" s="29" t="str">
+        <v/>
+      </c>
+      <c r="H249" t="str">
+        <v/>
+      </c>
+      <c r="I249" t="str">
+        <v/>
+      </c>
+      <c r="J249" t="str">
+        <v/>
+      </c>
+      <c r="K249" t="str">
+        <v/>
+      </c>
+      <c r="L249" t="str">
+        <v/>
+      </c>
+      <c r="M249" s="27">
         <v>0</v>
       </c>
-      <c r="N248" t="str">
-        <v/>
-      </c>
-      <c r="O248" t="str">
-        <v/>
-      </c>
-      <c r="P248" t="str">
-        <v/>
-      </c>
-      <c r="Q248" s="29" t="str">
-        <v/>
-      </c>
-      <c r="R248" t="str">
-        <v/>
-      </c>
-      <c r="S248" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T248" s="29" t="str">
-        <v/>
-      </c>
-      <c r="U248" s="29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="249" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="N249" t="str">
+        <v/>
+      </c>
+      <c r="O249" t="str">
+        <v/>
+      </c>
+      <c r="P249" t="str">
+        <v/>
+      </c>
+      <c r="Q249" s="29" t="str">
+        <v/>
+      </c>
+      <c r="R249" t="str">
+        <v/>
+      </c>
+      <c r="S249" s="29" t="str">
+        <v/>
+      </c>
+      <c r="T249" s="29" t="str">
+        <v/>
+      </c>
+      <c r="U249" s="29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -64,7 +64,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -108,12 +108,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF007F"/>
+        <fgColor rgb="FF579BFC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF579BFC"/>
+        <fgColor rgb="FFBB3354"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,7 +123,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAA1F1"/>
+        <fgColor rgb="FFFF007F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,17 +138,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF784BD1"/>
+        <fgColor rgb="FFFAA1F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF333333"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB3354"/>
+        <fgColor rgb="FF757575"/>
       </patternFill>
     </fill>
     <fill>
@@ -153,17 +153,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF757575"/>
+        <fgColor rgb="FF784BD1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7F5347"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCB00"/>
       </patternFill>
     </fill>
     <fill>
@@ -184,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -256,9 +251,6 @@
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -272,7 +264,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -748,7 +740,7 @@
         <v/>
       </c>
       <c r="O4" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1m1m1ZpJRg4bCHNU3XfJDXf948FfYcD0r</v>
+        <v/>
       </c>
       <c r="P4" s="6" t="str">
         <v>Banking</v>
@@ -1161,8 +1153,8 @@
       <c r="B16" t="str">
         <v/>
       </c>
-      <c r="C16" s="14" t="str">
-        <v>Deployment</v>
+      <c r="C16" s="13" t="str">
+        <v>In QA</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -1198,7 +1190,7 @@
         <v/>
       </c>
       <c r="O16" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1ED6Vd2DwAz4Cj5zAQ2-3ztab-vL9UGKF</v>
+        <v/>
       </c>
       <c r="P16" s="6" t="str">
         <v>Payments</v>
@@ -1539,7 +1531,7 @@
       <c r="C25" t="str">
         <v/>
       </c>
-      <c r="D25" s="15" t="str">
+      <c r="D25" s="14" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E25" s="6" t="str">
@@ -1574,7 +1566,7 @@
       <c r="C26" t="str">
         <v/>
       </c>
-      <c r="D26" s="15" t="str">
+      <c r="D26" s="14" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E26" s="6" t="str">
@@ -1671,8 +1663,8 @@
       <c r="B28" t="str">
         <v/>
       </c>
-      <c r="C28" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C28" s="15" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -1736,7 +1728,7 @@
       <c r="B29" t="str">
         <v/>
       </c>
-      <c r="C29" s="15" t="str">
+      <c r="C29" s="14" t="str">
         <v>Discovery</v>
       </c>
       <c r="D29" s="6" t="str">
@@ -1773,7 +1765,7 @@
         <v/>
       </c>
       <c r="O29" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1UETTI0WZBBzUrvcjSjBuiqSvDiZW_Yuv</v>
+        <v/>
       </c>
       <c r="P29" s="6" t="str">
         <v>Deposit, Payments</v>
@@ -1834,13 +1826,13 @@
         <v/>
       </c>
       <c r="B31" s="4" t="str">
-        <v>Deposit - Credit Card - Complex task -FTD</v>
+        <v>Deposit - Wire IBAN - Simple task</v>
       </c>
       <c r="C31" s="6" t="str">
-        <v>Noit Hoffman</v>
-      </c>
-      <c r="D31" s="16" t="str">
-        <v>QA</v>
+        <v>Joanna Fajga</v>
+      </c>
+      <c r="D31" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E31" s="6" t="str">
         <v/>
@@ -1852,10 +1844,10 @@
         <v/>
       </c>
       <c r="H31" s="8">
-        <v>46061</v>
+        <v>46134</v>
       </c>
       <c r="I31" s="8">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1869,13 +1861,13 @@
         <v/>
       </c>
       <c r="B32" s="4" t="str">
-        <v>Deposit - Wire IBAN - Simple task</v>
+        <v>Deposit - Credit Card - Complex task -FTD</v>
       </c>
       <c r="C32" s="6" t="str">
-        <v>Joanna Fajga</v>
-      </c>
-      <c r="D32" s="14" t="str">
-        <v>Groomed</v>
+        <v>Noit Hoffman</v>
+      </c>
+      <c r="D32" s="16" t="str">
+        <v>QA</v>
       </c>
       <c r="E32" s="6" t="str">
         <v/>
@@ -1886,11 +1878,11 @@
       <c r="G32" t="str">
         <v/>
       </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32" t="str">
-        <v/>
+      <c r="H32" s="8">
+        <v>46061</v>
+      </c>
+      <c r="I32" s="8">
+        <v>46149</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1909,7 +1901,7 @@
       <c r="C33" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D33" s="14" t="str">
+      <c r="D33" s="17" t="str">
         <v>Groomed</v>
       </c>
       <c r="E33" s="6" t="str">
@@ -1944,7 +1936,7 @@
       <c r="C34" s="6" t="str">
         <v>Noit Hoffman, Joanna Fajga</v>
       </c>
-      <c r="D34" s="14" t="str">
+      <c r="D34" s="17" t="str">
         <v>Groomed</v>
       </c>
       <c r="E34" s="6" t="str">
@@ -1979,8 +1971,8 @@
       <c r="C35" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D35" s="5" t="str">
-        <v>Dev - WIP</v>
+      <c r="D35" s="16" t="str">
+        <v>QA</v>
       </c>
       <c r="E35" s="6" t="str">
         <v/>
@@ -1995,7 +1987,7 @@
         <v>46061</v>
       </c>
       <c r="I35" s="8">
-        <v>46135</v>
+        <v>46147</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -2289,19 +2281,19 @@
         <v/>
       </c>
       <c r="B44" s="4" t="str">
-        <v>Flow - Deposit Wizard FTD</v>
-      </c>
-      <c r="C44" s="6" t="str">
-        <v>Noit Hoffman</v>
-      </c>
-      <c r="D44" s="17" t="str">
-        <v>Cancelled</v>
+        <v>Deposit- BFF</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E44" s="6" t="str">
         <v/>
       </c>
-      <c r="F44" t="str">
-        <v/>
+      <c r="F44" s="6" t="str">
+        <v>V3(18.5)</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2315,8 +2307,8 @@
       <c r="J44" t="str">
         <v/>
       </c>
-      <c r="K44" s="6">
-        <v>1</v>
+      <c r="K44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2324,34 +2316,34 @@
         <v/>
       </c>
       <c r="B45" s="4" t="str">
-        <v>Flow - Deposit Wizard - Redepositor</v>
+        <v>Deposit Paypal Redeposit</v>
       </c>
       <c r="C45" s="6" t="str">
-        <v>Noit Hoffman</v>
-      </c>
-      <c r="D45" s="17" t="str">
-        <v>Cancelled</v>
+        <v>Joanna Fajga</v>
+      </c>
+      <c r="D45" s="18" t="str">
+        <v>Grooming</v>
       </c>
       <c r="E45" s="6" t="str">
         <v/>
       </c>
-      <c r="F45" t="str">
-        <v/>
+      <c r="F45" s="6" t="str">
+        <v>V3(18.5)</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
-      <c r="H45" t="str">
-        <v/>
-      </c>
-      <c r="I45" t="str">
-        <v/>
+      <c r="H45" s="8">
+        <v>46146</v>
+      </c>
+      <c r="I45" s="8">
+        <v>46146</v>
       </c>
       <c r="J45" t="str">
         <v/>
       </c>
-      <c r="K45" s="6">
-        <v>1</v>
+      <c r="K45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2359,19 +2351,19 @@
         <v/>
       </c>
       <c r="B46" s="4" t="str">
-        <v>Flow - Deposit - Account selection</v>
+        <v>Deposit Credit Card Redeposit</v>
       </c>
       <c r="C46" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D46" s="17" t="str">
-        <v>Cancelled</v>
+      <c r="D46" s="18" t="str">
+        <v>Grooming</v>
       </c>
       <c r="E46" s="6" t="str">
         <v/>
       </c>
-      <c r="F46" t="str">
-        <v/>
+      <c r="F46" s="6" t="str">
+        <v>V3(18.5)</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2394,19 +2386,19 @@
         <v/>
       </c>
       <c r="B47" s="4" t="str">
-        <v>Deposit- BFF</v>
+        <v>Deposit Open Banking redeposit</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
-      <c r="D47" s="5" t="str">
-        <v>Dev - WIP</v>
+      <c r="D47" s="19" t="str">
+        <v>Not Started</v>
       </c>
       <c r="E47" s="6" t="str">
         <v/>
       </c>
-      <c r="F47" t="str">
-        <v/>
+      <c r="F47" s="6" t="str">
+        <v>V3(18.5)</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2429,13 +2421,13 @@
         <v/>
       </c>
       <c r="B48" s="4" t="str">
-        <v>Deposit Paypal Redeposit</v>
+        <v>Flow - Deposit Wizard - Redepositor</v>
       </c>
       <c r="C48" s="6" t="str">
-        <v>Joanna Fajga</v>
-      </c>
-      <c r="D48" s="18" t="str">
-        <v>Not Started</v>
+        <v>Noit Hoffman</v>
+      </c>
+      <c r="D48" s="20" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="E48" s="6" t="str">
         <v/>
@@ -2455,8 +2447,8 @@
       <c r="J48" t="str">
         <v/>
       </c>
-      <c r="K48" t="str">
-        <v/>
+      <c r="K48" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2464,13 +2456,13 @@
         <v/>
       </c>
       <c r="B49" s="4" t="str">
-        <v>Deposit Credit Card Redeposit</v>
+        <v>Flow - Deposit Wizard FTD</v>
       </c>
       <c r="C49" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D49" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D49" s="20" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="E49" s="6" t="str">
         <v/>
@@ -2490,8 +2482,8 @@
       <c r="J49" t="str">
         <v/>
       </c>
-      <c r="K49" t="str">
-        <v/>
+      <c r="K49" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2499,13 +2491,13 @@
         <v/>
       </c>
       <c r="B50" s="4" t="str">
-        <v>Open Banking redeposit</v>
-      </c>
-      <c r="C50" t="str">
-        <v/>
-      </c>
-      <c r="D50" s="18" t="str">
-        <v>Not Started</v>
+        <v>Flow - Deposit - Account selection</v>
+      </c>
+      <c r="C50" s="6" t="str">
+        <v>Noit Hoffman</v>
+      </c>
+      <c r="D50" s="20" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="E50" s="6" t="str">
         <v/>
@@ -2536,8 +2528,8 @@
       <c r="B51" t="str">
         <v/>
       </c>
-      <c r="C51" s="15" t="str">
-        <v>Discovery</v>
+      <c r="C51" s="21" t="str">
+        <v>Groomed</v>
       </c>
       <c r="D51" t="str">
         <v/>
@@ -2545,11 +2537,11 @@
       <c r="E51" t="str">
         <v/>
       </c>
-      <c r="F51" t="str">
-        <v/>
-      </c>
-      <c r="G51" t="str">
-        <v/>
+      <c r="F51" s="8">
+        <v>46145</v>
+      </c>
+      <c r="G51" s="8">
+        <v>46160</v>
       </c>
       <c r="H51" s="6" t="str">
         <v>V3(18.5)</v>
@@ -2639,8 +2631,8 @@
       <c r="C53" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D53" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D53" s="17" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E53" s="6" t="str">
         <v/>
@@ -2674,8 +2666,8 @@
       <c r="C54" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D54" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D54" s="17" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E54" s="6" t="str">
         <v/>
@@ -2709,8 +2701,8 @@
       <c r="C55" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D55" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D55" s="17" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E55" s="6" t="str">
         <v/>
@@ -2744,8 +2736,8 @@
       <c r="C56" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D56" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D56" s="17" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E56" s="6" t="str">
         <v/>
@@ -2779,8 +2771,8 @@
       <c r="C57" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D57" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D57" s="17" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E57" s="6" t="str">
         <v/>
@@ -2814,8 +2806,8 @@
       <c r="C58" t="str">
         <v/>
       </c>
-      <c r="D58" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D58" s="22" t="str">
+        <v>OnHold</v>
       </c>
       <c r="E58" s="6" t="str">
         <v/>
@@ -2844,12 +2836,12 @@
         <v/>
       </c>
       <c r="B59" s="4" t="str">
-        <v>Deposit flow for Desktop - Joanna is teh product</v>
+        <v>Deposit flow for Desktop - Joanna is the product</v>
       </c>
       <c r="C59" t="str">
         <v/>
       </c>
-      <c r="D59" s="19" t="str">
+      <c r="D59" s="23" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E59" s="6" t="str">
@@ -2881,7 +2873,7 @@
       <c r="B60" t="str">
         <v/>
       </c>
-      <c r="C60" s="18" t="str">
+      <c r="C60" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="D60" s="6" t="str">
@@ -2918,7 +2910,7 @@
         <v/>
       </c>
       <c r="O60" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1FWXRnhi0O2SFFPPtZkGZJ0lrDmfD8ElO</v>
+        <v/>
       </c>
       <c r="P60" s="6" t="str">
         <v>Banking</v>
@@ -2984,7 +2976,7 @@
       <c r="C62" t="str">
         <v/>
       </c>
-      <c r="D62" s="18" t="str">
+      <c r="D62" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E62" s="6" t="str">
@@ -3019,7 +3011,7 @@
       <c r="C63" t="str">
         <v/>
       </c>
-      <c r="D63" s="18" t="str">
+      <c r="D63" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E63" s="6" t="str">
@@ -3054,7 +3046,7 @@
       <c r="C64" t="str">
         <v/>
       </c>
-      <c r="D64" s="18" t="str">
+      <c r="D64" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E64" s="6" t="str">
@@ -3123,7 +3115,7 @@
         <v/>
       </c>
       <c r="O65" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1TUMyoZElqh662CF76uU0K3UJY0bomFzx</v>
+        <v/>
       </c>
       <c r="P65" s="6" t="str">
         <v>Crypto</v>
@@ -3294,8 +3286,8 @@
       <c r="C70" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D70" s="5" t="str">
-        <v>Dev - WIP</v>
+      <c r="D70" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E70" s="6" t="str">
         <v/>
@@ -3324,28 +3316,28 @@
         <v/>
       </c>
       <c r="B71" s="4" t="str">
-        <v>Custodial wallet crypto - Gaps infrastructure- Not travel rule</v>
+        <v>Custodial wallet crypto - Gaps - travel Rule recieve</v>
       </c>
       <c r="C71" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D71" s="14" t="str">
+      <c r="D71" s="17" t="str">
         <v>Groomed</v>
       </c>
       <c r="E71" s="6" t="str">
         <v/>
       </c>
       <c r="F71" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V2(4.5)</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" s="8">
+        <v>46132</v>
+      </c>
+      <c r="I71" s="8">
         <v>46146</v>
-      </c>
-      <c r="I71" s="8">
-        <v>46160</v>
       </c>
       <c r="J71" s="7">
         <v>46105</v>
@@ -3359,28 +3351,28 @@
         <v/>
       </c>
       <c r="B72" s="4" t="str">
-        <v>Custodial wallet crypto - Gaps - travel Rule recieve</v>
+        <v>Custodial wallet crypto - Gaps infrastructure- Not travel rule</v>
       </c>
       <c r="C72" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D72" s="14" t="str">
+      <c r="D72" s="17" t="str">
         <v>Groomed</v>
       </c>
       <c r="E72" s="6" t="str">
         <v/>
       </c>
       <c r="F72" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V3(18.5)</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" s="8">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="I72" s="8">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="J72" s="7">
         <v>46105</v>
@@ -3399,7 +3391,7 @@
       <c r="C73" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D73" s="14" t="str">
+      <c r="D73" s="17" t="str">
         <v>Groomed</v>
       </c>
       <c r="E73" s="6" t="str">
@@ -3429,13 +3421,13 @@
         <v/>
       </c>
       <c r="B74" s="4" t="str">
-        <v>Custodial wallet crypto - Receive -General</v>
+        <v>Custodial wallet crypto - Send</v>
       </c>
       <c r="C74" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D74" s="20" t="str">
-        <v>Grooming</v>
+      <c r="D74" s="17" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E74" s="6" t="str">
         <v/>
@@ -3464,12 +3456,12 @@
         <v/>
       </c>
       <c r="B75" s="4" t="str">
-        <v>Custodial wallet crypto - Send</v>
+        <v>Custodial wallet crypto - Send (with travel rule) CASP/Self Hosted</v>
       </c>
       <c r="C75" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D75" s="14" t="str">
+      <c r="D75" s="17" t="str">
         <v>Groomed</v>
       </c>
       <c r="E75" s="6" t="str">
@@ -3504,7 +3496,7 @@
       <c r="C76" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D76" s="21" t="str">
+      <c r="D76" s="15" t="str">
         <v>Design</v>
       </c>
       <c r="E76" s="6" t="str">
@@ -3534,13 +3526,13 @@
         <v/>
       </c>
       <c r="B77" s="4" t="str">
-        <v>Custodial wallet crypto - Send (with travel rule) CASP/Self Hosted</v>
+        <v>Portfolio - Crypto redeem</v>
       </c>
       <c r="C77" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D77" s="14" t="str">
-        <v>Groomed</v>
+      <c r="D77" s="15" t="str">
+        <v>Design</v>
       </c>
       <c r="E77" s="6" t="str">
         <v/>
@@ -3558,145 +3550,145 @@
         <v>46160</v>
       </c>
       <c r="J77" s="7">
-        <v>46106</v>
+        <v>46142</v>
       </c>
       <c r="K77" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" t="str">
-        <v/>
-      </c>
-      <c r="B78" s="4" t="str">
-        <v>Portfolio - Crypto redeem</v>
-      </c>
-      <c r="C78" s="6" t="str">
-        <v>Nikolaus Kulier</v>
-      </c>
-      <c r="D78" s="21" t="str">
-        <v>Design</v>
-      </c>
-      <c r="E78" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F78" s="6" t="str">
+    <row r="78" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="str">
+        <v>IBAN - Send Payment- Withdraw from IBAN</v>
+      </c>
+      <c r="B78" t="str">
+        <v/>
+      </c>
+      <c r="C78" s="13" t="str">
+        <v>In QA</v>
+      </c>
+      <c r="D78" s="6" t="str">
+        <v>sendPayment</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" s="8">
+        <v>46138</v>
+      </c>
+      <c r="G78" s="8">
+        <v>46150</v>
+      </c>
+      <c r="H78" s="6" t="str">
         <v>V3(18.5)</v>
       </c>
-      <c r="G78" t="str">
-        <v/>
-      </c>
-      <c r="H78" s="8">
-        <v>46146</v>
-      </c>
-      <c r="I78" s="8">
-        <v>46160</v>
-      </c>
-      <c r="J78" s="7">
-        <v>46142</v>
-      </c>
-      <c r="K78" s="6">
+      <c r="I78" s="6" t="str">
+        <v>Send Payment - GBP / EUR / AUD / DKK Payment Schemes</v>
+      </c>
+      <c r="J78" s="6" t="str">
+        <v>Adi</v>
+      </c>
+      <c r="K78" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L78" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M78" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="str">
-        <v>IBAN - Send Payment- Withdraw from IBAN</v>
-      </c>
-      <c r="B79" t="str">
-        <v/>
-      </c>
-      <c r="C79" s="5" t="str">
-        <v>FE DEV WIP</v>
-      </c>
-      <c r="D79" s="6" t="str">
-        <v>sendPayment</v>
-      </c>
-      <c r="E79" t="str">
-        <v/>
-      </c>
-      <c r="F79" s="8">
-        <v>46117</v>
-      </c>
-      <c r="G79" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H79" s="6" t="str">
-        <v>V3(18.5)</v>
-      </c>
-      <c r="I79" s="6" t="str">
-        <v>Send Payment - GBP / EUR / AUD / DKK Payment Schemes</v>
-      </c>
-      <c r="J79" s="6" t="str">
-        <v>Adi</v>
-      </c>
-      <c r="K79" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L79" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M79" s="6">
-        <v>2</v>
-      </c>
-      <c r="N79" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O79" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1cqLfzkkJdYpR8bVF73xOU89anuVCub81</v>
-      </c>
-      <c r="P79" s="6" t="str">
+      <c r="N78" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O78" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P78" s="6" t="str">
         <v>Banking, Deposit</v>
       </c>
-      <c r="Q79" s="7">
+      <c r="Q78" s="7">
         <v>46086</v>
       </c>
-      <c r="R79" s="6" t="str">
+      <c r="R78" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
-      <c r="S79" t="str">
-        <v/>
-      </c>
-      <c r="T79" t="str">
-        <v/>
-      </c>
-      <c r="U79" t="str">
-        <v/>
+      <c r="S78" t="str">
+        <v/>
+      </c>
+      <c r="T78" t="str">
+        <v/>
+      </c>
+      <c r="U78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="9" t="str">
+        <v>Subitems</v>
+      </c>
+      <c r="B79" s="10" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C79" s="10" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="D79" s="10" t="str">
+        <v>Status</v>
+      </c>
+      <c r="E79" s="10" t="str">
+        <v>JIRA</v>
+      </c>
+      <c r="F79" s="10" t="str">
+        <v>Drop</v>
+      </c>
+      <c r="G79" s="10" t="str">
+        <v>Team</v>
+      </c>
+      <c r="H79" s="10" t="str">
+        <v>Timeline - Start</v>
+      </c>
+      <c r="I79" s="10" t="str">
+        <v>Timeline - End</v>
+      </c>
+      <c r="J79" s="10" t="str">
+        <v>Groom Readiness Date</v>
+      </c>
+      <c r="K79" s="10" t="str">
+        <v>Priority</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="9" t="str">
-        <v>Subitems</v>
-      </c>
-      <c r="B80" s="10" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C80" s="10" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="D80" s="10" t="str">
-        <v>Status</v>
-      </c>
-      <c r="E80" s="10" t="str">
-        <v>JIRA</v>
-      </c>
-      <c r="F80" s="10" t="str">
-        <v>Drop</v>
-      </c>
-      <c r="G80" s="10" t="str">
-        <v>Team</v>
-      </c>
-      <c r="H80" s="10" t="str">
-        <v>Timeline - Start</v>
-      </c>
-      <c r="I80" s="10" t="str">
-        <v>Timeline - End</v>
-      </c>
-      <c r="J80" s="10" t="str">
-        <v>Groom Readiness Date</v>
-      </c>
-      <c r="K80" s="10" t="str">
-        <v>Priority</v>
+      <c r="A80" t="str">
+        <v/>
+      </c>
+      <c r="B80" s="4" t="str">
+        <v>Payee List and empty state</v>
+      </c>
+      <c r="C80" s="6" t="str">
+        <v>Joanna Fajga</v>
+      </c>
+      <c r="D80" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="E80" s="6" t="str">
+        <v>https://etoro-jira.atlassian.net/browse/PM-207</v>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v/>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3704,7 +3696,7 @@
         <v/>
       </c>
       <c r="B81" s="4" t="str">
-        <v>Payee List and empty state</v>
+        <v>Payee Details View/Delete</v>
       </c>
       <c r="C81" s="6" t="str">
         <v>Joanna Fajga</v>
@@ -3713,7 +3705,7 @@
         <v>Done</v>
       </c>
       <c r="E81" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-207</v>
+        <v>https://etoro-jira.atlassian.net/browse/PM-209</v>
       </c>
       <c r="F81" t="str">
         <v/>
@@ -3739,7 +3731,7 @@
         <v/>
       </c>
       <c r="B82" s="4" t="str">
-        <v>Payee Details View/Delete</v>
+        <v>Amend / Create a Payee</v>
       </c>
       <c r="C82" s="6" t="str">
         <v>Joanna Fajga</v>
@@ -3748,7 +3740,7 @@
         <v>Done</v>
       </c>
       <c r="E82" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-209</v>
+        <v>https://etoro-jira.atlassian.net/browse/PM-214</v>
       </c>
       <c r="F82" t="str">
         <v/>
@@ -3756,11 +3748,11 @@
       <c r="G82" t="str">
         <v/>
       </c>
-      <c r="H82" t="str">
-        <v/>
-      </c>
-      <c r="I82" t="str">
-        <v/>
+      <c r="H82" s="8">
+        <v>46117</v>
+      </c>
+      <c r="I82" s="8">
+        <v>46132</v>
       </c>
       <c r="J82" t="str">
         <v/>
@@ -3774,7 +3766,7 @@
         <v/>
       </c>
       <c r="B83" s="4" t="str">
-        <v>Amend / Create a Payee</v>
+        <v>Verification of Payees - Error state / Mismatch</v>
       </c>
       <c r="C83" s="6" t="str">
         <v>Joanna Fajga</v>
@@ -3783,7 +3775,7 @@
         <v>Done</v>
       </c>
       <c r="E83" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-214</v>
+        <v>https://etoro-jira.atlassian.net/browse/PM-215</v>
       </c>
       <c r="F83" t="str">
         <v/>
@@ -3800,8 +3792,8 @@
       <c r="J83" t="str">
         <v/>
       </c>
-      <c r="K83" t="str">
-        <v/>
+      <c r="K83" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3809,7 +3801,7 @@
         <v/>
       </c>
       <c r="B84" s="4" t="str">
-        <v>Verification of Payees - Error state / Mismatch</v>
+        <v>Send Payment - GBP / EUR / AUD / DKK Payment Schemes</v>
       </c>
       <c r="C84" s="6" t="str">
         <v>Joanna Fajga</v>
@@ -3818,7 +3810,7 @@
         <v>Done</v>
       </c>
       <c r="E84" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-215</v>
+        <v>https://etoro-jira.atlassian.net/browse/PM-211</v>
       </c>
       <c r="F84" t="str">
         <v/>
@@ -3826,11 +3818,11 @@
       <c r="G84" t="str">
         <v/>
       </c>
-      <c r="H84" s="8">
-        <v>46117</v>
-      </c>
-      <c r="I84" s="8">
-        <v>46132</v>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v/>
       </c>
       <c r="J84" t="str">
         <v/>
@@ -3844,16 +3836,16 @@
         <v/>
       </c>
       <c r="B85" s="4" t="str">
-        <v>IBAN Restricted State</v>
-      </c>
-      <c r="C85" s="6" t="str">
-        <v>Joanna Fajga</v>
-      </c>
-      <c r="D85" s="13" t="str">
-        <v>Discovery</v>
+        <v>QA - E2E</v>
+      </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85" s="19" t="str">
+        <v>Not Started</v>
       </c>
       <c r="E85" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-226</v>
+        <v/>
       </c>
       <c r="F85" t="str">
         <v/>
@@ -3879,16 +3871,16 @@
         <v/>
       </c>
       <c r="B86" s="4" t="str">
-        <v>Send Payment - GBP / EUR / AUD / DKK Payment Schemes</v>
-      </c>
-      <c r="C86" s="6" t="str">
-        <v>Joanna Fajga</v>
-      </c>
-      <c r="D86" s="11" t="str">
-        <v>Done</v>
+        <v>IBAN- Send Payment- BFF for WD from IBAN- Ron/Amichay Kafka</v>
+      </c>
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86" s="23" t="str">
+        <v>futureVersion</v>
       </c>
       <c r="E86" s="6" t="str">
-        <v>https://etoro-jira.atlassian.net/browse/PM-211</v>
+        <v/>
       </c>
       <c r="F86" t="str">
         <v/>
@@ -3914,13 +3906,13 @@
         <v/>
       </c>
       <c r="B87" s="4" t="str">
-        <v>Send Payment - Error Handling / Mapping</v>
-      </c>
-      <c r="C87" s="6" t="str">
-        <v>Joanna Fajga</v>
+        <v>Send Payment - Confirmation of Payee UK-</v>
+      </c>
+      <c r="C87" t="str">
+        <v/>
       </c>
       <c r="D87" s="20" t="str">
-        <v>Grooming</v>
+        <v>Cancelled</v>
       </c>
       <c r="E87" s="6" t="str">
         <v/>
@@ -3941,7 +3933,7 @@
         <v/>
       </c>
       <c r="K87" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3954,8 +3946,8 @@
       <c r="C88" t="str">
         <v/>
       </c>
-      <c r="D88" s="22" t="str">
-        <v>OnHold</v>
+      <c r="D88" s="20" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="E88" s="6" t="str">
         <v/>
@@ -3984,13 +3976,13 @@
         <v/>
       </c>
       <c r="B89" s="4" t="str">
-        <v>QA - E2E</v>
+        <v>Send Payment - Verification of Payee EU</v>
       </c>
       <c r="C89" t="str">
         <v/>
       </c>
-      <c r="D89" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D89" s="20" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="E89" s="6" t="str">
         <v/>
@@ -4010,8 +4002,8 @@
       <c r="J89" t="str">
         <v/>
       </c>
-      <c r="K89" t="str">
-        <v/>
+      <c r="K89" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -4019,13 +4011,13 @@
         <v/>
       </c>
       <c r="B90" s="4" t="str">
-        <v>IBAN- Send Payment- BFF for WD from IBAN- Ron/Amichay Kafka</v>
+        <v>Send Payment - Confirmation of Payee AU</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
-      <c r="D90" s="19" t="str">
-        <v>futureVersion</v>
+      <c r="D90" s="20" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="E90" s="6" t="str">
         <v/>
@@ -4046,7 +4038,7 @@
         <v/>
       </c>
       <c r="K90" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -4054,12 +4046,12 @@
         <v/>
       </c>
       <c r="B91" s="4" t="str">
-        <v>Send Payment - Confirmation of Payee UK-</v>
-      </c>
-      <c r="C91" t="str">
-        <v/>
-      </c>
-      <c r="D91" s="17" t="str">
+        <v>Send Payment - Error Handling / Mapping</v>
+      </c>
+      <c r="C91" s="6" t="str">
+        <v>Joanna Fajga</v>
+      </c>
+      <c r="D91" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E91" s="6" t="str">
@@ -4081,7 +4073,7 @@
         <v/>
       </c>
       <c r="K91" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -4089,13 +4081,13 @@
         <v/>
       </c>
       <c r="B92" s="4" t="str">
-        <v>Send Payment - Verification of Payee EU</v>
+        <v>Send Payment- 2FA</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
-      <c r="D92" s="17" t="str">
-        <v>Cancelled</v>
+      <c r="D92" s="14" t="str">
+        <v>Handle by other team</v>
       </c>
       <c r="E92" s="6" t="str">
         <v/>
@@ -4124,16 +4116,16 @@
         <v/>
       </c>
       <c r="B93" s="4" t="str">
-        <v>Send Payment - Confirmation of Payee AU</v>
-      </c>
-      <c r="C93" t="str">
-        <v/>
-      </c>
-      <c r="D93" s="17" t="str">
+        <v>IBAN Restricted State</v>
+      </c>
+      <c r="C93" s="6" t="str">
+        <v>Joanna Fajga</v>
+      </c>
+      <c r="D93" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E93" s="6" t="str">
-        <v/>
+        <v>https://etoro-jira.atlassian.net/browse/PM-226</v>
       </c>
       <c r="F93" t="str">
         <v/>
@@ -4150,143 +4142,143 @@
       <c r="J93" t="str">
         <v/>
       </c>
-      <c r="K93" s="6">
+      <c r="K93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="str">
+        <v>Withdraw USD</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" s="16" t="str">
+        <v>Grooming</v>
+      </c>
+      <c r="D94" s="6" t="str">
+        <v>withdrawWizard</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" s="8">
+        <v>46070</v>
+      </c>
+      <c r="G94" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H94" s="6" t="str">
+        <v>V3(18.5)</v>
+      </c>
+      <c r="I94" s="6" t="str">
+        <v>BFF</v>
+      </c>
+      <c r="J94" s="6" t="str">
+        <v>Shimi</v>
+      </c>
+      <c r="K94" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L94" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M94" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="94" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" t="str">
-        <v/>
-      </c>
-      <c r="B94" s="4" t="str">
-        <v>Send Payment- 2FA</v>
-      </c>
-      <c r="C94" t="str">
-        <v/>
-      </c>
-      <c r="D94" s="15" t="str">
-        <v>Handle by other team</v>
-      </c>
-      <c r="E94" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F94" t="str">
-        <v/>
-      </c>
-      <c r="G94" t="str">
-        <v/>
-      </c>
-      <c r="H94" t="str">
-        <v/>
-      </c>
-      <c r="I94" t="str">
-        <v/>
-      </c>
-      <c r="J94" t="str">
-        <v/>
-      </c>
-      <c r="K94" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="str">
-        <v>Withdraw USD</v>
-      </c>
-      <c r="B95" t="str">
-        <v/>
-      </c>
-      <c r="C95" s="5" t="str">
-        <v>FE DEV WIP</v>
-      </c>
-      <c r="D95" s="6" t="str">
-        <v>withdrawWizard</v>
-      </c>
-      <c r="E95" t="str">
-        <v/>
-      </c>
-      <c r="F95" s="8">
-        <v>46070</v>
-      </c>
-      <c r="G95" s="8">
-        <v>46134</v>
-      </c>
-      <c r="H95" s="6" t="str">
-        <v>V3(18.5)</v>
-      </c>
-      <c r="I95" s="6" t="str">
-        <v>BFF</v>
-      </c>
-      <c r="J95" s="6" t="str">
-        <v>Shimi</v>
-      </c>
-      <c r="K95" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L95" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M95" s="6">
-        <v>2</v>
-      </c>
-      <c r="N95" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O95" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/13rvXTFCTXPLR9rSBFXqDGB5Jldv5kH6m</v>
-      </c>
-      <c r="P95" s="6" t="str">
+      <c r="N94" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O94" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P94" s="6" t="str">
         <v>Withdraw</v>
       </c>
-      <c r="Q95" s="7">
+      <c r="Q94" s="7">
         <v>46098</v>
       </c>
-      <c r="R95" s="6" t="str">
+      <c r="R94" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
-      <c r="S95" t="str">
-        <v/>
-      </c>
-      <c r="T95" s="8">
+      <c r="S94" t="str">
+        <v/>
+      </c>
+      <c r="T94" s="8">
         <v>46089</v>
       </c>
-      <c r="U95" s="8">
+      <c r="U94" s="8">
         <v>46089</v>
       </c>
     </row>
+    <row r="95" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="9" t="str">
+        <v>Subitems</v>
+      </c>
+      <c r="B95" s="10" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C95" s="10" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="D95" s="10" t="str">
+        <v>Status</v>
+      </c>
+      <c r="E95" s="10" t="str">
+        <v>JIRA</v>
+      </c>
+      <c r="F95" s="10" t="str">
+        <v>Drop</v>
+      </c>
+      <c r="G95" s="10" t="str">
+        <v>Team</v>
+      </c>
+      <c r="H95" s="10" t="str">
+        <v>Timeline - Start</v>
+      </c>
+      <c r="I95" s="10" t="str">
+        <v>Timeline - End</v>
+      </c>
+      <c r="J95" s="10" t="str">
+        <v>Groom Readiness Date</v>
+      </c>
+      <c r="K95" s="10" t="str">
+        <v>Priority</v>
+      </c>
+    </row>
     <row r="96" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="9" t="str">
-        <v>Subitems</v>
-      </c>
-      <c r="B96" s="10" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C96" s="10" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="D96" s="10" t="str">
-        <v>Status</v>
-      </c>
-      <c r="E96" s="10" t="str">
-        <v>JIRA</v>
-      </c>
-      <c r="F96" s="10" t="str">
-        <v>Drop</v>
-      </c>
-      <c r="G96" s="10" t="str">
-        <v>Team</v>
-      </c>
-      <c r="H96" s="10" t="str">
-        <v>Timeline - Start</v>
-      </c>
-      <c r="I96" s="10" t="str">
-        <v>Timeline - End</v>
-      </c>
-      <c r="J96" s="10" t="str">
-        <v>Groom Readiness Date</v>
-      </c>
-      <c r="K96" s="10" t="str">
-        <v>Priority</v>
+      <c r="A96" t="str">
+        <v/>
+      </c>
+      <c r="B96" s="4" t="str">
+        <v>BFF for WD to USD- Merab</v>
+      </c>
+      <c r="C96" t="str">
+        <v/>
+      </c>
+      <c r="D96" s="18" t="str">
+        <v>Grooming</v>
+      </c>
+      <c r="E96" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v/>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -4294,13 +4286,13 @@
         <v/>
       </c>
       <c r="B97" s="4" t="str">
-        <v>BFF for WD to USD- Merab</v>
+        <v>Product requirements readiness- Shimi</v>
       </c>
       <c r="C97" t="str">
         <v/>
       </c>
-      <c r="D97" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D97" s="18" t="str">
+        <v>Grooming</v>
       </c>
       <c r="E97" s="6" t="str">
         <v/>
@@ -4311,11 +4303,11 @@
       <c r="G97" t="str">
         <v/>
       </c>
-      <c r="H97" t="str">
-        <v/>
-      </c>
-      <c r="I97" t="str">
-        <v/>
+      <c r="H97" s="8">
+        <v>46071</v>
+      </c>
+      <c r="I97" s="8">
+        <v>46089</v>
       </c>
       <c r="J97" t="str">
         <v/>
@@ -4329,13 +4321,13 @@
         <v/>
       </c>
       <c r="B98" s="4" t="str">
-        <v>Product requirements readiness- Shimi</v>
+        <v>Withdraw Blocked- Generic solution for Dep/WD</v>
       </c>
       <c r="C98" t="str">
         <v/>
       </c>
-      <c r="D98" s="20" t="str">
-        <v>Grooming</v>
+      <c r="D98" s="19" t="str">
+        <v>Not Started</v>
       </c>
       <c r="E98" s="6" t="str">
         <v/>
@@ -4346,11 +4338,11 @@
       <c r="G98" t="str">
         <v/>
       </c>
-      <c r="H98" s="8">
-        <v>46071</v>
-      </c>
-      <c r="I98" s="8">
-        <v>46089</v>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
       </c>
       <c r="J98" t="str">
         <v/>
@@ -4364,13 +4356,13 @@
         <v/>
       </c>
       <c r="B99" s="4" t="str">
-        <v>Withdraw Blocked- Generic solution for Dep/WD</v>
+        <v>FE effort</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99" s="18" t="str">
-        <v>Not Started</v>
+        <v>Grooming</v>
       </c>
       <c r="E99" s="6" t="str">
         <v/>
@@ -4401,8 +4393,8 @@
       <c r="B100" t="str">
         <v/>
       </c>
-      <c r="C100" s="23" t="str">
-        <v>Groomed</v>
+      <c r="C100" s="5" t="str">
+        <v>FE DEV WIP</v>
       </c>
       <c r="D100" s="6" t="str">
         <v>iBanManageCard</v>
@@ -4414,7 +4406,7 @@
         <v>46061</v>
       </c>
       <c r="G100" s="8">
-        <v>46075</v>
+        <v>46154</v>
       </c>
       <c r="H100" s="6" t="str">
         <v>V2(4.5)</v>
@@ -4438,7 +4430,7 @@
         <v/>
       </c>
       <c r="O100" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1mLvTPp1jkHGRDPftaLG6VX3L6-KSChBM</v>
+        <v/>
       </c>
       <c r="P100" s="6" t="str">
         <v>Banking, Card Mng.</v>
@@ -4539,7 +4531,7 @@
       <c r="C103" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D103" s="14" t="str">
+      <c r="D103" s="17" t="str">
         <v>Groomed</v>
       </c>
       <c r="E103" s="6" t="str">
@@ -4574,7 +4566,7 @@
       <c r="C104" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D104" s="14" t="str">
+      <c r="D104" s="17" t="str">
         <v>Groomed</v>
       </c>
       <c r="E104" s="6" t="str">
@@ -4609,7 +4601,7 @@
       <c r="C105" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D105" s="14" t="str">
+      <c r="D105" s="17" t="str">
         <v>Groomed</v>
       </c>
       <c r="E105" s="6" t="str">
@@ -4644,7 +4636,7 @@
       <c r="C106" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D106" s="14" t="str">
+      <c r="D106" s="17" t="str">
         <v>Groomed</v>
       </c>
       <c r="E106" s="6" t="str">
@@ -4679,8 +4671,8 @@
       <c r="C107" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D107" s="20" t="str">
-        <v>Grooming</v>
+      <c r="D107" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E107" s="6" t="str">
         <v/>
@@ -4714,8 +4706,8 @@
       <c r="C108" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D108" s="20" t="str">
-        <v>Grooming</v>
+      <c r="D108" s="17" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E108" s="6" t="str">
         <v/>
@@ -4749,8 +4741,8 @@
       <c r="C109" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D109" s="20" t="str">
-        <v>Grooming</v>
+      <c r="D109" s="17" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E109" s="6" t="str">
         <v/>
@@ -4784,8 +4776,8 @@
       <c r="C110" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D110" s="20" t="str">
-        <v>Grooming</v>
+      <c r="D110" s="17" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E110" s="6" t="str">
         <v/>
@@ -4814,13 +4806,13 @@
         <v/>
       </c>
       <c r="B111" s="4" t="str">
-        <v>Manage Card - Club Upgrades for Card Program</v>
+        <v>Manage Card - Apple Wallet touchpoint- The button to trigger the addition</v>
       </c>
       <c r="C111" s="6" t="str">
-        <v>Richard Whitehouse</v>
-      </c>
-      <c r="D111" s="13" t="str">
-        <v>Discovery</v>
+        <v>Richard Whitehouse, Inbal Escholi</v>
+      </c>
+      <c r="D111" s="17" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E111" s="6" t="str">
         <v/>
@@ -4849,13 +4841,13 @@
         <v/>
       </c>
       <c r="B112" s="4" t="str">
-        <v>Manage Card - Apple Wallet touchpoint- The button to trigger the addition</v>
+        <v>Manage Card - Google Wallet Manual Provision</v>
       </c>
       <c r="C112" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
       <c r="D112" s="20" t="str">
-        <v>Grooming</v>
+        <v>Cancelled</v>
       </c>
       <c r="E112" s="6" t="str">
         <v/>
@@ -4884,13 +4876,13 @@
         <v/>
       </c>
       <c r="B113" s="4" t="str">
-        <v>Manage Card - Google Wallet Manual Provision</v>
+        <v>Manage Card - Club Upgrades for Card Program</v>
       </c>
       <c r="C113" s="6" t="str">
-        <v>Richard Whitehouse, Inbal Escholi</v>
-      </c>
-      <c r="D113" s="17" t="str">
-        <v>Cancelled</v>
+        <v>Richard Whitehouse</v>
+      </c>
+      <c r="D113" s="23" t="str">
+        <v>futureVersion</v>
       </c>
       <c r="E113" s="6" t="str">
         <v/>
@@ -4916,7 +4908,7 @@
     </row>
     <row r="114" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="str">
-        <v>Card Management 3DS Flow</v>
+        <v>Card Management 3DS Flow- test</v>
       </c>
       <c r="B114" t="str">
         <v/>
@@ -4930,11 +4922,11 @@
       <c r="E114" t="str">
         <v/>
       </c>
-      <c r="F114" t="str">
-        <v/>
-      </c>
-      <c r="G114" t="str">
-        <v/>
+      <c r="F114" s="8">
+        <v>46154</v>
+      </c>
+      <c r="G114" s="8">
+        <v>46160</v>
       </c>
       <c r="H114" s="6" t="str">
         <v>V3(18.5)</v>
@@ -5089,8 +5081,8 @@
       <c r="C117" t="str">
         <v/>
       </c>
-      <c r="D117" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D117" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E117" s="6" t="str">
         <v/>
@@ -5124,8 +5116,8 @@
       <c r="C118" t="str">
         <v/>
       </c>
-      <c r="D118" s="18" t="str">
-        <v>Not Started</v>
+      <c r="D118" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E118" s="6" t="str">
         <v/>
@@ -5151,16 +5143,16 @@
     </row>
     <row r="119" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="str">
-        <v>Wallet tab - total value graph- Total Value Rolloup- Desktop</v>
+        <v>Account statement - Fees statement</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
-      <c r="C119" s="18" t="str">
-        <v>Not Started</v>
+      <c r="C119" s="14" t="str">
+        <v>Discovery</v>
       </c>
       <c r="D119" s="6" t="str">
-        <v>WalletTabTotalValueGraph</v>
+        <v>acctStatement</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -5174,11 +5166,11 @@
       <c r="H119" s="6" t="str">
         <v>V4(1.6)</v>
       </c>
-      <c r="I119" s="6" t="str">
-        <v>OOS - Wallet Tab - Balance Display - Total Value Rollup-</v>
+      <c r="I119" t="str">
+        <v/>
       </c>
       <c r="J119" s="6" t="str">
-        <v>Adi</v>
+        <v>Richard</v>
       </c>
       <c r="K119" s="6" t="str">
         <v/>
@@ -5187,19 +5179,19 @@
         <v/>
       </c>
       <c r="M119" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N119" s="6" t="str">
         <v/>
       </c>
       <c r="O119" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1FWMl54Cw95y4XBFRvgY-5TTl0MXk8IbT</v>
+        <v/>
       </c>
       <c r="P119" s="6" t="str">
-        <v>Balance</v>
+        <v>Banking</v>
       </c>
       <c r="Q119" s="7">
-        <v>46127</v>
+        <v>46104</v>
       </c>
       <c r="R119" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
@@ -5207,25 +5199,25 @@
       <c r="S119" t="str">
         <v/>
       </c>
-      <c r="T119" t="str">
-        <v/>
-      </c>
-      <c r="U119" t="str">
-        <v/>
+      <c r="T119" s="8">
+        <v>46104</v>
+      </c>
+      <c r="U119" s="8">
+        <v>46104</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="str">
-        <v>Settings</v>
+        <v>Wallet tab - total value graph- Total Value Rolloup- Desktop</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" s="19" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D120" t="str">
-        <v/>
+        <v>Not Started</v>
+      </c>
+      <c r="D120" s="6" t="str">
+        <v>WalletTabTotalValueGraph</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -5237,13 +5229,13 @@
         <v/>
       </c>
       <c r="H120" s="6" t="str">
-        <v>V3(18.5)</v>
-      </c>
-      <c r="I120" t="str">
-        <v/>
+        <v>V4(1.6)</v>
+      </c>
+      <c r="I120" s="6" t="str">
+        <v>OOS - Wallet Tab - Balance Display - Total Value Rollup-</v>
       </c>
       <c r="J120" s="6" t="str">
-        <v>Noit</v>
+        <v>Adi</v>
       </c>
       <c r="K120" s="6" t="str">
         <v/>
@@ -5257,96 +5249,126 @@
       <c r="N120" s="6" t="str">
         <v/>
       </c>
-      <c r="O120" t="str">
+      <c r="O120" s="6" t="str">
         <v/>
       </c>
       <c r="P120" s="6" t="str">
-        <v>Payments, Settings</v>
+        <v>Balance</v>
       </c>
       <c r="Q120" s="7">
         <v>46127</v>
       </c>
       <c r="R120" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S120" t="str">
+        <v/>
+      </c>
+      <c r="T120" t="str">
+        <v/>
+      </c>
+      <c r="U120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="B121" t="str">
+        <v/>
+      </c>
+      <c r="C121" s="23" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D121" t="str">
+        <v/>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" s="6" t="str">
+        <v>V3(18.5)</v>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" s="6" t="str">
+        <v>Noit</v>
+      </c>
+      <c r="K121" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L121" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M121" s="6">
+        <v>3</v>
+      </c>
+      <c r="N121" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" s="6" t="str">
+        <v>Payments, Settings</v>
+      </c>
+      <c r="Q121" s="7">
+        <v>46127</v>
+      </c>
+      <c r="R121" s="6" t="str">
         <v>Hagit Zamir Feb 5, 2026 4:10 PM</v>
       </c>
-      <c r="S120" t="str">
-        <v/>
-      </c>
-      <c r="T120" t="str">
-        <v/>
-      </c>
-      <c r="U120" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="9" t="str">
+      <c r="S121" t="str">
+        <v/>
+      </c>
+      <c r="T121" t="str">
+        <v/>
+      </c>
+      <c r="U121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B121" s="10" t="str">
+      <c r="B122" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C121" s="10" t="str">
+      <c r="C122" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D121" s="10" t="str">
+      <c r="D122" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E121" s="10" t="str">
+      <c r="E122" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F121" s="10" t="str">
+      <c r="F122" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G121" s="10" t="str">
+      <c r="G122" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H121" s="10" t="str">
+      <c r="H122" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I121" s="10" t="str">
+      <c r="I122" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J121" s="10" t="str">
+      <c r="J122" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K121" s="10" t="str">
+      <c r="K122" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" t="str">
-        <v/>
-      </c>
-      <c r="B122" s="4" t="str">
-        <v>Settings: Default currency for LC</v>
-      </c>
-      <c r="C122" t="str">
-        <v/>
-      </c>
-      <c r="D122" s="15" t="str">
-        <v>Handle by other team</v>
-      </c>
-      <c r="E122" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F122" t="str">
-        <v/>
-      </c>
-      <c r="G122" t="str">
-        <v/>
-      </c>
-      <c r="H122" t="str">
-        <v/>
-      </c>
-      <c r="I122" t="str">
-        <v/>
-      </c>
-      <c r="J122" t="str">
-        <v/>
-      </c>
-      <c r="K122" t="str">
-        <v/>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5354,12 +5376,12 @@
         <v/>
       </c>
       <c r="B123" s="4" t="str">
-        <v>Settings: Recurring Order, recurring deposit will be supported via link to web</v>
+        <v>Settings: Default currency for LC</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
-      <c r="D123" s="15" t="str">
+      <c r="D123" s="14" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E123" s="6" t="str">
@@ -5368,8 +5390,8 @@
       <c r="F123" t="str">
         <v/>
       </c>
-      <c r="G123" s="6" t="str">
-        <v>Payments</v>
+      <c r="G123" t="str">
+        <v/>
       </c>
       <c r="H123" t="str">
         <v/>
@@ -5389,50 +5411,50 @@
         <v/>
       </c>
       <c r="B124" s="4" t="str">
+        <v>Settings: Recurring Order, recurring deposit will be supported via link to web</v>
+      </c>
+      <c r="C124" t="str">
+        <v/>
+      </c>
+      <c r="D124" s="14" t="str">
+        <v>Handle by other team</v>
+      </c>
+      <c r="E124" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" s="6" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" t="str">
+        <v/>
+      </c>
+      <c r="B125" s="4" t="str">
         <v>Settings: Recurring Deposit flow - plan creation</v>
       </c>
-      <c r="C124" t="str">
-        <v/>
-      </c>
-      <c r="D124" s="17" t="str">
+      <c r="C125" t="str">
+        <v/>
+      </c>
+      <c r="D125" s="20" t="str">
         <v>Cancelled</v>
       </c>
-      <c r="E124" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F124" t="str">
-        <v/>
-      </c>
-      <c r="G124" t="str">
-        <v/>
-      </c>
-      <c r="H124" t="str">
-        <v/>
-      </c>
-      <c r="I124" t="str">
-        <v/>
-      </c>
-      <c r="J124" t="str">
-        <v/>
-      </c>
-      <c r="K124" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="str">
-        <v>Account statement - Fees statement</v>
-      </c>
-      <c r="B125" t="str">
-        <v/>
-      </c>
-      <c r="C125" s="15" t="str">
-        <v>Discovery</v>
-      </c>
-      <c r="D125" s="6" t="str">
-        <v>acctStatement</v>
-      </c>
-      <c r="E125" t="str">
+      <c r="E125" s="6" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
@@ -5441,47 +5463,17 @@
       <c r="G125" t="str">
         <v/>
       </c>
-      <c r="H125" s="6" t="str">
-        <v>V4(1.6)</v>
+      <c r="H125" t="str">
+        <v/>
       </c>
       <c r="I125" t="str">
         <v/>
       </c>
-      <c r="J125" s="6" t="str">
-        <v>Richard</v>
-      </c>
-      <c r="K125" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L125" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M125" s="6">
-        <v>5</v>
-      </c>
-      <c r="N125" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O125" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1e0om-xgw9NsChJPHa1NS2-VjxGJdDyH0</v>
-      </c>
-      <c r="P125" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="Q125" s="7">
-        <v>46104</v>
-      </c>
-      <c r="R125" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S125" t="str">
-        <v/>
-      </c>
-      <c r="T125" s="8">
-        <v>46104</v>
-      </c>
-      <c r="U125" s="8">
-        <v>46104</v>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v/>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -5491,8 +5483,8 @@
       <c r="B126" t="str">
         <v/>
       </c>
-      <c r="C126" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C126" s="12" t="str">
+        <v>Stuck</v>
       </c>
       <c r="D126" t="str">
         <v/>
@@ -5556,7 +5548,7 @@
       <c r="B127" t="str">
         <v/>
       </c>
-      <c r="C127" s="14" t="str">
+      <c r="C127" s="17" t="str">
         <v>Deployment</v>
       </c>
       <c r="D127" t="str">
@@ -5593,7 +5585,7 @@
         <v/>
       </c>
       <c r="O127" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1MmbR5lAYBNObxfbjaAaR0IyHvrI5RpD1</v>
+        <v/>
       </c>
       <c r="P127" s="6" t="str">
         <v>Balance</v>
@@ -5694,8 +5686,8 @@
       <c r="C130" t="str">
         <v/>
       </c>
-      <c r="D130" s="25" t="str">
-        <v>deployment</v>
+      <c r="D130" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E130" s="6" t="str">
         <v/>
@@ -5764,7 +5756,7 @@
       <c r="C132" t="str">
         <v/>
       </c>
-      <c r="D132" s="18" t="str">
+      <c r="D132" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E132" s="6" t="str">
@@ -5799,7 +5791,7 @@
       <c r="C133" t="str">
         <v/>
       </c>
-      <c r="D133" s="18" t="str">
+      <c r="D133" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E133" s="6" t="str">
@@ -5834,7 +5826,7 @@
       <c r="C134" s="6" t="str">
         <v>Eyal Boas</v>
       </c>
-      <c r="D134" s="17" t="str">
+      <c r="D134" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E134" s="6" t="str">
@@ -5869,7 +5861,7 @@
       <c r="C135" t="str">
         <v/>
       </c>
-      <c r="D135" s="17" t="str">
+      <c r="D135" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E135" s="6" t="str">
@@ -5904,7 +5896,7 @@
       <c r="C136" s="6" t="str">
         <v>Eyal Boas</v>
       </c>
-      <c r="D136" s="17" t="str">
+      <c r="D136" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E136" s="6" t="str">
@@ -5939,7 +5931,7 @@
       <c r="C137" t="str">
         <v/>
       </c>
-      <c r="D137" s="17" t="str">
+      <c r="D137" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E137" s="6" t="str">
@@ -5965,215 +5957,215 @@
       </c>
     </row>
     <row r="138" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A138" t="str">
-        <v/>
+      <c r="A138" s="4" t="str">
+        <v>Execution popup drawer</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
-      <c r="C138" t="str">
-        <v/>
-      </c>
-      <c r="D138" t="str">
-        <v/>
+      <c r="C138" s="14" t="str">
+        <v>Discovery</v>
+      </c>
+      <c r="D138" s="6" t="str">
+        <v>tradeIBAN</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
-      <c r="F138" s="26">
+      <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+      <c r="H138" s="6" t="str">
+        <v>V3(18.5)</v>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K138" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L138" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138" t="str">
+        <v/>
+      </c>
+      <c r="R138" s="6" t="str">
+        <v>Ilan Tatar Apr 27, 2026 6:21 PM</v>
+      </c>
+      <c r="S138" t="str">
+        <v/>
+      </c>
+      <c r="T138" t="str">
+        <v/>
+      </c>
+      <c r="U138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A139" t="str">
+        <v/>
+      </c>
+      <c r="B139" t="str">
+        <v/>
+      </c>
+      <c r="C139" t="str">
+        <v/>
+      </c>
+      <c r="D139" t="str">
+        <v/>
+      </c>
+      <c r="E139" t="str">
+        <v/>
+      </c>
+      <c r="F139" s="25">
         <v>46061</v>
       </c>
-      <c r="G138" s="26">
-        <v>46141</v>
-      </c>
-      <c r="H138" t="str">
-        <v/>
-      </c>
-      <c r="I138" t="str">
-        <v/>
-      </c>
-      <c r="J138" t="str">
-        <v/>
-      </c>
-      <c r="K138" t="str">
-        <v/>
-      </c>
-      <c r="L138" t="str">
-        <v/>
-      </c>
-      <c r="M138" s="27">
+      <c r="G139" s="25">
+        <v>46160</v>
+      </c>
+      <c r="H139" t="str">
+        <v/>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
+        <v/>
+      </c>
+      <c r="L139" t="str">
+        <v/>
+      </c>
+      <c r="M139" s="26">
         <v>38</v>
       </c>
-      <c r="N138" t="str">
-        <v/>
-      </c>
-      <c r="O138" t="str">
-        <v/>
-      </c>
-      <c r="P138" t="str">
-        <v/>
-      </c>
-      <c r="Q138" s="28" t="str">
+      <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139" s="27" t="str">
         <v>2026-02-02 to 2026-04-15</v>
       </c>
-      <c r="R138" t="str">
-        <v/>
-      </c>
-      <c r="S138" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T138" s="26">
+      <c r="R139" t="str">
+        <v/>
+      </c>
+      <c r="S139" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T139" s="25">
         <v>46058</v>
       </c>
-      <c r="U138" s="26">
+      <c r="U139" s="25">
         <v>46114</v>
       </c>
     </row>
-    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="30" t="str">
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="29" t="str">
         <v>In Focus</v>
       </c>
     </row>
-    <row r="141" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="str">
+    <row r="142" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B141" s="3" t="str">
+      <c r="B142" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C141" s="3" t="str">
+      <c r="C142" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D141" s="3" t="str">
+      <c r="D142" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E141" s="3" t="str">
+      <c r="E142" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F141" s="3" t="str">
+      <c r="F142" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G141" s="3" t="str">
+      <c r="G142" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H141" s="3" t="str">
+      <c r="H142" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I141" s="3" t="str">
+      <c r="I142" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J141" s="3" t="str">
+      <c r="J142" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K141" s="3" t="str">
+      <c r="K142" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L141" s="3" t="str">
+      <c r="L142" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M141" s="3" t="str">
+      <c r="M142" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N141" s="3" t="str">
+      <c r="N142" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O141" s="3" t="str">
+      <c r="O142" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P141" s="3" t="str">
+      <c r="P142" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q141" s="3" t="str">
+      <c r="Q142" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R141" s="3" t="str">
+      <c r="R142" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S141" s="3" t="str">
+      <c r="S142" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T141" s="3" t="str">
+      <c r="T142" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U141" s="3" t="str">
+      <c r="U142" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A142" s="4" t="str">
-        <v>Risk - PCI Audit for credit card deposit- Hagit to deliver details</v>
-      </c>
-      <c r="B142" t="str">
-        <v/>
-      </c>
-      <c r="C142" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="D142" t="str">
-        <v/>
-      </c>
-      <c r="E142" t="str">
-        <v/>
-      </c>
-      <c r="F142" t="str">
-        <v/>
-      </c>
-      <c r="G142" t="str">
-        <v/>
-      </c>
-      <c r="H142" t="str">
-        <v/>
-      </c>
-      <c r="I142" t="str">
-        <v/>
-      </c>
-      <c r="J142" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K142" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L142" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M142" t="str">
-        <v/>
-      </c>
-      <c r="N142" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O142" t="str">
-        <v/>
-      </c>
-      <c r="P142" t="str">
-        <v/>
-      </c>
-      <c r="Q142" t="str">
-        <v/>
-      </c>
-      <c r="R142" s="6" t="str">
-        <v>Ilan Tatar Mar 29, 2026 1:16 PM</v>
-      </c>
-      <c r="S142" t="str">
-        <v/>
-      </c>
-      <c r="T142" t="str">
-        <v/>
-      </c>
-      <c r="U142" t="str">
-        <v/>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="str">
-        <v>Sagiv- Deposit apporval rate check- in order to prioritize/remove other MOPs from scope</v>
+        <v>Risk - PCI Audit for credit card deposit- Hagit to deliver details</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
-      <c r="C143" s="15" t="str">
-        <v>Discovery</v>
+      <c r="C143" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D143" t="str">
         <v/>
@@ -6218,7 +6210,7 @@
         <v/>
       </c>
       <c r="R143" s="6" t="str">
-        <v>Ilan Tatar Mar 26, 2026 6:04 PM</v>
+        <v>Ilan Tatar Mar 29, 2026 1:16 PM</v>
       </c>
       <c r="S143" t="str">
         <v/>
@@ -6232,12 +6224,12 @@
     </row>
     <row r="144" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="str">
-        <v>Deleaniation - Compliance new requirement- to display the entity behind every balance</v>
+        <v>Sagiv- Deposit apporval rate check- in order to prioritize/remove other MOPs from scope</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
-      <c r="C144" s="15" t="str">
+      <c r="C144" s="14" t="str">
         <v>Discovery</v>
       </c>
       <c r="D144" t="str">
@@ -6283,7 +6275,7 @@
         <v/>
       </c>
       <c r="R144" s="6" t="str">
-        <v>Ilan Tatar Mar 8, 2026 2:13 PM</v>
+        <v>Ilan Tatar Mar 26, 2026 6:04 PM</v>
       </c>
       <c r="S144" t="str">
         <v/>
@@ -6297,13 +6289,13 @@
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="str">
-        <v>Withdraw risk- Work on MOP - or Deposit work is enough</v>
+        <v>Deleaniation - Compliance new requirement- to display the entity behind every balance</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
-      <c r="C145" s="31" t="str">
-        <v>Risk</v>
+      <c r="C145" s="14" t="str">
+        <v>Discovery</v>
       </c>
       <c r="D145" t="str">
         <v/>
@@ -6348,7 +6340,7 @@
         <v/>
       </c>
       <c r="R145" s="6" t="str">
-        <v>Ilan Tatar Mar 12, 2026 5:47 PM</v>
+        <v>Ilan Tatar Mar 8, 2026 2:13 PM</v>
       </c>
       <c r="S145" t="str">
         <v/>
@@ -6362,13 +6354,13 @@
     </row>
     <row r="146" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="str">
-        <v>Recurring Investment- Who will handle it in PLUS- Hodaya BE &amp; Hagit &amp; to advice</v>
+        <v>Withdraw risk- Work on MOP - or Deposit work is enough</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
-      <c r="C146" s="11" t="str">
-        <v>Done</v>
+      <c r="C146" s="30" t="str">
+        <v>Risk</v>
       </c>
       <c r="D146" t="str">
         <v/>
@@ -6413,7 +6405,7 @@
         <v/>
       </c>
       <c r="R146" s="6" t="str">
-        <v>Ilan Tatar Mar 8, 2026 2:06 PM</v>
+        <v>Ilan Tatar Mar 12, 2026 5:47 PM</v>
       </c>
       <c r="S146" t="str">
         <v/>
@@ -6427,7 +6419,7 @@
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="str">
-        <v>Main Risk : Deposit flow are waiting for ABC test for solution, develop will start Mid MArch only</v>
+        <v>Recurring Investment- Who will handle it in PLUS- Hodaya BE &amp; Hagit &amp; to advice</v>
       </c>
       <c r="B147" t="str">
         <v/>
@@ -6441,11 +6433,11 @@
       <c r="E147" t="str">
         <v/>
       </c>
-      <c r="F147" s="8">
-        <v>46082</v>
-      </c>
-      <c r="G147" s="8">
-        <v>46118</v>
+      <c r="F147" t="str">
+        <v/>
+      </c>
+      <c r="G147" t="str">
+        <v/>
       </c>
       <c r="H147" t="str">
         <v/>
@@ -6478,7 +6470,7 @@
         <v/>
       </c>
       <c r="R147" s="6" t="str">
-        <v>Ilan Tatar Feb 15, 2026 1:06 PM</v>
+        <v>Ilan Tatar Mar 8, 2026 2:06 PM</v>
       </c>
       <c r="S147" t="str">
         <v/>
@@ -6492,7 +6484,7 @@
     </row>
     <row r="148" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="str">
-        <v>Send Payment- issues with readiness to develop/Adi absence</v>
+        <v>Main Risk : Deposit flow are waiting for ABC test for solution, develop will start Mid MArch only</v>
       </c>
       <c r="B148" t="str">
         <v/>
@@ -6506,11 +6498,11 @@
       <c r="E148" t="str">
         <v/>
       </c>
-      <c r="F148" t="str">
-        <v/>
-      </c>
-      <c r="G148" t="str">
-        <v/>
+      <c r="F148" s="8">
+        <v>46082</v>
+      </c>
+      <c r="G148" s="8">
+        <v>46118</v>
       </c>
       <c r="H148" t="str">
         <v/>
@@ -6543,7 +6535,7 @@
         <v/>
       </c>
       <c r="R148" s="6" t="str">
-        <v>Ilan Tatar Mar 22, 2026 11:45 AM</v>
+        <v>Ilan Tatar Feb 15, 2026 1:06 PM</v>
       </c>
       <c r="S148" t="str">
         <v/>
@@ -6557,7 +6549,7 @@
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="str">
-        <v>Where we launch the cashflow on April 20 version? Sagiv to update 8.3</v>
+        <v>Send Payment- issues with readiness to develop/Adi absence</v>
       </c>
       <c r="B149" t="str">
         <v/>
@@ -6608,7 +6600,7 @@
         <v/>
       </c>
       <c r="R149" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:48 PM</v>
+        <v>Ilan Tatar Mar 22, 2026 11:45 AM</v>
       </c>
       <c r="S149" t="str">
         <v/>
@@ -6622,7 +6614,7 @@
     </row>
     <row r="150" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="str">
-        <v>Filipe- 1.4 get the 2 cards working + be- Ilan to coordinate</v>
+        <v>Where we launch the cashflow on April 20 version? Sagiv to update 8.3</v>
       </c>
       <c r="B150" t="str">
         <v/>
@@ -6673,7 +6665,7 @@
         <v/>
       </c>
       <c r="R150" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:50 PM</v>
+        <v>Ilan Tatar Mar 5, 2026 12:48 PM</v>
       </c>
       <c r="S150" t="str">
         <v/>
@@ -6687,7 +6679,7 @@
     </row>
     <row r="151" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="str">
-        <v>FTD ABC</v>
+        <v>Filipe- 1.4 get the 2 cards working + be- Ilan to coordinate</v>
       </c>
       <c r="B151" t="str">
         <v/>
@@ -6701,11 +6693,11 @@
       <c r="E151" t="str">
         <v/>
       </c>
-      <c r="F151" s="8">
-        <v>46057</v>
-      </c>
-      <c r="G151" s="8">
-        <v>46083</v>
+      <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151" t="str">
+        <v/>
       </c>
       <c r="H151" t="str">
         <v/>
@@ -6738,7 +6730,7 @@
         <v/>
       </c>
       <c r="R151" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:17 PM</v>
+        <v>Ilan Tatar Mar 5, 2026 12:50 PM</v>
       </c>
       <c r="S151" t="str">
         <v/>
@@ -6752,7 +6744,7 @@
     </row>
     <row r="152" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="str">
-        <v>Cash flow- Decision where to locate it in the new Website</v>
+        <v>FTD ABC</v>
       </c>
       <c r="B152" t="str">
         <v/>
@@ -6767,19 +6759,19 @@
         <v/>
       </c>
       <c r="F152" s="8">
-        <v>46054</v>
+        <v>46057</v>
       </c>
       <c r="G152" s="8">
-        <v>46062</v>
+        <v>46083</v>
       </c>
       <c r="H152" t="str">
         <v/>
       </c>
-      <c r="I152" s="6" t="str">
-        <v>Meeting 9.2- Sagiv</v>
+      <c r="I152" t="str">
+        <v/>
       </c>
       <c r="J152" s="6" t="str">
-        <v>Sagiv</v>
+        <v/>
       </c>
       <c r="K152" s="6" t="str">
         <v/>
@@ -6803,7 +6795,7 @@
         <v/>
       </c>
       <c r="R152" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:06 PM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:17 PM</v>
       </c>
       <c r="S152" t="str">
         <v/>
@@ -6817,7 +6809,7 @@
     </row>
     <row r="153" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="str">
-        <v>DOD for 20.4 to Inbal? Ilan with Tal/Igor</v>
+        <v>Cash flow- Decision where to locate it in the new Website</v>
       </c>
       <c r="B153" t="str">
         <v/>
@@ -6831,20 +6823,20 @@
       <c r="E153" t="str">
         <v/>
       </c>
-      <c r="F153" t="str">
-        <v/>
-      </c>
-      <c r="G153" t="str">
-        <v/>
+      <c r="F153" s="8">
+        <v>46054</v>
+      </c>
+      <c r="G153" s="8">
+        <v>46062</v>
       </c>
       <c r="H153" t="str">
         <v/>
       </c>
-      <c r="I153" t="str">
-        <v/>
+      <c r="I153" s="6" t="str">
+        <v>Meeting 9.2- Sagiv</v>
       </c>
       <c r="J153" s="6" t="str">
-        <v/>
+        <v>Sagiv</v>
       </c>
       <c r="K153" s="6" t="str">
         <v/>
@@ -6868,7 +6860,7 @@
         <v/>
       </c>
       <c r="R153" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:49 PM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:06 PM</v>
       </c>
       <c r="S153" t="str">
         <v/>
@@ -6882,7 +6874,7 @@
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="str">
-        <v>Cash info access in the new Application</v>
+        <v>DOD for 20.4 to Inbal? Ilan with Tal/Igor</v>
       </c>
       <c r="B154" t="str">
         <v/>
@@ -6905,8 +6897,8 @@
       <c r="H154" t="str">
         <v/>
       </c>
-      <c r="I154" s="6" t="str">
-        <v>Decision about Crypto and custodial wallet. Gili and Tuval are taking this. ETA? Update ? Sagiv?</v>
+      <c r="I154" t="str">
+        <v/>
       </c>
       <c r="J154" s="6" t="str">
         <v/>
@@ -6933,7 +6925,7 @@
         <v/>
       </c>
       <c r="R154" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:15 PM</v>
+        <v>Ilan Tatar Mar 5, 2026 12:49 PM</v>
       </c>
       <c r="S154" t="str">
         <v/>
@@ -6947,7 +6939,7 @@
     </row>
     <row r="155" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="str">
-        <v>Financial History API - Understanding and plans</v>
+        <v>Cash info access in the new Application</v>
       </c>
       <c r="B155" t="str">
         <v/>
@@ -6971,7 +6963,7 @@
         <v/>
       </c>
       <c r="I155" s="6" t="str">
-        <v>Itis the list of Dep/WD from Trading account  and IBAN</v>
+        <v>Decision about Crypto and custodial wallet. Gili and Tuval are taking this. ETA? Update ? Sagiv?</v>
       </c>
       <c r="J155" s="6" t="str">
         <v/>
@@ -6998,7 +6990,7 @@
         <v/>
       </c>
       <c r="R155" s="6" t="str">
-        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:15 PM</v>
       </c>
       <c r="S155" t="str">
         <v/>
@@ -7012,7 +7004,7 @@
     </row>
     <row r="156" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="str">
-        <v>Wallet  Custodial and Non Custodial</v>
+        <v>Financial History API - Understanding and plans</v>
       </c>
       <c r="B156" t="str">
         <v/>
@@ -7020,26 +7012,26 @@
       <c r="C156" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D156" s="6" t="str">
-        <v>plusDev</v>
+      <c r="D156" t="str">
+        <v/>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
-      <c r="F156" s="8">
-        <v>46054</v>
-      </c>
-      <c r="G156" s="8">
-        <v>46058</v>
+      <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156" t="str">
+        <v/>
       </c>
       <c r="H156" t="str">
         <v/>
       </c>
       <c r="I156" s="6" t="str">
-        <v>What is the solution to the Wallet tab functionality in the Plus app? Sagiv is taking this and should finalize by 5.2 the requirements</v>
+        <v>Itis the list of Dep/WD from Trading account  and IBAN</v>
       </c>
       <c r="J156" s="6" t="str">
-        <v>sagiv</v>
+        <v/>
       </c>
       <c r="K156" s="6" t="str">
         <v/>
@@ -7063,7 +7055,7 @@
         <v/>
       </c>
       <c r="R156" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 11:52 AM</v>
+        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
       </c>
       <c r="S156" t="str">
         <v/>
@@ -7077,7 +7069,7 @@
     </row>
     <row r="157" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="str">
-        <v>HP Graph - Gaps to launch on production</v>
+        <v>Wallet  Custodial and Non Custodial</v>
       </c>
       <c r="B157" t="str">
         <v/>
@@ -7085,26 +7077,26 @@
       <c r="C157" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D157" t="str">
-        <v/>
+      <c r="D157" s="6" t="str">
+        <v>plusDev</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" s="8">
-        <v>46056</v>
+        <v>46054</v>
       </c>
       <c r="G157" s="8">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="H157" t="str">
         <v/>
       </c>
       <c r="I157" s="6" t="str">
-        <v>Meeting 10.2 with Ofer and his team to plan the delivery</v>
+        <v>What is the solution to the Wallet tab functionality in the Plus app? Sagiv is taking this and should finalize by 5.2 the requirements</v>
       </c>
       <c r="J157" s="6" t="str">
-        <v/>
+        <v>sagiv</v>
       </c>
       <c r="K157" s="6" t="str">
         <v/>
@@ -7128,7 +7120,7 @@
         <v/>
       </c>
       <c r="R157" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:05 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 11:52 AM</v>
       </c>
       <c r="S157" t="str">
         <v/>
@@ -7142,7 +7134,7 @@
     </row>
     <row r="158" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="str">
-        <v>BFF- Who deliver what is the scope?</v>
+        <v>HP Graph - Gaps to launch on production</v>
       </c>
       <c r="B158" t="str">
         <v/>
@@ -7156,17 +7148,17 @@
       <c r="E158" t="str">
         <v/>
       </c>
-      <c r="F158" t="str">
-        <v/>
-      </c>
-      <c r="G158" t="str">
-        <v/>
+      <c r="F158" s="8">
+        <v>46056</v>
+      </c>
+      <c r="G158" s="8">
+        <v>46056</v>
       </c>
       <c r="H158" t="str">
         <v/>
       </c>
-      <c r="I158" t="str">
-        <v/>
+      <c r="I158" s="6" t="str">
+        <v>Meeting 10.2 with Ofer and his team to plan the delivery</v>
       </c>
       <c r="J158" s="6" t="str">
         <v/>
@@ -7193,7 +7185,7 @@
         <v/>
       </c>
       <c r="R158" s="6" t="str">
-        <v>Ilan Tatar Feb 12, 2026 12:19 PM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:05 PM</v>
       </c>
       <c r="S158" t="str">
         <v/>
@@ -7207,7 +7199,7 @@
     </row>
     <row r="159" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="str">
-        <v>Withdraw - R&amp;R between Elior/Hodaya</v>
+        <v>BFF- Who deliver what is the scope?</v>
       </c>
       <c r="B159" t="str">
         <v/>
@@ -7230,8 +7222,8 @@
       <c r="H159" t="str">
         <v/>
       </c>
-      <c r="I159" s="6" t="str">
-        <v>Elisheva said that it is not clear where it reside in RND?</v>
+      <c r="I159" t="str">
+        <v/>
       </c>
       <c r="J159" s="6" t="str">
         <v/>
@@ -7258,7 +7250,7 @@
         <v/>
       </c>
       <c r="R159" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:09 PM</v>
+        <v>Ilan Tatar Feb 12, 2026 12:19 PM</v>
       </c>
       <c r="S159" t="str">
         <v/>
@@ -7272,7 +7264,7 @@
     </row>
     <row r="160" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="str">
-        <v>EOD Balance depend on HP Graph data solution? Hagit to advise</v>
+        <v>Withdraw - R&amp;R between Elior/Hodaya</v>
       </c>
       <c r="B160" t="str">
         <v/>
@@ -7295,8 +7287,8 @@
       <c r="H160" t="str">
         <v/>
       </c>
-      <c r="I160" t="str">
-        <v/>
+      <c r="I160" s="6" t="str">
+        <v>Elisheva said that it is not clear where it reside in RND?</v>
       </c>
       <c r="J160" s="6" t="str">
         <v/>
@@ -7323,7 +7315,7 @@
         <v/>
       </c>
       <c r="R160" s="6" t="str">
-        <v>Ilan Tatar Feb 4, 2026 11:39 AM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:09 PM</v>
       </c>
       <c r="S160" t="str">
         <v/>
@@ -7337,7 +7329,7 @@
     </row>
     <row r="161" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="str">
-        <v>Work For Inbal next week?</v>
+        <v>EOD Balance depend on HP Graph data solution? Hagit to advise</v>
       </c>
       <c r="B161" t="str">
         <v/>
@@ -7388,7 +7380,7 @@
         <v/>
       </c>
       <c r="R161" s="6" t="str">
-        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
+        <v>Ilan Tatar Feb 4, 2026 11:39 AM</v>
       </c>
       <c r="S161" t="str">
         <v/>
@@ -7402,7 +7394,7 @@
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="str">
-        <v>Sagiv- open task for AB deposit wizard in Monday</v>
+        <v>Work For Inbal next week?</v>
       </c>
       <c r="B162" t="str">
         <v/>
@@ -7453,7 +7445,7 @@
         <v/>
       </c>
       <c r="R162" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:56 PM</v>
+        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
       </c>
       <c r="S162" t="str">
         <v/>
@@ -7467,7 +7459,7 @@
     </row>
     <row r="163" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="str">
-        <v>Inbal- There is nothing new in BE side delivery needed for 20.4 version</v>
+        <v>Sagiv- open task for AB deposit wizard in Monday</v>
       </c>
       <c r="B163" t="str">
         <v/>
@@ -7518,287 +7510,317 @@
         <v/>
       </c>
       <c r="R163" s="6" t="str">
+        <v>Ilan Tatar Mar 5, 2026 12:56 PM</v>
+      </c>
+      <c r="S163" t="str">
+        <v/>
+      </c>
+      <c r="T163" t="str">
+        <v/>
+      </c>
+      <c r="U163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="str">
+        <v>Inbal- There is nothing new in BE side delivery needed for 20.4 version</v>
+      </c>
+      <c r="B164" t="str">
+        <v/>
+      </c>
+      <c r="C164" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="D164" t="str">
+        <v/>
+      </c>
+      <c r="E164" t="str">
+        <v/>
+      </c>
+      <c r="F164" t="str">
+        <v/>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+      <c r="H164" t="str">
+        <v/>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
+      <c r="J164" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K164" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L164" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str">
+        <v/>
+      </c>
+      <c r="N164" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164" t="str">
+        <v/>
+      </c>
+      <c r="R164" s="6" t="str">
         <v>Ilan Tatar Mar 11, 2026 7:41 PM</v>
       </c>
-      <c r="S163" t="str">
-        <v/>
-      </c>
-      <c r="T163" t="str">
-        <v/>
-      </c>
-      <c r="U163" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="164" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A164" t="str">
-        <v/>
-      </c>
-      <c r="B164" t="str">
-        <v/>
-      </c>
-      <c r="C164" t="str">
-        <v/>
-      </c>
-      <c r="D164" t="str">
-        <v/>
-      </c>
-      <c r="E164" t="str">
-        <v/>
-      </c>
-      <c r="F164" s="26">
+      <c r="S164" t="str">
+        <v/>
+      </c>
+      <c r="T164" t="str">
+        <v/>
+      </c>
+      <c r="U164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A165" t="str">
+        <v/>
+      </c>
+      <c r="B165" t="str">
+        <v/>
+      </c>
+      <c r="C165" t="str">
+        <v/>
+      </c>
+      <c r="D165" t="str">
+        <v/>
+      </c>
+      <c r="E165" t="str">
+        <v/>
+      </c>
+      <c r="F165" s="25">
         <v>46054</v>
       </c>
-      <c r="G164" s="26">
+      <c r="G165" s="25">
         <v>46118</v>
       </c>
-      <c r="H164" t="str">
-        <v/>
-      </c>
-      <c r="I164" t="str">
-        <v/>
-      </c>
-      <c r="J164" t="str">
-        <v/>
-      </c>
-      <c r="K164" t="str">
-        <v/>
-      </c>
-      <c r="L164" t="str">
-        <v/>
-      </c>
-      <c r="M164" s="27">
+      <c r="H165" t="str">
+        <v/>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165" t="str">
+        <v/>
+      </c>
+      <c r="K165" t="str">
+        <v/>
+      </c>
+      <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" s="26">
         <v>0</v>
       </c>
-      <c r="N164" t="str">
-        <v/>
-      </c>
-      <c r="O164" t="str">
-        <v/>
-      </c>
-      <c r="P164" t="str">
-        <v/>
-      </c>
-      <c r="Q164" s="29" t="str">
-        <v/>
-      </c>
-      <c r="R164" t="str">
-        <v/>
-      </c>
-      <c r="S164" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T164" s="29" t="str">
-        <v/>
-      </c>
-      <c r="U164" s="29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="32" t="str">
+      <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165" s="28" t="str">
+        <v/>
+      </c>
+      <c r="R165" t="str">
+        <v/>
+      </c>
+      <c r="S165" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T165" s="28" t="str">
+        <v/>
+      </c>
+      <c r="U165" s="28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="31" t="str">
         <v>MVP - API /BFF project</v>
       </c>
     </row>
-    <row r="167" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A167" s="3" t="str">
+    <row r="168" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B167" s="3" t="str">
+      <c r="B168" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C167" s="3" t="str">
+      <c r="C168" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D167" s="3" t="str">
+      <c r="D168" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E167" s="3" t="str">
+      <c r="E168" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F167" s="3" t="str">
+      <c r="F168" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G167" s="3" t="str">
+      <c r="G168" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H167" s="3" t="str">
+      <c r="H168" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I167" s="3" t="str">
+      <c r="I168" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J167" s="3" t="str">
+      <c r="J168" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K167" s="3" t="str">
+      <c r="K168" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L167" s="3" t="str">
+      <c r="L168" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M167" s="3" t="str">
+      <c r="M168" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N167" s="3" t="str">
+      <c r="N168" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O167" s="3" t="str">
+      <c r="O168" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P167" s="3" t="str">
+      <c r="P168" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q167" s="3" t="str">
+      <c r="Q168" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R167" s="3" t="str">
+      <c r="R168" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S167" s="3" t="str">
+      <c r="S168" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T167" s="3" t="str">
+      <c r="T168" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U167" s="3" t="str">
+      <c r="U168" s="3" t="str">
         <v>Product ETA - End</v>
       </c>
     </row>
-    <row r="168" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A168" s="4" t="str">
+    <row r="169" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="str">
         <v>Real time Balance &amp; Equity APIs- Hagit</v>
       </c>
-      <c r="B168" t="str">
-        <v/>
-      </c>
-      <c r="C168" s="11" t="str">
+      <c r="B169" t="str">
+        <v/>
+      </c>
+      <c r="C169" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D168" s="6" t="str">
+      <c r="D169" s="6" t="str">
         <v>ApiForPlus</v>
       </c>
-      <c r="E168" s="6" t="str">
+      <c r="E169" s="6" t="str">
         <v>trading real time equity API</v>
       </c>
-      <c r="F168" s="8">
+      <c r="F169" s="8">
         <v>46036</v>
       </c>
-      <c r="G168" s="8">
+      <c r="G169" s="8">
         <v>46126</v>
       </c>
-      <c r="H168" s="6" t="str">
+      <c r="H169" s="6" t="str">
         <v>V1(20.4)</v>
       </c>
-      <c r="I168" t="str">
-        <v/>
-      </c>
-      <c r="J168" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K168" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L168" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M168" s="6">
+      <c r="I169" t="str">
+        <v/>
+      </c>
+      <c r="J169" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K169" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L169" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M169" s="6">
         <v>1</v>
       </c>
-      <c r="N168" s="6" t="str">
+      <c r="N169" s="6" t="str">
         <v>S</v>
       </c>
-      <c r="O168" t="str">
-        <v/>
-      </c>
-      <c r="P168" t="str">
-        <v/>
-      </c>
-      <c r="Q168" t="str">
-        <v/>
-      </c>
-      <c r="R168" s="6" t="str">
+      <c r="O169" t="str">
+        <v/>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169" t="str">
+        <v/>
+      </c>
+      <c r="R169" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
       </c>
-      <c r="S168" t="str">
-        <v/>
-      </c>
-      <c r="T168" t="str">
-        <v/>
-      </c>
-      <c r="U168" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="169" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A169" s="9" t="str">
+      <c r="S169" t="str">
+        <v/>
+      </c>
+      <c r="T169" t="str">
+        <v/>
+      </c>
+      <c r="U169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B169" s="10" t="str">
+      <c r="B170" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C169" s="10" t="str">
+      <c r="C170" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D169" s="10" t="str">
+      <c r="D170" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E169" s="10" t="str">
+      <c r="E170" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F169" s="10" t="str">
+      <c r="F170" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G169" s="10" t="str">
+      <c r="G170" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H169" s="10" t="str">
+      <c r="H170" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I169" s="10" t="str">
+      <c r="I170" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J169" s="10" t="str">
+      <c r="J170" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K169" s="10" t="str">
+      <c r="K170" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="170" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A170" t="str">
-        <v/>
-      </c>
-      <c r="B170" s="4" t="str">
-        <v>Swaggers for 2 APIS- Maksym</v>
-      </c>
-      <c r="C170" t="str">
-        <v/>
-      </c>
-      <c r="D170" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="E170" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F170" t="str">
-        <v/>
-      </c>
-      <c r="G170" t="str">
-        <v/>
-      </c>
-      <c r="H170" s="8">
-        <v>46049</v>
-      </c>
-      <c r="I170" s="8">
-        <v>46052</v>
-      </c>
-      <c r="J170" t="str">
-        <v/>
-      </c>
-      <c r="K170" t="str">
-        <v/>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -7806,7 +7828,7 @@
         <v/>
       </c>
       <c r="B171" s="4" t="str">
-        <v>Accessibility of balances from the various accounts - Elisheva</v>
+        <v>Swaggers for 2 APIS- Maksym</v>
       </c>
       <c r="C171" t="str">
         <v/>
@@ -7827,7 +7849,7 @@
         <v>46049</v>
       </c>
       <c r="I171" s="8">
-        <v>46055</v>
+        <v>46052</v>
       </c>
       <c r="J171" t="str">
         <v/>
@@ -7841,10 +7863,10 @@
         <v/>
       </c>
       <c r="B172" s="4" t="str">
-        <v>Dev - PAYUA-7623.- Maksym</v>
-      </c>
-      <c r="C172" s="6" t="str">
-        <v>Hagit Zamir</v>
+        <v>Accessibility of balances from the various accounts - Elisheva</v>
+      </c>
+      <c r="C172" t="str">
+        <v/>
       </c>
       <c r="D172" s="11" t="str">
         <v>Done</v>
@@ -7859,10 +7881,10 @@
         <v/>
       </c>
       <c r="H172" s="8">
-        <v>46075</v>
+        <v>46049</v>
       </c>
       <c r="I172" s="8">
-        <v>46119</v>
+        <v>46055</v>
       </c>
       <c r="J172" t="str">
         <v/>
@@ -7876,10 +7898,10 @@
         <v/>
       </c>
       <c r="B173" s="4" t="str">
-        <v>Dev Admin TAPI- Amit Glazer</v>
-      </c>
-      <c r="C173" t="str">
-        <v/>
+        <v>Dev - PAYUA-7623.- Maksym</v>
+      </c>
+      <c r="C173" s="6" t="str">
+        <v>Hagit Zamir</v>
       </c>
       <c r="D173" s="11" t="str">
         <v>Done</v>
@@ -7894,10 +7916,10 @@
         <v/>
       </c>
       <c r="H173" s="8">
-        <v>46098</v>
+        <v>46075</v>
       </c>
       <c r="I173" s="8">
-        <v>46124</v>
+        <v>46119</v>
       </c>
       <c r="J173" t="str">
         <v/>
@@ -7911,7 +7933,7 @@
         <v/>
       </c>
       <c r="B174" s="4" t="str">
-        <v>Dev- Crypto- Ofir Schwartz- CRYP-7716</v>
+        <v>Dev Admin TAPI- Amit Glazer</v>
       </c>
       <c r="C174" t="str">
         <v/>
@@ -7929,10 +7951,10 @@
         <v/>
       </c>
       <c r="H174" s="8">
-        <v>46110</v>
+        <v>46098</v>
       </c>
       <c r="I174" s="8">
-        <v>46119</v>
+        <v>46124</v>
       </c>
       <c r="J174" t="str">
         <v/>
@@ -7946,7 +7968,7 @@
         <v/>
       </c>
       <c r="B175" s="4" t="str">
-        <v>Production test with users- Anton</v>
+        <v>Dev- Crypto- Ofir Schwartz- CRYP-7716</v>
       </c>
       <c r="C175" t="str">
         <v/>
@@ -7963,11 +7985,11 @@
       <c r="G175" t="str">
         <v/>
       </c>
-      <c r="H175" t="str">
-        <v/>
-      </c>
-      <c r="I175" t="str">
-        <v/>
+      <c r="H175" s="8">
+        <v>46110</v>
+      </c>
+      <c r="I175" s="8">
+        <v>46119</v>
       </c>
       <c r="J175" t="str">
         <v/>
@@ -7981,7 +8003,7 @@
         <v/>
       </c>
       <c r="B176" s="4" t="str">
-        <v>Communicate with Exp ( Filipe/Renata) to implement it</v>
+        <v>Production test with users- Anton</v>
       </c>
       <c r="C176" t="str">
         <v/>
@@ -8011,74 +8033,44 @@
         <v/>
       </c>
     </row>
-    <row r="177" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A177" s="4" t="str">
-        <v>EOD Balance- Maksym PAYUA-7769</v>
-      </c>
-      <c r="B177" t="str">
-        <v/>
-      </c>
-      <c r="C177" s="11" t="str">
+    <row r="177" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" t="str">
+        <v/>
+      </c>
+      <c r="B177" s="4" t="str">
+        <v>Communicate with Exp ( Filipe/Renata) to implement it</v>
+      </c>
+      <c r="C177" t="str">
+        <v/>
+      </c>
+      <c r="D177" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D177" s="6" t="str">
-        <v>ApiForPlus</v>
-      </c>
-      <c r="E177" t="str">
-        <v/>
-      </c>
-      <c r="F177" s="8">
-        <v>46042</v>
-      </c>
-      <c r="G177" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H177" s="6" t="str">
-        <v>V2(4.5)</v>
-      </c>
-      <c r="I177" s="6" t="str">
-        <v>Need data to expose historical balances</v>
-      </c>
-      <c r="J177" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K177" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L177" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M177" s="6">
-        <v>2</v>
-      </c>
-      <c r="N177" s="6" t="str">
-        <v>XS</v>
-      </c>
-      <c r="O177" t="str">
-        <v/>
-      </c>
-      <c r="P177" t="str">
-        <v/>
-      </c>
-      <c r="Q177" t="str">
-        <v/>
-      </c>
-      <c r="R177" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
-      </c>
-      <c r="S177" t="str">
-        <v/>
-      </c>
-      <c r="T177" t="str">
-        <v/>
-      </c>
-      <c r="U177" t="str">
+      <c r="E177" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F177" t="str">
+        <v/>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+      <c r="H177" t="str">
+        <v/>
+      </c>
+      <c r="I177" t="str">
+        <v/>
+      </c>
+      <c r="J177" t="str">
+        <v/>
+      </c>
+      <c r="K177" t="str">
         <v/>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="str">
-        <v>Deposit APIs (using existing) +Payment Eligibility +Funding</v>
+        <v>EOD Balance- Maksym PAYUA-7769</v>
       </c>
       <c r="B178" t="str">
         <v/>
@@ -8093,16 +8085,16 @@
         <v/>
       </c>
       <c r="F178" s="8">
-        <v>46040</v>
+        <v>46042</v>
       </c>
       <c r="G178" s="8">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="H178" s="6" t="str">
-        <v>V1(20.4)</v>
-      </c>
-      <c r="I178" t="str">
-        <v/>
+        <v>V2(4.5)</v>
+      </c>
+      <c r="I178" s="6" t="str">
+        <v>Need data to expose historical balances</v>
       </c>
       <c r="J178" s="6" t="str">
         <v/>
@@ -8111,13 +8103,13 @@
         <v/>
       </c>
       <c r="L178" s="6" t="str">
-        <v>Shuky</v>
+        <v/>
       </c>
       <c r="M178" s="6">
         <v>2</v>
       </c>
       <c r="N178" s="6" t="str">
-        <v>S</v>
+        <v>XS</v>
       </c>
       <c r="O178" t="str">
         <v/>
@@ -8141,74 +8133,104 @@
         <v/>
       </c>
     </row>
-    <row r="179" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A179" s="9" t="str">
+    <row r="179" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="str">
+        <v>Deposit APIs (using existing) +Payment Eligibility +Funding</v>
+      </c>
+      <c r="B179" t="str">
+        <v/>
+      </c>
+      <c r="C179" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="D179" s="6" t="str">
+        <v>ApiForPlus</v>
+      </c>
+      <c r="E179" t="str">
+        <v/>
+      </c>
+      <c r="F179" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G179" s="8">
+        <v>46126</v>
+      </c>
+      <c r="H179" s="6" t="str">
+        <v>V1(20.4)</v>
+      </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
+      <c r="J179" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K179" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L179" s="6" t="str">
+        <v>Shuky</v>
+      </c>
+      <c r="M179" s="6">
+        <v>2</v>
+      </c>
+      <c r="N179" s="6" t="str">
+        <v>S</v>
+      </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
+      <c r="R179" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+      </c>
+      <c r="S179" t="str">
+        <v/>
+      </c>
+      <c r="T179" t="str">
+        <v/>
+      </c>
+      <c r="U179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B179" s="10" t="str">
+      <c r="B180" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C179" s="10" t="str">
+      <c r="C180" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D179" s="10" t="str">
+      <c r="D180" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E179" s="10" t="str">
+      <c r="E180" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F179" s="10" t="str">
+      <c r="F180" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G179" s="10" t="str">
+      <c r="G180" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H179" s="10" t="str">
+      <c r="H180" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I179" s="10" t="str">
+      <c r="I180" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J179" s="10" t="str">
+      <c r="J180" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K179" s="10" t="str">
+      <c r="K180" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="180" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A180" t="str">
-        <v/>
-      </c>
-      <c r="B180" s="4" t="str">
-        <v>get Eligible funding API (payment-methods/(PaymentMethodTypeId) - Shuky</v>
-      </c>
-      <c r="C180" t="str">
-        <v/>
-      </c>
-      <c r="D180" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="E180" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F180" t="str">
-        <v/>
-      </c>
-      <c r="G180" t="str">
-        <v/>
-      </c>
-      <c r="H180" t="str">
-        <v/>
-      </c>
-      <c r="I180" t="str">
-        <v/>
-      </c>
-      <c r="J180" t="str">
-        <v/>
-      </c>
-      <c r="K180" t="str">
-        <v/>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -8216,7 +8238,7 @@
         <v/>
       </c>
       <c r="B181" s="4" t="str">
-        <v>Mean of Payments (eligible-payment-method-types) API.- PAYIL-10721Shuky</v>
+        <v>get Eligible funding API (payment-methods/(PaymentMethodTypeId) - Shuky</v>
       </c>
       <c r="C181" t="str">
         <v/>
@@ -8233,11 +8255,11 @@
       <c r="G181" t="str">
         <v/>
       </c>
-      <c r="H181" s="8">
-        <v>46064</v>
-      </c>
-      <c r="I181" s="8">
-        <v>46100</v>
+      <c r="H181" t="str">
+        <v/>
+      </c>
+      <c r="I181" t="str">
+        <v/>
       </c>
       <c r="J181" t="str">
         <v/>
@@ -8251,7 +8273,7 @@
         <v/>
       </c>
       <c r="B182" s="4" t="str">
-        <v>Banking deposit MOP API- Maksym</v>
+        <v>Mean of Payments (eligible-payment-method-types) API.- PAYIL-10721Shuky</v>
       </c>
       <c r="C182" t="str">
         <v/>
@@ -8269,10 +8291,10 @@
         <v/>
       </c>
       <c r="H182" s="8">
-        <v>46055</v>
+        <v>46064</v>
       </c>
       <c r="I182" s="8">
-        <v>46125</v>
+        <v>46100</v>
       </c>
       <c r="J182" t="str">
         <v/>
@@ -8286,7 +8308,7 @@
         <v/>
       </c>
       <c r="B183" s="4" t="str">
-        <v>Swagger delivery</v>
+        <v>Banking deposit MOP API- Maksym</v>
       </c>
       <c r="C183" t="str">
         <v/>
@@ -8304,10 +8326,10 @@
         <v/>
       </c>
       <c r="H183" s="8">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="I183" s="8">
-        <v>46064</v>
+        <v>46125</v>
       </c>
       <c r="J183" t="str">
         <v/>
@@ -8321,7 +8343,7 @@
         <v/>
       </c>
       <c r="B184" s="4" t="str">
-        <v>Dictionary API- Shuky</v>
+        <v>Swagger delivery</v>
       </c>
       <c r="C184" t="str">
         <v/>
@@ -8338,11 +8360,11 @@
       <c r="G184" t="str">
         <v/>
       </c>
-      <c r="H184" t="str">
-        <v/>
-      </c>
-      <c r="I184" t="str">
-        <v/>
+      <c r="H184" s="8">
+        <v>46056</v>
+      </c>
+      <c r="I184" s="8">
+        <v>46064</v>
       </c>
       <c r="J184" t="str">
         <v/>
@@ -8356,7 +8378,7 @@
         <v/>
       </c>
       <c r="B185" s="4" t="str">
-        <v>Dictionary API- Maksym-</v>
+        <v>Dictionary API- Shuky</v>
       </c>
       <c r="C185" t="str">
         <v/>
@@ -8386,20 +8408,20 @@
         <v/>
       </c>
     </row>
-    <row r="186" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A186" s="4" t="str">
-        <v>cashflow bff - Zipi is working on it for one task</v>
-      </c>
-      <c r="B186" t="str">
-        <v/>
-      </c>
-      <c r="C186" s="11" t="str">
+    <row r="186" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" t="str">
+        <v/>
+      </c>
+      <c r="B186" s="4" t="str">
+        <v>Dictionary API- Maksym-</v>
+      </c>
+      <c r="C186" t="str">
+        <v/>
+      </c>
+      <c r="D186" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D186" t="str">
-        <v/>
-      </c>
-      <c r="E186" t="str">
+      <c r="E186" s="6" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
@@ -8414,52 +8436,22 @@
       <c r="I186" t="str">
         <v/>
       </c>
-      <c r="J186" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K186" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L186" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M186" s="6">
-        <v>1</v>
-      </c>
-      <c r="N186" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O186" t="str">
-        <v/>
-      </c>
-      <c r="P186" t="str">
-        <v/>
-      </c>
-      <c r="Q186" t="str">
-        <v/>
-      </c>
-      <c r="R186" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
-      </c>
-      <c r="S186" t="str">
-        <v/>
-      </c>
-      <c r="T186" t="str">
-        <v/>
-      </c>
-      <c r="U186" t="str">
+      <c r="J186" t="str">
+        <v/>
+      </c>
+      <c r="K186" t="str">
         <v/>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="str">
-        <v>deposit bff - we will start working on it soon. We are now preparing the contract</v>
+        <v>cashflow bff - Zipi is working on it for one task</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
-      <c r="C187" s="18" t="str">
-        <v>Not Started</v>
+      <c r="C187" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D187" t="str">
         <v/>
@@ -8489,7 +8481,7 @@
         <v/>
       </c>
       <c r="M187" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N187" s="6" t="str">
         <v/>
@@ -8504,7 +8496,7 @@
         <v/>
       </c>
       <c r="R187" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:17 PM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
       </c>
       <c r="S187" t="str">
         <v/>
@@ -8518,13 +8510,13 @@
     </row>
     <row r="188" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="str">
-        <v>banking bff - Amichai is working on it (for couple of tasks)</v>
+        <v>deposit bff - we will start working on it soon. We are now preparing the contract</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
-      <c r="C188" s="11" t="str">
-        <v>Done</v>
+      <c r="C188" s="19" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D188" t="str">
         <v/>
@@ -8554,7 +8546,7 @@
         <v/>
       </c>
       <c r="M188" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N188" s="6" t="str">
         <v/>
@@ -8569,7 +8561,7 @@
         <v/>
       </c>
       <c r="R188" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:17 PM</v>
       </c>
       <c r="S188" t="str">
         <v/>
@@ -8583,31 +8575,31 @@
     </row>
     <row r="189" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="str">
-        <v>Financial History M&amp;A</v>
+        <v>banking bff - Amichai is working on it (for couple of tasks)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
-      <c r="C189" s="18" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="D189" s="6" t="str">
-        <v>ApiForM&amp;A</v>
+      <c r="C189" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="D189" t="str">
+        <v/>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
-      <c r="F189" s="8">
-        <v>46040</v>
-      </c>
-      <c r="G189" s="8">
-        <v>46040</v>
+      <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189" t="str">
+        <v/>
       </c>
       <c r="H189" t="str">
         <v/>
       </c>
-      <c r="I189" s="6" t="str">
-        <v>add iban mimo &amp; card trx</v>
+      <c r="I189" t="str">
+        <v/>
       </c>
       <c r="J189" s="6" t="str">
         <v/>
@@ -8618,11 +8610,11 @@
       <c r="L189" s="6" t="str">
         <v/>
       </c>
-      <c r="M189" t="str">
-        <v/>
+      <c r="M189" s="6">
+        <v>1</v>
       </c>
       <c r="N189" s="6" t="str">
-        <v>S</v>
+        <v/>
       </c>
       <c r="O189" t="str">
         <v/>
@@ -8634,7 +8626,7 @@
         <v/>
       </c>
       <c r="R189" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 10:49 AM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
       </c>
       <c r="S189" t="str">
         <v/>
@@ -8648,13 +8640,13 @@
     </row>
     <row r="190" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="str">
-        <v>IBAN (balance, account, transactions, eligibility)</v>
+        <v>Financial History M&amp;A</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
-      <c r="C190" s="12" t="str">
-        <v>Stuck</v>
+      <c r="C190" s="19" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D190" s="6" t="str">
         <v>ApiForM&amp;A</v>
@@ -8662,17 +8654,17 @@
       <c r="E190" t="str">
         <v/>
       </c>
-      <c r="F190" t="str">
-        <v/>
-      </c>
-      <c r="G190" t="str">
-        <v/>
+      <c r="F190" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G190" s="8">
+        <v>46040</v>
       </c>
       <c r="H190" t="str">
         <v/>
       </c>
-      <c r="I190" t="str">
-        <v/>
+      <c r="I190" s="6" t="str">
+        <v>add iban mimo &amp; card trx</v>
       </c>
       <c r="J190" s="6" t="str">
         <v/>
@@ -8699,109 +8691,139 @@
         <v/>
       </c>
       <c r="R190" s="6" t="str">
+        <v>Ilan Tatar Jan 28, 2026 10:49 AM</v>
+      </c>
+      <c r="S190" t="str">
+        <v/>
+      </c>
+      <c r="T190" t="str">
+        <v/>
+      </c>
+      <c r="U190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="str">
+        <v>IBAN (balance, account, transactions, eligibility)</v>
+      </c>
+      <c r="B191" t="str">
+        <v/>
+      </c>
+      <c r="C191" s="12" t="str">
+        <v>Stuck</v>
+      </c>
+      <c r="D191" s="6" t="str">
+        <v>ApiForM&amp;A</v>
+      </c>
+      <c r="E191" t="str">
+        <v/>
+      </c>
+      <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v/>
+      </c>
+      <c r="I191" t="str">
+        <v/>
+      </c>
+      <c r="J191" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K191" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L191" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M191" t="str">
+        <v/>
+      </c>
+      <c r="N191" s="6" t="str">
+        <v>S</v>
+      </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191" t="str">
+        <v/>
+      </c>
+      <c r="R191" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
       </c>
-      <c r="S190" t="str">
-        <v/>
-      </c>
-      <c r="T190" t="str">
-        <v/>
-      </c>
-      <c r="U190" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="191" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A191" s="9" t="str">
+      <c r="S191" t="str">
+        <v/>
+      </c>
+      <c r="T191" t="str">
+        <v/>
+      </c>
+      <c r="U191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B191" s="10" t="str">
+      <c r="B192" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C191" s="10" t="str">
+      <c r="C192" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D191" s="10" t="str">
+      <c r="D192" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E191" s="10" t="str">
+      <c r="E192" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F191" s="10" t="str">
+      <c r="F192" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G191" s="10" t="str">
+      <c r="G192" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H191" s="10" t="str">
+      <c r="H192" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I191" s="10" t="str">
+      <c r="I192" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J191" s="10" t="str">
+      <c r="J192" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K191" s="10" t="str">
+      <c r="K192" s="10" t="str">
         <v>Priority</v>
       </c>
     </row>
-    <row r="192" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A192" t="str">
-        <v/>
-      </c>
-      <c r="B192" s="4" t="str">
+    <row r="193" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" t="str">
+        <v/>
+      </c>
+      <c r="B193" s="4" t="str">
         <v>getAccounts</v>
       </c>
-      <c r="C192" t="str">
-        <v/>
-      </c>
-      <c r="D192" s="12" t="str">
+      <c r="C193" t="str">
+        <v/>
+      </c>
+      <c r="D193" s="12" t="str">
         <v>Stuck</v>
       </c>
-      <c r="E192" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F192" t="str">
-        <v/>
-      </c>
-      <c r="G192" t="str">
-        <v/>
-      </c>
-      <c r="H192" t="str">
-        <v/>
-      </c>
-      <c r="I192" t="str">
-        <v/>
-      </c>
-      <c r="J192" t="str">
-        <v/>
-      </c>
-      <c r="K192" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="193" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A193" s="4" t="str">
-        <v>Transfer (money bus)</v>
-      </c>
-      <c r="B193" t="str">
-        <v/>
-      </c>
-      <c r="C193" s="12" t="str">
-        <v>Stuck</v>
-      </c>
-      <c r="D193" s="6" t="str">
-        <v>ApiForM&amp;A</v>
-      </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" s="8">
-        <v>46091</v>
-      </c>
-      <c r="G193" s="8">
-        <v>46134</v>
+      <c r="E193" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v/>
+      </c>
+      <c r="G193" t="str">
+        <v/>
       </c>
       <c r="H193" t="str">
         <v/>
@@ -8809,46 +8831,16 @@
       <c r="I193" t="str">
         <v/>
       </c>
-      <c r="J193" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K193" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L193" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M193" t="str">
-        <v/>
-      </c>
-      <c r="N193" s="6" t="str">
-        <v>XS</v>
-      </c>
-      <c r="O193" t="str">
-        <v/>
-      </c>
-      <c r="P193" t="str">
-        <v/>
-      </c>
-      <c r="Q193" t="str">
-        <v/>
-      </c>
-      <c r="R193" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
-      </c>
-      <c r="S193" t="str">
-        <v/>
-      </c>
-      <c r="T193" t="str">
-        <v/>
-      </c>
-      <c r="U193" t="str">
+      <c r="J193" t="str">
+        <v/>
+      </c>
+      <c r="K193" t="str">
         <v/>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="str">
-        <v>Global FTD</v>
+        <v>Transfer (money bus)</v>
       </c>
       <c r="B194" t="str">
         <v/>
@@ -8862,11 +8854,11 @@
       <c r="E194" t="str">
         <v/>
       </c>
-      <c r="F194" t="str">
-        <v/>
-      </c>
-      <c r="G194" t="str">
-        <v/>
+      <c r="F194" s="8">
+        <v>46091</v>
+      </c>
+      <c r="G194" s="8">
+        <v>46134</v>
       </c>
       <c r="H194" t="str">
         <v/>
@@ -8913,13 +8905,13 @@
     </row>
     <row r="195" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="str">
-        <v>Customer Finance</v>
+        <v>Global FTD</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
-      <c r="C195" s="18" t="str">
-        <v>Not Started</v>
+      <c r="C195" s="12" t="str">
+        <v>Stuck</v>
       </c>
       <c r="D195" s="6" t="str">
         <v>ApiForM&amp;A</v>
@@ -8978,12 +8970,12 @@
     </row>
     <row r="196" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="str">
-        <v>Banking (Payee, Withdraw)</v>
+        <v>Customer Finance</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
-      <c r="C196" s="18" t="str">
+      <c r="C196" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="D196" s="6" t="str">
@@ -9017,7 +9009,7 @@
         <v/>
       </c>
       <c r="N196" s="6" t="str">
-        <v/>
+        <v>XS</v>
       </c>
       <c r="O196" t="str">
         <v/>
@@ -9043,16 +9035,16 @@
     </row>
     <row r="197" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="str">
-        <v>CashFlow BFF- Hagit</v>
+        <v>Banking (Payee, Withdraw)</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
-      <c r="C197" s="15" t="str">
-        <v>Discovery</v>
-      </c>
-      <c r="D197" t="str">
-        <v/>
+      <c r="C197" s="19" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="D197" s="6" t="str">
+        <v>ApiForM&amp;A</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -9094,7 +9086,7 @@
         <v/>
       </c>
       <c r="R197" s="6" t="str">
-        <v>Ilan Tatar Feb 12, 2026 1:19 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
       </c>
       <c r="S197" t="str">
         <v/>
@@ -9108,12 +9100,12 @@
     </row>
     <row r="198" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="str">
-        <v>Cash Account BFF- Hagit</v>
+        <v>CashFlow BFF- Hagit</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
-      <c r="C198" s="15" t="str">
+      <c r="C198" s="14" t="str">
         <v>Discovery</v>
       </c>
       <c r="D198" t="str">
@@ -9173,19 +9165,19 @@
     </row>
     <row r="199" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="str">
-        <v>Buy from IBAN</v>
+        <v>Cash Account BFF- Hagit</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
-      <c r="C199" s="21" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="D199" s="6" t="str">
-        <v>ApiForPlus</v>
-      </c>
-      <c r="E199" s="6" t="str">
-        <v>trading BE orch</v>
+      <c r="C199" s="14" t="str">
+        <v>Discovery</v>
+      </c>
+      <c r="D199" t="str">
+        <v/>
+      </c>
+      <c r="E199" t="str">
+        <v/>
       </c>
       <c r="F199" t="str">
         <v/>
@@ -9212,7 +9204,7 @@
         <v/>
       </c>
       <c r="N199" s="6" t="str">
-        <v>XS</v>
+        <v/>
       </c>
       <c r="O199" t="str">
         <v/>
@@ -9224,7 +9216,7 @@
         <v/>
       </c>
       <c r="R199" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+        <v>Ilan Tatar Feb 12, 2026 1:19 PM</v>
       </c>
       <c r="S199" t="str">
         <v/>
@@ -9238,37 +9230,37 @@
     </row>
     <row r="200" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="str">
-        <v>Withdraw +Payment Eligibility</v>
+        <v>Buy from IBAN</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
-      <c r="C200" s="21" t="str">
+      <c r="C200" s="15" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D200" s="6" t="str">
         <v>ApiForPlus</v>
       </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" s="8">
-        <v>46040</v>
-      </c>
-      <c r="G200" s="8">
-        <v>46065</v>
+      <c r="E200" s="6" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="F200" t="str">
+        <v/>
+      </c>
+      <c r="G200" t="str">
+        <v/>
       </c>
       <c r="H200" t="str">
         <v/>
       </c>
-      <c r="I200" s="6" t="str">
-        <v>Using new money bus withdraw orch.</v>
+      <c r="I200" t="str">
+        <v/>
       </c>
       <c r="J200" s="6" t="str">
         <v/>
       </c>
       <c r="K200" s="6" t="str">
-        <v>IRena Plotkin</v>
+        <v/>
       </c>
       <c r="L200" s="6" t="str">
         <v/>
@@ -9277,7 +9269,7 @@
         <v/>
       </c>
       <c r="N200" s="6" t="str">
-        <v>S-M</v>
+        <v>XS</v>
       </c>
       <c r="O200" t="str">
         <v/>
@@ -9303,13 +9295,13 @@
     </row>
     <row r="201" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="str">
-        <v>Financial History- Hagit</v>
+        <v>Withdraw +Payment Eligibility</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
-      <c r="C201" s="19" t="str">
-        <v>Managed by other team</v>
+      <c r="C201" s="15" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="D201" s="6" t="str">
         <v>ApiForPlus</v>
@@ -9321,19 +9313,19 @@
         <v>46040</v>
       </c>
       <c r="G201" s="8">
-        <v>46040</v>
+        <v>46065</v>
       </c>
       <c r="H201" t="str">
         <v/>
       </c>
       <c r="I201" s="6" t="str">
-        <v>add iban mimo &amp; card trx</v>
+        <v>Using new money bus withdraw orch.</v>
       </c>
       <c r="J201" s="6" t="str">
         <v/>
       </c>
       <c r="K201" s="6" t="str">
-        <v/>
+        <v>IRena Plotkin</v>
       </c>
       <c r="L201" s="6" t="str">
         <v/>
@@ -9342,7 +9334,7 @@
         <v/>
       </c>
       <c r="N201" s="6" t="str">
-        <v>S</v>
+        <v>S-M</v>
       </c>
       <c r="O201" t="str">
         <v/>
@@ -9367,239 +9359,239 @@
       </c>
     </row>
     <row r="202" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A202" t="str">
-        <v/>
+      <c r="A202" s="4" t="str">
+        <v>Financial History- Hagit</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
-      <c r="C202" t="str">
-        <v/>
-      </c>
-      <c r="D202" t="str">
-        <v/>
+      <c r="C202" s="23" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D202" s="6" t="str">
+        <v>ApiForPlus</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
-      <c r="F202" s="26">
+      <c r="F202" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G202" s="8">
+        <v>46040</v>
+      </c>
+      <c r="H202" t="str">
+        <v/>
+      </c>
+      <c r="I202" s="6" t="str">
+        <v>add iban mimo &amp; card trx</v>
+      </c>
+      <c r="J202" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K202" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L202" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M202" t="str">
+        <v/>
+      </c>
+      <c r="N202" s="6" t="str">
+        <v>S</v>
+      </c>
+      <c r="O202" t="str">
+        <v/>
+      </c>
+      <c r="P202" t="str">
+        <v/>
+      </c>
+      <c r="Q202" t="str">
+        <v/>
+      </c>
+      <c r="R202" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+      </c>
+      <c r="S202" t="str">
+        <v/>
+      </c>
+      <c r="T202" t="str">
+        <v/>
+      </c>
+      <c r="U202" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A203" t="str">
+        <v/>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v/>
+      </c>
+      <c r="D203" t="str">
+        <v/>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" s="25">
         <v>46036</v>
       </c>
-      <c r="G202" s="26">
+      <c r="G203" s="25">
         <v>46134</v>
       </c>
-      <c r="H202" t="str">
-        <v/>
-      </c>
-      <c r="I202" t="str">
-        <v/>
-      </c>
-      <c r="J202" t="str">
-        <v/>
-      </c>
-      <c r="K202" t="str">
-        <v/>
-      </c>
-      <c r="L202" t="str">
-        <v/>
-      </c>
-      <c r="M202" s="27">
+      <c r="H203" t="str">
+        <v/>
+      </c>
+      <c r="I203" t="str">
+        <v/>
+      </c>
+      <c r="J203" t="str">
+        <v/>
+      </c>
+      <c r="K203" t="str">
+        <v/>
+      </c>
+      <c r="L203" t="str">
+        <v/>
+      </c>
+      <c r="M203" s="26">
         <v>9</v>
       </c>
-      <c r="N202" t="str">
-        <v/>
-      </c>
-      <c r="O202" t="str">
-        <v/>
-      </c>
-      <c r="P202" t="str">
-        <v/>
-      </c>
-      <c r="Q202" s="29" t="str">
-        <v/>
-      </c>
-      <c r="R202" t="str">
-        <v/>
-      </c>
-      <c r="S202" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T202" s="29" t="str">
-        <v/>
-      </c>
-      <c r="U202" s="29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="203" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A204" s="33" t="str">
+      <c r="N203" t="str">
+        <v/>
+      </c>
+      <c r="O203" t="str">
+        <v/>
+      </c>
+      <c r="P203" t="str">
+        <v/>
+      </c>
+      <c r="Q203" s="28" t="str">
+        <v/>
+      </c>
+      <c r="R203" t="str">
+        <v/>
+      </c>
+      <c r="S203" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T203" s="28" t="str">
+        <v/>
+      </c>
+      <c r="U203" s="28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="32" t="str">
         <v>Not in Money scope/Future versions</v>
       </c>
     </row>
-    <row r="205" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A205" s="3" t="str">
+    <row r="206" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B205" s="3" t="str">
+      <c r="B206" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C205" s="3" t="str">
+      <c r="C206" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D205" s="3" t="str">
+      <c r="D206" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E205" s="3" t="str">
+      <c r="E206" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F205" s="3" t="str">
+      <c r="F206" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G205" s="3" t="str">
+      <c r="G206" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H205" s="3" t="str">
+      <c r="H206" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I205" s="3" t="str">
+      <c r="I206" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J205" s="3" t="str">
+      <c r="J206" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K205" s="3" t="str">
+      <c r="K206" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L205" s="3" t="str">
+      <c r="L206" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M205" s="3" t="str">
+      <c r="M206" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N205" s="3" t="str">
+      <c r="N206" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O205" s="3" t="str">
+      <c r="O206" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P205" s="3" t="str">
+      <c r="P206" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q205" s="3" t="str">
+      <c r="Q206" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R205" s="3" t="str">
+      <c r="R206" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S205" s="3" t="str">
+      <c r="S206" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T205" s="3" t="str">
+      <c r="T206" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U205" s="3" t="str">
+      <c r="U206" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="206" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A206" s="4" t="str">
-        <v>Portfolio: Balance breakdown display</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" s="19" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D206" s="6" t="str">
-        <v>Home:Balances&amp; Graph</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" s="8">
-        <v>46076</v>
-      </c>
-      <c r="G206" s="8">
-        <v>46076</v>
-      </c>
-      <c r="H206" t="str">
-        <v/>
-      </c>
-      <c r="I206" t="str">
-        <v/>
-      </c>
-      <c r="J206" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K206" s="6" t="str">
-        <v>Inbal Escholi</v>
-      </c>
-      <c r="L206" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M206" s="6">
-        <v>99</v>
-      </c>
-      <c r="N206" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O206" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1mnu7wyyW4vQQQTn1fJ2Uz4OAAqlZYDXQ</v>
-      </c>
-      <c r="P206" s="6" t="str">
-        <v>Balance</v>
-      </c>
-      <c r="Q206" t="str">
-        <v/>
-      </c>
-      <c r="R206" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
-      </c>
-      <c r="S206" t="str">
-        <v/>
-      </c>
-      <c r="T206" t="str">
-        <v/>
-      </c>
-      <c r="U206" t="str">
-        <v/>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="str">
-        <v>Close to IBAN</v>
+        <v>Portfolio: Balance breakdown display</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
-      <c r="C207" s="19" t="str">
+      <c r="C207" s="23" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D207" s="6" t="str">
-        <v>tradeIBAN</v>
-      </c>
-      <c r="E207" s="6" t="str">
-        <v>trading BE orch</v>
-      </c>
-      <c r="F207" t="str">
-        <v/>
-      </c>
-      <c r="G207" t="str">
-        <v/>
+        <v>Home:Balances&amp; Graph</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" s="8">
+        <v>46076</v>
+      </c>
+      <c r="G207" s="8">
+        <v>46076</v>
       </c>
       <c r="H207" t="str">
         <v/>
       </c>
-      <c r="I207" s="6" t="str">
-        <v>Dependency with Trading- TBD</v>
+      <c r="I207" t="str">
+        <v/>
       </c>
       <c r="J207" s="6" t="str">
-        <v>Joanna</v>
+        <v/>
       </c>
       <c r="K207" s="6" t="str">
-        <v/>
+        <v>Inbal Escholi</v>
       </c>
       <c r="L207" s="6" t="str">
         <v/>
@@ -9611,16 +9603,16 @@
         <v/>
       </c>
       <c r="O207" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1ddNvCALwf6FEU0B0IL99tpwkLeoal_W_</v>
+        <v/>
       </c>
       <c r="P207" s="6" t="str">
-        <v>Local currency, Trading</v>
+        <v>Balance</v>
       </c>
       <c r="Q207" t="str">
         <v/>
       </c>
       <c r="R207" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
       </c>
       <c r="S207" t="str">
         <v/>
@@ -9634,12 +9626,12 @@
     </row>
     <row r="208" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="str">
-        <v>Trade from IBAN (local currency)</v>
+        <v>Close to IBAN</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
-      <c r="C208" s="19" t="str">
+      <c r="C208" s="23" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D208" s="6" t="str">
@@ -9676,7 +9668,7 @@
         <v/>
       </c>
       <c r="O208" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1coMCsTt9H1FUbALyki0_k30a77Ff3Hou</v>
+        <v/>
       </c>
       <c r="P208" s="6" t="str">
         <v>Local currency, Trading</v>
@@ -9699,12 +9691,12 @@
     </row>
     <row r="209" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="str">
-        <v>Exectuion popup - balance drawer</v>
+        <v>Trade from IBAN (local currency)</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
-      <c r="C209" s="19" t="str">
+      <c r="C209" s="23" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D209" s="6" t="str">
@@ -9723,7 +9715,7 @@
         <v/>
       </c>
       <c r="I209" s="6" t="str">
-        <v>Using the SDK + API. Need execution popup BFF</v>
+        <v>Dependency with Trading- TBD</v>
       </c>
       <c r="J209" s="6" t="str">
         <v>Joanna</v>
@@ -9741,10 +9733,10 @@
         <v/>
       </c>
       <c r="O209" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1uRBpFFz5LHbz_kS_QTlKAjAysLDykQKF</v>
+        <v/>
       </c>
       <c r="P209" s="6" t="str">
-        <v>Local currency, Payments</v>
+        <v>Local currency, Trading</v>
       </c>
       <c r="Q209" t="str">
         <v/>
@@ -9764,100 +9756,100 @@
     </row>
     <row r="210" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="str">
+        <v>Exectuion popup - balance drawer</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" s="23" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D210" s="6" t="str">
+        <v>tradeIBAN</v>
+      </c>
+      <c r="E210" s="6" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+      <c r="H210" t="str">
+        <v/>
+      </c>
+      <c r="I210" s="6" t="str">
+        <v>Using the SDK + API. Need execution popup BFF</v>
+      </c>
+      <c r="J210" s="6" t="str">
+        <v>Joanna</v>
+      </c>
+      <c r="K210" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L210" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M210" s="6">
+        <v>99</v>
+      </c>
+      <c r="N210" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O210" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P210" s="6" t="str">
+        <v>Local currency, Payments</v>
+      </c>
+      <c r="Q210" t="str">
+        <v/>
+      </c>
+      <c r="R210" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S210" t="str">
+        <v/>
+      </c>
+      <c r="T210" t="str">
+        <v/>
+      </c>
+      <c r="U210" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="211" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="str">
         <v>Home Page- Balance Display</v>
       </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" s="19" t="str">
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" s="23" t="str">
         <v>Managed by other team</v>
       </c>
-      <c r="D210" s="6" t="str">
+      <c r="D211" s="6" t="str">
         <v>Home:Balances&amp; Graph</v>
       </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" s="8">
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" s="8">
         <v>46076</v>
       </c>
-      <c r="G210" s="8">
+      <c r="G211" s="8">
         <v>46076</v>
       </c>
-      <c r="H210" t="str">
-        <v/>
-      </c>
-      <c r="I210" s="6" t="str">
+      <c r="H211" t="str">
+        <v/>
+      </c>
+      <c r="I211" s="6" t="str">
         <v>Require effort to expose the data from the lake
 Meeting 20/1 - home page redesign</v>
       </c>
-      <c r="J210" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K210" s="6" t="str">
-        <v>Inbal Escholi</v>
-      </c>
-      <c r="L210" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M210" s="6">
-        <v>99</v>
-      </c>
-      <c r="N210" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O210" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1ajgQLvU3kxLq70yAZZBcFppbac3M02Jm</v>
-      </c>
-      <c r="P210" s="6" t="str">
-        <v>Balance</v>
-      </c>
-      <c r="Q210" s="7">
-        <v>46083</v>
-      </c>
-      <c r="R210" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S210" t="str">
-        <v/>
-      </c>
-      <c r="T210" t="str">
-        <v/>
-      </c>
-      <c r="U210" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="211" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A211" s="4" t="str">
-        <v>Recurring Investment</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" s="19" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D211" s="6" t="str">
-        <v>recurInvestment</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" s="8">
-        <v>46105</v>
-      </c>
-      <c r="G211" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H211" t="str">
-        <v/>
-      </c>
-      <c r="I211" t="str">
-        <v/>
-      </c>
       <c r="J211" s="6" t="str">
-        <v>Noit</v>
+        <v/>
       </c>
       <c r="K211" s="6" t="str">
         <v>Inbal Escholi</v>
@@ -9871,14 +9863,14 @@
       <c r="N211" s="6" t="str">
         <v/>
       </c>
-      <c r="O211" t="str">
+      <c r="O211" s="6" t="str">
         <v/>
       </c>
       <c r="P211" s="6" t="str">
-        <v>Payments, Recurring Investment</v>
-      </c>
-      <c r="Q211" t="str">
-        <v/>
+        <v>Balance</v>
+      </c>
+      <c r="Q211" s="7">
+        <v>46083</v>
       </c>
       <c r="R211" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
@@ -9893,74 +9885,104 @@
         <v/>
       </c>
     </row>
-    <row r="212" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A212" s="9" t="str">
+    <row r="212" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="str">
+        <v>Recurring Investment</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" s="23" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D212" s="6" t="str">
+        <v>recurInvestment</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" s="8">
+        <v>46105</v>
+      </c>
+      <c r="G212" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H212" t="str">
+        <v/>
+      </c>
+      <c r="I212" t="str">
+        <v/>
+      </c>
+      <c r="J212" s="6" t="str">
+        <v>Noit</v>
+      </c>
+      <c r="K212" s="6" t="str">
+        <v>Inbal Escholi</v>
+      </c>
+      <c r="L212" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M212" s="6">
+        <v>99</v>
+      </c>
+      <c r="N212" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O212" t="str">
+        <v/>
+      </c>
+      <c r="P212" s="6" t="str">
+        <v>Payments, Recurring Investment</v>
+      </c>
+      <c r="Q212" t="str">
+        <v/>
+      </c>
+      <c r="R212" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S212" t="str">
+        <v/>
+      </c>
+      <c r="T212" t="str">
+        <v/>
+      </c>
+      <c r="U212" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="213" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A213" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B212" s="10" t="str">
+      <c r="B213" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C212" s="10" t="str">
+      <c r="C213" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D212" s="10" t="str">
+      <c r="D213" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E212" s="10" t="str">
+      <c r="E213" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F212" s="10" t="str">
+      <c r="F213" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G212" s="10" t="str">
+      <c r="G213" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H212" s="10" t="str">
+      <c r="H213" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I212" s="10" t="str">
+      <c r="I213" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J212" s="10" t="str">
+      <c r="J213" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K212" s="10" t="str">
+      <c r="K213" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="213" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A213" t="str">
-        <v/>
-      </c>
-      <c r="B213" s="4" t="str">
-        <v>Recurring investment - card details</v>
-      </c>
-      <c r="C213" t="str">
-        <v/>
-      </c>
-      <c r="D213" s="18" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="E213" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v/>
-      </c>
-      <c r="G213" s="6" t="str">
-        <v>Payments</v>
-      </c>
-      <c r="H213" t="str">
-        <v/>
-      </c>
-      <c r="I213" t="str">
-        <v/>
-      </c>
-      <c r="J213" t="str">
-        <v/>
-      </c>
-      <c r="K213" t="str">
-        <v/>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -9968,50 +9990,50 @@
         <v/>
       </c>
       <c r="B214" s="4" t="str">
+        <v>Recurring investment - card details</v>
+      </c>
+      <c r="C214" t="str">
+        <v/>
+      </c>
+      <c r="D214" s="19" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="E214" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v/>
+      </c>
+      <c r="G214" s="6" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="H214" t="str">
+        <v/>
+      </c>
+      <c r="I214" t="str">
+        <v/>
+      </c>
+      <c r="J214" t="str">
+        <v/>
+      </c>
+      <c r="K214" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="215" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A215" t="str">
+        <v/>
+      </c>
+      <c r="B215" s="4" t="str">
         <v>Recurring investment feature</v>
       </c>
-      <c r="C214" t="str">
-        <v/>
-      </c>
-      <c r="D214" s="18" t="str">
+      <c r="C215" t="str">
+        <v/>
+      </c>
+      <c r="D215" s="19" t="str">
         <v>Not Started</v>
       </c>
-      <c r="E214" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v/>
-      </c>
-      <c r="G214" t="str">
-        <v/>
-      </c>
-      <c r="H214" t="str">
-        <v/>
-      </c>
-      <c r="I214" t="str">
-        <v/>
-      </c>
-      <c r="J214" t="str">
-        <v/>
-      </c>
-      <c r="K214" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="215" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A215" s="4" t="str">
-        <v>IBAN - Club Upgrades for Account Programs</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" s="22" t="str">
-        <v>Future Version</v>
-      </c>
-      <c r="D215" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="E215" t="str">
+      <c r="E215" s="6" t="str">
         <v/>
       </c>
       <c r="F215" t="str">
@@ -10026,46 +10048,16 @@
       <c r="I215" t="str">
         <v/>
       </c>
-      <c r="J215" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K215" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L215" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M215" s="6">
-        <v>100</v>
-      </c>
-      <c r="N215" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O215" t="str">
-        <v/>
-      </c>
-      <c r="P215" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="Q215" t="str">
-        <v/>
-      </c>
-      <c r="R215" s="6" t="str">
-        <v>Hagit Zamir Feb 3, 2026 3:42 PM</v>
-      </c>
-      <c r="S215" t="str">
-        <v/>
-      </c>
-      <c r="T215" t="str">
-        <v/>
-      </c>
-      <c r="U215" t="str">
+      <c r="J215" t="str">
+        <v/>
+      </c>
+      <c r="K215" t="str">
         <v/>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="str">
-        <v>Wallet tab - IBAN - Direct Debit</v>
+        <v>IBAN - Club Upgrades for Account Programs</v>
       </c>
       <c r="B216" t="str">
         <v/>
@@ -10074,7 +10066,7 @@
         <v>Future Version</v>
       </c>
       <c r="D216" s="6" t="str">
-        <v>ManageDirectDebit</v>
+        <v>Banking</v>
       </c>
       <c r="E216" t="str">
         <v/>
@@ -10088,11 +10080,11 @@
       <c r="H216" t="str">
         <v/>
       </c>
-      <c r="I216" s="6" t="str">
-        <v>Web only (mobile web is optional)</v>
+      <c r="I216" t="str">
+        <v/>
       </c>
       <c r="J216" s="6" t="str">
-        <v>Adi</v>
+        <v/>
       </c>
       <c r="K216" s="6" t="str">
         <v/>
@@ -10106,8 +10098,8 @@
       <c r="N216" s="6" t="str">
         <v/>
       </c>
-      <c r="O216" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1ckH93ib0CmcIINKUzOdZWWhqNbnIAiZi</v>
+      <c r="O216" t="str">
+        <v/>
       </c>
       <c r="P216" s="6" t="str">
         <v>Banking</v>
@@ -10116,7 +10108,7 @@
         <v/>
       </c>
       <c r="R216" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+        <v>Hagit Zamir Feb 3, 2026 3:42 PM</v>
       </c>
       <c r="S216" t="str">
         <v/>
@@ -10130,7 +10122,7 @@
     </row>
     <row r="217" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="str">
-        <v>Crypto-in/out - New Flow</v>
+        <v>Wallet tab - IBAN - Direct Debit</v>
       </c>
       <c r="B217" t="str">
         <v/>
@@ -10138,29 +10130,29 @@
       <c r="C217" s="22" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D217" t="str">
-        <v/>
+      <c r="D217" s="6" t="str">
+        <v>ManageDirectDebit</v>
       </c>
       <c r="E217" t="str">
         <v/>
       </c>
-      <c r="F217" s="8">
-        <v>46061</v>
-      </c>
-      <c r="G217" s="8">
-        <v>46075</v>
+      <c r="F217" t="str">
+        <v/>
+      </c>
+      <c r="G217" t="str">
+        <v/>
       </c>
       <c r="H217" t="str">
         <v/>
       </c>
-      <c r="I217" t="str">
-        <v/>
+      <c r="I217" s="6" t="str">
+        <v>Web only (mobile web is optional)</v>
       </c>
       <c r="J217" s="6" t="str">
-        <v>Nikolaus Kulier</v>
+        <v>Adi</v>
       </c>
       <c r="K217" s="6" t="str">
-        <v>Inbal Escholi</v>
+        <v/>
       </c>
       <c r="L217" s="6" t="str">
         <v/>
@@ -10172,95 +10164,125 @@
         <v/>
       </c>
       <c r="O217" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1T9bzCpQdskwwMHl_F_RF-WzMtTOtaaem</v>
+        <v/>
       </c>
       <c r="P217" s="6" t="str">
+        <v>Banking</v>
+      </c>
+      <c r="Q217" t="str">
+        <v/>
+      </c>
+      <c r="R217" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S217" t="str">
+        <v/>
+      </c>
+      <c r="T217" t="str">
+        <v/>
+      </c>
+      <c r="U217" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="218" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="str">
+        <v>Crypto-in/out - New Flow</v>
+      </c>
+      <c r="B218" t="str">
+        <v/>
+      </c>
+      <c r="C218" s="22" t="str">
+        <v>Future Version</v>
+      </c>
+      <c r="D218" t="str">
+        <v/>
+      </c>
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" s="8">
+        <v>46061</v>
+      </c>
+      <c r="G218" s="8">
+        <v>46075</v>
+      </c>
+      <c r="H218" t="str">
+        <v/>
+      </c>
+      <c r="I218" t="str">
+        <v/>
+      </c>
+      <c r="J218" s="6" t="str">
+        <v>Nikolaus Kulier</v>
+      </c>
+      <c r="K218" s="6" t="str">
+        <v>Inbal Escholi</v>
+      </c>
+      <c r="L218" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M218" s="6">
+        <v>100</v>
+      </c>
+      <c r="N218" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O218" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P218" s="6" t="str">
         <v>Crypto</v>
       </c>
-      <c r="Q217" t="str">
-        <v/>
-      </c>
-      <c r="R217" s="6" t="str">
+      <c r="Q218" t="str">
+        <v/>
+      </c>
+      <c r="R218" s="6" t="str">
         <v>Hagit Zamir Feb 3, 2026 11:58 AM</v>
       </c>
-      <c r="S217" t="str">
-        <v/>
-      </c>
-      <c r="T217" t="str">
-        <v/>
-      </c>
-      <c r="U217" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="218" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A218" s="9" t="str">
+      <c r="S218" t="str">
+        <v/>
+      </c>
+      <c r="T218" t="str">
+        <v/>
+      </c>
+      <c r="U218" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="219" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A219" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B218" s="10" t="str">
+      <c r="B219" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C218" s="10" t="str">
+      <c r="C219" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D218" s="10" t="str">
+      <c r="D219" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E218" s="10" t="str">
+      <c r="E219" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F218" s="10" t="str">
+      <c r="F219" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G218" s="10" t="str">
+      <c r="G219" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H218" s="10" t="str">
+      <c r="H219" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I218" s="10" t="str">
+      <c r="I219" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J218" s="10" t="str">
+      <c r="J219" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K218" s="10" t="str">
+      <c r="K219" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="219" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A219" t="str">
-        <v/>
-      </c>
-      <c r="B219" s="4" t="str">
-        <v>New Crypto in flow</v>
-      </c>
-      <c r="C219" t="str">
-        <v/>
-      </c>
-      <c r="D219" s="18" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="E219" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F219" t="str">
-        <v/>
-      </c>
-      <c r="G219" t="str">
-        <v/>
-      </c>
-      <c r="H219" t="str">
-        <v/>
-      </c>
-      <c r="I219" t="str">
-        <v/>
-      </c>
-      <c r="J219" t="str">
-        <v/>
-      </c>
-      <c r="K219" t="str">
-        <v/>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -10268,50 +10290,50 @@
         <v/>
       </c>
       <c r="B220" s="4" t="str">
+        <v>New Crypto in flow</v>
+      </c>
+      <c r="C220" t="str">
+        <v/>
+      </c>
+      <c r="D220" s="19" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="E220" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
+        <v/>
+      </c>
+      <c r="G220" t="str">
+        <v/>
+      </c>
+      <c r="H220" t="str">
+        <v/>
+      </c>
+      <c r="I220" t="str">
+        <v/>
+      </c>
+      <c r="J220" t="str">
+        <v/>
+      </c>
+      <c r="K220" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="221" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A221" t="str">
+        <v/>
+      </c>
+      <c r="B221" s="4" t="str">
         <v>New Crypto out flow</v>
       </c>
-      <c r="C220" t="str">
-        <v/>
-      </c>
-      <c r="D220" s="18" t="str">
+      <c r="C221" t="str">
+        <v/>
+      </c>
+      <c r="D221" s="19" t="str">
         <v>Not Started</v>
       </c>
-      <c r="E220" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F220" t="str">
-        <v/>
-      </c>
-      <c r="G220" t="str">
-        <v/>
-      </c>
-      <c r="H220" t="str">
-        <v/>
-      </c>
-      <c r="I220" t="str">
-        <v/>
-      </c>
-      <c r="J220" t="str">
-        <v/>
-      </c>
-      <c r="K220" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="221" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A221" s="4" t="str">
-        <v>Account statement - IBAN</v>
-      </c>
-      <c r="B221" t="str">
-        <v/>
-      </c>
-      <c r="C221" s="22" t="str">
-        <v>Future Version</v>
-      </c>
-      <c r="D221" s="6" t="str">
-        <v>acctStatement</v>
-      </c>
-      <c r="E221" t="str">
+      <c r="E221" s="6" t="str">
         <v/>
       </c>
       <c r="F221" t="str">
@@ -10326,46 +10348,16 @@
       <c r="I221" t="str">
         <v/>
       </c>
-      <c r="J221" s="6" t="str">
-        <v>Richard</v>
-      </c>
-      <c r="K221" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L221" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M221" s="6">
-        <v>100</v>
-      </c>
-      <c r="N221" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O221" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1YGwoAq790Wb8Iudfx3nh276XbPp4uDF1</v>
-      </c>
-      <c r="P221" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="Q221" t="str">
-        <v/>
-      </c>
-      <c r="R221" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S221" t="str">
-        <v/>
-      </c>
-      <c r="T221" t="str">
-        <v/>
-      </c>
-      <c r="U221" t="str">
+      <c r="J221" t="str">
+        <v/>
+      </c>
+      <c r="K221" t="str">
         <v/>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="str">
-        <v>Wallet tab - Global banners- Transactional Banners</v>
+        <v>Account statement - IBAN</v>
       </c>
       <c r="B222" t="str">
         <v/>
@@ -10374,7 +10366,7 @@
         <v>Future Version</v>
       </c>
       <c r="D222" s="6" t="str">
-        <v>WalletTab</v>
+        <v>acctStatement</v>
       </c>
       <c r="E222" t="str">
         <v/>
@@ -10388,11 +10380,11 @@
       <c r="H222" t="str">
         <v/>
       </c>
-      <c r="I222" s="6" t="str">
-        <v>Meeting 20/1 - home page redesign</v>
+      <c r="I222" t="str">
+        <v/>
       </c>
       <c r="J222" s="6" t="str">
-        <v>Adi</v>
+        <v>Richard</v>
       </c>
       <c r="K222" s="6" t="str">
         <v/>
@@ -10407,10 +10399,10 @@
         <v/>
       </c>
       <c r="O222" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1lvshcV8HLj_Iyu76ode34g2d_JhKBOze</v>
+        <v/>
       </c>
       <c r="P222" s="6" t="str">
-        <v>Banking, Card Mng.</v>
+        <v>Banking</v>
       </c>
       <c r="Q222" t="str">
         <v/>
@@ -10430,7 +10422,7 @@
     </row>
     <row r="223" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="str">
-        <v>Long term solution for Trade button between Money and Trading</v>
+        <v>Wallet tab - Global banners- Transactional Banners</v>
       </c>
       <c r="B223" t="str">
         <v/>
@@ -10438,8 +10430,8 @@
       <c r="C223" s="22" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D223" t="str">
-        <v/>
+      <c r="D223" s="6" t="str">
+        <v>WalletTab</v>
       </c>
       <c r="E223" t="str">
         <v/>
@@ -10453,11 +10445,11 @@
       <c r="H223" t="str">
         <v/>
       </c>
-      <c r="I223" t="str">
-        <v/>
+      <c r="I223" s="6" t="str">
+        <v>Meeting 20/1 - home page redesign</v>
       </c>
       <c r="J223" s="6" t="str">
-        <v/>
+        <v>Adi</v>
       </c>
       <c r="K223" s="6" t="str">
         <v/>
@@ -10471,17 +10463,17 @@
       <c r="N223" s="6" t="str">
         <v/>
       </c>
-      <c r="O223" t="str">
-        <v/>
-      </c>
-      <c r="P223" t="str">
-        <v/>
+      <c r="O223" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P223" s="6" t="str">
+        <v>Banking, Card Mng.</v>
       </c>
       <c r="Q223" t="str">
         <v/>
       </c>
       <c r="R223" s="6" t="str">
-        <v>Ilan Tatar Mar 9, 2026 2:46 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
       <c r="S223" t="str">
         <v/>
@@ -10495,7 +10487,7 @@
     </row>
     <row r="224" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="str">
-        <v>NCW in eToro Plus</v>
+        <v>Long term solution for Trade button between Money and Trading</v>
       </c>
       <c r="B224" t="str">
         <v/>
@@ -10518,11 +10510,11 @@
       <c r="H224" t="str">
         <v/>
       </c>
-      <c r="I224" s="6" t="str">
-        <v>Dependency with Compliance</v>
+      <c r="I224" t="str">
+        <v/>
       </c>
       <c r="J224" s="6" t="str">
-        <v>Nikolaus Kulier</v>
+        <v/>
       </c>
       <c r="K224" s="6" t="str">
         <v/>
@@ -10536,17 +10528,17 @@
       <c r="N224" s="6" t="str">
         <v/>
       </c>
-      <c r="O224" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1pmEz5faaG4dEEUBCP93uCA8HuUcY4q5r</v>
-      </c>
-      <c r="P224" s="6" t="str">
-        <v>Crypto</v>
+      <c r="O224" t="str">
+        <v/>
+      </c>
+      <c r="P224" t="str">
+        <v/>
       </c>
       <c r="Q224" t="str">
         <v/>
       </c>
       <c r="R224" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+        <v>Ilan Tatar Mar 9, 2026 2:46 PM</v>
       </c>
       <c r="S224" t="str">
         <v/>
@@ -10560,7 +10552,7 @@
     </row>
     <row r="225" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="str">
-        <v>Wallet Tab - Product Promotions (all products - Local Accounts / ISA / Crypto etc etc)</v>
+        <v>NCW in eToro Plus</v>
       </c>
       <c r="B225" t="str">
         <v/>
@@ -10568,8 +10560,8 @@
       <c r="C225" s="22" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D225" s="6" t="str">
-        <v>WalletTabTotalValueGraph</v>
+      <c r="D225" t="str">
+        <v/>
       </c>
       <c r="E225" t="str">
         <v/>
@@ -10583,11 +10575,11 @@
       <c r="H225" t="str">
         <v/>
       </c>
-      <c r="I225" t="str">
-        <v/>
+      <c r="I225" s="6" t="str">
+        <v>Dependency with Compliance</v>
       </c>
       <c r="J225" s="6" t="str">
-        <v>Adi</v>
+        <v>Nikolaus Kulier</v>
       </c>
       <c r="K225" s="6" t="str">
         <v/>
@@ -10596,22 +10588,22 @@
         <v/>
       </c>
       <c r="M225" s="6">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="N225" s="6" t="str">
         <v/>
       </c>
       <c r="O225" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1lu17LS1984RvIkY8iqJEjH6fS-wJvZta</v>
+        <v/>
       </c>
       <c r="P225" s="6" t="str">
-        <v>Wallet Tab</v>
+        <v>Crypto</v>
       </c>
       <c r="Q225" t="str">
         <v/>
       </c>
       <c r="R225" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:28 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
       <c r="S225" t="str">
         <v/>
@@ -10625,16 +10617,16 @@
     </row>
     <row r="226" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="str">
-        <v>Trigger Web Deposit workaround for 20.4- Inbal</v>
+        <v>Wallet Tab - Product Promotions (all products - Local Accounts / ISA / Crypto etc etc)</v>
       </c>
       <c r="B226" t="str">
         <v/>
       </c>
-      <c r="C226" s="21" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="D226" t="str">
-        <v/>
+      <c r="C226" s="22" t="str">
+        <v>Future Version</v>
+      </c>
+      <c r="D226" s="6" t="str">
+        <v>WalletTabTotalValueGraph</v>
       </c>
       <c r="E226" t="str">
         <v/>
@@ -10652,7 +10644,7 @@
         <v/>
       </c>
       <c r="J226" s="6" t="str">
-        <v>Richard</v>
+        <v>Adi</v>
       </c>
       <c r="K226" s="6" t="str">
         <v/>
@@ -10661,22 +10653,22 @@
         <v/>
       </c>
       <c r="M226" s="6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N226" s="6" t="str">
         <v/>
       </c>
-      <c r="O226" t="str">
-        <v/>
-      </c>
-      <c r="P226" t="str">
-        <v/>
+      <c r="O226" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P226" s="6" t="str">
+        <v>Wallet Tab</v>
       </c>
       <c r="Q226" t="str">
         <v/>
       </c>
       <c r="R226" s="6" t="str">
-        <v>Ilan Tatar Mar 4, 2026 2:45 PM</v>
+        <v>Ilan Tatar Jan 28, 2026 6:28 PM</v>
       </c>
       <c r="S226" t="str">
         <v/>
@@ -10690,16 +10682,16 @@
     </row>
     <row r="227" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="str">
-        <v>Wallet Tab - Balances list</v>
+        <v>Trigger Web Deposit workaround for 20.4- Inbal</v>
       </c>
       <c r="B227" t="str">
         <v/>
       </c>
-      <c r="C227" s="21" t="str">
+      <c r="C227" s="15" t="str">
         <v>Cancelled</v>
       </c>
-      <c r="D227" s="6" t="str">
-        <v>WalletTabTotalValueGraph</v>
+      <c r="D227" t="str">
+        <v/>
       </c>
       <c r="E227" t="str">
         <v/>
@@ -10717,7 +10709,7 @@
         <v/>
       </c>
       <c r="J227" s="6" t="str">
-        <v>Adi</v>
+        <v>Richard</v>
       </c>
       <c r="K227" s="6" t="str">
         <v/>
@@ -10726,22 +10718,22 @@
         <v/>
       </c>
       <c r="M227" s="6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N227" s="6" t="str">
         <v/>
       </c>
-      <c r="O227" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/10j0uo11-TGKBFj82pUueB78g_uihED_F</v>
-      </c>
-      <c r="P227" s="6" t="str">
-        <v>Balance</v>
+      <c r="O227" t="str">
+        <v/>
+      </c>
+      <c r="P227" t="str">
+        <v/>
       </c>
       <c r="Q227" t="str">
         <v/>
       </c>
       <c r="R227" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:16 PM</v>
+        <v>Ilan Tatar Mar 4, 2026 2:45 PM</v>
       </c>
       <c r="S227" t="str">
         <v/>
@@ -10755,25 +10747,25 @@
     </row>
     <row r="228" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="str">
-        <v>Watchlist: Balance breakdown display</v>
+        <v>Wallet Tab - Balances list</v>
       </c>
       <c r="B228" t="str">
         <v/>
       </c>
-      <c r="C228" s="21" t="str">
+      <c r="C228" s="15" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D228" s="6" t="str">
-        <v>Home:Balances&amp; Graph</v>
+        <v>WalletTabTotalValueGraph</v>
       </c>
       <c r="E228" t="str">
         <v/>
       </c>
-      <c r="F228" s="8">
-        <v>46076</v>
-      </c>
-      <c r="G228" s="8">
-        <v>46076</v>
+      <c r="F228" t="str">
+        <v/>
+      </c>
+      <c r="G228" t="str">
+        <v/>
       </c>
       <c r="H228" t="str">
         <v/>
@@ -10782,10 +10774,10 @@
         <v/>
       </c>
       <c r="J228" s="6" t="str">
-        <v/>
+        <v>Adi</v>
       </c>
       <c r="K228" s="6" t="str">
-        <v>Inbal Escholi</v>
+        <v/>
       </c>
       <c r="L228" s="6" t="str">
         <v/>
@@ -10797,7 +10789,7 @@
         <v/>
       </c>
       <c r="O228" s="6" t="str">
-        <v>https://drive.google.com/drive/u/0/folders/1zjptd0Ar2VSiDWkXRLTOFCR4pUHOZSJH</v>
+        <v/>
       </c>
       <c r="P228" s="6" t="str">
         <v>Balance</v>
@@ -10806,7 +10798,7 @@
         <v/>
       </c>
       <c r="R228" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
+        <v>Ilan Tatar Jan 28, 2026 6:16 PM</v>
       </c>
       <c r="S228" t="str">
         <v/>
@@ -10820,279 +10812,279 @@
     </row>
     <row r="229" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="str">
+        <v>Watchlist: Balance breakdown display</v>
+      </c>
+      <c r="B229" t="str">
+        <v/>
+      </c>
+      <c r="C229" s="15" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D229" s="6" t="str">
+        <v>Home:Balances&amp; Graph</v>
+      </c>
+      <c r="E229" t="str">
+        <v/>
+      </c>
+      <c r="F229" s="8">
+        <v>46076</v>
+      </c>
+      <c r="G229" s="8">
+        <v>46076</v>
+      </c>
+      <c r="H229" t="str">
+        <v/>
+      </c>
+      <c r="I229" t="str">
+        <v/>
+      </c>
+      <c r="J229" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K229" s="6" t="str">
+        <v>Inbal Escholi</v>
+      </c>
+      <c r="L229" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M229" s="6">
+        <v>-1</v>
+      </c>
+      <c r="N229" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O229" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P229" s="6" t="str">
+        <v>Balance</v>
+      </c>
+      <c r="Q229" t="str">
+        <v/>
+      </c>
+      <c r="R229" s="6" t="str">
+        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
+      </c>
+      <c r="S229" t="str">
+        <v/>
+      </c>
+      <c r="T229" t="str">
+        <v/>
+      </c>
+      <c r="U229" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="230" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="str">
         <v>Payment Client Technical gaps for aftr launch</v>
       </c>
-      <c r="B229" t="str">
-        <v/>
-      </c>
-      <c r="C229" s="22" t="str">
+      <c r="B230" t="str">
+        <v/>
+      </c>
+      <c r="C230" s="22" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D229" t="str">
-        <v/>
-      </c>
-      <c r="E229" t="str">
-        <v/>
-      </c>
-      <c r="F229" t="str">
-        <v/>
-      </c>
-      <c r="G229" t="str">
-        <v/>
-      </c>
-      <c r="H229" t="str">
-        <v/>
-      </c>
-      <c r="I229" t="str">
-        <v/>
-      </c>
-      <c r="J229" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K229" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L229" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M229" t="str">
-        <v/>
-      </c>
-      <c r="N229" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O229" t="str">
-        <v/>
-      </c>
-      <c r="P229" t="str">
-        <v/>
-      </c>
-      <c r="Q229" t="str">
-        <v/>
-      </c>
-      <c r="R229" s="6" t="str">
+      <c r="D230" t="str">
+        <v/>
+      </c>
+      <c r="E230" t="str">
+        <v/>
+      </c>
+      <c r="F230" t="str">
+        <v/>
+      </c>
+      <c r="G230" t="str">
+        <v/>
+      </c>
+      <c r="H230" t="str">
+        <v/>
+      </c>
+      <c r="I230" t="str">
+        <v/>
+      </c>
+      <c r="J230" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K230" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L230" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M230" t="str">
+        <v/>
+      </c>
+      <c r="N230" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O230" t="str">
+        <v/>
+      </c>
+      <c r="P230" t="str">
+        <v/>
+      </c>
+      <c r="Q230" t="str">
+        <v/>
+      </c>
+      <c r="R230" s="6" t="str">
         <v>Ilan Tatar Apr 12, 2026 12:56 PM</v>
       </c>
-      <c r="S229" t="str">
-        <v/>
-      </c>
-      <c r="T229" t="str">
-        <v/>
-      </c>
-      <c r="U229" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="230" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A230" t="str">
-        <v/>
-      </c>
-      <c r="B230" t="str">
-        <v/>
-      </c>
-      <c r="C230" t="str">
-        <v/>
-      </c>
-      <c r="D230" t="str">
-        <v/>
-      </c>
-      <c r="E230" t="str">
-        <v/>
-      </c>
-      <c r="F230" s="26">
+      <c r="S230" t="str">
+        <v/>
+      </c>
+      <c r="T230" t="str">
+        <v/>
+      </c>
+      <c r="U230" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A231" t="str">
+        <v/>
+      </c>
+      <c r="B231" t="str">
+        <v/>
+      </c>
+      <c r="C231" t="str">
+        <v/>
+      </c>
+      <c r="D231" t="str">
+        <v/>
+      </c>
+      <c r="E231" t="str">
+        <v/>
+      </c>
+      <c r="F231" s="25">
         <v>46061</v>
       </c>
-      <c r="G230" s="26">
+      <c r="G231" s="25">
         <v>46132</v>
       </c>
-      <c r="H230" t="str">
-        <v/>
-      </c>
-      <c r="I230" t="str">
-        <v/>
-      </c>
-      <c r="J230" t="str">
-        <v/>
-      </c>
-      <c r="K230" t="str">
-        <v/>
-      </c>
-      <c r="L230" t="str">
-        <v/>
-      </c>
-      <c r="M230" s="27">
+      <c r="H231" t="str">
+        <v/>
+      </c>
+      <c r="I231" t="str">
+        <v/>
+      </c>
+      <c r="J231" t="str">
+        <v/>
+      </c>
+      <c r="K231" t="str">
+        <v/>
+      </c>
+      <c r="L231" t="str">
+        <v/>
+      </c>
+      <c r="M231" s="26">
         <v>1292</v>
       </c>
-      <c r="N230" t="str">
-        <v/>
-      </c>
-      <c r="O230" t="str">
-        <v/>
-      </c>
-      <c r="P230" t="str">
-        <v/>
-      </c>
-      <c r="Q230" s="28" t="str">
+      <c r="N231" t="str">
+        <v/>
+      </c>
+      <c r="O231" t="str">
+        <v/>
+      </c>
+      <c r="P231" t="str">
+        <v/>
+      </c>
+      <c r="Q231" s="27" t="str">
         <v>2026-03-02</v>
       </c>
-      <c r="R230" t="str">
-        <v/>
-      </c>
-      <c r="S230" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T230" s="29" t="str">
-        <v/>
-      </c>
-      <c r="U230" s="29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="231" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232" s="34" t="str">
+      <c r="R231" t="str">
+        <v/>
+      </c>
+      <c r="S231" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T231" s="28" t="str">
+        <v/>
+      </c>
+      <c r="U231" s="28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="232" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="33" t="str">
         <v>Program Milestones</v>
       </c>
     </row>
-    <row r="233" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A233" s="3" t="str">
+    <row r="234" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A234" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B233" s="3" t="str">
+      <c r="B234" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C233" s="3" t="str">
+      <c r="C234" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D233" s="3" t="str">
+      <c r="D234" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E233" s="3" t="str">
+      <c r="E234" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F233" s="3" t="str">
+      <c r="F234" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G233" s="3" t="str">
+      <c r="G234" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H233" s="3" t="str">
+      <c r="H234" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I233" s="3" t="str">
+      <c r="I234" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J233" s="3" t="str">
+      <c r="J234" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K233" s="3" t="str">
+      <c r="K234" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L233" s="3" t="str">
+      <c r="L234" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M233" s="3" t="str">
+      <c r="M234" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N233" s="3" t="str">
+      <c r="N234" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O233" s="3" t="str">
+      <c r="O234" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P233" s="3" t="str">
+      <c r="P234" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q233" s="3" t="str">
+      <c r="Q234" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R233" s="3" t="str">
+      <c r="R234" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S233" s="3" t="str">
+      <c r="S234" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T233" s="3" t="str">
+      <c r="T234" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U233" s="3" t="str">
+      <c r="U234" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="234" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A234" s="4" t="str">
-        <v>STD + Swaggers</v>
-      </c>
-      <c r="B234" t="str">
-        <v/>
-      </c>
-      <c r="C234" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="D234" t="str">
-        <v/>
-      </c>
-      <c r="E234" t="str">
-        <v/>
-      </c>
-      <c r="F234" s="8">
-        <v>46048</v>
-      </c>
-      <c r="G234" s="8">
-        <v>46048</v>
-      </c>
-      <c r="H234" t="str">
-        <v/>
-      </c>
-      <c r="I234" t="str">
-        <v/>
-      </c>
-      <c r="J234" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K234" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L234" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M234" t="str">
-        <v/>
-      </c>
-      <c r="N234" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O234" t="str">
-        <v/>
-      </c>
-      <c r="P234" t="str">
-        <v/>
-      </c>
-      <c r="Q234" t="str">
-        <v/>
-      </c>
-      <c r="R234" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:19 PM</v>
-      </c>
-      <c r="S234" t="str">
-        <v/>
-      </c>
-      <c r="T234" t="str">
-        <v/>
-      </c>
-      <c r="U234" t="str">
-        <v/>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="str">
-        <v>Critical APIs in production</v>
+        <v>STD + Swaggers</v>
       </c>
       <c r="B235" t="str">
         <v/>
       </c>
-      <c r="C235" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C235" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D235" t="str">
         <v/>
@@ -11101,10 +11093,10 @@
         <v/>
       </c>
       <c r="F235" s="8">
-        <v>46112</v>
+        <v>46048</v>
       </c>
       <c r="G235" s="8">
-        <v>46127</v>
+        <v>46048</v>
       </c>
       <c r="H235" t="str">
         <v/>
@@ -11137,7 +11129,7 @@
         <v/>
       </c>
       <c r="R235" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:15 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:19 PM</v>
       </c>
       <c r="S235" t="str">
         <v/>
@@ -11151,7 +11143,7 @@
     </row>
     <row r="236" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="str">
-        <v>Non critical APIs in prodcution</v>
+        <v>Critical APIs in production</v>
       </c>
       <c r="B236" t="str">
         <v/>
@@ -11166,11 +11158,11 @@
         <v/>
       </c>
       <c r="F236" s="8">
+        <v>46112</v>
+      </c>
+      <c r="G236" s="8">
         <v>46127</v>
       </c>
-      <c r="G236" s="8">
-        <v>46142</v>
-      </c>
       <c r="H236" t="str">
         <v/>
       </c>
@@ -11202,7 +11194,7 @@
         <v/>
       </c>
       <c r="R236" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:15 PM</v>
       </c>
       <c r="S236" t="str">
         <v/>
@@ -11216,13 +11208,13 @@
     </row>
     <row r="237" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="str">
-        <v>E2E readiness</v>
+        <v>Non critical APIs in prodcution</v>
       </c>
       <c r="B237" t="str">
         <v/>
       </c>
-      <c r="C237" s="18" t="str">
-        <v>Not Started</v>
+      <c r="C237" s="5" t="str">
+        <v>FE DEV WIP</v>
       </c>
       <c r="D237" t="str">
         <v/>
@@ -11231,16 +11223,16 @@
         <v/>
       </c>
       <c r="F237" s="8">
-        <v>46145</v>
+        <v>46127</v>
       </c>
       <c r="G237" s="8">
-        <v>46145</v>
+        <v>46142</v>
       </c>
       <c r="H237" t="str">
         <v/>
       </c>
-      <c r="I237" s="6" t="str">
-        <v>E2E to start in Mid May + 1.5 weeks buffer</v>
+      <c r="I237" t="str">
+        <v/>
       </c>
       <c r="J237" s="6" t="str">
         <v/>
@@ -11281,13 +11273,13 @@
     </row>
     <row r="238" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="str">
-        <v>Drop 1 Super- 20.4</v>
+        <v>E2E readiness</v>
       </c>
       <c r="B238" t="str">
         <v/>
       </c>
-      <c r="C238" s="14" t="str">
-        <v>Deployment</v>
+      <c r="C238" s="19" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D238" t="str">
         <v/>
@@ -11295,17 +11287,17 @@
       <c r="E238" t="str">
         <v/>
       </c>
-      <c r="F238" t="str">
-        <v/>
-      </c>
-      <c r="G238" t="str">
-        <v/>
+      <c r="F238" s="8">
+        <v>46145</v>
+      </c>
+      <c r="G238" s="8">
+        <v>46145</v>
       </c>
       <c r="H238" t="str">
         <v/>
       </c>
-      <c r="I238" t="str">
-        <v/>
+      <c r="I238" s="6" t="str">
+        <v>E2E to start in Mid May + 1.5 weeks buffer</v>
       </c>
       <c r="J238" s="6" t="str">
         <v/>
@@ -11332,7 +11324,7 @@
         <v/>
       </c>
       <c r="R238" s="6" t="str">
-        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
       </c>
       <c r="S238" t="str">
         <v/>
@@ -11346,13 +11338,13 @@
     </row>
     <row r="239" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="str">
-        <v>Drop 2 - Super 4.5</v>
+        <v>Drop 1 Super- 20.4</v>
       </c>
       <c r="B239" t="str">
         <v/>
       </c>
-      <c r="C239" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C239" s="17" t="str">
+        <v>Deployment</v>
       </c>
       <c r="D239" t="str">
         <v/>
@@ -11411,7 +11403,7 @@
     </row>
     <row r="240" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="str">
-        <v>Drop 3 Super - 18.5</v>
+        <v>Drop 2 - Super 4.5</v>
       </c>
       <c r="B240" t="str">
         <v/>
@@ -11476,13 +11468,13 @@
     </row>
     <row r="241" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="str">
-        <v>Drop 4- Super - 1.6</v>
+        <v>Drop 3 Super - 18.5</v>
       </c>
       <c r="B241" t="str">
         <v/>
       </c>
-      <c r="C241" s="15" t="str">
-        <v>Discovery</v>
+      <c r="C241" s="5" t="str">
+        <v>FE DEV WIP</v>
       </c>
       <c r="D241" t="str">
         <v/>
@@ -11540,14 +11532,14 @@
       </c>
     </row>
     <row r="242" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A242" t="str">
-        <v/>
+      <c r="A242" s="4" t="str">
+        <v>Drop 4- Super - 1.6</v>
       </c>
       <c r="B242" t="str">
         <v/>
       </c>
-      <c r="C242" t="str">
-        <v/>
+      <c r="C242" s="14" t="str">
+        <v>Discovery</v>
       </c>
       <c r="D242" t="str">
         <v/>
@@ -11555,200 +11547,200 @@
       <c r="E242" t="str">
         <v/>
       </c>
-      <c r="F242" s="26">
+      <c r="F242" t="str">
+        <v/>
+      </c>
+      <c r="G242" t="str">
+        <v/>
+      </c>
+      <c r="H242" t="str">
+        <v/>
+      </c>
+      <c r="I242" t="str">
+        <v/>
+      </c>
+      <c r="J242" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K242" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L242" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M242" t="str">
+        <v/>
+      </c>
+      <c r="N242" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O242" t="str">
+        <v/>
+      </c>
+      <c r="P242" t="str">
+        <v/>
+      </c>
+      <c r="Q242" t="str">
+        <v/>
+      </c>
+      <c r="R242" s="6" t="str">
+        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+      </c>
+      <c r="S242" t="str">
+        <v/>
+      </c>
+      <c r="T242" t="str">
+        <v/>
+      </c>
+      <c r="U242" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="243" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A243" t="str">
+        <v/>
+      </c>
+      <c r="B243" t="str">
+        <v/>
+      </c>
+      <c r="C243" t="str">
+        <v/>
+      </c>
+      <c r="D243" t="str">
+        <v/>
+      </c>
+      <c r="E243" t="str">
+        <v/>
+      </c>
+      <c r="F243" s="25">
         <v>46048</v>
       </c>
-      <c r="G242" s="26">
+      <c r="G243" s="25">
         <v>46145</v>
       </c>
-      <c r="H242" t="str">
-        <v/>
-      </c>
-      <c r="I242" t="str">
-        <v/>
-      </c>
-      <c r="J242" t="str">
-        <v/>
-      </c>
-      <c r="K242" t="str">
-        <v/>
-      </c>
-      <c r="L242" t="str">
-        <v/>
-      </c>
-      <c r="M242" s="27">
+      <c r="H243" t="str">
+        <v/>
+      </c>
+      <c r="I243" t="str">
+        <v/>
+      </c>
+      <c r="J243" t="str">
+        <v/>
+      </c>
+      <c r="K243" t="str">
+        <v/>
+      </c>
+      <c r="L243" t="str">
+        <v/>
+      </c>
+      <c r="M243" s="26">
         <v>0</v>
       </c>
-      <c r="N242" t="str">
-        <v/>
-      </c>
-      <c r="O242" t="str">
-        <v/>
-      </c>
-      <c r="P242" t="str">
-        <v/>
-      </c>
-      <c r="Q242" s="29" t="str">
-        <v/>
-      </c>
-      <c r="R242" t="str">
-        <v/>
-      </c>
-      <c r="S242" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T242" s="29" t="str">
-        <v/>
-      </c>
-      <c r="U242" s="29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="243" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244" s="30" t="str">
+      <c r="N243" t="str">
+        <v/>
+      </c>
+      <c r="O243" t="str">
+        <v/>
+      </c>
+      <c r="P243" t="str">
+        <v/>
+      </c>
+      <c r="Q243" s="28" t="str">
+        <v/>
+      </c>
+      <c r="R243" t="str">
+        <v/>
+      </c>
+      <c r="S243" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T243" s="28" t="str">
+        <v/>
+      </c>
+      <c r="U243" s="28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="244" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" s="29" t="str">
         <v>Dependencies</v>
       </c>
     </row>
-    <row r="245" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A245" s="3" t="str">
+    <row r="246" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A246" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B245" s="3" t="str">
+      <c r="B246" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C245" s="3" t="str">
+      <c r="C246" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D245" s="3" t="str">
+      <c r="D246" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E245" s="3" t="str">
+      <c r="E246" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F245" s="3" t="str">
+      <c r="F246" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G245" s="3" t="str">
+      <c r="G246" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H245" s="3" t="str">
+      <c r="H246" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I245" s="3" t="str">
+      <c r="I246" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J245" s="3" t="str">
+      <c r="J246" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K245" s="3" t="str">
+      <c r="K246" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L245" s="3" t="str">
+      <c r="L246" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M245" s="3" t="str">
+      <c r="M246" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N245" s="3" t="str">
+      <c r="N246" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O245" s="3" t="str">
+      <c r="O246" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P245" s="3" t="str">
+      <c r="P246" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q245" s="3" t="str">
+      <c r="Q246" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R245" s="3" t="str">
+      <c r="R246" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S245" s="3" t="str">
+      <c r="S246" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T245" s="3" t="str">
+      <c r="T246" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U245" s="3" t="str">
+      <c r="U246" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="246" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A246" s="4" t="str">
-        <v>trading real time equity API</v>
-      </c>
-      <c r="B246" t="str">
-        <v/>
-      </c>
-      <c r="C246" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="D246" t="str">
-        <v/>
-      </c>
-      <c r="E246" t="str">
-        <v/>
-      </c>
-      <c r="F246" t="str">
-        <v/>
-      </c>
-      <c r="G246" t="str">
-        <v/>
-      </c>
-      <c r="H246" t="str">
-        <v/>
-      </c>
-      <c r="I246" t="str">
-        <v/>
-      </c>
-      <c r="J246" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K246" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L246" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M246" t="str">
-        <v/>
-      </c>
-      <c r="N246" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O246" t="str">
-        <v/>
-      </c>
-      <c r="P246" t="str">
-        <v/>
-      </c>
-      <c r="Q246" t="str">
-        <v/>
-      </c>
-      <c r="R246" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 11:31 AM</v>
-      </c>
-      <c r="S246" t="str">
-        <v/>
-      </c>
-      <c r="T246" t="str">
-        <v/>
-      </c>
-      <c r="U246" t="str">
-        <v/>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="str">
-        <v>trading BE orch</v>
+        <v>trading real time equity API</v>
       </c>
       <c r="B247" t="str">
         <v/>
       </c>
-      <c r="C247" s="21" t="str">
-        <v>Cancelled</v>
+      <c r="C247" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D247" t="str">
         <v/>
@@ -11793,7 +11785,7 @@
         <v/>
       </c>
       <c r="R247" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 11:50 AM</v>
+        <v>Ilan Tatar Jan 25, 2026 11:31 AM</v>
       </c>
       <c r="S247" t="str">
         <v/>
@@ -11807,135 +11799,200 @@
     </row>
     <row r="248" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="B248" t="str">
+        <v/>
+      </c>
+      <c r="C248" s="15" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D248" t="str">
+        <v/>
+      </c>
+      <c r="E248" t="str">
+        <v/>
+      </c>
+      <c r="F248" t="str">
+        <v/>
+      </c>
+      <c r="G248" t="str">
+        <v/>
+      </c>
+      <c r="H248" t="str">
+        <v/>
+      </c>
+      <c r="I248" t="str">
+        <v/>
+      </c>
+      <c r="J248" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K248" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L248" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M248" t="str">
+        <v/>
+      </c>
+      <c r="N248" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O248" t="str">
+        <v/>
+      </c>
+      <c r="P248" t="str">
+        <v/>
+      </c>
+      <c r="Q248" t="str">
+        <v/>
+      </c>
+      <c r="R248" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 11:50 AM</v>
+      </c>
+      <c r="S248" t="str">
+        <v/>
+      </c>
+      <c r="T248" t="str">
+        <v/>
+      </c>
+      <c r="U248" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="249" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A249" s="4" t="str">
         <v>Banking deposit MOP</v>
       </c>
-      <c r="B248" t="str">
-        <v/>
-      </c>
-      <c r="C248" s="11" t="str">
+      <c r="B249" t="str">
+        <v/>
+      </c>
+      <c r="C249" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D248" t="str">
-        <v/>
-      </c>
-      <c r="E248" t="str">
-        <v/>
-      </c>
-      <c r="F248" t="str">
-        <v/>
-      </c>
-      <c r="G248" t="str">
-        <v/>
-      </c>
-      <c r="H248" t="str">
-        <v/>
-      </c>
-      <c r="I248" t="str">
-        <v/>
-      </c>
-      <c r="J248" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K248" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L248" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M248" t="str">
-        <v/>
-      </c>
-      <c r="N248" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O248" t="str">
-        <v/>
-      </c>
-      <c r="P248" t="str">
-        <v/>
-      </c>
-      <c r="Q248" t="str">
-        <v/>
-      </c>
-      <c r="R248" s="6" t="str">
+      <c r="D249" t="str">
+        <v/>
+      </c>
+      <c r="E249" t="str">
+        <v/>
+      </c>
+      <c r="F249" t="str">
+        <v/>
+      </c>
+      <c r="G249" t="str">
+        <v/>
+      </c>
+      <c r="H249" t="str">
+        <v/>
+      </c>
+      <c r="I249" t="str">
+        <v/>
+      </c>
+      <c r="J249" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K249" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L249" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M249" t="str">
+        <v/>
+      </c>
+      <c r="N249" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O249" t="str">
+        <v/>
+      </c>
+      <c r="P249" t="str">
+        <v/>
+      </c>
+      <c r="Q249" t="str">
+        <v/>
+      </c>
+      <c r="R249" s="6" t="str">
         <v>Hagit Zamir Feb 5, 2026 4:03 PM</v>
       </c>
-      <c r="S248" t="str">
-        <v/>
-      </c>
-      <c r="T248" t="str">
-        <v/>
-      </c>
-      <c r="U248" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="249" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A249" t="str">
-        <v/>
-      </c>
-      <c r="B249" t="str">
-        <v/>
-      </c>
-      <c r="C249" t="str">
-        <v/>
-      </c>
-      <c r="D249" t="str">
-        <v/>
-      </c>
-      <c r="E249" t="str">
-        <v/>
-      </c>
-      <c r="F249" s="29" t="str">
-        <v/>
-      </c>
-      <c r="G249" s="29" t="str">
-        <v/>
-      </c>
-      <c r="H249" t="str">
-        <v/>
-      </c>
-      <c r="I249" t="str">
-        <v/>
-      </c>
-      <c r="J249" t="str">
-        <v/>
-      </c>
-      <c r="K249" t="str">
-        <v/>
-      </c>
-      <c r="L249" t="str">
-        <v/>
-      </c>
-      <c r="M249" s="27">
+      <c r="S249" t="str">
+        <v/>
+      </c>
+      <c r="T249" t="str">
+        <v/>
+      </c>
+      <c r="U249" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A250" t="str">
+        <v/>
+      </c>
+      <c r="B250" t="str">
+        <v/>
+      </c>
+      <c r="C250" t="str">
+        <v/>
+      </c>
+      <c r="D250" t="str">
+        <v/>
+      </c>
+      <c r="E250" t="str">
+        <v/>
+      </c>
+      <c r="F250" s="28" t="str">
+        <v/>
+      </c>
+      <c r="G250" s="28" t="str">
+        <v/>
+      </c>
+      <c r="H250" t="str">
+        <v/>
+      </c>
+      <c r="I250" t="str">
+        <v/>
+      </c>
+      <c r="J250" t="str">
+        <v/>
+      </c>
+      <c r="K250" t="str">
+        <v/>
+      </c>
+      <c r="L250" t="str">
+        <v/>
+      </c>
+      <c r="M250" s="26">
         <v>0</v>
       </c>
-      <c r="N249" t="str">
-        <v/>
-      </c>
-      <c r="O249" t="str">
-        <v/>
-      </c>
-      <c r="P249" t="str">
-        <v/>
-      </c>
-      <c r="Q249" s="29" t="str">
-        <v/>
-      </c>
-      <c r="R249" t="str">
-        <v/>
-      </c>
-      <c r="S249" s="29" t="str">
-        <v/>
-      </c>
-      <c r="T249" s="29" t="str">
-        <v/>
-      </c>
-      <c r="U249" s="29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="250" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="N250" t="str">
+        <v/>
+      </c>
+      <c r="O250" t="str">
+        <v/>
+      </c>
+      <c r="P250" t="str">
+        <v/>
+      </c>
+      <c r="Q250" s="28" t="str">
+        <v/>
+      </c>
+      <c r="R250" t="str">
+        <v/>
+      </c>
+      <c r="S250" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T250" s="28" t="str">
+        <v/>
+      </c>
+      <c r="U250" s="28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="251" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -113,22 +113,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBB3354"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCAB641"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF007F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
@@ -154,6 +144,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF784BD1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB3354"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
@@ -1658,167 +1658,137 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="str">
-        <v>Drop 1 gaps implementation- Inbal</v>
+        <v>Deposit MOPs</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
-      <c r="C28" s="15" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="D28" t="str">
-        <v/>
+      <c r="C28" s="14" t="str">
+        <v>Discovery</v>
+      </c>
+      <c r="D28" s="6" t="str">
+        <v>DepositWizard</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" s="8">
-        <v>46131</v>
+        <v>46062</v>
       </c>
       <c r="G28" s="8">
+        <v>46075</v>
+      </c>
+      <c r="H28" s="6" t="str">
+        <v>V2(4.5), V3(18.5)</v>
+      </c>
+      <c r="I28" s="6" t="str">
+        <v>WIP - planning A/B between old cashier, FTD wizard and Select balance</v>
+      </c>
+      <c r="J28" s="6" t="str">
+        <v>Noit</v>
+      </c>
+      <c r="K28" s="6" t="str">
+        <v>Inbal Escholi</v>
+      </c>
+      <c r="L28" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M28" s="6">
+        <v>2</v>
+      </c>
+      <c r="N28" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O28" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P28" s="6" t="str">
+        <v>Deposit, Payments</v>
+      </c>
+      <c r="Q28" s="7">
+        <v>46104</v>
+      </c>
+      <c r="R28" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S28" t="str">
+        <v/>
+      </c>
+      <c r="T28" s="8">
+        <v>46089</v>
+      </c>
+      <c r="U28" s="8">
+        <v>46089</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="str">
+        <v>Subitems</v>
+      </c>
+      <c r="B29" s="10" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C29" s="10" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="D29" s="10" t="str">
+        <v>Status</v>
+      </c>
+      <c r="E29" s="10" t="str">
+        <v>JIRA</v>
+      </c>
+      <c r="F29" s="10" t="str">
+        <v>Drop</v>
+      </c>
+      <c r="G29" s="10" t="str">
+        <v>Team</v>
+      </c>
+      <c r="H29" s="10" t="str">
+        <v>Timeline - Start</v>
+      </c>
+      <c r="I29" s="10" t="str">
+        <v>Timeline - End</v>
+      </c>
+      <c r="J29" s="10" t="str">
+        <v>Groom Readiness Date</v>
+      </c>
+      <c r="K29" s="10" t="str">
+        <v>Priority</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+      <c r="B30" s="4" t="str">
+        <v>Deposit - Wire IBAN - Simple task</v>
+      </c>
+      <c r="C30" s="6" t="str">
+        <v>Joanna Fajga</v>
+      </c>
+      <c r="D30" s="15" t="str">
+        <v>QA</v>
+      </c>
+      <c r="E30" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F30" s="6" t="str">
+        <v>V2(4.5)</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" s="8">
         <v>46134</v>
       </c>
-      <c r="H28" s="6" t="str">
-        <v>V1(20.4)</v>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K28" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L28" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M28" s="6">
-        <v>1</v>
-      </c>
-      <c r="N28" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O28" t="str">
-        <v/>
-      </c>
-      <c r="P28" t="str">
-        <v/>
-      </c>
-      <c r="Q28" t="str">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="str">
-        <v>Ilan Tatar Apr 19, 2026 11:17 AM</v>
-      </c>
-      <c r="S28" t="str">
-        <v/>
-      </c>
-      <c r="T28" t="str">
-        <v/>
-      </c>
-      <c r="U28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="str">
-        <v>Deposit MOPs</v>
-      </c>
-      <c r="B29" t="str">
-        <v/>
-      </c>
-      <c r="C29" s="14" t="str">
-        <v>Discovery</v>
-      </c>
-      <c r="D29" s="6" t="str">
-        <v>DepositWizard</v>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" s="8">
-        <v>46062</v>
-      </c>
-      <c r="G29" s="8">
-        <v>46075</v>
-      </c>
-      <c r="H29" s="6" t="str">
-        <v>V2(4.5), V3(18.5)</v>
-      </c>
-      <c r="I29" s="6" t="str">
-        <v>WIP - planning A/B between old cashier, FTD wizard and Select balance</v>
-      </c>
-      <c r="J29" s="6" t="str">
-        <v>Noit</v>
-      </c>
-      <c r="K29" s="6" t="str">
-        <v>Inbal Escholi</v>
-      </c>
-      <c r="L29" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M29" s="6">
+      <c r="I30" s="8">
+        <v>46147</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" s="6">
         <v>2</v>
-      </c>
-      <c r="N29" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O29" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P29" s="6" t="str">
-        <v>Deposit, Payments</v>
-      </c>
-      <c r="Q29" s="7">
-        <v>46104</v>
-      </c>
-      <c r="R29" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S29" t="str">
-        <v/>
-      </c>
-      <c r="T29" s="8">
-        <v>46089</v>
-      </c>
-      <c r="U29" s="8">
-        <v>46089</v>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="str">
-        <v>Subitems</v>
-      </c>
-      <c r="B30" s="10" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C30" s="10" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="D30" s="10" t="str">
-        <v>Status</v>
-      </c>
-      <c r="E30" s="10" t="str">
-        <v>JIRA</v>
-      </c>
-      <c r="F30" s="10" t="str">
-        <v>Drop</v>
-      </c>
-      <c r="G30" s="10" t="str">
-        <v>Team</v>
-      </c>
-      <c r="H30" s="10" t="str">
-        <v>Timeline - Start</v>
-      </c>
-      <c r="I30" s="10" t="str">
-        <v>Timeline - End</v>
-      </c>
-      <c r="J30" s="10" t="str">
-        <v>Groom Readiness Date</v>
-      </c>
-      <c r="K30" s="10" t="str">
-        <v>Priority</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1826,13 +1796,13 @@
         <v/>
       </c>
       <c r="B31" s="4" t="str">
-        <v>Deposit - Wire IBAN - Simple task</v>
+        <v>Deposit - Credit Card - Complex task -FTD</v>
       </c>
       <c r="C31" s="6" t="str">
-        <v>Joanna Fajga</v>
-      </c>
-      <c r="D31" s="5" t="str">
-        <v>Dev - WIP</v>
+        <v>Noit Hoffman</v>
+      </c>
+      <c r="D31" s="15" t="str">
+        <v>QA</v>
       </c>
       <c r="E31" s="6" t="str">
         <v/>
@@ -1844,10 +1814,10 @@
         <v/>
       </c>
       <c r="H31" s="8">
-        <v>46134</v>
+        <v>46061</v>
       </c>
       <c r="I31" s="8">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1861,13 +1831,13 @@
         <v/>
       </c>
       <c r="B32" s="4" t="str">
-        <v>Deposit - Credit Card - Complex task -FTD</v>
+        <v>Deposit  - Open Banking(tink/volt) - FTD</v>
       </c>
       <c r="C32" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
       <c r="D32" s="16" t="str">
-        <v>QA</v>
+        <v>Groomed</v>
       </c>
       <c r="E32" s="6" t="str">
         <v/>
@@ -1878,11 +1848,11 @@
       <c r="G32" t="str">
         <v/>
       </c>
-      <c r="H32" s="8">
-        <v>46061</v>
-      </c>
-      <c r="I32" s="8">
-        <v>46149</v>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1896,12 +1866,12 @@
         <v/>
       </c>
       <c r="B33" s="4" t="str">
-        <v>Deposit  - Open Banking(tink/volt) - FTD</v>
+        <v>Deposit - PayPal- Simple task to implement - FTD</v>
       </c>
       <c r="C33" s="6" t="str">
-        <v>Noit Hoffman</v>
-      </c>
-      <c r="D33" s="17" t="str">
+        <v>Noit Hoffman, Joanna Fajga</v>
+      </c>
+      <c r="D33" s="16" t="str">
         <v>Groomed</v>
       </c>
       <c r="E33" s="6" t="str">
@@ -1931,13 +1901,13 @@
         <v/>
       </c>
       <c r="B34" s="4" t="str">
-        <v>Deposit - PayPal- Simple task to implement - FTD</v>
+        <v>Deposit - Wire USD- Easy task</v>
       </c>
       <c r="C34" s="6" t="str">
-        <v>Noit Hoffman, Joanna Fajga</v>
-      </c>
-      <c r="D34" s="17" t="str">
-        <v>Groomed</v>
+        <v>Joanna Fajga</v>
+      </c>
+      <c r="D34" s="15" t="str">
+        <v>QA</v>
       </c>
       <c r="E34" s="6" t="str">
         <v/>
@@ -1948,11 +1918,11 @@
       <c r="G34" t="str">
         <v/>
       </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
-      <c r="I34" t="str">
-        <v/>
+      <c r="H34" s="8">
+        <v>46061</v>
+      </c>
+      <c r="I34" s="8">
+        <v>46147</v>
       </c>
       <c r="J34" t="str">
         <v/>
@@ -1966,28 +1936,28 @@
         <v/>
       </c>
       <c r="B35" s="4" t="str">
-        <v>Deposit - Wire USD- Easy task</v>
+        <v>Deposit - Lean</v>
       </c>
       <c r="C35" s="6" t="str">
-        <v>Joanna Fajga</v>
-      </c>
-      <c r="D35" s="16" t="str">
-        <v>QA</v>
+        <v>Noit Hoffman</v>
+      </c>
+      <c r="D35" s="13" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E35" s="6" t="str">
         <v/>
       </c>
       <c r="F35" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V3(18.5)</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
-      <c r="H35" s="8">
-        <v>46061</v>
-      </c>
-      <c r="I35" s="8">
-        <v>46147</v>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -2001,13 +1971,13 @@
         <v/>
       </c>
       <c r="B36" s="4" t="str">
-        <v>Deposit - Lean</v>
+        <v>Deposit - iDeal</v>
       </c>
       <c r="C36" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D36" s="12" t="str">
-        <v>Stuck</v>
+      <c r="D36" s="13" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E36" s="6" t="str">
         <v/>
@@ -2028,7 +1998,7 @@
         <v/>
       </c>
       <c r="K36" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2106,7 +2076,7 @@
         <v/>
       </c>
       <c r="B39" s="4" t="str">
-        <v>Deposit - iDeal</v>
+        <v>Deposit - PWMB</v>
       </c>
       <c r="C39" s="6" t="str">
         <v>Noit Hoffman</v>
@@ -2141,7 +2111,7 @@
         <v/>
       </c>
       <c r="B40" s="4" t="str">
-        <v>Deposit - PWMB</v>
+        <v>Deposit - Trustly</v>
       </c>
       <c r="C40" s="6" t="str">
         <v>Noit Hoffman</v>
@@ -2176,7 +2146,7 @@
         <v/>
       </c>
       <c r="B41" s="4" t="str">
-        <v>Deposit - Trustly</v>
+        <v>Deposit - Skrill</v>
       </c>
       <c r="C41" s="6" t="str">
         <v>Noit Hoffman</v>
@@ -2211,7 +2181,7 @@
         <v/>
       </c>
       <c r="B42" s="4" t="str">
-        <v>Deposit - Skrill</v>
+        <v>Deposit - Neteller</v>
       </c>
       <c r="C42" s="6" t="str">
         <v>Noit Hoffman</v>
@@ -2246,13 +2216,13 @@
         <v/>
       </c>
       <c r="B43" s="4" t="str">
-        <v>Deposit - Neteller</v>
-      </c>
-      <c r="C43" s="6" t="str">
-        <v>Noit Hoffman</v>
-      </c>
-      <c r="D43" s="13" t="str">
-        <v>Discovery</v>
+        <v>Deposit- BFF</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E43" s="6" t="str">
         <v/>
@@ -2272,8 +2242,8 @@
       <c r="J43" t="str">
         <v/>
       </c>
-      <c r="K43" s="6">
-        <v>3</v>
+      <c r="K43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2281,13 +2251,13 @@
         <v/>
       </c>
       <c r="B44" s="4" t="str">
-        <v>Deposit- BFF</v>
-      </c>
-      <c r="C44" t="str">
-        <v/>
-      </c>
-      <c r="D44" s="5" t="str">
-        <v>Dev - WIP</v>
+        <v>Deposit Paypal Redeposit</v>
+      </c>
+      <c r="C44" s="6" t="str">
+        <v>Joanna Fajga</v>
+      </c>
+      <c r="D44" s="16" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E44" s="6" t="str">
         <v/>
@@ -2298,11 +2268,11 @@
       <c r="G44" t="str">
         <v/>
       </c>
-      <c r="H44" t="str">
-        <v/>
-      </c>
-      <c r="I44" t="str">
-        <v/>
+      <c r="H44" s="8">
+        <v>46146</v>
+      </c>
+      <c r="I44" s="8">
+        <v>46146</v>
       </c>
       <c r="J44" t="str">
         <v/>
@@ -2316,13 +2286,13 @@
         <v/>
       </c>
       <c r="B45" s="4" t="str">
-        <v>Deposit Paypal Redeposit</v>
+        <v>Deposit Credit Card Redeposit</v>
       </c>
       <c r="C45" s="6" t="str">
-        <v>Joanna Fajga</v>
-      </c>
-      <c r="D45" s="18" t="str">
-        <v>Grooming</v>
+        <v>Noit Hoffman</v>
+      </c>
+      <c r="D45" s="16" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E45" s="6" t="str">
         <v/>
@@ -2333,11 +2303,11 @@
       <c r="G45" t="str">
         <v/>
       </c>
-      <c r="H45" s="8">
-        <v>46146</v>
-      </c>
-      <c r="I45" s="8">
-        <v>46146</v>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -2351,13 +2321,13 @@
         <v/>
       </c>
       <c r="B46" s="4" t="str">
-        <v>Deposit Credit Card Redeposit</v>
-      </c>
-      <c r="C46" s="6" t="str">
-        <v>Noit Hoffman</v>
-      </c>
-      <c r="D46" s="18" t="str">
-        <v>Grooming</v>
+        <v>Deposit Open Banking redeposit</v>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" s="17" t="str">
+        <v>Not Started</v>
       </c>
       <c r="E46" s="6" t="str">
         <v/>
@@ -2386,19 +2356,19 @@
         <v/>
       </c>
       <c r="B47" s="4" t="str">
-        <v>Deposit Open Banking redeposit</v>
-      </c>
-      <c r="C47" t="str">
-        <v/>
-      </c>
-      <c r="D47" s="19" t="str">
-        <v>Not Started</v>
+        <v>Flow - Deposit Wizard - Redepositor</v>
+      </c>
+      <c r="C47" s="6" t="str">
+        <v>Noit Hoffman</v>
+      </c>
+      <c r="D47" s="18" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="E47" s="6" t="str">
         <v/>
       </c>
-      <c r="F47" s="6" t="str">
-        <v>V3(18.5)</v>
+      <c r="F47" t="str">
+        <v/>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2412,8 +2382,8 @@
       <c r="J47" t="str">
         <v/>
       </c>
-      <c r="K47" t="str">
-        <v/>
+      <c r="K47" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2421,12 +2391,12 @@
         <v/>
       </c>
       <c r="B48" s="4" t="str">
-        <v>Flow - Deposit Wizard - Redepositor</v>
+        <v>Flow - Deposit Wizard FTD</v>
       </c>
       <c r="C48" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D48" s="20" t="str">
+      <c r="D48" s="18" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E48" s="6" t="str">
@@ -2456,12 +2426,12 @@
         <v/>
       </c>
       <c r="B49" s="4" t="str">
-        <v>Flow - Deposit Wizard FTD</v>
+        <v>Flow - Deposit - Account selection</v>
       </c>
       <c r="C49" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D49" s="20" t="str">
+      <c r="D49" s="18" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E49" s="6" t="str">
@@ -2482,8 +2452,8 @@
       <c r="J49" t="str">
         <v/>
       </c>
-      <c r="K49" s="6">
-        <v>1</v>
+      <c r="K49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2491,13 +2461,13 @@
         <v/>
       </c>
       <c r="B50" s="4" t="str">
-        <v>Flow - Deposit - Account selection</v>
-      </c>
-      <c r="C50" s="6" t="str">
-        <v>Noit Hoffman</v>
-      </c>
-      <c r="D50" s="20" t="str">
-        <v>Cancelled</v>
+        <v>Spike to reduce MOP scope in Deposit- Ilia</v>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" s="13" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E50" s="6" t="str">
         <v/>
@@ -2528,7 +2498,7 @@
       <c r="B51" t="str">
         <v/>
       </c>
-      <c r="C51" s="21" t="str">
+      <c r="C51" s="19" t="str">
         <v>Groomed</v>
       </c>
       <c r="D51" t="str">
@@ -2631,8 +2601,8 @@
       <c r="C53" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D53" s="17" t="str">
-        <v>Groomed</v>
+      <c r="D53" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E53" s="6" t="str">
         <v/>
@@ -2666,8 +2636,8 @@
       <c r="C54" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D54" s="17" t="str">
-        <v>Groomed</v>
+      <c r="D54" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E54" s="6" t="str">
         <v/>
@@ -2701,8 +2671,8 @@
       <c r="C55" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D55" s="17" t="str">
-        <v>Groomed</v>
+      <c r="D55" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E55" s="6" t="str">
         <v/>
@@ -2736,8 +2706,8 @@
       <c r="C56" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D56" s="17" t="str">
-        <v>Groomed</v>
+      <c r="D56" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E56" s="6" t="str">
         <v/>
@@ -2771,8 +2741,8 @@
       <c r="C57" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D57" s="17" t="str">
-        <v>Groomed</v>
+      <c r="D57" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E57" s="6" t="str">
         <v/>
@@ -2806,7 +2776,7 @@
       <c r="C58" t="str">
         <v/>
       </c>
-      <c r="D58" s="22" t="str">
+      <c r="D58" s="20" t="str">
         <v>OnHold</v>
       </c>
       <c r="E58" s="6" t="str">
@@ -2841,7 +2811,7 @@
       <c r="C59" t="str">
         <v/>
       </c>
-      <c r="D59" s="23" t="str">
+      <c r="D59" s="21" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E59" s="6" t="str">
@@ -2873,7 +2843,7 @@
       <c r="B60" t="str">
         <v/>
       </c>
-      <c r="C60" s="19" t="str">
+      <c r="C60" s="17" t="str">
         <v>Not Started</v>
       </c>
       <c r="D60" s="6" t="str">
@@ -2976,7 +2946,7 @@
       <c r="C62" t="str">
         <v/>
       </c>
-      <c r="D62" s="19" t="str">
+      <c r="D62" s="17" t="str">
         <v>Not Started</v>
       </c>
       <c r="E62" s="6" t="str">
@@ -3011,7 +2981,7 @@
       <c r="C63" t="str">
         <v/>
       </c>
-      <c r="D63" s="19" t="str">
+      <c r="D63" s="17" t="str">
         <v>Not Started</v>
       </c>
       <c r="E63" s="6" t="str">
@@ -3046,7 +3016,7 @@
       <c r="C64" t="str">
         <v/>
       </c>
-      <c r="D64" s="19" t="str">
+      <c r="D64" s="17" t="str">
         <v>Not Started</v>
       </c>
       <c r="E64" s="6" t="str">
@@ -3321,7 +3291,7 @@
       <c r="C71" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D71" s="17" t="str">
+      <c r="D71" s="16" t="str">
         <v>Groomed</v>
       </c>
       <c r="E71" s="6" t="str">
@@ -3356,7 +3326,7 @@
       <c r="C72" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D72" s="17" t="str">
+      <c r="D72" s="16" t="str">
         <v>Groomed</v>
       </c>
       <c r="E72" s="6" t="str">
@@ -3386,12 +3356,12 @@
         <v/>
       </c>
       <c r="B73" s="4" t="str">
-        <v>Custodial wallet crypto - Receive (with travel rule) CASP/ Self Hosted</v>
+        <v>Custodial wallet crypto - Receive (not travel rule)</v>
       </c>
       <c r="C73" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D73" s="17" t="str">
+      <c r="D73" s="16" t="str">
         <v>Groomed</v>
       </c>
       <c r="E73" s="6" t="str">
@@ -3426,7 +3396,7 @@
       <c r="C74" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D74" s="17" t="str">
+      <c r="D74" s="16" t="str">
         <v>Groomed</v>
       </c>
       <c r="E74" s="6" t="str">
@@ -3461,7 +3431,7 @@
       <c r="C75" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D75" s="17" t="str">
+      <c r="D75" s="16" t="str">
         <v>Groomed</v>
       </c>
       <c r="E75" s="6" t="str">
@@ -3477,7 +3447,7 @@
         <v>46146</v>
       </c>
       <c r="I75" s="8">
-        <v>46160</v>
+        <v>46181</v>
       </c>
       <c r="J75" s="7">
         <v>46106</v>
@@ -3496,7 +3466,7 @@
       <c r="C76" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D76" s="15" t="str">
+      <c r="D76" s="22" t="str">
         <v>Design</v>
       </c>
       <c r="E76" s="6" t="str">
@@ -3531,7 +3501,7 @@
       <c r="C77" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D77" s="15" t="str">
+      <c r="D77" s="22" t="str">
         <v>Design</v>
       </c>
       <c r="E77" s="6" t="str">
@@ -3841,7 +3811,7 @@
       <c r="C85" t="str">
         <v/>
       </c>
-      <c r="D85" s="19" t="str">
+      <c r="D85" s="17" t="str">
         <v>Not Started</v>
       </c>
       <c r="E85" s="6" t="str">
@@ -3876,7 +3846,7 @@
       <c r="C86" t="str">
         <v/>
       </c>
-      <c r="D86" s="23" t="str">
+      <c r="D86" s="21" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E86" s="6" t="str">
@@ -3911,7 +3881,7 @@
       <c r="C87" t="str">
         <v/>
       </c>
-      <c r="D87" s="20" t="str">
+      <c r="D87" s="18" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E87" s="6" t="str">
@@ -3946,7 +3916,7 @@
       <c r="C88" t="str">
         <v/>
       </c>
-      <c r="D88" s="20" t="str">
+      <c r="D88" s="18" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E88" s="6" t="str">
@@ -3981,7 +3951,7 @@
       <c r="C89" t="str">
         <v/>
       </c>
-      <c r="D89" s="20" t="str">
+      <c r="D89" s="18" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E89" s="6" t="str">
@@ -4016,7 +3986,7 @@
       <c r="C90" t="str">
         <v/>
       </c>
-      <c r="D90" s="20" t="str">
+      <c r="D90" s="18" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E90" s="6" t="str">
@@ -4051,7 +4021,7 @@
       <c r="C91" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D91" s="20" t="str">
+      <c r="D91" s="18" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E91" s="6" t="str">
@@ -4121,7 +4091,7 @@
       <c r="C93" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D93" s="20" t="str">
+      <c r="D93" s="18" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E93" s="6" t="str">
@@ -4153,7 +4123,7 @@
       <c r="B94" t="str">
         <v/>
       </c>
-      <c r="C94" s="16" t="str">
+      <c r="C94" s="15" t="str">
         <v>Grooming</v>
       </c>
       <c r="D94" s="6" t="str">
@@ -4256,7 +4226,7 @@
       <c r="C96" t="str">
         <v/>
       </c>
-      <c r="D96" s="18" t="str">
+      <c r="D96" s="23" t="str">
         <v>Grooming</v>
       </c>
       <c r="E96" s="6" t="str">
@@ -4291,7 +4261,7 @@
       <c r="C97" t="str">
         <v/>
       </c>
-      <c r="D97" s="18" t="str">
+      <c r="D97" s="23" t="str">
         <v>Grooming</v>
       </c>
       <c r="E97" s="6" t="str">
@@ -4326,7 +4296,7 @@
       <c r="C98" t="str">
         <v/>
       </c>
-      <c r="D98" s="19" t="str">
+      <c r="D98" s="17" t="str">
         <v>Not Started</v>
       </c>
       <c r="E98" s="6" t="str">
@@ -4361,7 +4331,7 @@
       <c r="C99" t="str">
         <v/>
       </c>
-      <c r="D99" s="18" t="str">
+      <c r="D99" s="23" t="str">
         <v>Grooming</v>
       </c>
       <c r="E99" s="6" t="str">
@@ -4496,8 +4466,8 @@
       <c r="C102" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D102" s="5" t="str">
-        <v>Dev - WIP</v>
+      <c r="D102" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E102" s="6" t="str">
         <v/>
@@ -4526,18 +4496,18 @@
         <v/>
       </c>
       <c r="B103" s="4" t="str">
-        <v>Manage Card - Card Status Management</v>
+        <v>Manage Card - Activate Card</v>
       </c>
       <c r="C103" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D103" s="17" t="str">
+      <c r="D103" s="16" t="str">
         <v>Groomed</v>
       </c>
       <c r="E103" s="6" t="str">
         <v/>
       </c>
-      <c r="F103" s="6" t="str">
+      <c r="F103" t="str">
         <v/>
       </c>
       <c r="G103" t="str">
@@ -4561,13 +4531,13 @@
         <v/>
       </c>
       <c r="B104" s="4" t="str">
-        <v>Manage Card - Activate Card</v>
+        <v>Manage Card - View Card Details</v>
       </c>
       <c r="C104" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D104" s="17" t="str">
-        <v>Groomed</v>
+      <c r="D104" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E104" s="6" t="str">
         <v/>
@@ -4596,13 +4566,13 @@
         <v/>
       </c>
       <c r="B105" s="4" t="str">
-        <v>Manage Card - View Card Details</v>
+        <v>Manage Card - PIN Reminder</v>
       </c>
       <c r="C105" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D105" s="17" t="str">
-        <v>Groomed</v>
+      <c r="D105" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E105" s="6" t="str">
         <v/>
@@ -4631,13 +4601,13 @@
         <v/>
       </c>
       <c r="B106" s="4" t="str">
-        <v>Manage Card - PIN Reminder</v>
+        <v>Manage Card - Freeze Card</v>
       </c>
       <c r="C106" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D106" s="17" t="str">
-        <v>Groomed</v>
+      <c r="D106" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="E106" s="6" t="str">
         <v/>
@@ -4666,13 +4636,13 @@
         <v/>
       </c>
       <c r="B107" s="4" t="str">
-        <v>Manage Card - Freeze Card</v>
+        <v>Manage Card - Mark Lost / Stolen</v>
       </c>
       <c r="C107" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D107" s="5" t="str">
-        <v>Dev - WIP</v>
+      <c r="D107" s="16" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E107" s="6" t="str">
         <v/>
@@ -4701,12 +4671,12 @@
         <v/>
       </c>
       <c r="B108" s="4" t="str">
-        <v>Manage Card - Mark Lost / Stolen</v>
+        <v>Manage Card - Reissue Flow</v>
       </c>
       <c r="C108" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D108" s="17" t="str">
+      <c r="D108" s="16" t="str">
         <v>Groomed</v>
       </c>
       <c r="E108" s="6" t="str">
@@ -4736,12 +4706,12 @@
         <v/>
       </c>
       <c r="B109" s="4" t="str">
-        <v>Manage Card - Reissue Flow</v>
+        <v>Manage Card - Expiry Flow</v>
       </c>
       <c r="C109" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D109" s="17" t="str">
+      <c r="D109" s="16" t="str">
         <v>Groomed</v>
       </c>
       <c r="E109" s="6" t="str">
@@ -4771,12 +4741,12 @@
         <v/>
       </c>
       <c r="B110" s="4" t="str">
-        <v>Manage Card - Expiry Flow</v>
+        <v>Manage Card - Apple Wallet touchpoint- The button to trigger the addition</v>
       </c>
       <c r="C110" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D110" s="17" t="str">
+      <c r="D110" s="16" t="str">
         <v>Groomed</v>
       </c>
       <c r="E110" s="6" t="str">
@@ -4806,13 +4776,13 @@
         <v/>
       </c>
       <c r="B111" s="4" t="str">
-        <v>Manage Card - Apple Wallet touchpoint- The button to trigger the addition</v>
+        <v>Manage Card - Google Wallet Manual Provision</v>
       </c>
       <c r="C111" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D111" s="17" t="str">
-        <v>Groomed</v>
+      <c r="D111" s="13" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E111" s="6" t="str">
         <v/>
@@ -4841,804 +4811,744 @@
         <v/>
       </c>
       <c r="B112" s="4" t="str">
-        <v>Manage Card - Google Wallet Manual Provision</v>
+        <v>Manage Card - Club Upgrades for Card Program</v>
       </c>
       <c r="C112" s="6" t="str">
-        <v>Richard Whitehouse, Inbal Escholi</v>
-      </c>
-      <c r="D112" s="20" t="str">
+        <v>Richard Whitehouse</v>
+      </c>
+      <c r="D112" s="21" t="str">
+        <v>futureVersion</v>
+      </c>
+      <c r="E112" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="str">
+        <v>Card Management - Add To Apple Wallet- SDK</v>
+      </c>
+      <c r="B113" t="str">
+        <v/>
+      </c>
+      <c r="C113" s="5" t="str">
+        <v>FE DEV WIP</v>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" s="6" t="str">
+        <v>V3(18.5)</v>
+      </c>
+      <c r="I113" s="6" t="str">
+        <v>Awaiting some feedback from Apple</v>
+      </c>
+      <c r="J113" s="6" t="str">
+        <v>Richard</v>
+      </c>
+      <c r="K113" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L113" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M113" s="6">
+        <v>2</v>
+      </c>
+      <c r="N113" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113" s="7">
+        <v>46127</v>
+      </c>
+      <c r="R113" s="6" t="str">
+        <v>Richard Whitehouse Mar 4, 2026 2:31 PM</v>
+      </c>
+      <c r="S113" t="str">
+        <v/>
+      </c>
+      <c r="T113" s="8">
+        <v>46093</v>
+      </c>
+      <c r="U113" s="8">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" s="9" t="str">
+        <v>Subitems</v>
+      </c>
+      <c r="B114" s="10" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C114" s="10" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="D114" s="10" t="str">
+        <v>Status</v>
+      </c>
+      <c r="E114" s="10" t="str">
+        <v>JIRA</v>
+      </c>
+      <c r="F114" s="10" t="str">
+        <v>Drop</v>
+      </c>
+      <c r="G114" s="10" t="str">
+        <v>Team</v>
+      </c>
+      <c r="H114" s="10" t="str">
+        <v>Timeline - Start</v>
+      </c>
+      <c r="I114" s="10" t="str">
+        <v>Timeline - End</v>
+      </c>
+      <c r="J114" s="10" t="str">
+        <v>Groom Readiness Date</v>
+      </c>
+      <c r="K114" s="10" t="str">
+        <v>Priority</v>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" t="str">
+        <v/>
+      </c>
+      <c r="B115" s="4" t="str">
+        <v>SDK Implimentation</v>
+      </c>
+      <c r="C115" t="str">
+        <v/>
+      </c>
+      <c r="D115" s="5" t="str">
+        <v>Dev - WIP</v>
+      </c>
+      <c r="E115" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" t="str">
+        <v/>
+      </c>
+      <c r="B116" s="4" t="str">
+        <v>Apple Pay Status -  State Management ABCDE</v>
+      </c>
+      <c r="C116" t="str">
+        <v/>
+      </c>
+      <c r="D116" s="5" t="str">
+        <v>Dev - WIP</v>
+      </c>
+      <c r="E116" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="str">
+        <v>Wallet tab - total value graph- Total Value Rolloup- Desktop</v>
+      </c>
+      <c r="B117" t="str">
+        <v/>
+      </c>
+      <c r="C117" s="17" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="D117" s="6" t="str">
+        <v>WalletTabTotalValueGraph</v>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" s="6" t="str">
+        <v>V4(1.6)</v>
+      </c>
+      <c r="I117" s="6" t="str">
+        <v>OOS - Wallet Tab - Balance Display - Total Value Rollup-</v>
+      </c>
+      <c r="J117" s="6" t="str">
+        <v>Adi</v>
+      </c>
+      <c r="K117" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L117" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M117" s="6">
+        <v>3</v>
+      </c>
+      <c r="N117" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O117" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P117" s="6" t="str">
+        <v>Balance</v>
+      </c>
+      <c r="Q117" s="7">
+        <v>46127</v>
+      </c>
+      <c r="R117" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S117" t="str">
+        <v/>
+      </c>
+      <c r="T117" t="str">
+        <v/>
+      </c>
+      <c r="U117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="B118" t="str">
+        <v/>
+      </c>
+      <c r="C118" s="21" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" s="6" t="str">
+        <v>V3(18.5)</v>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" s="6" t="str">
+        <v>Noit</v>
+      </c>
+      <c r="K118" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L118" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M118" s="6">
+        <v>3</v>
+      </c>
+      <c r="N118" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" s="6" t="str">
+        <v>Payments, Settings</v>
+      </c>
+      <c r="Q118" s="7">
+        <v>46127</v>
+      </c>
+      <c r="R118" s="6" t="str">
+        <v>Hagit Zamir Feb 5, 2026 4:10 PM</v>
+      </c>
+      <c r="S118" t="str">
+        <v/>
+      </c>
+      <c r="T118" t="str">
+        <v/>
+      </c>
+      <c r="U118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" s="9" t="str">
+        <v>Subitems</v>
+      </c>
+      <c r="B119" s="10" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C119" s="10" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="D119" s="10" t="str">
+        <v>Status</v>
+      </c>
+      <c r="E119" s="10" t="str">
+        <v>JIRA</v>
+      </c>
+      <c r="F119" s="10" t="str">
+        <v>Drop</v>
+      </c>
+      <c r="G119" s="10" t="str">
+        <v>Team</v>
+      </c>
+      <c r="H119" s="10" t="str">
+        <v>Timeline - Start</v>
+      </c>
+      <c r="I119" s="10" t="str">
+        <v>Timeline - End</v>
+      </c>
+      <c r="J119" s="10" t="str">
+        <v>Groom Readiness Date</v>
+      </c>
+      <c r="K119" s="10" t="str">
+        <v>Priority</v>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" t="str">
+        <v/>
+      </c>
+      <c r="B120" s="4" t="str">
+        <v>Settings: Default currency for LC</v>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120" s="14" t="str">
+        <v>Handle by other team</v>
+      </c>
+      <c r="E120" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" t="str">
+        <v/>
+      </c>
+      <c r="B121" s="4" t="str">
+        <v>Settings: Recurring Order, recurring deposit will be supported via link to web</v>
+      </c>
+      <c r="C121" t="str">
+        <v/>
+      </c>
+      <c r="D121" s="17" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="E121" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" s="6" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" t="str">
+        <v/>
+      </c>
+      <c r="B122" s="4" t="str">
+        <v>Settings: Recurring Deposit flow - plan creation</v>
+      </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+      <c r="D122" s="18" t="str">
         <v>Cancelled</v>
       </c>
-      <c r="E112" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F112" t="str">
-        <v/>
-      </c>
-      <c r="G112" t="str">
-        <v/>
-      </c>
-      <c r="H112" t="str">
-        <v/>
-      </c>
-      <c r="I112" t="str">
-        <v/>
-      </c>
-      <c r="J112" t="str">
-        <v/>
-      </c>
-      <c r="K112" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" t="str">
-        <v/>
-      </c>
-      <c r="B113" s="4" t="str">
-        <v>Manage Card - Club Upgrades for Card Program</v>
-      </c>
-      <c r="C113" s="6" t="str">
-        <v>Richard Whitehouse</v>
-      </c>
-      <c r="D113" s="23" t="str">
-        <v>futureVersion</v>
-      </c>
-      <c r="E113" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F113" t="str">
-        <v/>
-      </c>
-      <c r="G113" t="str">
-        <v/>
-      </c>
-      <c r="H113" t="str">
-        <v/>
-      </c>
-      <c r="I113" t="str">
-        <v/>
-      </c>
-      <c r="J113" t="str">
-        <v/>
-      </c>
-      <c r="K113" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="str">
-        <v>Card Management 3DS Flow- test</v>
-      </c>
-      <c r="B114" t="str">
-        <v/>
-      </c>
-      <c r="C114" s="24" t="str">
-        <v>Dependency</v>
-      </c>
-      <c r="D114" t="str">
-        <v/>
-      </c>
-      <c r="E114" t="str">
-        <v/>
-      </c>
-      <c r="F114" s="8">
-        <v>46154</v>
-      </c>
-      <c r="G114" s="8">
-        <v>46160</v>
-      </c>
-      <c r="H114" s="6" t="str">
-        <v>V3(18.5)</v>
-      </c>
-      <c r="I114" t="str">
-        <v/>
-      </c>
-      <c r="J114" s="6" t="str">
-        <v>Richard</v>
-      </c>
-      <c r="K114" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L114" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M114" s="6">
-        <v>3</v>
-      </c>
-      <c r="N114" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O114" t="str">
-        <v/>
-      </c>
-      <c r="P114" t="str">
-        <v/>
-      </c>
-      <c r="Q114" s="7">
+      <c r="E122" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="str">
+        <v>Crypto staking</v>
+      </c>
+      <c r="B123" t="str">
+        <v/>
+      </c>
+      <c r="C123" s="14" t="str">
+        <v>Discovery</v>
+      </c>
+      <c r="D123" t="str">
+        <v/>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" s="8">
+        <v>46062</v>
+      </c>
+      <c r="G123" s="8">
+        <v>46141</v>
+      </c>
+      <c r="H123" s="6" t="str">
+        <v>V2(4.5)</v>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" s="6" t="str">
+        <v>Nikolaus Kulier</v>
+      </c>
+      <c r="K123" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L123" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123" s="7">
         <v>46127</v>
       </c>
-      <c r="R114" s="6" t="str">
-        <v>Richard Whitehouse Mar 4, 2026 2:30 PM</v>
-      </c>
-      <c r="S114" t="str">
-        <v/>
-      </c>
-      <c r="T114" s="8">
-        <v>46114</v>
-      </c>
-      <c r="U114" s="8">
-        <v>46114</v>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="str">
-        <v>Card Management - Add To Apple Wallet- SDK</v>
-      </c>
-      <c r="B115" t="str">
-        <v/>
-      </c>
-      <c r="C115" s="5" t="str">
-        <v>FE DEV WIP</v>
-      </c>
-      <c r="D115" t="str">
-        <v/>
-      </c>
-      <c r="E115" t="str">
-        <v/>
-      </c>
-      <c r="F115" t="str">
-        <v/>
-      </c>
-      <c r="G115" t="str">
-        <v/>
-      </c>
-      <c r="H115" s="6" t="str">
-        <v>V3(18.5)</v>
-      </c>
-      <c r="I115" s="6" t="str">
-        <v>Awaiting some feedback from Apple</v>
-      </c>
-      <c r="J115" s="6" t="str">
-        <v>Richard</v>
-      </c>
-      <c r="K115" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L115" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M115" s="6">
+      <c r="R123" s="6" t="str">
+        <v>Ilan Tatar Jan 28, 2026 7:18 PM</v>
+      </c>
+      <c r="S123" t="str">
+        <v/>
+      </c>
+      <c r="T123" t="str">
+        <v/>
+      </c>
+      <c r="U123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="str">
+        <v>Home Page Graph FE\BE</v>
+      </c>
+      <c r="B124" t="str">
+        <v/>
+      </c>
+      <c r="C124" s="16" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" s="8">
+        <v>46082</v>
+      </c>
+      <c r="G124" s="8">
+        <v>46127</v>
+      </c>
+      <c r="H124" s="6" t="str">
+        <v>V2(4.5)</v>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K124" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L124" s="6" t="str">
+        <v>Eyal Boas+ Ron Lukovitsky</v>
+      </c>
+      <c r="M124" s="6">
         <v>2</v>
       </c>
-      <c r="N115" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O115" t="str">
-        <v/>
-      </c>
-      <c r="P115" t="str">
-        <v/>
-      </c>
-      <c r="Q115" s="7">
-        <v>46127</v>
-      </c>
-      <c r="R115" s="6" t="str">
-        <v>Richard Whitehouse Mar 4, 2026 2:31 PM</v>
-      </c>
-      <c r="S115" t="str">
-        <v/>
-      </c>
-      <c r="T115" s="8">
-        <v>46093</v>
-      </c>
-      <c r="U115" s="8">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" s="9" t="str">
+      <c r="N124" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O124" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P124" s="6" t="str">
+        <v>Balance</v>
+      </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
+      <c r="R124" s="6" t="str">
+        <v>Ilan Tatar Feb 2, 2026 10:23 AM</v>
+      </c>
+      <c r="S124" t="str">
+        <v/>
+      </c>
+      <c r="T124" t="str">
+        <v/>
+      </c>
+      <c r="U124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B116" s="10" t="str">
+      <c r="B125" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C116" s="10" t="str">
+      <c r="C125" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D116" s="10" t="str">
+      <c r="D125" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E116" s="10" t="str">
+      <c r="E125" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F116" s="10" t="str">
+      <c r="F125" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G116" s="10" t="str">
+      <c r="G125" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H116" s="10" t="str">
+      <c r="H125" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I116" s="10" t="str">
+      <c r="I125" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J116" s="10" t="str">
+      <c r="J125" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K116" s="10" t="str">
+      <c r="K125" s="10" t="str">
         <v>Priority</v>
       </c>
     </row>
-    <row r="117" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" t="str">
-        <v/>
-      </c>
-      <c r="B117" s="4" t="str">
-        <v>SDK Implimentation</v>
-      </c>
-      <c r="C117" t="str">
-        <v/>
-      </c>
-      <c r="D117" s="5" t="str">
-        <v>Dev - WIP</v>
-      </c>
-      <c r="E117" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F117" t="str">
-        <v/>
-      </c>
-      <c r="G117" t="str">
-        <v/>
-      </c>
-      <c r="H117" t="str">
-        <v/>
-      </c>
-      <c r="I117" t="str">
-        <v/>
-      </c>
-      <c r="J117" t="str">
-        <v/>
-      </c>
-      <c r="K117" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" t="str">
-        <v/>
-      </c>
-      <c r="B118" s="4" t="str">
-        <v>Apple Pay Status -  State Management ABCDE</v>
-      </c>
-      <c r="C118" t="str">
-        <v/>
-      </c>
-      <c r="D118" s="5" t="str">
-        <v>Dev - WIP</v>
-      </c>
-      <c r="E118" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F118" t="str">
-        <v/>
-      </c>
-      <c r="G118" t="str">
-        <v/>
-      </c>
-      <c r="H118" t="str">
-        <v/>
-      </c>
-      <c r="I118" t="str">
-        <v/>
-      </c>
-      <c r="J118" t="str">
-        <v/>
-      </c>
-      <c r="K118" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A119" s="4" t="str">
-        <v>Account statement - Fees statement</v>
-      </c>
-      <c r="B119" t="str">
-        <v/>
-      </c>
-      <c r="C119" s="14" t="str">
+    <row r="126" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" t="str">
+        <v/>
+      </c>
+      <c r="B126" s="4" t="str">
+        <v>prod-dbrcks-money-we - Anton</v>
+      </c>
+      <c r="C126" s="6" t="str">
+        <v>Hagit Zamir</v>
+      </c>
+      <c r="D126" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="E126" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" s="8">
+        <v>46068</v>
+      </c>
+      <c r="I126" s="8">
+        <v>46078</v>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" t="str">
+        <v/>
+      </c>
+      <c r="B127" s="4" t="str">
+        <v>Gold table data verification- Yosi Elias/Lior Ben Tzur</v>
+      </c>
+      <c r="C127" t="str">
+        <v/>
+      </c>
+      <c r="D127" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="E127" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" s="8">
+        <v>46070</v>
+      </c>
+      <c r="I127" s="8">
+        <v>46128</v>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" t="str">
+        <v/>
+      </c>
+      <c r="B128" s="4" t="str">
+        <v>Home page for Plus- Filipe- Luka T</v>
+      </c>
+      <c r="C128" t="str">
+        <v/>
+      </c>
+      <c r="D128" s="13" t="str">
         <v>Discovery</v>
       </c>
-      <c r="D119" s="6" t="str">
-        <v>acctStatement</v>
-      </c>
-      <c r="E119" t="str">
-        <v/>
-      </c>
-      <c r="F119" t="str">
-        <v/>
-      </c>
-      <c r="G119" t="str">
-        <v/>
-      </c>
-      <c r="H119" s="6" t="str">
-        <v>V4(1.6)</v>
-      </c>
-      <c r="I119" t="str">
-        <v/>
-      </c>
-      <c r="J119" s="6" t="str">
-        <v>Richard</v>
-      </c>
-      <c r="K119" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L119" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M119" s="6">
-        <v>5</v>
-      </c>
-      <c r="N119" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O119" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P119" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="Q119" s="7">
-        <v>46104</v>
-      </c>
-      <c r="R119" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S119" t="str">
-        <v/>
-      </c>
-      <c r="T119" s="8">
-        <v>46104</v>
-      </c>
-      <c r="U119" s="8">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="str">
-        <v>Wallet tab - total value graph- Total Value Rolloup- Desktop</v>
-      </c>
-      <c r="B120" t="str">
-        <v/>
-      </c>
-      <c r="C120" s="19" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="D120" s="6" t="str">
-        <v>WalletTabTotalValueGraph</v>
-      </c>
-      <c r="E120" t="str">
-        <v/>
-      </c>
-      <c r="F120" t="str">
-        <v/>
-      </c>
-      <c r="G120" t="str">
-        <v/>
-      </c>
-      <c r="H120" s="6" t="str">
-        <v>V4(1.6)</v>
-      </c>
-      <c r="I120" s="6" t="str">
-        <v>OOS - Wallet Tab - Balance Display - Total Value Rollup-</v>
-      </c>
-      <c r="J120" s="6" t="str">
-        <v>Adi</v>
-      </c>
-      <c r="K120" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L120" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M120" s="6">
-        <v>3</v>
-      </c>
-      <c r="N120" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O120" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P120" s="6" t="str">
-        <v>Balance</v>
-      </c>
-      <c r="Q120" s="7">
-        <v>46127</v>
-      </c>
-      <c r="R120" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S120" t="str">
-        <v/>
-      </c>
-      <c r="T120" t="str">
-        <v/>
-      </c>
-      <c r="U120" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="str">
-        <v>Settings</v>
-      </c>
-      <c r="B121" t="str">
-        <v/>
-      </c>
-      <c r="C121" s="23" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D121" t="str">
-        <v/>
-      </c>
-      <c r="E121" t="str">
-        <v/>
-      </c>
-      <c r="F121" t="str">
-        <v/>
-      </c>
-      <c r="G121" t="str">
-        <v/>
-      </c>
-      <c r="H121" s="6" t="str">
-        <v>V3(18.5)</v>
-      </c>
-      <c r="I121" t="str">
-        <v/>
-      </c>
-      <c r="J121" s="6" t="str">
-        <v>Noit</v>
-      </c>
-      <c r="K121" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L121" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M121" s="6">
-        <v>3</v>
-      </c>
-      <c r="N121" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O121" t="str">
-        <v/>
-      </c>
-      <c r="P121" s="6" t="str">
-        <v>Payments, Settings</v>
-      </c>
-      <c r="Q121" s="7">
-        <v>46127</v>
-      </c>
-      <c r="R121" s="6" t="str">
-        <v>Hagit Zamir Feb 5, 2026 4:10 PM</v>
-      </c>
-      <c r="S121" t="str">
-        <v/>
-      </c>
-      <c r="T121" t="str">
-        <v/>
-      </c>
-      <c r="U121" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" s="9" t="str">
-        <v>Subitems</v>
-      </c>
-      <c r="B122" s="10" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C122" s="10" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="D122" s="10" t="str">
-        <v>Status</v>
-      </c>
-      <c r="E122" s="10" t="str">
-        <v>JIRA</v>
-      </c>
-      <c r="F122" s="10" t="str">
-        <v>Drop</v>
-      </c>
-      <c r="G122" s="10" t="str">
-        <v>Team</v>
-      </c>
-      <c r="H122" s="10" t="str">
-        <v>Timeline - Start</v>
-      </c>
-      <c r="I122" s="10" t="str">
-        <v>Timeline - End</v>
-      </c>
-      <c r="J122" s="10" t="str">
-        <v>Groom Readiness Date</v>
-      </c>
-      <c r="K122" s="10" t="str">
-        <v>Priority</v>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" t="str">
-        <v/>
-      </c>
-      <c r="B123" s="4" t="str">
-        <v>Settings: Default currency for LC</v>
-      </c>
-      <c r="C123" t="str">
-        <v/>
-      </c>
-      <c r="D123" s="14" t="str">
-        <v>Handle by other team</v>
-      </c>
-      <c r="E123" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F123" t="str">
-        <v/>
-      </c>
-      <c r="G123" t="str">
-        <v/>
-      </c>
-      <c r="H123" t="str">
-        <v/>
-      </c>
-      <c r="I123" t="str">
-        <v/>
-      </c>
-      <c r="J123" t="str">
-        <v/>
-      </c>
-      <c r="K123" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" t="str">
-        <v/>
-      </c>
-      <c r="B124" s="4" t="str">
-        <v>Settings: Recurring Order, recurring deposit will be supported via link to web</v>
-      </c>
-      <c r="C124" t="str">
-        <v/>
-      </c>
-      <c r="D124" s="14" t="str">
-        <v>Handle by other team</v>
-      </c>
-      <c r="E124" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F124" t="str">
-        <v/>
-      </c>
-      <c r="G124" s="6" t="str">
-        <v>Payments</v>
-      </c>
-      <c r="H124" t="str">
-        <v/>
-      </c>
-      <c r="I124" t="str">
-        <v/>
-      </c>
-      <c r="J124" t="str">
-        <v/>
-      </c>
-      <c r="K124" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" t="str">
-        <v/>
-      </c>
-      <c r="B125" s="4" t="str">
-        <v>Settings: Recurring Deposit flow - plan creation</v>
-      </c>
-      <c r="C125" t="str">
-        <v/>
-      </c>
-      <c r="D125" s="20" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="E125" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F125" t="str">
-        <v/>
-      </c>
-      <c r="G125" t="str">
-        <v/>
-      </c>
-      <c r="H125" t="str">
-        <v/>
-      </c>
-      <c r="I125" t="str">
-        <v/>
-      </c>
-      <c r="J125" t="str">
-        <v/>
-      </c>
-      <c r="K125" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A126" s="4" t="str">
-        <v>Crypto staking</v>
-      </c>
-      <c r="B126" t="str">
-        <v/>
-      </c>
-      <c r="C126" s="12" t="str">
-        <v>Stuck</v>
-      </c>
-      <c r="D126" t="str">
-        <v/>
-      </c>
-      <c r="E126" t="str">
-        <v/>
-      </c>
-      <c r="F126" s="8">
-        <v>46062</v>
-      </c>
-      <c r="G126" s="8">
-        <v>46141</v>
-      </c>
-      <c r="H126" s="6" t="str">
-        <v>V2(4.5)</v>
-      </c>
-      <c r="I126" t="str">
-        <v/>
-      </c>
-      <c r="J126" s="6" t="str">
-        <v>Nikolaus Kulier</v>
-      </c>
-      <c r="K126" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L126" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M126" t="str">
-        <v/>
-      </c>
-      <c r="N126" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O126" t="str">
-        <v/>
-      </c>
-      <c r="P126" t="str">
-        <v/>
-      </c>
-      <c r="Q126" s="7">
-        <v>46127</v>
-      </c>
-      <c r="R126" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 7:18 PM</v>
-      </c>
-      <c r="S126" t="str">
-        <v/>
-      </c>
-      <c r="T126" t="str">
-        <v/>
-      </c>
-      <c r="U126" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="str">
-        <v>Home Page Graph FE\BE</v>
-      </c>
-      <c r="B127" t="str">
-        <v/>
-      </c>
-      <c r="C127" s="17" t="str">
-        <v>Deployment</v>
-      </c>
-      <c r="D127" t="str">
-        <v/>
-      </c>
-      <c r="E127" t="str">
-        <v/>
-      </c>
-      <c r="F127" s="8">
-        <v>46082</v>
-      </c>
-      <c r="G127" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H127" s="6" t="str">
-        <v>V2(4.5)</v>
-      </c>
-      <c r="I127" t="str">
-        <v/>
-      </c>
-      <c r="J127" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K127" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L127" s="6" t="str">
-        <v>Eyal Boas+ Ron Lukovitsky</v>
-      </c>
-      <c r="M127" s="6">
-        <v>2</v>
-      </c>
-      <c r="N127" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O127" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P127" s="6" t="str">
-        <v>Balance</v>
-      </c>
-      <c r="Q127" t="str">
-        <v/>
-      </c>
-      <c r="R127" s="6" t="str">
-        <v>Ilan Tatar Feb 2, 2026 10:23 AM</v>
-      </c>
-      <c r="S127" t="str">
-        <v/>
-      </c>
-      <c r="T127" t="str">
-        <v/>
-      </c>
-      <c r="U127" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" s="9" t="str">
-        <v>Subitems</v>
-      </c>
-      <c r="B128" s="10" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C128" s="10" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="D128" s="10" t="str">
-        <v>Status</v>
-      </c>
-      <c r="E128" s="10" t="str">
-        <v>JIRA</v>
-      </c>
-      <c r="F128" s="10" t="str">
-        <v>Drop</v>
-      </c>
-      <c r="G128" s="10" t="str">
-        <v>Team</v>
-      </c>
-      <c r="H128" s="10" t="str">
-        <v>Timeline - Start</v>
-      </c>
-      <c r="I128" s="10" t="str">
-        <v>Timeline - End</v>
-      </c>
-      <c r="J128" s="10" t="str">
-        <v>Groom Readiness Date</v>
-      </c>
-      <c r="K128" s="10" t="str">
-        <v>Priority</v>
+      <c r="E128" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v/>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5646,13 +5556,13 @@
         <v/>
       </c>
       <c r="B129" s="4" t="str">
-        <v>prod-dbrcks-money-we - Anton</v>
-      </c>
-      <c r="C129" s="6" t="str">
-        <v>Hagit Zamir</v>
-      </c>
-      <c r="D129" s="11" t="str">
-        <v>Done</v>
+        <v>Home page Graph for Desktop/Existing App- Hila/Oleg</v>
+      </c>
+      <c r="C129" t="str">
+        <v/>
+      </c>
+      <c r="D129" s="17" t="str">
+        <v>Not Started</v>
       </c>
       <c r="E129" s="6" t="str">
         <v/>
@@ -5664,10 +5574,10 @@
         <v/>
       </c>
       <c r="H129" s="8">
-        <v>46068</v>
+        <v>46082</v>
       </c>
       <c r="I129" s="8">
-        <v>46078</v>
+        <v>46112</v>
       </c>
       <c r="J129" t="str">
         <v/>
@@ -5681,13 +5591,13 @@
         <v/>
       </c>
       <c r="B130" s="4" t="str">
-        <v>Gold table data verification- Yosi Elias/Lior Ben Tzur</v>
+        <v>BFF for Home Page Graph- Filipe &amp; Luka</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
-      <c r="D130" s="11" t="str">
-        <v>Done</v>
+      <c r="D130" s="17" t="str">
+        <v>Not Started</v>
       </c>
       <c r="E130" s="6" t="str">
         <v/>
@@ -5698,11 +5608,11 @@
       <c r="G130" t="str">
         <v/>
       </c>
-      <c r="H130" s="8">
-        <v>46070</v>
-      </c>
-      <c r="I130" s="8">
-        <v>46128</v>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v/>
       </c>
       <c r="J130" t="str">
         <v/>
@@ -5716,13 +5626,13 @@
         <v/>
       </c>
       <c r="B131" s="4" t="str">
-        <v>Home page for Plus- Filipe- Luka T</v>
-      </c>
-      <c r="C131" t="str">
-        <v/>
-      </c>
-      <c r="D131" s="13" t="str">
-        <v>Discovery</v>
+        <v>Lake to SQL server daily extract- Inbal</v>
+      </c>
+      <c r="C131" s="6" t="str">
+        <v>Eyal Boas</v>
+      </c>
+      <c r="D131" s="18" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="E131" s="6" t="str">
         <v/>
@@ -5733,11 +5643,11 @@
       <c r="G131" t="str">
         <v/>
       </c>
-      <c r="H131" t="str">
-        <v/>
-      </c>
-      <c r="I131" t="str">
-        <v/>
+      <c r="H131" s="8">
+        <v>46070</v>
+      </c>
+      <c r="I131" s="8">
+        <v>46096</v>
       </c>
       <c r="J131" t="str">
         <v/>
@@ -5751,13 +5661,13 @@
         <v/>
       </c>
       <c r="B132" s="4" t="str">
-        <v>Home page Graph for Desktop/Existing App- Hila/Oleg</v>
+        <v>Balance API for Graph- Maksym Shpanovsky</v>
       </c>
       <c r="C132" t="str">
         <v/>
       </c>
-      <c r="D132" s="19" t="str">
-        <v>Not Started</v>
+      <c r="D132" s="18" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="E132" s="6" t="str">
         <v/>
@@ -5768,11 +5678,11 @@
       <c r="G132" t="str">
         <v/>
       </c>
-      <c r="H132" s="8">
-        <v>46082</v>
-      </c>
-      <c r="I132" s="8">
-        <v>46112</v>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v/>
       </c>
       <c r="J132" t="str">
         <v/>
@@ -5786,13 +5696,13 @@
         <v/>
       </c>
       <c r="B133" s="4" t="str">
-        <v>BFF for Home Page Graph- Filipe &amp; Luka</v>
-      </c>
-      <c r="C133" t="str">
-        <v/>
-      </c>
-      <c r="D133" s="19" t="str">
-        <v>Not Started</v>
+        <v>dldataplatformprodwe- Eyal- Monitoring</v>
+      </c>
+      <c r="C133" s="6" t="str">
+        <v>Eyal Boas</v>
+      </c>
+      <c r="D133" s="18" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="E133" s="6" t="str">
         <v/>
@@ -5821,12 +5731,12 @@
         <v/>
       </c>
       <c r="B134" s="4" t="str">
-        <v>Lake to SQL server daily extract- Inbal</v>
-      </c>
-      <c r="C134" s="6" t="str">
-        <v>Eyal Boas</v>
-      </c>
-      <c r="D134" s="20" t="str">
+        <v>EOD Balance API handshake- Table readiness- Anton</v>
+      </c>
+      <c r="C134" t="str">
+        <v/>
+      </c>
+      <c r="D134" s="18" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E134" s="6" t="str">
@@ -5839,10 +5749,10 @@
         <v/>
       </c>
       <c r="H134" s="8">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="I134" s="8">
-        <v>46096</v>
+        <v>46078</v>
       </c>
       <c r="J134" t="str">
         <v/>
@@ -5851,74 +5761,104 @@
         <v/>
       </c>
     </row>
-    <row r="135" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135" t="str">
-        <v/>
-      </c>
-      <c r="B135" s="4" t="str">
-        <v>Balance API for Graph- Maksym Shpanovsky</v>
-      </c>
-      <c r="C135" t="str">
-        <v/>
-      </c>
-      <c r="D135" s="20" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="E135" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F135" t="str">
-        <v/>
-      </c>
-      <c r="G135" t="str">
-        <v/>
-      </c>
-      <c r="H135" t="str">
-        <v/>
+    <row r="135" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="str">
+        <v>Card Management 3DS Flow</v>
+      </c>
+      <c r="B135" t="str">
+        <v/>
+      </c>
+      <c r="C135" s="24" t="str">
+        <v>Dependency</v>
+      </c>
+      <c r="D135" t="str">
+        <v/>
+      </c>
+      <c r="E135" t="str">
+        <v/>
+      </c>
+      <c r="F135" s="8">
+        <v>46154</v>
+      </c>
+      <c r="G135" s="8">
+        <v>46160</v>
+      </c>
+      <c r="H135" s="6" t="str">
+        <v>V3(18.5)</v>
       </c>
       <c r="I135" t="str">
         <v/>
       </c>
-      <c r="J135" t="str">
-        <v/>
-      </c>
-      <c r="K135" t="str">
-        <v/>
+      <c r="J135" s="6" t="str">
+        <v>Richard</v>
+      </c>
+      <c r="K135" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L135" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M135" s="6">
+        <v>3</v>
+      </c>
+      <c r="N135" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135" s="7">
+        <v>46127</v>
+      </c>
+      <c r="R135" s="6" t="str">
+        <v>Richard Whitehouse Mar 4, 2026 2:30 PM</v>
+      </c>
+      <c r="S135" t="str">
+        <v/>
+      </c>
+      <c r="T135" s="8">
+        <v>46114</v>
+      </c>
+      <c r="U135" s="8">
+        <v>46114</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A136" t="str">
-        <v/>
-      </c>
-      <c r="B136" s="4" t="str">
-        <v>dldataplatformprodwe- Eyal- Monitoring</v>
-      </c>
-      <c r="C136" s="6" t="str">
-        <v>Eyal Boas</v>
-      </c>
-      <c r="D136" s="20" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="E136" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F136" t="str">
-        <v/>
-      </c>
-      <c r="G136" t="str">
-        <v/>
-      </c>
-      <c r="H136" t="str">
-        <v/>
-      </c>
-      <c r="I136" t="str">
-        <v/>
-      </c>
-      <c r="J136" t="str">
-        <v/>
-      </c>
-      <c r="K136" t="str">
-        <v/>
+      <c r="A136" s="9" t="str">
+        <v>Subitems</v>
+      </c>
+      <c r="B136" s="10" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C136" s="10" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="D136" s="10" t="str">
+        <v>Status</v>
+      </c>
+      <c r="E136" s="10" t="str">
+        <v>JIRA</v>
+      </c>
+      <c r="F136" s="10" t="str">
+        <v>Drop</v>
+      </c>
+      <c r="G136" s="10" t="str">
+        <v>Team</v>
+      </c>
+      <c r="H136" s="10" t="str">
+        <v>Timeline - Start</v>
+      </c>
+      <c r="I136" s="10" t="str">
+        <v>Timeline - End</v>
+      </c>
+      <c r="J136" s="10" t="str">
+        <v>Groom Readiness Date</v>
+      </c>
+      <c r="K136" s="10" t="str">
+        <v>Priority</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5926,13 +5866,13 @@
         <v/>
       </c>
       <c r="B137" s="4" t="str">
-        <v>EOD Balance API handshake- Table readiness- Anton</v>
+        <v>Screen flow - 5 days effort- Wait for Shir to design, later this week</v>
       </c>
       <c r="C137" t="str">
         <v/>
       </c>
-      <c r="D137" s="20" t="str">
-        <v>Cancelled</v>
+      <c r="D137" s="22" t="str">
+        <v>Design</v>
       </c>
       <c r="E137" s="6" t="str">
         <v/>
@@ -5943,11 +5883,11 @@
       <c r="G137" t="str">
         <v/>
       </c>
-      <c r="H137" s="8">
-        <v>46076</v>
-      </c>
-      <c r="I137" s="8">
-        <v>46078</v>
+      <c r="H137" t="str">
+        <v/>
+      </c>
+      <c r="I137" t="str">
+        <v/>
       </c>
       <c r="J137" t="str">
         <v/>
@@ -6022,14 +5962,14 @@
       </c>
     </row>
     <row r="139" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A139" t="str">
-        <v/>
+      <c r="A139" s="4" t="str">
+        <v>Push Notifications for Money!</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
-      <c r="C139" t="str">
-        <v/>
+      <c r="C139" s="14" t="str">
+        <v>Discovery</v>
       </c>
       <c r="D139" t="str">
         <v/>
@@ -6037,200 +5977,200 @@
       <c r="E139" t="str">
         <v/>
       </c>
-      <c r="F139" s="25">
+      <c r="F139" t="str">
+        <v/>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+      <c r="H139" t="str">
+        <v/>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K139" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L139" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M139" t="str">
+        <v/>
+      </c>
+      <c r="N139" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139" t="str">
+        <v/>
+      </c>
+      <c r="R139" s="6" t="str">
+        <v>Richard Whitehouse Apr 29, 2026 2:35 PM</v>
+      </c>
+      <c r="S139" t="str">
+        <v/>
+      </c>
+      <c r="T139" t="str">
+        <v/>
+      </c>
+      <c r="U139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A140" t="str">
+        <v/>
+      </c>
+      <c r="B140" t="str">
+        <v/>
+      </c>
+      <c r="C140" t="str">
+        <v/>
+      </c>
+      <c r="D140" t="str">
+        <v/>
+      </c>
+      <c r="E140" t="str">
+        <v/>
+      </c>
+      <c r="F140" s="25">
         <v>46061</v>
       </c>
-      <c r="G139" s="25">
+      <c r="G140" s="25">
         <v>46160</v>
       </c>
-      <c r="H139" t="str">
-        <v/>
-      </c>
-      <c r="I139" t="str">
-        <v/>
-      </c>
-      <c r="J139" t="str">
-        <v/>
-      </c>
-      <c r="K139" t="str">
-        <v/>
-      </c>
-      <c r="L139" t="str">
-        <v/>
-      </c>
-      <c r="M139" s="26">
-        <v>38</v>
-      </c>
-      <c r="N139" t="str">
-        <v/>
-      </c>
-      <c r="O139" t="str">
-        <v/>
-      </c>
-      <c r="P139" t="str">
-        <v/>
-      </c>
-      <c r="Q139" s="27" t="str">
+      <c r="H140" t="str">
+        <v/>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
+        <v/>
+      </c>
+      <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" s="26">
+        <v>32</v>
+      </c>
+      <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140" s="27" t="str">
         <v>2026-02-02 to 2026-04-15</v>
       </c>
-      <c r="R139" t="str">
-        <v/>
-      </c>
-      <c r="S139" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T139" s="25">
+      <c r="R140" t="str">
+        <v/>
+      </c>
+      <c r="S140" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T140" s="25">
         <v>46058</v>
       </c>
-      <c r="U139" s="25">
+      <c r="U140" s="25">
         <v>46114</v>
       </c>
     </row>
-    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="29" t="str">
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="29" t="str">
         <v>In Focus</v>
       </c>
     </row>
-    <row r="142" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="str">
+    <row r="143" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B142" s="3" t="str">
+      <c r="B143" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C142" s="3" t="str">
+      <c r="C143" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D142" s="3" t="str">
+      <c r="D143" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E142" s="3" t="str">
+      <c r="E143" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F142" s="3" t="str">
+      <c r="F143" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G142" s="3" t="str">
+      <c r="G143" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H142" s="3" t="str">
+      <c r="H143" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I142" s="3" t="str">
+      <c r="I143" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J142" s="3" t="str">
+      <c r="J143" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K142" s="3" t="str">
+      <c r="K143" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L142" s="3" t="str">
+      <c r="L143" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M142" s="3" t="str">
+      <c r="M143" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N142" s="3" t="str">
+      <c r="N143" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O142" s="3" t="str">
+      <c r="O143" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P142" s="3" t="str">
+      <c r="P143" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q142" s="3" t="str">
+      <c r="Q143" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R142" s="3" t="str">
+      <c r="R143" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S142" s="3" t="str">
+      <c r="S143" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T142" s="3" t="str">
+      <c r="T143" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U142" s="3" t="str">
+      <c r="U143" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A143" s="4" t="str">
-        <v>Risk - PCI Audit for credit card deposit- Hagit to deliver details</v>
-      </c>
-      <c r="B143" t="str">
-        <v/>
-      </c>
-      <c r="C143" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="D143" t="str">
-        <v/>
-      </c>
-      <c r="E143" t="str">
-        <v/>
-      </c>
-      <c r="F143" t="str">
-        <v/>
-      </c>
-      <c r="G143" t="str">
-        <v/>
-      </c>
-      <c r="H143" t="str">
-        <v/>
-      </c>
-      <c r="I143" t="str">
-        <v/>
-      </c>
-      <c r="J143" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K143" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L143" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M143" t="str">
-        <v/>
-      </c>
-      <c r="N143" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O143" t="str">
-        <v/>
-      </c>
-      <c r="P143" t="str">
-        <v/>
-      </c>
-      <c r="Q143" t="str">
-        <v/>
-      </c>
-      <c r="R143" s="6" t="str">
-        <v>Ilan Tatar Mar 29, 2026 1:16 PM</v>
-      </c>
-      <c r="S143" t="str">
-        <v/>
-      </c>
-      <c r="T143" t="str">
-        <v/>
-      </c>
-      <c r="U143" t="str">
-        <v/>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="str">
-        <v>Sagiv- Deposit apporval rate check- in order to prioritize/remove other MOPs from scope</v>
+        <v>Risk - PCI Audit for credit card deposit- Hagit to deliver details</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
-      <c r="C144" s="14" t="str">
-        <v>Discovery</v>
+      <c r="C144" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D144" t="str">
         <v/>
@@ -6275,7 +6215,7 @@
         <v/>
       </c>
       <c r="R144" s="6" t="str">
-        <v>Ilan Tatar Mar 26, 2026 6:04 PM</v>
+        <v>Ilan Tatar Mar 29, 2026 1:16 PM</v>
       </c>
       <c r="S144" t="str">
         <v/>
@@ -6289,7 +6229,7 @@
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="str">
-        <v>Deleaniation - Compliance new requirement- to display the entity behind every balance</v>
+        <v>Sagiv- Deposit apporval rate check- in order to prioritize/remove other MOPs from scope</v>
       </c>
       <c r="B145" t="str">
         <v/>
@@ -6340,7 +6280,7 @@
         <v/>
       </c>
       <c r="R145" s="6" t="str">
-        <v>Ilan Tatar Mar 8, 2026 2:13 PM</v>
+        <v>Ilan Tatar Mar 26, 2026 6:04 PM</v>
       </c>
       <c r="S145" t="str">
         <v/>
@@ -6354,13 +6294,13 @@
     </row>
     <row r="146" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="str">
-        <v>Withdraw risk- Work on MOP - or Deposit work is enough</v>
+        <v>Deleaniation - Compliance new requirement- to display the entity behind every balance</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
-      <c r="C146" s="30" t="str">
-        <v>Risk</v>
+      <c r="C146" s="14" t="str">
+        <v>Discovery</v>
       </c>
       <c r="D146" t="str">
         <v/>
@@ -6405,7 +6345,7 @@
         <v/>
       </c>
       <c r="R146" s="6" t="str">
-        <v>Ilan Tatar Mar 12, 2026 5:47 PM</v>
+        <v>Ilan Tatar Mar 8, 2026 2:13 PM</v>
       </c>
       <c r="S146" t="str">
         <v/>
@@ -6419,13 +6359,13 @@
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="str">
-        <v>Recurring Investment- Who will handle it in PLUS- Hodaya BE &amp; Hagit &amp; to advice</v>
+        <v>Withdraw risk- Work on MOP - or Deposit work is enough</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
-      <c r="C147" s="11" t="str">
-        <v>Done</v>
+      <c r="C147" s="30" t="str">
+        <v>Risk</v>
       </c>
       <c r="D147" t="str">
         <v/>
@@ -6470,7 +6410,7 @@
         <v/>
       </c>
       <c r="R147" s="6" t="str">
-        <v>Ilan Tatar Mar 8, 2026 2:06 PM</v>
+        <v>Ilan Tatar Mar 12, 2026 5:47 PM</v>
       </c>
       <c r="S147" t="str">
         <v/>
@@ -6484,7 +6424,7 @@
     </row>
     <row r="148" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="str">
-        <v>Main Risk : Deposit flow are waiting for ABC test for solution, develop will start Mid MArch only</v>
+        <v>Recurring Investment- Who will handle it in PLUS- Hodaya BE &amp; Hagit &amp; to advice</v>
       </c>
       <c r="B148" t="str">
         <v/>
@@ -6498,11 +6438,11 @@
       <c r="E148" t="str">
         <v/>
       </c>
-      <c r="F148" s="8">
-        <v>46082</v>
-      </c>
-      <c r="G148" s="8">
-        <v>46118</v>
+      <c r="F148" t="str">
+        <v/>
+      </c>
+      <c r="G148" t="str">
+        <v/>
       </c>
       <c r="H148" t="str">
         <v/>
@@ -6535,7 +6475,7 @@
         <v/>
       </c>
       <c r="R148" s="6" t="str">
-        <v>Ilan Tatar Feb 15, 2026 1:06 PM</v>
+        <v>Ilan Tatar Mar 8, 2026 2:06 PM</v>
       </c>
       <c r="S148" t="str">
         <v/>
@@ -6549,7 +6489,7 @@
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="str">
-        <v>Send Payment- issues with readiness to develop/Adi absence</v>
+        <v>Main Risk : Deposit flow are waiting for ABC test for solution, develop will start Mid MArch only</v>
       </c>
       <c r="B149" t="str">
         <v/>
@@ -6563,11 +6503,11 @@
       <c r="E149" t="str">
         <v/>
       </c>
-      <c r="F149" t="str">
-        <v/>
-      </c>
-      <c r="G149" t="str">
-        <v/>
+      <c r="F149" s="8">
+        <v>46082</v>
+      </c>
+      <c r="G149" s="8">
+        <v>46118</v>
       </c>
       <c r="H149" t="str">
         <v/>
@@ -6600,7 +6540,7 @@
         <v/>
       </c>
       <c r="R149" s="6" t="str">
-        <v>Ilan Tatar Mar 22, 2026 11:45 AM</v>
+        <v>Ilan Tatar Feb 15, 2026 1:06 PM</v>
       </c>
       <c r="S149" t="str">
         <v/>
@@ -6614,7 +6554,7 @@
     </row>
     <row r="150" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="str">
-        <v>Where we launch the cashflow on April 20 version? Sagiv to update 8.3</v>
+        <v>Send Payment- issues with readiness to develop/Adi absence</v>
       </c>
       <c r="B150" t="str">
         <v/>
@@ -6665,7 +6605,7 @@
         <v/>
       </c>
       <c r="R150" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:48 PM</v>
+        <v>Ilan Tatar Mar 22, 2026 11:45 AM</v>
       </c>
       <c r="S150" t="str">
         <v/>
@@ -6679,7 +6619,7 @@
     </row>
     <row r="151" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="str">
-        <v>Filipe- 1.4 get the 2 cards working + be- Ilan to coordinate</v>
+        <v>Where we launch the cashflow on April 20 version? Sagiv to update 8.3</v>
       </c>
       <c r="B151" t="str">
         <v/>
@@ -6730,7 +6670,7 @@
         <v/>
       </c>
       <c r="R151" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:50 PM</v>
+        <v>Ilan Tatar Mar 5, 2026 12:48 PM</v>
       </c>
       <c r="S151" t="str">
         <v/>
@@ -6744,7 +6684,7 @@
     </row>
     <row r="152" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="str">
-        <v>FTD ABC</v>
+        <v>Filipe- 1.4 get the 2 cards working + be- Ilan to coordinate</v>
       </c>
       <c r="B152" t="str">
         <v/>
@@ -6758,11 +6698,11 @@
       <c r="E152" t="str">
         <v/>
       </c>
-      <c r="F152" s="8">
-        <v>46057</v>
-      </c>
-      <c r="G152" s="8">
-        <v>46083</v>
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v/>
       </c>
       <c r="H152" t="str">
         <v/>
@@ -6795,7 +6735,7 @@
         <v/>
       </c>
       <c r="R152" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:17 PM</v>
+        <v>Ilan Tatar Mar 5, 2026 12:50 PM</v>
       </c>
       <c r="S152" t="str">
         <v/>
@@ -6809,7 +6749,7 @@
     </row>
     <row r="153" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="str">
-        <v>Cash flow- Decision where to locate it in the new Website</v>
+        <v>FTD ABC</v>
       </c>
       <c r="B153" t="str">
         <v/>
@@ -6824,19 +6764,19 @@
         <v/>
       </c>
       <c r="F153" s="8">
-        <v>46054</v>
+        <v>46057</v>
       </c>
       <c r="G153" s="8">
-        <v>46062</v>
+        <v>46083</v>
       </c>
       <c r="H153" t="str">
         <v/>
       </c>
-      <c r="I153" s="6" t="str">
-        <v>Meeting 9.2- Sagiv</v>
+      <c r="I153" t="str">
+        <v/>
       </c>
       <c r="J153" s="6" t="str">
-        <v>Sagiv</v>
+        <v/>
       </c>
       <c r="K153" s="6" t="str">
         <v/>
@@ -6860,7 +6800,7 @@
         <v/>
       </c>
       <c r="R153" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:06 PM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:17 PM</v>
       </c>
       <c r="S153" t="str">
         <v/>
@@ -6874,7 +6814,7 @@
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="str">
-        <v>DOD for 20.4 to Inbal? Ilan with Tal/Igor</v>
+        <v>Cash flow- Decision where to locate it in the new Website</v>
       </c>
       <c r="B154" t="str">
         <v/>
@@ -6888,20 +6828,20 @@
       <c r="E154" t="str">
         <v/>
       </c>
-      <c r="F154" t="str">
-        <v/>
-      </c>
-      <c r="G154" t="str">
-        <v/>
+      <c r="F154" s="8">
+        <v>46054</v>
+      </c>
+      <c r="G154" s="8">
+        <v>46062</v>
       </c>
       <c r="H154" t="str">
         <v/>
       </c>
-      <c r="I154" t="str">
-        <v/>
+      <c r="I154" s="6" t="str">
+        <v>Meeting 9.2- Sagiv</v>
       </c>
       <c r="J154" s="6" t="str">
-        <v/>
+        <v>Sagiv</v>
       </c>
       <c r="K154" s="6" t="str">
         <v/>
@@ -6925,7 +6865,7 @@
         <v/>
       </c>
       <c r="R154" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:49 PM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:06 PM</v>
       </c>
       <c r="S154" t="str">
         <v/>
@@ -6939,7 +6879,7 @@
     </row>
     <row r="155" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="str">
-        <v>Cash info access in the new Application</v>
+        <v>DOD for 20.4 to Inbal? Ilan with Tal/Igor</v>
       </c>
       <c r="B155" t="str">
         <v/>
@@ -6962,8 +6902,8 @@
       <c r="H155" t="str">
         <v/>
       </c>
-      <c r="I155" s="6" t="str">
-        <v>Decision about Crypto and custodial wallet. Gili and Tuval are taking this. ETA? Update ? Sagiv?</v>
+      <c r="I155" t="str">
+        <v/>
       </c>
       <c r="J155" s="6" t="str">
         <v/>
@@ -6990,7 +6930,7 @@
         <v/>
       </c>
       <c r="R155" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:15 PM</v>
+        <v>Ilan Tatar Mar 5, 2026 12:49 PM</v>
       </c>
       <c r="S155" t="str">
         <v/>
@@ -7004,7 +6944,7 @@
     </row>
     <row r="156" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="str">
-        <v>Financial History API - Understanding and plans</v>
+        <v>Cash info access in the new Application</v>
       </c>
       <c r="B156" t="str">
         <v/>
@@ -7028,7 +6968,7 @@
         <v/>
       </c>
       <c r="I156" s="6" t="str">
-        <v>Itis the list of Dep/WD from Trading account  and IBAN</v>
+        <v>Decision about Crypto and custodial wallet. Gili and Tuval are taking this. ETA? Update ? Sagiv?</v>
       </c>
       <c r="J156" s="6" t="str">
         <v/>
@@ -7055,7 +6995,7 @@
         <v/>
       </c>
       <c r="R156" s="6" t="str">
-        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:15 PM</v>
       </c>
       <c r="S156" t="str">
         <v/>
@@ -7069,7 +7009,7 @@
     </row>
     <row r="157" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="str">
-        <v>Wallet  Custodial and Non Custodial</v>
+        <v>Financial History API - Understanding and plans</v>
       </c>
       <c r="B157" t="str">
         <v/>
@@ -7077,26 +7017,26 @@
       <c r="C157" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D157" s="6" t="str">
-        <v>plusDev</v>
+      <c r="D157" t="str">
+        <v/>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
-      <c r="F157" s="8">
-        <v>46054</v>
-      </c>
-      <c r="G157" s="8">
-        <v>46058</v>
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v/>
       </c>
       <c r="H157" t="str">
         <v/>
       </c>
       <c r="I157" s="6" t="str">
-        <v>What is the solution to the Wallet tab functionality in the Plus app? Sagiv is taking this and should finalize by 5.2 the requirements</v>
+        <v>Itis the list of Dep/WD from Trading account  and IBAN</v>
       </c>
       <c r="J157" s="6" t="str">
-        <v>sagiv</v>
+        <v/>
       </c>
       <c r="K157" s="6" t="str">
         <v/>
@@ -7120,7 +7060,7 @@
         <v/>
       </c>
       <c r="R157" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 11:52 AM</v>
+        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
       </c>
       <c r="S157" t="str">
         <v/>
@@ -7134,7 +7074,7 @@
     </row>
     <row r="158" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="str">
-        <v>HP Graph - Gaps to launch on production</v>
+        <v>Wallet  Custodial and Non Custodial</v>
       </c>
       <c r="B158" t="str">
         <v/>
@@ -7142,26 +7082,26 @@
       <c r="C158" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D158" t="str">
-        <v/>
+      <c r="D158" s="6" t="str">
+        <v>plusDev</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" s="8">
-        <v>46056</v>
+        <v>46054</v>
       </c>
       <c r="G158" s="8">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="H158" t="str">
         <v/>
       </c>
       <c r="I158" s="6" t="str">
-        <v>Meeting 10.2 with Ofer and his team to plan the delivery</v>
+        <v>What is the solution to the Wallet tab functionality in the Plus app? Sagiv is taking this and should finalize by 5.2 the requirements</v>
       </c>
       <c r="J158" s="6" t="str">
-        <v/>
+        <v>sagiv</v>
       </c>
       <c r="K158" s="6" t="str">
         <v/>
@@ -7185,7 +7125,7 @@
         <v/>
       </c>
       <c r="R158" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:05 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 11:52 AM</v>
       </c>
       <c r="S158" t="str">
         <v/>
@@ -7199,7 +7139,7 @@
     </row>
     <row r="159" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="str">
-        <v>BFF- Who deliver what is the scope?</v>
+        <v>HP Graph - Gaps to launch on production</v>
       </c>
       <c r="B159" t="str">
         <v/>
@@ -7213,17 +7153,17 @@
       <c r="E159" t="str">
         <v/>
       </c>
-      <c r="F159" t="str">
-        <v/>
-      </c>
-      <c r="G159" t="str">
-        <v/>
+      <c r="F159" s="8">
+        <v>46056</v>
+      </c>
+      <c r="G159" s="8">
+        <v>46056</v>
       </c>
       <c r="H159" t="str">
         <v/>
       </c>
-      <c r="I159" t="str">
-        <v/>
+      <c r="I159" s="6" t="str">
+        <v>Meeting 10.2 with Ofer and his team to plan the delivery</v>
       </c>
       <c r="J159" s="6" t="str">
         <v/>
@@ -7250,7 +7190,7 @@
         <v/>
       </c>
       <c r="R159" s="6" t="str">
-        <v>Ilan Tatar Feb 12, 2026 12:19 PM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:05 PM</v>
       </c>
       <c r="S159" t="str">
         <v/>
@@ -7264,7 +7204,7 @@
     </row>
     <row r="160" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="str">
-        <v>Withdraw - R&amp;R between Elior/Hodaya</v>
+        <v>BFF- Who deliver what is the scope?</v>
       </c>
       <c r="B160" t="str">
         <v/>
@@ -7287,8 +7227,8 @@
       <c r="H160" t="str">
         <v/>
       </c>
-      <c r="I160" s="6" t="str">
-        <v>Elisheva said that it is not clear where it reside in RND?</v>
+      <c r="I160" t="str">
+        <v/>
       </c>
       <c r="J160" s="6" t="str">
         <v/>
@@ -7315,7 +7255,7 @@
         <v/>
       </c>
       <c r="R160" s="6" t="str">
-        <v>Ilan Tatar Feb 3, 2026 1:09 PM</v>
+        <v>Ilan Tatar Feb 12, 2026 12:19 PM</v>
       </c>
       <c r="S160" t="str">
         <v/>
@@ -7329,7 +7269,7 @@
     </row>
     <row r="161" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="str">
-        <v>EOD Balance depend on HP Graph data solution? Hagit to advise</v>
+        <v>Withdraw - R&amp;R between Elior/Hodaya</v>
       </c>
       <c r="B161" t="str">
         <v/>
@@ -7352,8 +7292,8 @@
       <c r="H161" t="str">
         <v/>
       </c>
-      <c r="I161" t="str">
-        <v/>
+      <c r="I161" s="6" t="str">
+        <v>Elisheva said that it is not clear where it reside in RND?</v>
       </c>
       <c r="J161" s="6" t="str">
         <v/>
@@ -7380,7 +7320,7 @@
         <v/>
       </c>
       <c r="R161" s="6" t="str">
-        <v>Ilan Tatar Feb 4, 2026 11:39 AM</v>
+        <v>Ilan Tatar Feb 3, 2026 1:09 PM</v>
       </c>
       <c r="S161" t="str">
         <v/>
@@ -7394,7 +7334,7 @@
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="str">
-        <v>Work For Inbal next week?</v>
+        <v>EOD Balance depend on HP Graph data solution? Hagit to advise</v>
       </c>
       <c r="B162" t="str">
         <v/>
@@ -7445,7 +7385,7 @@
         <v/>
       </c>
       <c r="R162" s="6" t="str">
-        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
+        <v>Ilan Tatar Feb 4, 2026 11:39 AM</v>
       </c>
       <c r="S162" t="str">
         <v/>
@@ -7459,7 +7399,7 @@
     </row>
     <row r="163" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="str">
-        <v>Sagiv- open task for AB deposit wizard in Monday</v>
+        <v>Work For Inbal next week?</v>
       </c>
       <c r="B163" t="str">
         <v/>
@@ -7510,7 +7450,7 @@
         <v/>
       </c>
       <c r="R163" s="6" t="str">
-        <v>Ilan Tatar Mar 5, 2026 12:56 PM</v>
+        <v>Ilan Tatar Feb 4, 2026 11:38 AM</v>
       </c>
       <c r="S163" t="str">
         <v/>
@@ -7524,7 +7464,7 @@
     </row>
     <row r="164" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="str">
-        <v>Inbal- There is nothing new in BE side delivery needed for 20.4 version</v>
+        <v>Sagiv- open task for AB deposit wizard in Monday</v>
       </c>
       <c r="B164" t="str">
         <v/>
@@ -7575,287 +7515,317 @@
         <v/>
       </c>
       <c r="R164" s="6" t="str">
+        <v>Ilan Tatar Mar 5, 2026 12:56 PM</v>
+      </c>
+      <c r="S164" t="str">
+        <v/>
+      </c>
+      <c r="T164" t="str">
+        <v/>
+      </c>
+      <c r="U164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="str">
+        <v>Inbal- There is nothing new in BE side delivery needed for 20.4 version</v>
+      </c>
+      <c r="B165" t="str">
+        <v/>
+      </c>
+      <c r="C165" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="D165" t="str">
+        <v/>
+      </c>
+      <c r="E165" t="str">
+        <v/>
+      </c>
+      <c r="F165" t="str">
+        <v/>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+      <c r="H165" t="str">
+        <v/>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K165" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L165" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str">
+        <v/>
+      </c>
+      <c r="N165" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165" t="str">
+        <v/>
+      </c>
+      <c r="R165" s="6" t="str">
         <v>Ilan Tatar Mar 11, 2026 7:41 PM</v>
       </c>
-      <c r="S164" t="str">
-        <v/>
-      </c>
-      <c r="T164" t="str">
-        <v/>
-      </c>
-      <c r="U164" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="165" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A165" t="str">
-        <v/>
-      </c>
-      <c r="B165" t="str">
-        <v/>
-      </c>
-      <c r="C165" t="str">
-        <v/>
-      </c>
-      <c r="D165" t="str">
-        <v/>
-      </c>
-      <c r="E165" t="str">
-        <v/>
-      </c>
-      <c r="F165" s="25">
+      <c r="S165" t="str">
+        <v/>
+      </c>
+      <c r="T165" t="str">
+        <v/>
+      </c>
+      <c r="U165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A166" t="str">
+        <v/>
+      </c>
+      <c r="B166" t="str">
+        <v/>
+      </c>
+      <c r="C166" t="str">
+        <v/>
+      </c>
+      <c r="D166" t="str">
+        <v/>
+      </c>
+      <c r="E166" t="str">
+        <v/>
+      </c>
+      <c r="F166" s="25">
         <v>46054</v>
       </c>
-      <c r="G165" s="25">
+      <c r="G166" s="25">
         <v>46118</v>
       </c>
-      <c r="H165" t="str">
-        <v/>
-      </c>
-      <c r="I165" t="str">
-        <v/>
-      </c>
-      <c r="J165" t="str">
-        <v/>
-      </c>
-      <c r="K165" t="str">
-        <v/>
-      </c>
-      <c r="L165" t="str">
-        <v/>
-      </c>
-      <c r="M165" s="26">
+      <c r="H166" t="str">
+        <v/>
+      </c>
+      <c r="I166" t="str">
+        <v/>
+      </c>
+      <c r="J166" t="str">
+        <v/>
+      </c>
+      <c r="K166" t="str">
+        <v/>
+      </c>
+      <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" s="26">
         <v>0</v>
       </c>
-      <c r="N165" t="str">
-        <v/>
-      </c>
-      <c r="O165" t="str">
-        <v/>
-      </c>
-      <c r="P165" t="str">
-        <v/>
-      </c>
-      <c r="Q165" s="28" t="str">
-        <v/>
-      </c>
-      <c r="R165" t="str">
-        <v/>
-      </c>
-      <c r="S165" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T165" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U165" s="28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="166" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="31" t="str">
+      <c r="N166" t="str">
+        <v/>
+      </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166" s="28" t="str">
+        <v/>
+      </c>
+      <c r="R166" t="str">
+        <v/>
+      </c>
+      <c r="S166" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T166" s="28" t="str">
+        <v/>
+      </c>
+      <c r="U166" s="28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="31" t="str">
         <v>MVP - API /BFF project</v>
       </c>
     </row>
-    <row r="168" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A168" s="3" t="str">
+    <row r="169" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B168" s="3" t="str">
+      <c r="B169" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C168" s="3" t="str">
+      <c r="C169" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D168" s="3" t="str">
+      <c r="D169" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E168" s="3" t="str">
+      <c r="E169" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F168" s="3" t="str">
+      <c r="F169" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G168" s="3" t="str">
+      <c r="G169" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H168" s="3" t="str">
+      <c r="H169" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I168" s="3" t="str">
+      <c r="I169" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J168" s="3" t="str">
+      <c r="J169" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K168" s="3" t="str">
+      <c r="K169" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L168" s="3" t="str">
+      <c r="L169" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M168" s="3" t="str">
+      <c r="M169" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N168" s="3" t="str">
+      <c r="N169" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O168" s="3" t="str">
+      <c r="O169" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P168" s="3" t="str">
+      <c r="P169" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q168" s="3" t="str">
+      <c r="Q169" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R168" s="3" t="str">
+      <c r="R169" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S168" s="3" t="str">
+      <c r="S169" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T168" s="3" t="str">
+      <c r="T169" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U168" s="3" t="str">
+      <c r="U169" s="3" t="str">
         <v>Product ETA - End</v>
       </c>
     </row>
-    <row r="169" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A169" s="4" t="str">
+    <row r="170" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="str">
         <v>Real time Balance &amp; Equity APIs- Hagit</v>
       </c>
-      <c r="B169" t="str">
-        <v/>
-      </c>
-      <c r="C169" s="11" t="str">
+      <c r="B170" t="str">
+        <v/>
+      </c>
+      <c r="C170" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D169" s="6" t="str">
+      <c r="D170" s="6" t="str">
         <v>ApiForPlus</v>
       </c>
-      <c r="E169" s="6" t="str">
+      <c r="E170" s="6" t="str">
         <v>trading real time equity API</v>
       </c>
-      <c r="F169" s="8">
+      <c r="F170" s="8">
         <v>46036</v>
       </c>
-      <c r="G169" s="8">
+      <c r="G170" s="8">
         <v>46126</v>
       </c>
-      <c r="H169" s="6" t="str">
+      <c r="H170" s="6" t="str">
         <v>V1(20.4)</v>
       </c>
-      <c r="I169" t="str">
-        <v/>
-      </c>
-      <c r="J169" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K169" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L169" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M169" s="6">
+      <c r="I170" t="str">
+        <v/>
+      </c>
+      <c r="J170" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K170" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L170" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M170" s="6">
         <v>1</v>
       </c>
-      <c r="N169" s="6" t="str">
+      <c r="N170" s="6" t="str">
         <v>S</v>
       </c>
-      <c r="O169" t="str">
-        <v/>
-      </c>
-      <c r="P169" t="str">
-        <v/>
-      </c>
-      <c r="Q169" t="str">
-        <v/>
-      </c>
-      <c r="R169" s="6" t="str">
+      <c r="O170" t="str">
+        <v/>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170" t="str">
+        <v/>
+      </c>
+      <c r="R170" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
       </c>
-      <c r="S169" t="str">
-        <v/>
-      </c>
-      <c r="T169" t="str">
-        <v/>
-      </c>
-      <c r="U169" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="170" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A170" s="9" t="str">
+      <c r="S170" t="str">
+        <v/>
+      </c>
+      <c r="T170" t="str">
+        <v/>
+      </c>
+      <c r="U170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B170" s="10" t="str">
+      <c r="B171" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C170" s="10" t="str">
+      <c r="C171" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D170" s="10" t="str">
+      <c r="D171" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E170" s="10" t="str">
+      <c r="E171" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F170" s="10" t="str">
+      <c r="F171" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G170" s="10" t="str">
+      <c r="G171" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H170" s="10" t="str">
+      <c r="H171" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I170" s="10" t="str">
+      <c r="I171" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J170" s="10" t="str">
+      <c r="J171" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K170" s="10" t="str">
+      <c r="K171" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="171" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A171" t="str">
-        <v/>
-      </c>
-      <c r="B171" s="4" t="str">
-        <v>Swaggers for 2 APIS- Maksym</v>
-      </c>
-      <c r="C171" t="str">
-        <v/>
-      </c>
-      <c r="D171" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="E171" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F171" t="str">
-        <v/>
-      </c>
-      <c r="G171" t="str">
-        <v/>
-      </c>
-      <c r="H171" s="8">
-        <v>46049</v>
-      </c>
-      <c r="I171" s="8">
-        <v>46052</v>
-      </c>
-      <c r="J171" t="str">
-        <v/>
-      </c>
-      <c r="K171" t="str">
-        <v/>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -7863,7 +7833,7 @@
         <v/>
       </c>
       <c r="B172" s="4" t="str">
-        <v>Accessibility of balances from the various accounts - Elisheva</v>
+        <v>Swaggers for 2 APIS- Maksym</v>
       </c>
       <c r="C172" t="str">
         <v/>
@@ -7884,7 +7854,7 @@
         <v>46049</v>
       </c>
       <c r="I172" s="8">
-        <v>46055</v>
+        <v>46052</v>
       </c>
       <c r="J172" t="str">
         <v/>
@@ -7898,10 +7868,10 @@
         <v/>
       </c>
       <c r="B173" s="4" t="str">
-        <v>Dev - PAYUA-7623.- Maksym</v>
-      </c>
-      <c r="C173" s="6" t="str">
-        <v>Hagit Zamir</v>
+        <v>Accessibility of balances from the various accounts - Elisheva</v>
+      </c>
+      <c r="C173" t="str">
+        <v/>
       </c>
       <c r="D173" s="11" t="str">
         <v>Done</v>
@@ -7916,10 +7886,10 @@
         <v/>
       </c>
       <c r="H173" s="8">
-        <v>46075</v>
+        <v>46049</v>
       </c>
       <c r="I173" s="8">
-        <v>46119</v>
+        <v>46055</v>
       </c>
       <c r="J173" t="str">
         <v/>
@@ -7933,10 +7903,10 @@
         <v/>
       </c>
       <c r="B174" s="4" t="str">
-        <v>Dev Admin TAPI- Amit Glazer</v>
-      </c>
-      <c r="C174" t="str">
-        <v/>
+        <v>Dev - PAYUA-7623.- Maksym</v>
+      </c>
+      <c r="C174" s="6" t="str">
+        <v>Hagit Zamir</v>
       </c>
       <c r="D174" s="11" t="str">
         <v>Done</v>
@@ -7951,10 +7921,10 @@
         <v/>
       </c>
       <c r="H174" s="8">
-        <v>46098</v>
+        <v>46075</v>
       </c>
       <c r="I174" s="8">
-        <v>46124</v>
+        <v>46119</v>
       </c>
       <c r="J174" t="str">
         <v/>
@@ -7968,7 +7938,7 @@
         <v/>
       </c>
       <c r="B175" s="4" t="str">
-        <v>Dev- Crypto- Ofir Schwartz- CRYP-7716</v>
+        <v>Dev Admin TAPI- Amit Glazer</v>
       </c>
       <c r="C175" t="str">
         <v/>
@@ -7986,10 +7956,10 @@
         <v/>
       </c>
       <c r="H175" s="8">
-        <v>46110</v>
+        <v>46098</v>
       </c>
       <c r="I175" s="8">
-        <v>46119</v>
+        <v>46124</v>
       </c>
       <c r="J175" t="str">
         <v/>
@@ -8003,7 +7973,7 @@
         <v/>
       </c>
       <c r="B176" s="4" t="str">
-        <v>Production test with users- Anton</v>
+        <v>Dev- Crypto- Ofir Schwartz- CRYP-7716</v>
       </c>
       <c r="C176" t="str">
         <v/>
@@ -8020,11 +7990,11 @@
       <c r="G176" t="str">
         <v/>
       </c>
-      <c r="H176" t="str">
-        <v/>
-      </c>
-      <c r="I176" t="str">
-        <v/>
+      <c r="H176" s="8">
+        <v>46110</v>
+      </c>
+      <c r="I176" s="8">
+        <v>46119</v>
       </c>
       <c r="J176" t="str">
         <v/>
@@ -8038,7 +8008,7 @@
         <v/>
       </c>
       <c r="B177" s="4" t="str">
-        <v>Communicate with Exp ( Filipe/Renata) to implement it</v>
+        <v>Production test with users- Anton</v>
       </c>
       <c r="C177" t="str">
         <v/>
@@ -8068,74 +8038,44 @@
         <v/>
       </c>
     </row>
-    <row r="178" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A178" s="4" t="str">
-        <v>EOD Balance- Maksym PAYUA-7769</v>
-      </c>
-      <c r="B178" t="str">
-        <v/>
-      </c>
-      <c r="C178" s="11" t="str">
+    <row r="178" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" t="str">
+        <v/>
+      </c>
+      <c r="B178" s="4" t="str">
+        <v>Communicate with Exp ( Filipe/Renata) to implement it</v>
+      </c>
+      <c r="C178" t="str">
+        <v/>
+      </c>
+      <c r="D178" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D178" s="6" t="str">
-        <v>ApiForPlus</v>
-      </c>
-      <c r="E178" t="str">
-        <v/>
-      </c>
-      <c r="F178" s="8">
-        <v>46042</v>
-      </c>
-      <c r="G178" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H178" s="6" t="str">
-        <v>V2(4.5)</v>
-      </c>
-      <c r="I178" s="6" t="str">
-        <v>Need data to expose historical balances</v>
-      </c>
-      <c r="J178" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K178" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L178" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M178" s="6">
-        <v>2</v>
-      </c>
-      <c r="N178" s="6" t="str">
-        <v>XS</v>
-      </c>
-      <c r="O178" t="str">
-        <v/>
-      </c>
-      <c r="P178" t="str">
-        <v/>
-      </c>
-      <c r="Q178" t="str">
-        <v/>
-      </c>
-      <c r="R178" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
-      </c>
-      <c r="S178" t="str">
-        <v/>
-      </c>
-      <c r="T178" t="str">
-        <v/>
-      </c>
-      <c r="U178" t="str">
+      <c r="E178" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+      <c r="H178" t="str">
+        <v/>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178" t="str">
+        <v/>
+      </c>
+      <c r="K178" t="str">
         <v/>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="str">
-        <v>Deposit APIs (using existing) +Payment Eligibility +Funding</v>
+        <v>EOD Balance- Maksym PAYUA-7769</v>
       </c>
       <c r="B179" t="str">
         <v/>
@@ -8150,16 +8090,16 @@
         <v/>
       </c>
       <c r="F179" s="8">
-        <v>46040</v>
+        <v>46042</v>
       </c>
       <c r="G179" s="8">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="H179" s="6" t="str">
-        <v>V1(20.4)</v>
-      </c>
-      <c r="I179" t="str">
-        <v/>
+        <v>V2(4.5)</v>
+      </c>
+      <c r="I179" s="6" t="str">
+        <v>Need data to expose historical balances</v>
       </c>
       <c r="J179" s="6" t="str">
         <v/>
@@ -8168,13 +8108,13 @@
         <v/>
       </c>
       <c r="L179" s="6" t="str">
-        <v>Shuky</v>
+        <v/>
       </c>
       <c r="M179" s="6">
         <v>2</v>
       </c>
       <c r="N179" s="6" t="str">
-        <v>S</v>
+        <v>XS</v>
       </c>
       <c r="O179" t="str">
         <v/>
@@ -8198,74 +8138,104 @@
         <v/>
       </c>
     </row>
-    <row r="180" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A180" s="9" t="str">
+    <row r="180" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="str">
+        <v>Deposit APIs (using existing) +Payment Eligibility +Funding</v>
+      </c>
+      <c r="B180" t="str">
+        <v/>
+      </c>
+      <c r="C180" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="D180" s="6" t="str">
+        <v>ApiForPlus</v>
+      </c>
+      <c r="E180" t="str">
+        <v/>
+      </c>
+      <c r="F180" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G180" s="8">
+        <v>46126</v>
+      </c>
+      <c r="H180" s="6" t="str">
+        <v>V1(20.4)</v>
+      </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
+      <c r="J180" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K180" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L180" s="6" t="str">
+        <v>Shuky</v>
+      </c>
+      <c r="M180" s="6">
+        <v>2</v>
+      </c>
+      <c r="N180" s="6" t="str">
+        <v>S</v>
+      </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
+      <c r="R180" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+      </c>
+      <c r="S180" t="str">
+        <v/>
+      </c>
+      <c r="T180" t="str">
+        <v/>
+      </c>
+      <c r="U180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B180" s="10" t="str">
+      <c r="B181" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C180" s="10" t="str">
+      <c r="C181" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D180" s="10" t="str">
+      <c r="D181" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E180" s="10" t="str">
+      <c r="E181" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F180" s="10" t="str">
+      <c r="F181" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G180" s="10" t="str">
+      <c r="G181" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H180" s="10" t="str">
+      <c r="H181" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I180" s="10" t="str">
+      <c r="I181" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J180" s="10" t="str">
+      <c r="J181" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K180" s="10" t="str">
+      <c r="K181" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="181" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A181" t="str">
-        <v/>
-      </c>
-      <c r="B181" s="4" t="str">
-        <v>get Eligible funding API (payment-methods/(PaymentMethodTypeId) - Shuky</v>
-      </c>
-      <c r="C181" t="str">
-        <v/>
-      </c>
-      <c r="D181" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="E181" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F181" t="str">
-        <v/>
-      </c>
-      <c r="G181" t="str">
-        <v/>
-      </c>
-      <c r="H181" t="str">
-        <v/>
-      </c>
-      <c r="I181" t="str">
-        <v/>
-      </c>
-      <c r="J181" t="str">
-        <v/>
-      </c>
-      <c r="K181" t="str">
-        <v/>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -8273,7 +8243,7 @@
         <v/>
       </c>
       <c r="B182" s="4" t="str">
-        <v>Mean of Payments (eligible-payment-method-types) API.- PAYIL-10721Shuky</v>
+        <v>get Eligible funding API (payment-methods/(PaymentMethodTypeId) - Shuky</v>
       </c>
       <c r="C182" t="str">
         <v/>
@@ -8290,11 +8260,11 @@
       <c r="G182" t="str">
         <v/>
       </c>
-      <c r="H182" s="8">
-        <v>46064</v>
-      </c>
-      <c r="I182" s="8">
-        <v>46100</v>
+      <c r="H182" t="str">
+        <v/>
+      </c>
+      <c r="I182" t="str">
+        <v/>
       </c>
       <c r="J182" t="str">
         <v/>
@@ -8308,7 +8278,7 @@
         <v/>
       </c>
       <c r="B183" s="4" t="str">
-        <v>Banking deposit MOP API- Maksym</v>
+        <v>Mean of Payments (eligible-payment-method-types) API.- PAYIL-10721Shuky</v>
       </c>
       <c r="C183" t="str">
         <v/>
@@ -8326,10 +8296,10 @@
         <v/>
       </c>
       <c r="H183" s="8">
-        <v>46055</v>
+        <v>46064</v>
       </c>
       <c r="I183" s="8">
-        <v>46125</v>
+        <v>46100</v>
       </c>
       <c r="J183" t="str">
         <v/>
@@ -8343,7 +8313,7 @@
         <v/>
       </c>
       <c r="B184" s="4" t="str">
-        <v>Swagger delivery</v>
+        <v>Banking deposit MOP API- Maksym</v>
       </c>
       <c r="C184" t="str">
         <v/>
@@ -8361,10 +8331,10 @@
         <v/>
       </c>
       <c r="H184" s="8">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="I184" s="8">
-        <v>46064</v>
+        <v>46125</v>
       </c>
       <c r="J184" t="str">
         <v/>
@@ -8378,7 +8348,7 @@
         <v/>
       </c>
       <c r="B185" s="4" t="str">
-        <v>Dictionary API- Shuky</v>
+        <v>Swagger delivery</v>
       </c>
       <c r="C185" t="str">
         <v/>
@@ -8395,11 +8365,11 @@
       <c r="G185" t="str">
         <v/>
       </c>
-      <c r="H185" t="str">
-        <v/>
-      </c>
-      <c r="I185" t="str">
-        <v/>
+      <c r="H185" s="8">
+        <v>46056</v>
+      </c>
+      <c r="I185" s="8">
+        <v>46064</v>
       </c>
       <c r="J185" t="str">
         <v/>
@@ -8413,7 +8383,7 @@
         <v/>
       </c>
       <c r="B186" s="4" t="str">
-        <v>Dictionary API- Maksym-</v>
+        <v>Dictionary API- Shuky</v>
       </c>
       <c r="C186" t="str">
         <v/>
@@ -8443,20 +8413,20 @@
         <v/>
       </c>
     </row>
-    <row r="187" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A187" s="4" t="str">
-        <v>cashflow bff - Zipi is working on it for one task</v>
-      </c>
-      <c r="B187" t="str">
-        <v/>
-      </c>
-      <c r="C187" s="11" t="str">
+    <row r="187" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" t="str">
+        <v/>
+      </c>
+      <c r="B187" s="4" t="str">
+        <v>Dictionary API- Maksym-</v>
+      </c>
+      <c r="C187" t="str">
+        <v/>
+      </c>
+      <c r="D187" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D187" t="str">
-        <v/>
-      </c>
-      <c r="E187" t="str">
+      <c r="E187" s="6" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
@@ -8471,52 +8441,22 @@
       <c r="I187" t="str">
         <v/>
       </c>
-      <c r="J187" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K187" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L187" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M187" s="6">
-        <v>1</v>
-      </c>
-      <c r="N187" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O187" t="str">
-        <v/>
-      </c>
-      <c r="P187" t="str">
-        <v/>
-      </c>
-      <c r="Q187" t="str">
-        <v/>
-      </c>
-      <c r="R187" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
-      </c>
-      <c r="S187" t="str">
-        <v/>
-      </c>
-      <c r="T187" t="str">
-        <v/>
-      </c>
-      <c r="U187" t="str">
+      <c r="J187" t="str">
+        <v/>
+      </c>
+      <c r="K187" t="str">
         <v/>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="str">
-        <v>deposit bff - we will start working on it soon. We are now preparing the contract</v>
+        <v>cashflow bff - Zipi is working on it for one task</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
-      <c r="C188" s="19" t="str">
-        <v>Not Started</v>
+      <c r="C188" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D188" t="str">
         <v/>
@@ -8546,7 +8486,7 @@
         <v/>
       </c>
       <c r="M188" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N188" s="6" t="str">
         <v/>
@@ -8561,7 +8501,7 @@
         <v/>
       </c>
       <c r="R188" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:17 PM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
       </c>
       <c r="S188" t="str">
         <v/>
@@ -8575,13 +8515,13 @@
     </row>
     <row r="189" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="str">
-        <v>banking bff - Amichai is working on it (for couple of tasks)</v>
+        <v>deposit bff - we will start working on it soon. We are now preparing the contract</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
-      <c r="C189" s="11" t="str">
-        <v>Done</v>
+      <c r="C189" s="17" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D189" t="str">
         <v/>
@@ -8611,7 +8551,7 @@
         <v/>
       </c>
       <c r="M189" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N189" s="6" t="str">
         <v/>
@@ -8626,7 +8566,7 @@
         <v/>
       </c>
       <c r="R189" s="6" t="str">
-        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:17 PM</v>
       </c>
       <c r="S189" t="str">
         <v/>
@@ -8640,31 +8580,31 @@
     </row>
     <row r="190" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="str">
-        <v>Financial History M&amp;A</v>
+        <v>banking bff - Amichai is working on it (for couple of tasks)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
-      <c r="C190" s="19" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="D190" s="6" t="str">
-        <v>ApiForM&amp;A</v>
+      <c r="C190" s="11" t="str">
+        <v>Done</v>
+      </c>
+      <c r="D190" t="str">
+        <v/>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
-      <c r="F190" s="8">
-        <v>46040</v>
-      </c>
-      <c r="G190" s="8">
-        <v>46040</v>
+      <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190" t="str">
+        <v/>
       </c>
       <c r="H190" t="str">
         <v/>
       </c>
-      <c r="I190" s="6" t="str">
-        <v>add iban mimo &amp; card trx</v>
+      <c r="I190" t="str">
+        <v/>
       </c>
       <c r="J190" s="6" t="str">
         <v/>
@@ -8675,11 +8615,11 @@
       <c r="L190" s="6" t="str">
         <v/>
       </c>
-      <c r="M190" t="str">
-        <v/>
+      <c r="M190" s="6">
+        <v>1</v>
       </c>
       <c r="N190" s="6" t="str">
-        <v>S</v>
+        <v/>
       </c>
       <c r="O190" t="str">
         <v/>
@@ -8691,7 +8631,7 @@
         <v/>
       </c>
       <c r="R190" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 10:49 AM</v>
+        <v>Ilan Tatar Mar 11, 2026 7:16 PM</v>
       </c>
       <c r="S190" t="str">
         <v/>
@@ -8705,13 +8645,13 @@
     </row>
     <row r="191" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="str">
-        <v>IBAN (balance, account, transactions, eligibility)</v>
+        <v>Financial History M&amp;A</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
-      <c r="C191" s="12" t="str">
-        <v>Stuck</v>
+      <c r="C191" s="17" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D191" s="6" t="str">
         <v>ApiForM&amp;A</v>
@@ -8719,17 +8659,17 @@
       <c r="E191" t="str">
         <v/>
       </c>
-      <c r="F191" t="str">
-        <v/>
-      </c>
-      <c r="G191" t="str">
-        <v/>
+      <c r="F191" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G191" s="8">
+        <v>46040</v>
       </c>
       <c r="H191" t="str">
         <v/>
       </c>
-      <c r="I191" t="str">
-        <v/>
+      <c r="I191" s="6" t="str">
+        <v>add iban mimo &amp; card trx</v>
       </c>
       <c r="J191" s="6" t="str">
         <v/>
@@ -8756,109 +8696,139 @@
         <v/>
       </c>
       <c r="R191" s="6" t="str">
+        <v>Ilan Tatar Jan 28, 2026 10:49 AM</v>
+      </c>
+      <c r="S191" t="str">
+        <v/>
+      </c>
+      <c r="T191" t="str">
+        <v/>
+      </c>
+      <c r="U191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="str">
+        <v>IBAN (balance, account, transactions, eligibility)</v>
+      </c>
+      <c r="B192" t="str">
+        <v/>
+      </c>
+      <c r="C192" s="12" t="str">
+        <v>Stuck</v>
+      </c>
+      <c r="D192" s="6" t="str">
+        <v>ApiForM&amp;A</v>
+      </c>
+      <c r="E192" t="str">
+        <v/>
+      </c>
+      <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v/>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
+      <c r="J192" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K192" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L192" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str">
+        <v/>
+      </c>
+      <c r="N192" s="6" t="str">
+        <v>S</v>
+      </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
+      <c r="R192" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
       </c>
-      <c r="S191" t="str">
-        <v/>
-      </c>
-      <c r="T191" t="str">
-        <v/>
-      </c>
-      <c r="U191" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="192" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A192" s="9" t="str">
+      <c r="S192" t="str">
+        <v/>
+      </c>
+      <c r="T192" t="str">
+        <v/>
+      </c>
+      <c r="U192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B192" s="10" t="str">
+      <c r="B193" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C192" s="10" t="str">
+      <c r="C193" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D192" s="10" t="str">
+      <c r="D193" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E192" s="10" t="str">
+      <c r="E193" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F192" s="10" t="str">
+      <c r="F193" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G192" s="10" t="str">
+      <c r="G193" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H192" s="10" t="str">
+      <c r="H193" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I192" s="10" t="str">
+      <c r="I193" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J192" s="10" t="str">
+      <c r="J193" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K192" s="10" t="str">
+      <c r="K193" s="10" t="str">
         <v>Priority</v>
       </c>
     </row>
-    <row r="193" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A193" t="str">
-        <v/>
-      </c>
-      <c r="B193" s="4" t="str">
+    <row r="194" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" t="str">
+        <v/>
+      </c>
+      <c r="B194" s="4" t="str">
         <v>getAccounts</v>
       </c>
-      <c r="C193" t="str">
-        <v/>
-      </c>
-      <c r="D193" s="12" t="str">
+      <c r="C194" t="str">
+        <v/>
+      </c>
+      <c r="D194" s="12" t="str">
         <v>Stuck</v>
       </c>
-      <c r="E193" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
-        <v/>
-      </c>
-      <c r="G193" t="str">
-        <v/>
-      </c>
-      <c r="H193" t="str">
-        <v/>
-      </c>
-      <c r="I193" t="str">
-        <v/>
-      </c>
-      <c r="J193" t="str">
-        <v/>
-      </c>
-      <c r="K193" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="194" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A194" s="4" t="str">
-        <v>Transfer (money bus)</v>
-      </c>
-      <c r="B194" t="str">
-        <v/>
-      </c>
-      <c r="C194" s="12" t="str">
-        <v>Stuck</v>
-      </c>
-      <c r="D194" s="6" t="str">
-        <v>ApiForM&amp;A</v>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" s="8">
-        <v>46091</v>
-      </c>
-      <c r="G194" s="8">
-        <v>46134</v>
+      <c r="E194" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194" t="str">
+        <v/>
       </c>
       <c r="H194" t="str">
         <v/>
@@ -8866,46 +8836,16 @@
       <c r="I194" t="str">
         <v/>
       </c>
-      <c r="J194" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K194" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L194" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M194" t="str">
-        <v/>
-      </c>
-      <c r="N194" s="6" t="str">
-        <v>XS</v>
-      </c>
-      <c r="O194" t="str">
-        <v/>
-      </c>
-      <c r="P194" t="str">
-        <v/>
-      </c>
-      <c r="Q194" t="str">
-        <v/>
-      </c>
-      <c r="R194" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
-      </c>
-      <c r="S194" t="str">
-        <v/>
-      </c>
-      <c r="T194" t="str">
-        <v/>
-      </c>
-      <c r="U194" t="str">
+      <c r="J194" t="str">
+        <v/>
+      </c>
+      <c r="K194" t="str">
         <v/>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="str">
-        <v>Global FTD</v>
+        <v>Transfer (money bus)</v>
       </c>
       <c r="B195" t="str">
         <v/>
@@ -8919,11 +8859,11 @@
       <c r="E195" t="str">
         <v/>
       </c>
-      <c r="F195" t="str">
-        <v/>
-      </c>
-      <c r="G195" t="str">
-        <v/>
+      <c r="F195" s="8">
+        <v>46091</v>
+      </c>
+      <c r="G195" s="8">
+        <v>46134</v>
       </c>
       <c r="H195" t="str">
         <v/>
@@ -8970,13 +8910,13 @@
     </row>
     <row r="196" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="str">
-        <v>Customer Finance</v>
+        <v>Global FTD</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
-      <c r="C196" s="19" t="str">
-        <v>Not Started</v>
+      <c r="C196" s="12" t="str">
+        <v>Stuck</v>
       </c>
       <c r="D196" s="6" t="str">
         <v>ApiForM&amp;A</v>
@@ -9035,12 +8975,12 @@
     </row>
     <row r="197" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="str">
-        <v>Banking (Payee, Withdraw)</v>
+        <v>Customer Finance</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
-      <c r="C197" s="19" t="str">
+      <c r="C197" s="17" t="str">
         <v>Not Started</v>
       </c>
       <c r="D197" s="6" t="str">
@@ -9074,7 +9014,7 @@
         <v/>
       </c>
       <c r="N197" s="6" t="str">
-        <v/>
+        <v>XS</v>
       </c>
       <c r="O197" t="str">
         <v/>
@@ -9100,16 +9040,16 @@
     </row>
     <row r="198" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="str">
-        <v>CashFlow BFF- Hagit</v>
+        <v>Banking (Payee, Withdraw)</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
-      <c r="C198" s="14" t="str">
-        <v>Discovery</v>
-      </c>
-      <c r="D198" t="str">
-        <v/>
+      <c r="C198" s="17" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="D198" s="6" t="str">
+        <v>ApiForM&amp;A</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -9151,7 +9091,7 @@
         <v/>
       </c>
       <c r="R198" s="6" t="str">
-        <v>Ilan Tatar Feb 12, 2026 1:19 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 9:52 AM</v>
       </c>
       <c r="S198" t="str">
         <v/>
@@ -9165,7 +9105,7 @@
     </row>
     <row r="199" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="str">
-        <v>Cash Account BFF- Hagit</v>
+        <v>CashFlow BFF- Hagit</v>
       </c>
       <c r="B199" t="str">
         <v/>
@@ -9230,19 +9170,19 @@
     </row>
     <row r="200" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="str">
-        <v>Buy from IBAN</v>
+        <v>Cash Account BFF- Hagit</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
-      <c r="C200" s="15" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="D200" s="6" t="str">
-        <v>ApiForPlus</v>
-      </c>
-      <c r="E200" s="6" t="str">
-        <v>trading BE orch</v>
+      <c r="C200" s="14" t="str">
+        <v>Discovery</v>
+      </c>
+      <c r="D200" t="str">
+        <v/>
+      </c>
+      <c r="E200" t="str">
+        <v/>
       </c>
       <c r="F200" t="str">
         <v/>
@@ -9269,7 +9209,7 @@
         <v/>
       </c>
       <c r="N200" s="6" t="str">
-        <v>XS</v>
+        <v/>
       </c>
       <c r="O200" t="str">
         <v/>
@@ -9281,7 +9221,7 @@
         <v/>
       </c>
       <c r="R200" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+        <v>Ilan Tatar Feb 12, 2026 1:19 PM</v>
       </c>
       <c r="S200" t="str">
         <v/>
@@ -9295,37 +9235,37 @@
     </row>
     <row r="201" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="str">
-        <v>Withdraw +Payment Eligibility</v>
+        <v>Buy from IBAN</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
-      <c r="C201" s="15" t="str">
+      <c r="C201" s="22" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D201" s="6" t="str">
         <v>ApiForPlus</v>
       </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" s="8">
-        <v>46040</v>
-      </c>
-      <c r="G201" s="8">
-        <v>46065</v>
+      <c r="E201" s="6" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="F201" t="str">
+        <v/>
+      </c>
+      <c r="G201" t="str">
+        <v/>
       </c>
       <c r="H201" t="str">
         <v/>
       </c>
-      <c r="I201" s="6" t="str">
-        <v>Using new money bus withdraw orch.</v>
+      <c r="I201" t="str">
+        <v/>
       </c>
       <c r="J201" s="6" t="str">
         <v/>
       </c>
       <c r="K201" s="6" t="str">
-        <v>IRena Plotkin</v>
+        <v/>
       </c>
       <c r="L201" s="6" t="str">
         <v/>
@@ -9334,7 +9274,7 @@
         <v/>
       </c>
       <c r="N201" s="6" t="str">
-        <v>S-M</v>
+        <v>XS</v>
       </c>
       <c r="O201" t="str">
         <v/>
@@ -9360,13 +9300,13 @@
     </row>
     <row r="202" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="str">
-        <v>Financial History- Hagit</v>
+        <v>Withdraw +Payment Eligibility</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
-      <c r="C202" s="23" t="str">
-        <v>Managed by other team</v>
+      <c r="C202" s="22" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="D202" s="6" t="str">
         <v>ApiForPlus</v>
@@ -9378,19 +9318,19 @@
         <v>46040</v>
       </c>
       <c r="G202" s="8">
-        <v>46040</v>
+        <v>46065</v>
       </c>
       <c r="H202" t="str">
         <v/>
       </c>
       <c r="I202" s="6" t="str">
-        <v>add iban mimo &amp; card trx</v>
+        <v>Using new money bus withdraw orch.</v>
       </c>
       <c r="J202" s="6" t="str">
         <v/>
       </c>
       <c r="K202" s="6" t="str">
-        <v/>
+        <v>IRena Plotkin</v>
       </c>
       <c r="L202" s="6" t="str">
         <v/>
@@ -9399,7 +9339,7 @@
         <v/>
       </c>
       <c r="N202" s="6" t="str">
-        <v>S</v>
+        <v>S-M</v>
       </c>
       <c r="O202" t="str">
         <v/>
@@ -9424,239 +9364,239 @@
       </c>
     </row>
     <row r="203" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A203" t="str">
-        <v/>
+      <c r="A203" s="4" t="str">
+        <v>Financial History- Hagit</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
-      <c r="C203" t="str">
-        <v/>
-      </c>
-      <c r="D203" t="str">
-        <v/>
+      <c r="C203" s="21" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D203" s="6" t="str">
+        <v>ApiForPlus</v>
       </c>
       <c r="E203" t="str">
         <v/>
       </c>
-      <c r="F203" s="25">
+      <c r="F203" s="8">
+        <v>46040</v>
+      </c>
+      <c r="G203" s="8">
+        <v>46040</v>
+      </c>
+      <c r="H203" t="str">
+        <v/>
+      </c>
+      <c r="I203" s="6" t="str">
+        <v>add iban mimo &amp; card trx</v>
+      </c>
+      <c r="J203" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K203" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L203" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M203" t="str">
+        <v/>
+      </c>
+      <c r="N203" s="6" t="str">
+        <v>S</v>
+      </c>
+      <c r="O203" t="str">
+        <v/>
+      </c>
+      <c r="P203" t="str">
+        <v/>
+      </c>
+      <c r="Q203" t="str">
+        <v/>
+      </c>
+      <c r="R203" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 9:50 AM</v>
+      </c>
+      <c r="S203" t="str">
+        <v/>
+      </c>
+      <c r="T203" t="str">
+        <v/>
+      </c>
+      <c r="U203" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A204" t="str">
+        <v/>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v/>
+      </c>
+      <c r="D204" t="str">
+        <v/>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" s="25">
         <v>46036</v>
       </c>
-      <c r="G203" s="25">
+      <c r="G204" s="25">
         <v>46134</v>
       </c>
-      <c r="H203" t="str">
-        <v/>
-      </c>
-      <c r="I203" t="str">
-        <v/>
-      </c>
-      <c r="J203" t="str">
-        <v/>
-      </c>
-      <c r="K203" t="str">
-        <v/>
-      </c>
-      <c r="L203" t="str">
-        <v/>
-      </c>
-      <c r="M203" s="26">
+      <c r="H204" t="str">
+        <v/>
+      </c>
+      <c r="I204" t="str">
+        <v/>
+      </c>
+      <c r="J204" t="str">
+        <v/>
+      </c>
+      <c r="K204" t="str">
+        <v/>
+      </c>
+      <c r="L204" t="str">
+        <v/>
+      </c>
+      <c r="M204" s="26">
         <v>9</v>
       </c>
-      <c r="N203" t="str">
-        <v/>
-      </c>
-      <c r="O203" t="str">
-        <v/>
-      </c>
-      <c r="P203" t="str">
-        <v/>
-      </c>
-      <c r="Q203" s="28" t="str">
-        <v/>
-      </c>
-      <c r="R203" t="str">
-        <v/>
-      </c>
-      <c r="S203" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T203" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U203" s="28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="204" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A205" s="32" t="str">
+      <c r="N204" t="str">
+        <v/>
+      </c>
+      <c r="O204" t="str">
+        <v/>
+      </c>
+      <c r="P204" t="str">
+        <v/>
+      </c>
+      <c r="Q204" s="28" t="str">
+        <v/>
+      </c>
+      <c r="R204" t="str">
+        <v/>
+      </c>
+      <c r="S204" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T204" s="28" t="str">
+        <v/>
+      </c>
+      <c r="U204" s="28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="205" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="32" t="str">
         <v>Not in Money scope/Future versions</v>
       </c>
     </row>
-    <row r="206" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A206" s="3" t="str">
+    <row r="207" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A207" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B206" s="3" t="str">
+      <c r="B207" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C206" s="3" t="str">
+      <c r="C207" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D206" s="3" t="str">
+      <c r="D207" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E206" s="3" t="str">
+      <c r="E207" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F206" s="3" t="str">
+      <c r="F207" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G206" s="3" t="str">
+      <c r="G207" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H206" s="3" t="str">
+      <c r="H207" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I206" s="3" t="str">
+      <c r="I207" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J206" s="3" t="str">
+      <c r="J207" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K206" s="3" t="str">
+      <c r="K207" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L206" s="3" t="str">
+      <c r="L207" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M206" s="3" t="str">
+      <c r="M207" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N206" s="3" t="str">
+      <c r="N207" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O206" s="3" t="str">
+      <c r="O207" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P206" s="3" t="str">
+      <c r="P207" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q206" s="3" t="str">
+      <c r="Q207" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R206" s="3" t="str">
+      <c r="R207" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S206" s="3" t="str">
+      <c r="S207" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T206" s="3" t="str">
+      <c r="T207" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U206" s="3" t="str">
+      <c r="U207" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="207" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A207" s="4" t="str">
-        <v>Portfolio: Balance breakdown display</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" s="23" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D207" s="6" t="str">
-        <v>Home:Balances&amp; Graph</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" s="8">
-        <v>46076</v>
-      </c>
-      <c r="G207" s="8">
-        <v>46076</v>
-      </c>
-      <c r="H207" t="str">
-        <v/>
-      </c>
-      <c r="I207" t="str">
-        <v/>
-      </c>
-      <c r="J207" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K207" s="6" t="str">
-        <v>Inbal Escholi</v>
-      </c>
-      <c r="L207" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M207" s="6">
-        <v>99</v>
-      </c>
-      <c r="N207" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O207" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P207" s="6" t="str">
-        <v>Balance</v>
-      </c>
-      <c r="Q207" t="str">
-        <v/>
-      </c>
-      <c r="R207" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
-      </c>
-      <c r="S207" t="str">
-        <v/>
-      </c>
-      <c r="T207" t="str">
-        <v/>
-      </c>
-      <c r="U207" t="str">
-        <v/>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="str">
-        <v>Close to IBAN</v>
+        <v>Portfolio: Balance breakdown display</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
-      <c r="C208" s="23" t="str">
+      <c r="C208" s="21" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D208" s="6" t="str">
-        <v>tradeIBAN</v>
-      </c>
-      <c r="E208" s="6" t="str">
-        <v>trading BE orch</v>
-      </c>
-      <c r="F208" t="str">
-        <v/>
-      </c>
-      <c r="G208" t="str">
-        <v/>
+        <v>Home:Balances&amp; Graph</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" s="8">
+        <v>46076</v>
+      </c>
+      <c r="G208" s="8">
+        <v>46076</v>
       </c>
       <c r="H208" t="str">
         <v/>
       </c>
-      <c r="I208" s="6" t="str">
-        <v>Dependency with Trading- TBD</v>
+      <c r="I208" t="str">
+        <v/>
       </c>
       <c r="J208" s="6" t="str">
-        <v>Joanna</v>
+        <v/>
       </c>
       <c r="K208" s="6" t="str">
-        <v/>
+        <v>Inbal Escholi</v>
       </c>
       <c r="L208" s="6" t="str">
         <v/>
@@ -9671,13 +9611,13 @@
         <v/>
       </c>
       <c r="P208" s="6" t="str">
-        <v>Local currency, Trading</v>
+        <v>Balance</v>
       </c>
       <c r="Q208" t="str">
         <v/>
       </c>
       <c r="R208" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
       </c>
       <c r="S208" t="str">
         <v/>
@@ -9691,12 +9631,12 @@
     </row>
     <row r="209" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="str">
-        <v>Trade from IBAN (local currency)</v>
+        <v>Close to IBAN</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
-      <c r="C209" s="23" t="str">
+      <c r="C209" s="21" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D209" s="6" t="str">
@@ -9756,12 +9696,12 @@
     </row>
     <row r="210" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="str">
-        <v>Exectuion popup - balance drawer</v>
+        <v>Trade from IBAN (local currency)</v>
       </c>
       <c r="B210" t="str">
         <v/>
       </c>
-      <c r="C210" s="23" t="str">
+      <c r="C210" s="21" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D210" s="6" t="str">
@@ -9780,7 +9720,7 @@
         <v/>
       </c>
       <c r="I210" s="6" t="str">
-        <v>Using the SDK + API. Need execution popup BFF</v>
+        <v>Dependency with Trading- TBD</v>
       </c>
       <c r="J210" s="6" t="str">
         <v>Joanna</v>
@@ -9801,7 +9741,7 @@
         <v/>
       </c>
       <c r="P210" s="6" t="str">
-        <v>Local currency, Payments</v>
+        <v>Local currency, Trading</v>
       </c>
       <c r="Q210" t="str">
         <v/>
@@ -9821,100 +9761,100 @@
     </row>
     <row r="211" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="str">
+        <v>Exectuion popup - balance drawer</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" s="21" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D211" s="6" t="str">
+        <v>tradeIBAN</v>
+      </c>
+      <c r="E211" s="6" t="str">
+        <v>trading BE orch</v>
+      </c>
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+      <c r="H211" t="str">
+        <v/>
+      </c>
+      <c r="I211" s="6" t="str">
+        <v>Using the SDK + API. Need execution popup BFF</v>
+      </c>
+      <c r="J211" s="6" t="str">
+        <v>Joanna</v>
+      </c>
+      <c r="K211" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L211" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M211" s="6">
+        <v>99</v>
+      </c>
+      <c r="N211" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O211" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P211" s="6" t="str">
+        <v>Local currency, Payments</v>
+      </c>
+      <c r="Q211" t="str">
+        <v/>
+      </c>
+      <c r="R211" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S211" t="str">
+        <v/>
+      </c>
+      <c r="T211" t="str">
+        <v/>
+      </c>
+      <c r="U211" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="str">
         <v>Home Page- Balance Display</v>
       </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" s="23" t="str">
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" s="21" t="str">
         <v>Managed by other team</v>
       </c>
-      <c r="D211" s="6" t="str">
+      <c r="D212" s="6" t="str">
         <v>Home:Balances&amp; Graph</v>
       </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" s="8">
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" s="8">
         <v>46076</v>
       </c>
-      <c r="G211" s="8">
+      <c r="G212" s="8">
         <v>46076</v>
       </c>
-      <c r="H211" t="str">
-        <v/>
-      </c>
-      <c r="I211" s="6" t="str">
+      <c r="H212" t="str">
+        <v/>
+      </c>
+      <c r="I212" s="6" t="str">
         <v>Require effort to expose the data from the lake
 Meeting 20/1 - home page redesign</v>
       </c>
-      <c r="J211" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K211" s="6" t="str">
-        <v>Inbal Escholi</v>
-      </c>
-      <c r="L211" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M211" s="6">
-        <v>99</v>
-      </c>
-      <c r="N211" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O211" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P211" s="6" t="str">
-        <v>Balance</v>
-      </c>
-      <c r="Q211" s="7">
-        <v>46083</v>
-      </c>
-      <c r="R211" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S211" t="str">
-        <v/>
-      </c>
-      <c r="T211" t="str">
-        <v/>
-      </c>
-      <c r="U211" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="212" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A212" s="4" t="str">
-        <v>Recurring Investment</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" s="23" t="str">
-        <v>Managed by other team</v>
-      </c>
-      <c r="D212" s="6" t="str">
-        <v>recurInvestment</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" s="8">
-        <v>46105</v>
-      </c>
-      <c r="G212" s="8">
-        <v>46132</v>
-      </c>
-      <c r="H212" t="str">
-        <v/>
-      </c>
-      <c r="I212" t="str">
-        <v/>
-      </c>
       <c r="J212" s="6" t="str">
-        <v>Noit</v>
+        <v/>
       </c>
       <c r="K212" s="6" t="str">
         <v>Inbal Escholi</v>
@@ -9928,14 +9868,14 @@
       <c r="N212" s="6" t="str">
         <v/>
       </c>
-      <c r="O212" t="str">
+      <c r="O212" s="6" t="str">
         <v/>
       </c>
       <c r="P212" s="6" t="str">
-        <v>Payments, Recurring Investment</v>
-      </c>
-      <c r="Q212" t="str">
-        <v/>
+        <v>Balance</v>
+      </c>
+      <c r="Q212" s="7">
+        <v>46083</v>
       </c>
       <c r="R212" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
@@ -9950,74 +9890,104 @@
         <v/>
       </c>
     </row>
-    <row r="213" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A213" s="9" t="str">
+    <row r="213" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="str">
+        <v>Recurring Investment</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" s="21" t="str">
+        <v>Managed by other team</v>
+      </c>
+      <c r="D213" s="6" t="str">
+        <v>recurInvestment</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" s="8">
+        <v>46105</v>
+      </c>
+      <c r="G213" s="8">
+        <v>46132</v>
+      </c>
+      <c r="H213" t="str">
+        <v/>
+      </c>
+      <c r="I213" t="str">
+        <v/>
+      </c>
+      <c r="J213" s="6" t="str">
+        <v>Noit</v>
+      </c>
+      <c r="K213" s="6" t="str">
+        <v>Inbal Escholi</v>
+      </c>
+      <c r="L213" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M213" s="6">
+        <v>99</v>
+      </c>
+      <c r="N213" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O213" t="str">
+        <v/>
+      </c>
+      <c r="P213" s="6" t="str">
+        <v>Payments, Recurring Investment</v>
+      </c>
+      <c r="Q213" t="str">
+        <v/>
+      </c>
+      <c r="R213" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S213" t="str">
+        <v/>
+      </c>
+      <c r="T213" t="str">
+        <v/>
+      </c>
+      <c r="U213" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="214" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A214" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B213" s="10" t="str">
+      <c r="B214" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C213" s="10" t="str">
+      <c r="C214" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D213" s="10" t="str">
+      <c r="D214" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E213" s="10" t="str">
+      <c r="E214" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F213" s="10" t="str">
+      <c r="F214" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G213" s="10" t="str">
+      <c r="G214" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H213" s="10" t="str">
+      <c r="H214" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I213" s="10" t="str">
+      <c r="I214" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J213" s="10" t="str">
+      <c r="J214" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K213" s="10" t="str">
+      <c r="K214" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="214" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A214" t="str">
-        <v/>
-      </c>
-      <c r="B214" s="4" t="str">
-        <v>Recurring investment - card details</v>
-      </c>
-      <c r="C214" t="str">
-        <v/>
-      </c>
-      <c r="D214" s="19" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="E214" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v/>
-      </c>
-      <c r="G214" s="6" t="str">
-        <v>Payments</v>
-      </c>
-      <c r="H214" t="str">
-        <v/>
-      </c>
-      <c r="I214" t="str">
-        <v/>
-      </c>
-      <c r="J214" t="str">
-        <v/>
-      </c>
-      <c r="K214" t="str">
-        <v/>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -10025,50 +9995,50 @@
         <v/>
       </c>
       <c r="B215" s="4" t="str">
+        <v>Recurring investment - card details</v>
+      </c>
+      <c r="C215" t="str">
+        <v/>
+      </c>
+      <c r="D215" s="17" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="E215" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v/>
+      </c>
+      <c r="G215" s="6" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="H215" t="str">
+        <v/>
+      </c>
+      <c r="I215" t="str">
+        <v/>
+      </c>
+      <c r="J215" t="str">
+        <v/>
+      </c>
+      <c r="K215" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="216" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216" t="str">
+        <v/>
+      </c>
+      <c r="B216" s="4" t="str">
         <v>Recurring investment feature</v>
       </c>
-      <c r="C215" t="str">
-        <v/>
-      </c>
-      <c r="D215" s="19" t="str">
+      <c r="C216" t="str">
+        <v/>
+      </c>
+      <c r="D216" s="17" t="str">
         <v>Not Started</v>
       </c>
-      <c r="E215" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v/>
-      </c>
-      <c r="G215" t="str">
-        <v/>
-      </c>
-      <c r="H215" t="str">
-        <v/>
-      </c>
-      <c r="I215" t="str">
-        <v/>
-      </c>
-      <c r="J215" t="str">
-        <v/>
-      </c>
-      <c r="K215" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="216" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A216" s="4" t="str">
-        <v>IBAN - Club Upgrades for Account Programs</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" s="22" t="str">
-        <v>Future Version</v>
-      </c>
-      <c r="D216" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="E216" t="str">
+      <c r="E216" s="6" t="str">
         <v/>
       </c>
       <c r="F216" t="str">
@@ -10083,55 +10053,25 @@
       <c r="I216" t="str">
         <v/>
       </c>
-      <c r="J216" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K216" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L216" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M216" s="6">
-        <v>100</v>
-      </c>
-      <c r="N216" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O216" t="str">
-        <v/>
-      </c>
-      <c r="P216" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="Q216" t="str">
-        <v/>
-      </c>
-      <c r="R216" s="6" t="str">
-        <v>Hagit Zamir Feb 3, 2026 3:42 PM</v>
-      </c>
-      <c r="S216" t="str">
-        <v/>
-      </c>
-      <c r="T216" t="str">
-        <v/>
-      </c>
-      <c r="U216" t="str">
+      <c r="J216" t="str">
+        <v/>
+      </c>
+      <c r="K216" t="str">
         <v/>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="str">
-        <v>Wallet tab - IBAN - Direct Debit</v>
+        <v>IBAN - Club Upgrades for Account Programs</v>
       </c>
       <c r="B217" t="str">
         <v/>
       </c>
-      <c r="C217" s="22" t="str">
+      <c r="C217" s="20" t="str">
         <v>Future Version</v>
       </c>
       <c r="D217" s="6" t="str">
-        <v>ManageDirectDebit</v>
+        <v>Banking</v>
       </c>
       <c r="E217" t="str">
         <v/>
@@ -10145,11 +10085,11 @@
       <c r="H217" t="str">
         <v/>
       </c>
-      <c r="I217" s="6" t="str">
-        <v>Web only (mobile web is optional)</v>
+      <c r="I217" t="str">
+        <v/>
       </c>
       <c r="J217" s="6" t="str">
-        <v>Adi</v>
+        <v/>
       </c>
       <c r="K217" s="6" t="str">
         <v/>
@@ -10163,7 +10103,7 @@
       <c r="N217" s="6" t="str">
         <v/>
       </c>
-      <c r="O217" s="6" t="str">
+      <c r="O217" t="str">
         <v/>
       </c>
       <c r="P217" s="6" t="str">
@@ -10173,7 +10113,7 @@
         <v/>
       </c>
       <c r="R217" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+        <v>Hagit Zamir Feb 3, 2026 3:42 PM</v>
       </c>
       <c r="S217" t="str">
         <v/>
@@ -10187,37 +10127,37 @@
     </row>
     <row r="218" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="str">
-        <v>Crypto-in/out - New Flow</v>
+        <v>Wallet tab - IBAN - Direct Debit</v>
       </c>
       <c r="B218" t="str">
         <v/>
       </c>
-      <c r="C218" s="22" t="str">
+      <c r="C218" s="20" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D218" t="str">
-        <v/>
+      <c r="D218" s="6" t="str">
+        <v>ManageDirectDebit</v>
       </c>
       <c r="E218" t="str">
         <v/>
       </c>
-      <c r="F218" s="8">
-        <v>46061</v>
-      </c>
-      <c r="G218" s="8">
-        <v>46075</v>
+      <c r="F218" t="str">
+        <v/>
+      </c>
+      <c r="G218" t="str">
+        <v/>
       </c>
       <c r="H218" t="str">
         <v/>
       </c>
-      <c r="I218" t="str">
-        <v/>
+      <c r="I218" s="6" t="str">
+        <v>Web only (mobile web is optional)</v>
       </c>
       <c r="J218" s="6" t="str">
-        <v>Nikolaus Kulier</v>
+        <v>Adi</v>
       </c>
       <c r="K218" s="6" t="str">
-        <v>Inbal Escholi</v>
+        <v/>
       </c>
       <c r="L218" s="6" t="str">
         <v/>
@@ -10232,92 +10172,122 @@
         <v/>
       </c>
       <c r="P218" s="6" t="str">
+        <v>Banking</v>
+      </c>
+      <c r="Q218" t="str">
+        <v/>
+      </c>
+      <c r="R218" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S218" t="str">
+        <v/>
+      </c>
+      <c r="T218" t="str">
+        <v/>
+      </c>
+      <c r="U218" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="219" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="str">
+        <v>Crypto-in/out - New Flow</v>
+      </c>
+      <c r="B219" t="str">
+        <v/>
+      </c>
+      <c r="C219" s="20" t="str">
+        <v>Future Version</v>
+      </c>
+      <c r="D219" t="str">
+        <v/>
+      </c>
+      <c r="E219" t="str">
+        <v/>
+      </c>
+      <c r="F219" s="8">
+        <v>46061</v>
+      </c>
+      <c r="G219" s="8">
+        <v>46075</v>
+      </c>
+      <c r="H219" t="str">
+        <v/>
+      </c>
+      <c r="I219" t="str">
+        <v/>
+      </c>
+      <c r="J219" s="6" t="str">
+        <v>Nikolaus Kulier</v>
+      </c>
+      <c r="K219" s="6" t="str">
+        <v>Inbal Escholi</v>
+      </c>
+      <c r="L219" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M219" s="6">
+        <v>100</v>
+      </c>
+      <c r="N219" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O219" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P219" s="6" t="str">
         <v>Crypto</v>
       </c>
-      <c r="Q218" t="str">
-        <v/>
-      </c>
-      <c r="R218" s="6" t="str">
+      <c r="Q219" t="str">
+        <v/>
+      </c>
+      <c r="R219" s="6" t="str">
         <v>Hagit Zamir Feb 3, 2026 11:58 AM</v>
       </c>
-      <c r="S218" t="str">
-        <v/>
-      </c>
-      <c r="T218" t="str">
-        <v/>
-      </c>
-      <c r="U218" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="219" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A219" s="9" t="str">
+      <c r="S219" t="str">
+        <v/>
+      </c>
+      <c r="T219" t="str">
+        <v/>
+      </c>
+      <c r="U219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="220" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A220" s="9" t="str">
         <v>Subitems</v>
       </c>
-      <c r="B219" s="10" t="str">
+      <c r="B220" s="10" t="str">
         <v>Name</v>
       </c>
-      <c r="C219" s="10" t="str">
+      <c r="C220" s="10" t="str">
         <v>Owner</v>
       </c>
-      <c r="D219" s="10" t="str">
+      <c r="D220" s="10" t="str">
         <v>Status</v>
       </c>
-      <c r="E219" s="10" t="str">
+      <c r="E220" s="10" t="str">
         <v>JIRA</v>
       </c>
-      <c r="F219" s="10" t="str">
+      <c r="F220" s="10" t="str">
         <v>Drop</v>
       </c>
-      <c r="G219" s="10" t="str">
+      <c r="G220" s="10" t="str">
         <v>Team</v>
       </c>
-      <c r="H219" s="10" t="str">
+      <c r="H220" s="10" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="I219" s="10" t="str">
+      <c r="I220" s="10" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="J219" s="10" t="str">
+      <c r="J220" s="10" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="K219" s="10" t="str">
+      <c r="K220" s="10" t="str">
         <v>Priority</v>
-      </c>
-    </row>
-    <row r="220" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A220" t="str">
-        <v/>
-      </c>
-      <c r="B220" s="4" t="str">
-        <v>New Crypto in flow</v>
-      </c>
-      <c r="C220" t="str">
-        <v/>
-      </c>
-      <c r="D220" s="19" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="E220" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F220" t="str">
-        <v/>
-      </c>
-      <c r="G220" t="str">
-        <v/>
-      </c>
-      <c r="H220" t="str">
-        <v/>
-      </c>
-      <c r="I220" t="str">
-        <v/>
-      </c>
-      <c r="J220" t="str">
-        <v/>
-      </c>
-      <c r="K220" t="str">
-        <v/>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -10325,50 +10295,50 @@
         <v/>
       </c>
       <c r="B221" s="4" t="str">
+        <v>New Crypto in flow</v>
+      </c>
+      <c r="C221" t="str">
+        <v/>
+      </c>
+      <c r="D221" s="17" t="str">
+        <v>Not Started</v>
+      </c>
+      <c r="E221" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F221" t="str">
+        <v/>
+      </c>
+      <c r="G221" t="str">
+        <v/>
+      </c>
+      <c r="H221" t="str">
+        <v/>
+      </c>
+      <c r="I221" t="str">
+        <v/>
+      </c>
+      <c r="J221" t="str">
+        <v/>
+      </c>
+      <c r="K221" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="222" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A222" t="str">
+        <v/>
+      </c>
+      <c r="B222" s="4" t="str">
         <v>New Crypto out flow</v>
       </c>
-      <c r="C221" t="str">
-        <v/>
-      </c>
-      <c r="D221" s="19" t="str">
+      <c r="C222" t="str">
+        <v/>
+      </c>
+      <c r="D222" s="17" t="str">
         <v>Not Started</v>
       </c>
-      <c r="E221" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F221" t="str">
-        <v/>
-      </c>
-      <c r="G221" t="str">
-        <v/>
-      </c>
-      <c r="H221" t="str">
-        <v/>
-      </c>
-      <c r="I221" t="str">
-        <v/>
-      </c>
-      <c r="J221" t="str">
-        <v/>
-      </c>
-      <c r="K221" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="222" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A222" s="4" t="str">
-        <v>Account statement - IBAN</v>
-      </c>
-      <c r="B222" t="str">
-        <v/>
-      </c>
-      <c r="C222" s="22" t="str">
-        <v>Future Version</v>
-      </c>
-      <c r="D222" s="6" t="str">
-        <v>acctStatement</v>
-      </c>
-      <c r="E222" t="str">
+      <c r="E222" s="6" t="str">
         <v/>
       </c>
       <c r="F222" t="str">
@@ -10383,55 +10353,25 @@
       <c r="I222" t="str">
         <v/>
       </c>
-      <c r="J222" s="6" t="str">
-        <v>Richard</v>
-      </c>
-      <c r="K222" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L222" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M222" s="6">
-        <v>100</v>
-      </c>
-      <c r="N222" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O222" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P222" s="6" t="str">
-        <v>Banking</v>
-      </c>
-      <c r="Q222" t="str">
-        <v/>
-      </c>
-      <c r="R222" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
-      </c>
-      <c r="S222" t="str">
-        <v/>
-      </c>
-      <c r="T222" t="str">
-        <v/>
-      </c>
-      <c r="U222" t="str">
+      <c r="J222" t="str">
+        <v/>
+      </c>
+      <c r="K222" t="str">
         <v/>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="str">
-        <v>Wallet tab - Global banners- Transactional Banners</v>
+        <v>Account statement - IBAN</v>
       </c>
       <c r="B223" t="str">
         <v/>
       </c>
-      <c r="C223" s="22" t="str">
+      <c r="C223" s="20" t="str">
         <v>Future Version</v>
       </c>
       <c r="D223" s="6" t="str">
-        <v>WalletTab</v>
+        <v>acctStatement</v>
       </c>
       <c r="E223" t="str">
         <v/>
@@ -10445,11 +10385,11 @@
       <c r="H223" t="str">
         <v/>
       </c>
-      <c r="I223" s="6" t="str">
-        <v>Meeting 20/1 - home page redesign</v>
+      <c r="I223" t="str">
+        <v/>
       </c>
       <c r="J223" s="6" t="str">
-        <v>Adi</v>
+        <v>Richard</v>
       </c>
       <c r="K223" s="6" t="str">
         <v/>
@@ -10467,7 +10407,7 @@
         <v/>
       </c>
       <c r="P223" s="6" t="str">
-        <v>Banking, Card Mng.</v>
+        <v>Banking</v>
       </c>
       <c r="Q223" t="str">
         <v/>
@@ -10487,16 +10427,16 @@
     </row>
     <row r="224" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="str">
-        <v>Long term solution for Trade button between Money and Trading</v>
+        <v>Wallet tab - Global banners- Transactional Banners</v>
       </c>
       <c r="B224" t="str">
         <v/>
       </c>
-      <c r="C224" s="22" t="str">
+      <c r="C224" s="20" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D224" t="str">
-        <v/>
+      <c r="D224" s="6" t="str">
+        <v>WalletTab</v>
       </c>
       <c r="E224" t="str">
         <v/>
@@ -10510,11 +10450,11 @@
       <c r="H224" t="str">
         <v/>
       </c>
-      <c r="I224" t="str">
-        <v/>
+      <c r="I224" s="6" t="str">
+        <v>Meeting 20/1 - home page redesign</v>
       </c>
       <c r="J224" s="6" t="str">
-        <v/>
+        <v>Adi</v>
       </c>
       <c r="K224" s="6" t="str">
         <v/>
@@ -10528,17 +10468,17 @@
       <c r="N224" s="6" t="str">
         <v/>
       </c>
-      <c r="O224" t="str">
-        <v/>
-      </c>
-      <c r="P224" t="str">
-        <v/>
+      <c r="O224" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P224" s="6" t="str">
+        <v>Banking, Card Mng.</v>
       </c>
       <c r="Q224" t="str">
         <v/>
       </c>
       <c r="R224" s="6" t="str">
-        <v>Ilan Tatar Mar 9, 2026 2:46 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
       <c r="S224" t="str">
         <v/>
@@ -10552,12 +10492,12 @@
     </row>
     <row r="225" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="str">
-        <v>NCW in eToro Plus</v>
+        <v>Long term solution for Trade button between Money and Trading</v>
       </c>
       <c r="B225" t="str">
         <v/>
       </c>
-      <c r="C225" s="22" t="str">
+      <c r="C225" s="20" t="str">
         <v>Future Version</v>
       </c>
       <c r="D225" t="str">
@@ -10575,11 +10515,11 @@
       <c r="H225" t="str">
         <v/>
       </c>
-      <c r="I225" s="6" t="str">
-        <v>Dependency with Compliance</v>
+      <c r="I225" t="str">
+        <v/>
       </c>
       <c r="J225" s="6" t="str">
-        <v>Nikolaus Kulier</v>
+        <v/>
       </c>
       <c r="K225" s="6" t="str">
         <v/>
@@ -10593,17 +10533,17 @@
       <c r="N225" s="6" t="str">
         <v/>
       </c>
-      <c r="O225" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P225" s="6" t="str">
-        <v>Crypto</v>
+      <c r="O225" t="str">
+        <v/>
+      </c>
+      <c r="P225" t="str">
+        <v/>
       </c>
       <c r="Q225" t="str">
         <v/>
       </c>
       <c r="R225" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+        <v>Ilan Tatar Mar 9, 2026 2:46 PM</v>
       </c>
       <c r="S225" t="str">
         <v/>
@@ -10617,16 +10557,16 @@
     </row>
     <row r="226" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="str">
-        <v>Wallet Tab - Product Promotions (all products - Local Accounts / ISA / Crypto etc etc)</v>
+        <v>NCW in eToro Plus</v>
       </c>
       <c r="B226" t="str">
         <v/>
       </c>
-      <c r="C226" s="22" t="str">
+      <c r="C226" s="20" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D226" s="6" t="str">
-        <v>WalletTabTotalValueGraph</v>
+      <c r="D226" t="str">
+        <v/>
       </c>
       <c r="E226" t="str">
         <v/>
@@ -10640,11 +10580,11 @@
       <c r="H226" t="str">
         <v/>
       </c>
-      <c r="I226" t="str">
-        <v/>
+      <c r="I226" s="6" t="str">
+        <v>Dependency with Compliance</v>
       </c>
       <c r="J226" s="6" t="str">
-        <v>Adi</v>
+        <v>Nikolaus Kulier</v>
       </c>
       <c r="K226" s="6" t="str">
         <v/>
@@ -10653,7 +10593,7 @@
         <v/>
       </c>
       <c r="M226" s="6">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="N226" s="6" t="str">
         <v/>
@@ -10662,13 +10602,13 @@
         <v/>
       </c>
       <c r="P226" s="6" t="str">
-        <v>Wallet Tab</v>
+        <v>Crypto</v>
       </c>
       <c r="Q226" t="str">
         <v/>
       </c>
       <c r="R226" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:28 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
       </c>
       <c r="S226" t="str">
         <v/>
@@ -10682,16 +10622,16 @@
     </row>
     <row r="227" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="str">
-        <v>Trigger Web Deposit workaround for 20.4- Inbal</v>
+        <v>Wallet Tab - Product Promotions (all products - Local Accounts / ISA / Crypto etc etc)</v>
       </c>
       <c r="B227" t="str">
         <v/>
       </c>
-      <c r="C227" s="15" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="D227" t="str">
-        <v/>
+      <c r="C227" s="20" t="str">
+        <v>Future Version</v>
+      </c>
+      <c r="D227" s="6" t="str">
+        <v>WalletTabTotalValueGraph</v>
       </c>
       <c r="E227" t="str">
         <v/>
@@ -10709,7 +10649,7 @@
         <v/>
       </c>
       <c r="J227" s="6" t="str">
-        <v>Richard</v>
+        <v>Adi</v>
       </c>
       <c r="K227" s="6" t="str">
         <v/>
@@ -10718,22 +10658,22 @@
         <v/>
       </c>
       <c r="M227" s="6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N227" s="6" t="str">
         <v/>
       </c>
-      <c r="O227" t="str">
-        <v/>
-      </c>
-      <c r="P227" t="str">
-        <v/>
+      <c r="O227" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P227" s="6" t="str">
+        <v>Wallet Tab</v>
       </c>
       <c r="Q227" t="str">
         <v/>
       </c>
       <c r="R227" s="6" t="str">
-        <v>Ilan Tatar Mar 4, 2026 2:45 PM</v>
+        <v>Ilan Tatar Jan 28, 2026 6:28 PM</v>
       </c>
       <c r="S227" t="str">
         <v/>
@@ -10747,16 +10687,16 @@
     </row>
     <row r="228" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="str">
-        <v>Wallet Tab - Balances list</v>
+        <v>Trigger Web Deposit workaround for 20.4- Inbal</v>
       </c>
       <c r="B228" t="str">
         <v/>
       </c>
-      <c r="C228" s="15" t="str">
+      <c r="C228" s="22" t="str">
         <v>Cancelled</v>
       </c>
-      <c r="D228" s="6" t="str">
-        <v>WalletTabTotalValueGraph</v>
+      <c r="D228" t="str">
+        <v/>
       </c>
       <c r="E228" t="str">
         <v/>
@@ -10774,7 +10714,7 @@
         <v/>
       </c>
       <c r="J228" s="6" t="str">
-        <v>Adi</v>
+        <v>Richard</v>
       </c>
       <c r="K228" s="6" t="str">
         <v/>
@@ -10783,22 +10723,22 @@
         <v/>
       </c>
       <c r="M228" s="6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N228" s="6" t="str">
         <v/>
       </c>
-      <c r="O228" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P228" s="6" t="str">
-        <v>Balance</v>
+      <c r="O228" t="str">
+        <v/>
+      </c>
+      <c r="P228" t="str">
+        <v/>
       </c>
       <c r="Q228" t="str">
         <v/>
       </c>
       <c r="R228" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:16 PM</v>
+        <v>Ilan Tatar Mar 4, 2026 2:45 PM</v>
       </c>
       <c r="S228" t="str">
         <v/>
@@ -10812,25 +10752,25 @@
     </row>
     <row r="229" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="str">
-        <v>Watchlist: Balance breakdown display</v>
+        <v>Wallet Tab - Balances list</v>
       </c>
       <c r="B229" t="str">
         <v/>
       </c>
-      <c r="C229" s="15" t="str">
+      <c r="C229" s="22" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D229" s="6" t="str">
-        <v>Home:Balances&amp; Graph</v>
+        <v>WalletTabTotalValueGraph</v>
       </c>
       <c r="E229" t="str">
         <v/>
       </c>
-      <c r="F229" s="8">
-        <v>46076</v>
-      </c>
-      <c r="G229" s="8">
-        <v>46076</v>
+      <c r="F229" t="str">
+        <v/>
+      </c>
+      <c r="G229" t="str">
+        <v/>
       </c>
       <c r="H229" t="str">
         <v/>
@@ -10839,10 +10779,10 @@
         <v/>
       </c>
       <c r="J229" s="6" t="str">
-        <v/>
+        <v>Adi</v>
       </c>
       <c r="K229" s="6" t="str">
-        <v>Inbal Escholi</v>
+        <v/>
       </c>
       <c r="L229" s="6" t="str">
         <v/>
@@ -10863,7 +10803,7 @@
         <v/>
       </c>
       <c r="R229" s="6" t="str">
-        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
+        <v>Ilan Tatar Jan 28, 2026 6:16 PM</v>
       </c>
       <c r="S229" t="str">
         <v/>
@@ -10877,409 +10817,409 @@
     </row>
     <row r="230" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="str">
+        <v>Drop 1 gaps implementation- Inbal</v>
+      </c>
+      <c r="B230" t="str">
+        <v/>
+      </c>
+      <c r="C230" s="22" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D230" t="str">
+        <v/>
+      </c>
+      <c r="E230" t="str">
+        <v/>
+      </c>
+      <c r="F230" s="8">
+        <v>46131</v>
+      </c>
+      <c r="G230" s="8">
+        <v>46134</v>
+      </c>
+      <c r="H230" s="6" t="str">
+        <v>V1(20.4)</v>
+      </c>
+      <c r="I230" t="str">
+        <v/>
+      </c>
+      <c r="J230" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K230" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L230" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M230" s="6">
+        <v>1</v>
+      </c>
+      <c r="N230" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O230" t="str">
+        <v/>
+      </c>
+      <c r="P230" t="str">
+        <v/>
+      </c>
+      <c r="Q230" t="str">
+        <v/>
+      </c>
+      <c r="R230" s="6" t="str">
+        <v>Ilan Tatar Apr 19, 2026 11:17 AM</v>
+      </c>
+      <c r="S230" t="str">
+        <v/>
+      </c>
+      <c r="T230" t="str">
+        <v/>
+      </c>
+      <c r="U230" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="str">
+        <v>Watchlist: Balance breakdown display</v>
+      </c>
+      <c r="B231" t="str">
+        <v/>
+      </c>
+      <c r="C231" s="22" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D231" s="6" t="str">
+        <v>Home:Balances&amp; Graph</v>
+      </c>
+      <c r="E231" t="str">
+        <v/>
+      </c>
+      <c r="F231" s="8">
+        <v>46076</v>
+      </c>
+      <c r="G231" s="8">
+        <v>46076</v>
+      </c>
+      <c r="H231" t="str">
+        <v/>
+      </c>
+      <c r="I231" t="str">
+        <v/>
+      </c>
+      <c r="J231" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K231" s="6" t="str">
+        <v>Inbal Escholi</v>
+      </c>
+      <c r="L231" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M231" s="6">
+        <v>-1</v>
+      </c>
+      <c r="N231" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O231" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P231" s="6" t="str">
+        <v>Balance</v>
+      </c>
+      <c r="Q231" t="str">
+        <v/>
+      </c>
+      <c r="R231" s="6" t="str">
+        <v>Ilan Tatar Jan 28, 2026 6:10 PM</v>
+      </c>
+      <c r="S231" t="str">
+        <v/>
+      </c>
+      <c r="T231" t="str">
+        <v/>
+      </c>
+      <c r="U231" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="232" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="str">
         <v>Payment Client Technical gaps for aftr launch</v>
       </c>
-      <c r="B230" t="str">
-        <v/>
-      </c>
-      <c r="C230" s="22" t="str">
+      <c r="B232" t="str">
+        <v/>
+      </c>
+      <c r="C232" s="20" t="str">
         <v>Future Version</v>
       </c>
-      <c r="D230" t="str">
-        <v/>
-      </c>
-      <c r="E230" t="str">
-        <v/>
-      </c>
-      <c r="F230" t="str">
-        <v/>
-      </c>
-      <c r="G230" t="str">
-        <v/>
-      </c>
-      <c r="H230" t="str">
-        <v/>
-      </c>
-      <c r="I230" t="str">
-        <v/>
-      </c>
-      <c r="J230" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K230" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L230" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M230" t="str">
-        <v/>
-      </c>
-      <c r="N230" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O230" t="str">
-        <v/>
-      </c>
-      <c r="P230" t="str">
-        <v/>
-      </c>
-      <c r="Q230" t="str">
-        <v/>
-      </c>
-      <c r="R230" s="6" t="str">
+      <c r="D232" t="str">
+        <v/>
+      </c>
+      <c r="E232" t="str">
+        <v/>
+      </c>
+      <c r="F232" t="str">
+        <v/>
+      </c>
+      <c r="G232" t="str">
+        <v/>
+      </c>
+      <c r="H232" t="str">
+        <v/>
+      </c>
+      <c r="I232" t="str">
+        <v/>
+      </c>
+      <c r="J232" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K232" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L232" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M232" t="str">
+        <v/>
+      </c>
+      <c r="N232" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O232" t="str">
+        <v/>
+      </c>
+      <c r="P232" t="str">
+        <v/>
+      </c>
+      <c r="Q232" t="str">
+        <v/>
+      </c>
+      <c r="R232" s="6" t="str">
         <v>Ilan Tatar Apr 12, 2026 12:56 PM</v>
       </c>
-      <c r="S230" t="str">
-        <v/>
-      </c>
-      <c r="T230" t="str">
-        <v/>
-      </c>
-      <c r="U230" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="231" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A231" t="str">
-        <v/>
-      </c>
-      <c r="B231" t="str">
-        <v/>
-      </c>
-      <c r="C231" t="str">
-        <v/>
-      </c>
-      <c r="D231" t="str">
-        <v/>
-      </c>
-      <c r="E231" t="str">
-        <v/>
-      </c>
-      <c r="F231" s="25">
+      <c r="S232" t="str">
+        <v/>
+      </c>
+      <c r="T232" t="str">
+        <v/>
+      </c>
+      <c r="U232" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="233" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="str">
+        <v>Account statement - Fees statement</v>
+      </c>
+      <c r="B233" t="str">
+        <v/>
+      </c>
+      <c r="C233" s="20" t="str">
+        <v>Future Version</v>
+      </c>
+      <c r="D233" s="6" t="str">
+        <v>acctStatement</v>
+      </c>
+      <c r="E233" t="str">
+        <v/>
+      </c>
+      <c r="F233" t="str">
+        <v/>
+      </c>
+      <c r="G233" t="str">
+        <v/>
+      </c>
+      <c r="H233" s="6" t="str">
+        <v>V4(1.6)</v>
+      </c>
+      <c r="I233" t="str">
+        <v/>
+      </c>
+      <c r="J233" s="6" t="str">
+        <v>Richard</v>
+      </c>
+      <c r="K233" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L233" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M233" s="6">
+        <v>5</v>
+      </c>
+      <c r="N233" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O233" s="6" t="str">
+        <v/>
+      </c>
+      <c r="P233" s="6" t="str">
+        <v>Banking</v>
+      </c>
+      <c r="Q233" s="7">
+        <v>46104</v>
+      </c>
+      <c r="R233" s="6" t="str">
+        <v>Ilan Tatar Jan 25, 2026 12:17 PM</v>
+      </c>
+      <c r="S233" t="str">
+        <v/>
+      </c>
+      <c r="T233" s="8">
+        <v>46104</v>
+      </c>
+      <c r="U233" s="8">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="234" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A234" t="str">
+        <v/>
+      </c>
+      <c r="B234" t="str">
+        <v/>
+      </c>
+      <c r="C234" t="str">
+        <v/>
+      </c>
+      <c r="D234" t="str">
+        <v/>
+      </c>
+      <c r="E234" t="str">
+        <v/>
+      </c>
+      <c r="F234" s="25">
         <v>46061</v>
       </c>
-      <c r="G231" s="25">
-        <v>46132</v>
-      </c>
-      <c r="H231" t="str">
-        <v/>
-      </c>
-      <c r="I231" t="str">
-        <v/>
-      </c>
-      <c r="J231" t="str">
-        <v/>
-      </c>
-      <c r="K231" t="str">
-        <v/>
-      </c>
-      <c r="L231" t="str">
-        <v/>
-      </c>
-      <c r="M231" s="26">
-        <v>1292</v>
-      </c>
-      <c r="N231" t="str">
-        <v/>
-      </c>
-      <c r="O231" t="str">
-        <v/>
-      </c>
-      <c r="P231" t="str">
-        <v/>
-      </c>
-      <c r="Q231" s="27" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="R231" t="str">
-        <v/>
-      </c>
-      <c r="S231" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T231" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U231" s="28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="232" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233" s="33" t="str">
+      <c r="G234" s="25">
+        <v>46134</v>
+      </c>
+      <c r="H234" t="str">
+        <v/>
+      </c>
+      <c r="I234" t="str">
+        <v/>
+      </c>
+      <c r="J234" t="str">
+        <v/>
+      </c>
+      <c r="K234" t="str">
+        <v/>
+      </c>
+      <c r="L234" t="str">
+        <v/>
+      </c>
+      <c r="M234" s="26">
+        <v>1298</v>
+      </c>
+      <c r="N234" t="str">
+        <v/>
+      </c>
+      <c r="O234" t="str">
+        <v/>
+      </c>
+      <c r="P234" t="str">
+        <v/>
+      </c>
+      <c r="Q234" s="27" t="str">
+        <v>2026-03-02 to 2026-03-23</v>
+      </c>
+      <c r="R234" t="str">
+        <v/>
+      </c>
+      <c r="S234" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T234" s="25">
+        <v>46104</v>
+      </c>
+      <c r="U234" s="25">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="235" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="33" t="str">
         <v>Program Milestones</v>
       </c>
     </row>
-    <row r="234" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A234" s="3" t="str">
+    <row r="237" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A237" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B234" s="3" t="str">
+      <c r="B237" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C234" s="3" t="str">
+      <c r="C237" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D234" s="3" t="str">
+      <c r="D237" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E234" s="3" t="str">
+      <c r="E237" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F234" s="3" t="str">
+      <c r="F237" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G234" s="3" t="str">
+      <c r="G237" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H234" s="3" t="str">
+      <c r="H237" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I234" s="3" t="str">
+      <c r="I237" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J234" s="3" t="str">
+      <c r="J237" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K234" s="3" t="str">
+      <c r="K237" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L234" s="3" t="str">
+      <c r="L237" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M234" s="3" t="str">
+      <c r="M237" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N234" s="3" t="str">
+      <c r="N237" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O234" s="3" t="str">
+      <c r="O237" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P234" s="3" t="str">
+      <c r="P237" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q234" s="3" t="str">
+      <c r="Q237" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R234" s="3" t="str">
+      <c r="R237" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S234" s="3" t="str">
+      <c r="S237" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T234" s="3" t="str">
+      <c r="T237" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U234" s="3" t="str">
+      <c r="U237" s="3" t="str">
         <v>Product ETA - End</v>
-      </c>
-    </row>
-    <row r="235" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A235" s="4" t="str">
-        <v>STD + Swaggers</v>
-      </c>
-      <c r="B235" t="str">
-        <v/>
-      </c>
-      <c r="C235" s="11" t="str">
-        <v>Done</v>
-      </c>
-      <c r="D235" t="str">
-        <v/>
-      </c>
-      <c r="E235" t="str">
-        <v/>
-      </c>
-      <c r="F235" s="8">
-        <v>46048</v>
-      </c>
-      <c r="G235" s="8">
-        <v>46048</v>
-      </c>
-      <c r="H235" t="str">
-        <v/>
-      </c>
-      <c r="I235" t="str">
-        <v/>
-      </c>
-      <c r="J235" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K235" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L235" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M235" t="str">
-        <v/>
-      </c>
-      <c r="N235" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O235" t="str">
-        <v/>
-      </c>
-      <c r="P235" t="str">
-        <v/>
-      </c>
-      <c r="Q235" t="str">
-        <v/>
-      </c>
-      <c r="R235" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:19 PM</v>
-      </c>
-      <c r="S235" t="str">
-        <v/>
-      </c>
-      <c r="T235" t="str">
-        <v/>
-      </c>
-      <c r="U235" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="236" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A236" s="4" t="str">
-        <v>Critical APIs in production</v>
-      </c>
-      <c r="B236" t="str">
-        <v/>
-      </c>
-      <c r="C236" s="5" t="str">
-        <v>FE DEV WIP</v>
-      </c>
-      <c r="D236" t="str">
-        <v/>
-      </c>
-      <c r="E236" t="str">
-        <v/>
-      </c>
-      <c r="F236" s="8">
-        <v>46112</v>
-      </c>
-      <c r="G236" s="8">
-        <v>46127</v>
-      </c>
-      <c r="H236" t="str">
-        <v/>
-      </c>
-      <c r="I236" t="str">
-        <v/>
-      </c>
-      <c r="J236" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K236" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L236" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M236" t="str">
-        <v/>
-      </c>
-      <c r="N236" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O236" t="str">
-        <v/>
-      </c>
-      <c r="P236" t="str">
-        <v/>
-      </c>
-      <c r="Q236" t="str">
-        <v/>
-      </c>
-      <c r="R236" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:15 PM</v>
-      </c>
-      <c r="S236" t="str">
-        <v/>
-      </c>
-      <c r="T236" t="str">
-        <v/>
-      </c>
-      <c r="U236" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="237" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A237" s="4" t="str">
-        <v>Non critical APIs in prodcution</v>
-      </c>
-      <c r="B237" t="str">
-        <v/>
-      </c>
-      <c r="C237" s="5" t="str">
-        <v>FE DEV WIP</v>
-      </c>
-      <c r="D237" t="str">
-        <v/>
-      </c>
-      <c r="E237" t="str">
-        <v/>
-      </c>
-      <c r="F237" s="8">
-        <v>46127</v>
-      </c>
-      <c r="G237" s="8">
-        <v>46142</v>
-      </c>
-      <c r="H237" t="str">
-        <v/>
-      </c>
-      <c r="I237" t="str">
-        <v/>
-      </c>
-      <c r="J237" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K237" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L237" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M237" t="str">
-        <v/>
-      </c>
-      <c r="N237" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O237" t="str">
-        <v/>
-      </c>
-      <c r="P237" t="str">
-        <v/>
-      </c>
-      <c r="Q237" t="str">
-        <v/>
-      </c>
-      <c r="R237" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
-      </c>
-      <c r="S237" t="str">
-        <v/>
-      </c>
-      <c r="T237" t="str">
-        <v/>
-      </c>
-      <c r="U237" t="str">
-        <v/>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="str">
-        <v>E2E readiness</v>
+        <v>STD + Swaggers</v>
       </c>
       <c r="B238" t="str">
         <v/>
       </c>
-      <c r="C238" s="19" t="str">
-        <v>Not Started</v>
+      <c r="C238" s="11" t="str">
+        <v>Done</v>
       </c>
       <c r="D238" t="str">
         <v/>
@@ -11288,16 +11228,16 @@
         <v/>
       </c>
       <c r="F238" s="8">
-        <v>46145</v>
+        <v>46048</v>
       </c>
       <c r="G238" s="8">
-        <v>46145</v>
+        <v>46048</v>
       </c>
       <c r="H238" t="str">
         <v/>
       </c>
-      <c r="I238" s="6" t="str">
-        <v>E2E to start in Mid May + 1.5 weeks buffer</v>
+      <c r="I238" t="str">
+        <v/>
       </c>
       <c r="J238" s="6" t="str">
         <v/>
@@ -11324,7 +11264,7 @@
         <v/>
       </c>
       <c r="R238" s="6" t="str">
-        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:19 PM</v>
       </c>
       <c r="S238" t="str">
         <v/>
@@ -11338,13 +11278,13 @@
     </row>
     <row r="239" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="str">
-        <v>Drop 1 Super- 20.4</v>
+        <v>Critical APIs in production</v>
       </c>
       <c r="B239" t="str">
         <v/>
       </c>
-      <c r="C239" s="17" t="str">
-        <v>Deployment</v>
+      <c r="C239" s="5" t="str">
+        <v>FE DEV WIP</v>
       </c>
       <c r="D239" t="str">
         <v/>
@@ -11352,11 +11292,11 @@
       <c r="E239" t="str">
         <v/>
       </c>
-      <c r="F239" t="str">
-        <v/>
-      </c>
-      <c r="G239" t="str">
-        <v/>
+      <c r="F239" s="8">
+        <v>46112</v>
+      </c>
+      <c r="G239" s="8">
+        <v>46127</v>
       </c>
       <c r="H239" t="str">
         <v/>
@@ -11389,7 +11329,7 @@
         <v/>
       </c>
       <c r="R239" s="6" t="str">
-        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:15 PM</v>
       </c>
       <c r="S239" t="str">
         <v/>
@@ -11403,7 +11343,7 @@
     </row>
     <row r="240" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="str">
-        <v>Drop 2 - Super 4.5</v>
+        <v>Non critical APIs in prodcution</v>
       </c>
       <c r="B240" t="str">
         <v/>
@@ -11417,11 +11357,11 @@
       <c r="E240" t="str">
         <v/>
       </c>
-      <c r="F240" t="str">
-        <v/>
-      </c>
-      <c r="G240" t="str">
-        <v/>
+      <c r="F240" s="8">
+        <v>46127</v>
+      </c>
+      <c r="G240" s="8">
+        <v>46142</v>
       </c>
       <c r="H240" t="str">
         <v/>
@@ -11454,7 +11394,7 @@
         <v/>
       </c>
       <c r="R240" s="6" t="str">
-        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
       </c>
       <c r="S240" t="str">
         <v/>
@@ -11468,13 +11408,13 @@
     </row>
     <row r="241" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="str">
-        <v>Drop 3 Super - 18.5</v>
+        <v>E2E readiness</v>
       </c>
       <c r="B241" t="str">
         <v/>
       </c>
-      <c r="C241" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C241" s="17" t="str">
+        <v>Not Started</v>
       </c>
       <c r="D241" t="str">
         <v/>
@@ -11482,17 +11422,17 @@
       <c r="E241" t="str">
         <v/>
       </c>
-      <c r="F241" t="str">
-        <v/>
-      </c>
-      <c r="G241" t="str">
-        <v/>
+      <c r="F241" s="8">
+        <v>46145</v>
+      </c>
+      <c r="G241" s="8">
+        <v>46145</v>
       </c>
       <c r="H241" t="str">
         <v/>
       </c>
-      <c r="I241" t="str">
-        <v/>
+      <c r="I241" s="6" t="str">
+        <v>E2E to start in Mid May + 1.5 weeks buffer</v>
       </c>
       <c r="J241" s="6" t="str">
         <v/>
@@ -11519,7 +11459,7 @@
         <v/>
       </c>
       <c r="R241" s="6" t="str">
-        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+        <v>Ilan Tatar Jan 25, 2026 1:16 PM</v>
       </c>
       <c r="S241" t="str">
         <v/>
@@ -11533,13 +11473,13 @@
     </row>
     <row r="242" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="str">
-        <v>Drop 4- Super - 1.6</v>
+        <v>Drop 1 Super- 20.4</v>
       </c>
       <c r="B242" t="str">
         <v/>
       </c>
-      <c r="C242" s="14" t="str">
-        <v>Discovery</v>
+      <c r="C242" s="16" t="str">
+        <v>Deployment</v>
       </c>
       <c r="D242" t="str">
         <v/>
@@ -11597,14 +11537,14 @@
       </c>
     </row>
     <row r="243" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A243" t="str">
-        <v/>
+      <c r="A243" s="4" t="str">
+        <v>Drop 2 - Super 4.5</v>
       </c>
       <c r="B243" t="str">
         <v/>
       </c>
-      <c r="C243" t="str">
-        <v/>
+      <c r="C243" s="5" t="str">
+        <v>FE DEV WIP</v>
       </c>
       <c r="D243" t="str">
         <v/>
@@ -11612,387 +11552,582 @@
       <c r="E243" t="str">
         <v/>
       </c>
-      <c r="F243" s="25">
+      <c r="F243" t="str">
+        <v/>
+      </c>
+      <c r="G243" t="str">
+        <v/>
+      </c>
+      <c r="H243" t="str">
+        <v/>
+      </c>
+      <c r="I243" t="str">
+        <v/>
+      </c>
+      <c r="J243" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K243" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L243" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M243" t="str">
+        <v/>
+      </c>
+      <c r="N243" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O243" t="str">
+        <v/>
+      </c>
+      <c r="P243" t="str">
+        <v/>
+      </c>
+      <c r="Q243" t="str">
+        <v/>
+      </c>
+      <c r="R243" s="6" t="str">
+        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+      </c>
+      <c r="S243" t="str">
+        <v/>
+      </c>
+      <c r="T243" t="str">
+        <v/>
+      </c>
+      <c r="U243" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="244" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="str">
+        <v>Drop 3 Super - 18.5</v>
+      </c>
+      <c r="B244" t="str">
+        <v/>
+      </c>
+      <c r="C244" s="5" t="str">
+        <v>FE DEV WIP</v>
+      </c>
+      <c r="D244" t="str">
+        <v/>
+      </c>
+      <c r="E244" t="str">
+        <v/>
+      </c>
+      <c r="F244" t="str">
+        <v/>
+      </c>
+      <c r="G244" t="str">
+        <v/>
+      </c>
+      <c r="H244" t="str">
+        <v/>
+      </c>
+      <c r="I244" t="str">
+        <v/>
+      </c>
+      <c r="J244" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K244" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L244" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M244" t="str">
+        <v/>
+      </c>
+      <c r="N244" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O244" t="str">
+        <v/>
+      </c>
+      <c r="P244" t="str">
+        <v/>
+      </c>
+      <c r="Q244" t="str">
+        <v/>
+      </c>
+      <c r="R244" s="6" t="str">
+        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+      </c>
+      <c r="S244" t="str">
+        <v/>
+      </c>
+      <c r="T244" t="str">
+        <v/>
+      </c>
+      <c r="U244" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="245" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A245" s="4" t="str">
+        <v>Drop 4- Super - 1.6</v>
+      </c>
+      <c r="B245" t="str">
+        <v/>
+      </c>
+      <c r="C245" s="14" t="str">
+        <v>Discovery</v>
+      </c>
+      <c r="D245" t="str">
+        <v/>
+      </c>
+      <c r="E245" t="str">
+        <v/>
+      </c>
+      <c r="F245" t="str">
+        <v/>
+      </c>
+      <c r="G245" t="str">
+        <v/>
+      </c>
+      <c r="H245" t="str">
+        <v/>
+      </c>
+      <c r="I245" t="str">
+        <v/>
+      </c>
+      <c r="J245" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K245" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L245" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M245" t="str">
+        <v/>
+      </c>
+      <c r="N245" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O245" t="str">
+        <v/>
+      </c>
+      <c r="P245" t="str">
+        <v/>
+      </c>
+      <c r="Q245" t="str">
+        <v/>
+      </c>
+      <c r="R245" s="6" t="str">
+        <v>Ilan Tatar Apr 13, 2026 12:51 PM</v>
+      </c>
+      <c r="S245" t="str">
+        <v/>
+      </c>
+      <c r="T245" t="str">
+        <v/>
+      </c>
+      <c r="U245" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="246" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A246" t="str">
+        <v/>
+      </c>
+      <c r="B246" t="str">
+        <v/>
+      </c>
+      <c r="C246" t="str">
+        <v/>
+      </c>
+      <c r="D246" t="str">
+        <v/>
+      </c>
+      <c r="E246" t="str">
+        <v/>
+      </c>
+      <c r="F246" s="25">
         <v>46048</v>
       </c>
-      <c r="G243" s="25">
+      <c r="G246" s="25">
         <v>46145</v>
       </c>
-      <c r="H243" t="str">
-        <v/>
-      </c>
-      <c r="I243" t="str">
-        <v/>
-      </c>
-      <c r="J243" t="str">
-        <v/>
-      </c>
-      <c r="K243" t="str">
-        <v/>
-      </c>
-      <c r="L243" t="str">
-        <v/>
-      </c>
-      <c r="M243" s="26">
+      <c r="H246" t="str">
+        <v/>
+      </c>
+      <c r="I246" t="str">
+        <v/>
+      </c>
+      <c r="J246" t="str">
+        <v/>
+      </c>
+      <c r="K246" t="str">
+        <v/>
+      </c>
+      <c r="L246" t="str">
+        <v/>
+      </c>
+      <c r="M246" s="26">
         <v>0</v>
       </c>
-      <c r="N243" t="str">
-        <v/>
-      </c>
-      <c r="O243" t="str">
-        <v/>
-      </c>
-      <c r="P243" t="str">
-        <v/>
-      </c>
-      <c r="Q243" s="28" t="str">
-        <v/>
-      </c>
-      <c r="R243" t="str">
-        <v/>
-      </c>
-      <c r="S243" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T243" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U243" s="28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="244" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A245" s="29" t="str">
+      <c r="N246" t="str">
+        <v/>
+      </c>
+      <c r="O246" t="str">
+        <v/>
+      </c>
+      <c r="P246" t="str">
+        <v/>
+      </c>
+      <c r="Q246" s="28" t="str">
+        <v/>
+      </c>
+      <c r="R246" t="str">
+        <v/>
+      </c>
+      <c r="S246" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T246" s="28" t="str">
+        <v/>
+      </c>
+      <c r="U246" s="28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="247" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" s="29" t="str">
         <v>Dependencies</v>
       </c>
     </row>
-    <row r="246" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A246" s="3" t="str">
+    <row r="249" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A249" s="3" t="str">
         <v>Name</v>
       </c>
-      <c r="B246" s="3" t="str">
+      <c r="B249" s="3" t="str">
         <v>Subitems</v>
       </c>
-      <c r="C246" s="3" t="str">
+      <c r="C249" s="3" t="str">
         <v>Status</v>
       </c>
-      <c r="D246" s="3" t="str">
+      <c r="D249" s="3" t="str">
         <v>Aggregated desc</v>
       </c>
-      <c r="E246" s="3" t="str">
+      <c r="E249" s="3" t="str">
         <v>Dependent On</v>
       </c>
-      <c r="F246" s="3" t="str">
+      <c r="F249" s="3" t="str">
         <v>Timeline - Start</v>
       </c>
-      <c r="G246" s="3" t="str">
+      <c r="G249" s="3" t="str">
         <v>Timeline - End</v>
       </c>
-      <c r="H246" s="3" t="str">
+      <c r="H249" s="3" t="str">
         <v>Drop</v>
       </c>
-      <c r="I246" s="3" t="str">
+      <c r="I249" s="3" t="str">
         <v>Project notes</v>
       </c>
-      <c r="J246" s="3" t="str">
+      <c r="J249" s="3" t="str">
         <v>PM</v>
       </c>
-      <c r="K246" s="3" t="str">
+      <c r="K249" s="3" t="str">
         <v>FE</v>
       </c>
-      <c r="L246" s="3" t="str">
+      <c r="L249" s="3" t="str">
         <v>BE</v>
       </c>
-      <c r="M246" s="3" t="str">
+      <c r="M249" s="3" t="str">
         <v>Priority</v>
       </c>
-      <c r="N246" s="3" t="str">
+      <c r="N249" s="3" t="str">
         <v>Effort</v>
       </c>
-      <c r="O246" s="3" t="str">
+      <c r="O249" s="3" t="str">
         <v>MD Specs Folder</v>
       </c>
-      <c r="P246" s="3" t="str">
+      <c r="P249" s="3" t="str">
         <v>Domain</v>
       </c>
-      <c r="Q246" s="3" t="str">
+      <c r="Q249" s="3" t="str">
         <v>Groom Readiness Date</v>
       </c>
-      <c r="R246" s="3" t="str">
+      <c r="R249" s="3" t="str">
         <v>Creation log</v>
       </c>
-      <c r="S246" s="3" t="str">
+      <c r="S249" s="3" t="str">
         <v>Spec Readiness Due Date</v>
       </c>
-      <c r="T246" s="3" t="str">
+      <c r="T249" s="3" t="str">
         <v>Product ETA - Start</v>
       </c>
-      <c r="U246" s="3" t="str">
+      <c r="U249" s="3" t="str">
         <v>Product ETA - End</v>
       </c>
     </row>
-    <row r="247" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A247" s="4" t="str">
+    <row r="250" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="str">
         <v>trading real time equity API</v>
       </c>
-      <c r="B247" t="str">
-        <v/>
-      </c>
-      <c r="C247" s="11" t="str">
+      <c r="B250" t="str">
+        <v/>
+      </c>
+      <c r="C250" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D247" t="str">
-        <v/>
-      </c>
-      <c r="E247" t="str">
-        <v/>
-      </c>
-      <c r="F247" t="str">
-        <v/>
-      </c>
-      <c r="G247" t="str">
-        <v/>
-      </c>
-      <c r="H247" t="str">
-        <v/>
-      </c>
-      <c r="I247" t="str">
-        <v/>
-      </c>
-      <c r="J247" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K247" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L247" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M247" t="str">
-        <v/>
-      </c>
-      <c r="N247" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O247" t="str">
-        <v/>
-      </c>
-      <c r="P247" t="str">
-        <v/>
-      </c>
-      <c r="Q247" t="str">
-        <v/>
-      </c>
-      <c r="R247" s="6" t="str">
+      <c r="D250" t="str">
+        <v/>
+      </c>
+      <c r="E250" t="str">
+        <v/>
+      </c>
+      <c r="F250" t="str">
+        <v/>
+      </c>
+      <c r="G250" t="str">
+        <v/>
+      </c>
+      <c r="H250" t="str">
+        <v/>
+      </c>
+      <c r="I250" t="str">
+        <v/>
+      </c>
+      <c r="J250" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K250" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L250" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M250" t="str">
+        <v/>
+      </c>
+      <c r="N250" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O250" t="str">
+        <v/>
+      </c>
+      <c r="P250" t="str">
+        <v/>
+      </c>
+      <c r="Q250" t="str">
+        <v/>
+      </c>
+      <c r="R250" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 11:31 AM</v>
       </c>
-      <c r="S247" t="str">
-        <v/>
-      </c>
-      <c r="T247" t="str">
-        <v/>
-      </c>
-      <c r="U247" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="248" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A248" s="4" t="str">
+      <c r="S250" t="str">
+        <v/>
+      </c>
+      <c r="T250" t="str">
+        <v/>
+      </c>
+      <c r="U250" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="251" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="str">
         <v>trading BE orch</v>
       </c>
-      <c r="B248" t="str">
-        <v/>
-      </c>
-      <c r="C248" s="15" t="str">
+      <c r="B251" t="str">
+        <v/>
+      </c>
+      <c r="C251" s="22" t="str">
         <v>Cancelled</v>
       </c>
-      <c r="D248" t="str">
-        <v/>
-      </c>
-      <c r="E248" t="str">
-        <v/>
-      </c>
-      <c r="F248" t="str">
-        <v/>
-      </c>
-      <c r="G248" t="str">
-        <v/>
-      </c>
-      <c r="H248" t="str">
-        <v/>
-      </c>
-      <c r="I248" t="str">
-        <v/>
-      </c>
-      <c r="J248" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K248" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L248" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M248" t="str">
-        <v/>
-      </c>
-      <c r="N248" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O248" t="str">
-        <v/>
-      </c>
-      <c r="P248" t="str">
-        <v/>
-      </c>
-      <c r="Q248" t="str">
-        <v/>
-      </c>
-      <c r="R248" s="6" t="str">
+      <c r="D251" t="str">
+        <v/>
+      </c>
+      <c r="E251" t="str">
+        <v/>
+      </c>
+      <c r="F251" t="str">
+        <v/>
+      </c>
+      <c r="G251" t="str">
+        <v/>
+      </c>
+      <c r="H251" t="str">
+        <v/>
+      </c>
+      <c r="I251" t="str">
+        <v/>
+      </c>
+      <c r="J251" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K251" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L251" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M251" t="str">
+        <v/>
+      </c>
+      <c r="N251" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O251" t="str">
+        <v/>
+      </c>
+      <c r="P251" t="str">
+        <v/>
+      </c>
+      <c r="Q251" t="str">
+        <v/>
+      </c>
+      <c r="R251" s="6" t="str">
         <v>Ilan Tatar Jan 25, 2026 11:50 AM</v>
       </c>
-      <c r="S248" t="str">
-        <v/>
-      </c>
-      <c r="T248" t="str">
-        <v/>
-      </c>
-      <c r="U248" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="249" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A249" s="4" t="str">
+      <c r="S251" t="str">
+        <v/>
+      </c>
+      <c r="T251" t="str">
+        <v/>
+      </c>
+      <c r="U251" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="252" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="str">
         <v>Banking deposit MOP</v>
       </c>
-      <c r="B249" t="str">
-        <v/>
-      </c>
-      <c r="C249" s="11" t="str">
+      <c r="B252" t="str">
+        <v/>
+      </c>
+      <c r="C252" s="11" t="str">
         <v>Done</v>
       </c>
-      <c r="D249" t="str">
-        <v/>
-      </c>
-      <c r="E249" t="str">
-        <v/>
-      </c>
-      <c r="F249" t="str">
-        <v/>
-      </c>
-      <c r="G249" t="str">
-        <v/>
-      </c>
-      <c r="H249" t="str">
-        <v/>
-      </c>
-      <c r="I249" t="str">
-        <v/>
-      </c>
-      <c r="J249" s="6" t="str">
-        <v/>
-      </c>
-      <c r="K249" s="6" t="str">
-        <v/>
-      </c>
-      <c r="L249" s="6" t="str">
-        <v/>
-      </c>
-      <c r="M249" t="str">
-        <v/>
-      </c>
-      <c r="N249" s="6" t="str">
-        <v/>
-      </c>
-      <c r="O249" t="str">
-        <v/>
-      </c>
-      <c r="P249" t="str">
-        <v/>
-      </c>
-      <c r="Q249" t="str">
-        <v/>
-      </c>
-      <c r="R249" s="6" t="str">
+      <c r="D252" t="str">
+        <v/>
+      </c>
+      <c r="E252" t="str">
+        <v/>
+      </c>
+      <c r="F252" t="str">
+        <v/>
+      </c>
+      <c r="G252" t="str">
+        <v/>
+      </c>
+      <c r="H252" t="str">
+        <v/>
+      </c>
+      <c r="I252" t="str">
+        <v/>
+      </c>
+      <c r="J252" s="6" t="str">
+        <v/>
+      </c>
+      <c r="K252" s="6" t="str">
+        <v/>
+      </c>
+      <c r="L252" s="6" t="str">
+        <v/>
+      </c>
+      <c r="M252" t="str">
+        <v/>
+      </c>
+      <c r="N252" s="6" t="str">
+        <v/>
+      </c>
+      <c r="O252" t="str">
+        <v/>
+      </c>
+      <c r="P252" t="str">
+        <v/>
+      </c>
+      <c r="Q252" t="str">
+        <v/>
+      </c>
+      <c r="R252" s="6" t="str">
         <v>Hagit Zamir Feb 5, 2026 4:03 PM</v>
       </c>
-      <c r="S249" t="str">
-        <v/>
-      </c>
-      <c r="T249" t="str">
-        <v/>
-      </c>
-      <c r="U249" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="250" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A250" t="str">
-        <v/>
-      </c>
-      <c r="B250" t="str">
-        <v/>
-      </c>
-      <c r="C250" t="str">
-        <v/>
-      </c>
-      <c r="D250" t="str">
-        <v/>
-      </c>
-      <c r="E250" t="str">
-        <v/>
-      </c>
-      <c r="F250" s="28" t="str">
-        <v/>
-      </c>
-      <c r="G250" s="28" t="str">
-        <v/>
-      </c>
-      <c r="H250" t="str">
-        <v/>
-      </c>
-      <c r="I250" t="str">
-        <v/>
-      </c>
-      <c r="J250" t="str">
-        <v/>
-      </c>
-      <c r="K250" t="str">
-        <v/>
-      </c>
-      <c r="L250" t="str">
-        <v/>
-      </c>
-      <c r="M250" s="26">
+      <c r="S252" t="str">
+        <v/>
+      </c>
+      <c r="T252" t="str">
+        <v/>
+      </c>
+      <c r="U252" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="253" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A253" t="str">
+        <v/>
+      </c>
+      <c r="B253" t="str">
+        <v/>
+      </c>
+      <c r="C253" t="str">
+        <v/>
+      </c>
+      <c r="D253" t="str">
+        <v/>
+      </c>
+      <c r="E253" t="str">
+        <v/>
+      </c>
+      <c r="F253" s="28" t="str">
+        <v/>
+      </c>
+      <c r="G253" s="28" t="str">
+        <v/>
+      </c>
+      <c r="H253" t="str">
+        <v/>
+      </c>
+      <c r="I253" t="str">
+        <v/>
+      </c>
+      <c r="J253" t="str">
+        <v/>
+      </c>
+      <c r="K253" t="str">
+        <v/>
+      </c>
+      <c r="L253" t="str">
+        <v/>
+      </c>
+      <c r="M253" s="26">
         <v>0</v>
       </c>
-      <c r="N250" t="str">
-        <v/>
-      </c>
-      <c r="O250" t="str">
-        <v/>
-      </c>
-      <c r="P250" t="str">
-        <v/>
-      </c>
-      <c r="Q250" s="28" t="str">
-        <v/>
-      </c>
-      <c r="R250" t="str">
-        <v/>
-      </c>
-      <c r="S250" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T250" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U250" s="28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="251" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="N253" t="str">
+        <v/>
+      </c>
+      <c r="O253" t="str">
+        <v/>
+      </c>
+      <c r="P253" t="str">
+        <v/>
+      </c>
+      <c r="Q253" s="28" t="str">
+        <v/>
+      </c>
+      <c r="R253" t="str">
+        <v/>
+      </c>
+      <c r="S253" s="28" t="str">
+        <v/>
+      </c>
+      <c r="T253" s="28" t="str">
+        <v/>
+      </c>
+      <c r="U253" s="28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="254" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -64,7 +64,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -133,11 +133,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF757575"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF5AC4"/>
       </patternFill>
     </fill>
@@ -179,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -248,9 +243,6 @@
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -264,7 +256,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1023,7 +1015,7 @@
         <v/>
       </c>
       <c r="F12" s="6" t="str">
-        <v>V1(20.4), V2(4.5)</v>
+        <v>V2(4.5)</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -2498,8 +2490,8 @@
       <c r="B51" t="str">
         <v/>
       </c>
-      <c r="C51" s="19" t="str">
-        <v>Groomed</v>
+      <c r="C51" s="5" t="str">
+        <v>FE DEV WIP</v>
       </c>
       <c r="D51" t="str">
         <v/>
@@ -2776,7 +2768,7 @@
       <c r="C58" t="str">
         <v/>
       </c>
-      <c r="D58" s="20" t="str">
+      <c r="D58" s="19" t="str">
         <v>OnHold</v>
       </c>
       <c r="E58" s="6" t="str">
@@ -2811,7 +2803,7 @@
       <c r="C59" t="str">
         <v/>
       </c>
-      <c r="D59" s="21" t="str">
+      <c r="D59" s="20" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E59" s="6" t="str">
@@ -3466,7 +3458,7 @@
       <c r="C76" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D76" s="22" t="str">
+      <c r="D76" s="21" t="str">
         <v>Design</v>
       </c>
       <c r="E76" s="6" t="str">
@@ -3501,7 +3493,7 @@
       <c r="C77" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D77" s="22" t="str">
+      <c r="D77" s="21" t="str">
         <v>Design</v>
       </c>
       <c r="E77" s="6" t="str">
@@ -3846,7 +3838,7 @@
       <c r="C86" t="str">
         <v/>
       </c>
-      <c r="D86" s="21" t="str">
+      <c r="D86" s="20" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E86" s="6" t="str">
@@ -4226,7 +4218,7 @@
       <c r="C96" t="str">
         <v/>
       </c>
-      <c r="D96" s="23" t="str">
+      <c r="D96" s="22" t="str">
         <v>Grooming</v>
       </c>
       <c r="E96" s="6" t="str">
@@ -4261,7 +4253,7 @@
       <c r="C97" t="str">
         <v/>
       </c>
-      <c r="D97" s="23" t="str">
+      <c r="D97" s="22" t="str">
         <v>Grooming</v>
       </c>
       <c r="E97" s="6" t="str">
@@ -4331,7 +4323,7 @@
       <c r="C99" t="str">
         <v/>
       </c>
-      <c r="D99" s="23" t="str">
+      <c r="D99" s="22" t="str">
         <v>Grooming</v>
       </c>
       <c r="E99" s="6" t="str">
@@ -4816,7 +4808,7 @@
       <c r="C112" s="6" t="str">
         <v>Richard Whitehouse</v>
       </c>
-      <c r="D112" s="21" t="str">
+      <c r="D112" s="20" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E112" s="6" t="str">
@@ -5083,7 +5075,7 @@
       <c r="B118" t="str">
         <v/>
       </c>
-      <c r="C118" s="21" t="str">
+      <c r="C118" s="20" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D118" t="str">
@@ -5768,7 +5760,7 @@
       <c r="B135" t="str">
         <v/>
       </c>
-      <c r="C135" s="24" t="str">
+      <c r="C135" s="23" t="str">
         <v>Dependency</v>
       </c>
       <c r="D135" t="str">
@@ -5871,7 +5863,7 @@
       <c r="C137" t="str">
         <v/>
       </c>
-      <c r="D137" s="22" t="str">
+      <c r="D137" s="21" t="str">
         <v>Design</v>
       </c>
       <c r="E137" s="6" t="str">
@@ -6042,10 +6034,10 @@
       <c r="E140" t="str">
         <v/>
       </c>
-      <c r="F140" s="25">
+      <c r="F140" s="24">
         <v>46061</v>
       </c>
-      <c r="G140" s="25">
+      <c r="G140" s="24">
         <v>46160</v>
       </c>
       <c r="H140" t="str">
@@ -6063,7 +6055,7 @@
       <c r="L140" t="str">
         <v/>
       </c>
-      <c r="M140" s="26">
+      <c r="M140" s="25">
         <v>32</v>
       </c>
       <c r="N140" t="str">
@@ -6075,25 +6067,25 @@
       <c r="P140" t="str">
         <v/>
       </c>
-      <c r="Q140" s="27" t="str">
+      <c r="Q140" s="26" t="str">
         <v>2026-02-02 to 2026-04-15</v>
       </c>
       <c r="R140" t="str">
         <v/>
       </c>
-      <c r="S140" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T140" s="25">
+      <c r="S140" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T140" s="24">
         <v>46058</v>
       </c>
-      <c r="U140" s="25">
+      <c r="U140" s="24">
         <v>46114</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="142" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="29" t="str">
+      <c r="A142" s="28" t="str">
         <v>In Focus</v>
       </c>
     </row>
@@ -6364,7 +6356,7 @@
       <c r="B147" t="str">
         <v/>
       </c>
-      <c r="C147" s="30" t="str">
+      <c r="C147" s="29" t="str">
         <v>Risk</v>
       </c>
       <c r="D147" t="str">
@@ -7608,10 +7600,10 @@
       <c r="E166" t="str">
         <v/>
       </c>
-      <c r="F166" s="25">
+      <c r="F166" s="24">
         <v>46054</v>
       </c>
-      <c r="G166" s="25">
+      <c r="G166" s="24">
         <v>46118</v>
       </c>
       <c r="H166" t="str">
@@ -7629,7 +7621,7 @@
       <c r="L166" t="str">
         <v/>
       </c>
-      <c r="M166" s="26">
+      <c r="M166" s="25">
         <v>0</v>
       </c>
       <c r="N166" t="str">
@@ -7641,25 +7633,25 @@
       <c r="P166" t="str">
         <v/>
       </c>
-      <c r="Q166" s="28" t="str">
+      <c r="Q166" s="27" t="str">
         <v/>
       </c>
       <c r="R166" t="str">
         <v/>
       </c>
-      <c r="S166" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T166" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U166" s="28" t="str">
+      <c r="S166" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T166" s="27" t="str">
+        <v/>
+      </c>
+      <c r="U166" s="27" t="str">
         <v/>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="168" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="31" t="str">
+      <c r="A168" s="30" t="str">
         <v>MVP - API /BFF project</v>
       </c>
     </row>
@@ -9240,7 +9232,7 @@
       <c r="B201" t="str">
         <v/>
       </c>
-      <c r="C201" s="22" t="str">
+      <c r="C201" s="21" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D201" s="6" t="str">
@@ -9305,7 +9297,7 @@
       <c r="B202" t="str">
         <v/>
       </c>
-      <c r="C202" s="22" t="str">
+      <c r="C202" s="21" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D202" s="6" t="str">
@@ -9370,7 +9362,7 @@
       <c r="B203" t="str">
         <v/>
       </c>
-      <c r="C203" s="21" t="str">
+      <c r="C203" s="20" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D203" s="6" t="str">
@@ -9444,10 +9436,10 @@
       <c r="E204" t="str">
         <v/>
       </c>
-      <c r="F204" s="25">
+      <c r="F204" s="24">
         <v>46036</v>
       </c>
-      <c r="G204" s="25">
+      <c r="G204" s="24">
         <v>46134</v>
       </c>
       <c r="H204" t="str">
@@ -9465,7 +9457,7 @@
       <c r="L204" t="str">
         <v/>
       </c>
-      <c r="M204" s="26">
+      <c r="M204" s="25">
         <v>9</v>
       </c>
       <c r="N204" t="str">
@@ -9477,25 +9469,25 @@
       <c r="P204" t="str">
         <v/>
       </c>
-      <c r="Q204" s="28" t="str">
+      <c r="Q204" s="27" t="str">
         <v/>
       </c>
       <c r="R204" t="str">
         <v/>
       </c>
-      <c r="S204" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T204" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U204" s="28" t="str">
+      <c r="S204" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T204" s="27" t="str">
+        <v/>
+      </c>
+      <c r="U204" s="27" t="str">
         <v/>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="206" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A206" s="32" t="str">
+      <c r="A206" s="31" t="str">
         <v>Not in Money scope/Future versions</v>
       </c>
     </row>
@@ -9571,7 +9563,7 @@
       <c r="B208" t="str">
         <v/>
       </c>
-      <c r="C208" s="21" t="str">
+      <c r="C208" s="20" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D208" s="6" t="str">
@@ -9636,7 +9628,7 @@
       <c r="B209" t="str">
         <v/>
       </c>
-      <c r="C209" s="21" t="str">
+      <c r="C209" s="20" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D209" s="6" t="str">
@@ -9701,7 +9693,7 @@
       <c r="B210" t="str">
         <v/>
       </c>
-      <c r="C210" s="21" t="str">
+      <c r="C210" s="20" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D210" s="6" t="str">
@@ -9766,7 +9758,7 @@
       <c r="B211" t="str">
         <v/>
       </c>
-      <c r="C211" s="21" t="str">
+      <c r="C211" s="20" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D211" s="6" t="str">
@@ -9831,7 +9823,7 @@
       <c r="B212" t="str">
         <v/>
       </c>
-      <c r="C212" s="21" t="str">
+      <c r="C212" s="20" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D212" s="6" t="str">
@@ -9897,7 +9889,7 @@
       <c r="B213" t="str">
         <v/>
       </c>
-      <c r="C213" s="21" t="str">
+      <c r="C213" s="20" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D213" s="6" t="str">
@@ -10067,7 +10059,7 @@
       <c r="B217" t="str">
         <v/>
       </c>
-      <c r="C217" s="20" t="str">
+      <c r="C217" s="19" t="str">
         <v>Future Version</v>
       </c>
       <c r="D217" s="6" t="str">
@@ -10132,7 +10124,7 @@
       <c r="B218" t="str">
         <v/>
       </c>
-      <c r="C218" s="20" t="str">
+      <c r="C218" s="19" t="str">
         <v>Future Version</v>
       </c>
       <c r="D218" s="6" t="str">
@@ -10197,7 +10189,7 @@
       <c r="B219" t="str">
         <v/>
       </c>
-      <c r="C219" s="20" t="str">
+      <c r="C219" s="19" t="str">
         <v>Future Version</v>
       </c>
       <c r="D219" t="str">
@@ -10367,7 +10359,7 @@
       <c r="B223" t="str">
         <v/>
       </c>
-      <c r="C223" s="20" t="str">
+      <c r="C223" s="19" t="str">
         <v>Future Version</v>
       </c>
       <c r="D223" s="6" t="str">
@@ -10432,7 +10424,7 @@
       <c r="B224" t="str">
         <v/>
       </c>
-      <c r="C224" s="20" t="str">
+      <c r="C224" s="19" t="str">
         <v>Future Version</v>
       </c>
       <c r="D224" s="6" t="str">
@@ -10497,7 +10489,7 @@
       <c r="B225" t="str">
         <v/>
       </c>
-      <c r="C225" s="20" t="str">
+      <c r="C225" s="19" t="str">
         <v>Future Version</v>
       </c>
       <c r="D225" t="str">
@@ -10562,7 +10554,7 @@
       <c r="B226" t="str">
         <v/>
       </c>
-      <c r="C226" s="20" t="str">
+      <c r="C226" s="19" t="str">
         <v>Future Version</v>
       </c>
       <c r="D226" t="str">
@@ -10627,7 +10619,7 @@
       <c r="B227" t="str">
         <v/>
       </c>
-      <c r="C227" s="20" t="str">
+      <c r="C227" s="19" t="str">
         <v>Future Version</v>
       </c>
       <c r="D227" s="6" t="str">
@@ -10692,7 +10684,7 @@
       <c r="B228" t="str">
         <v/>
       </c>
-      <c r="C228" s="22" t="str">
+      <c r="C228" s="21" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D228" t="str">
@@ -10757,7 +10749,7 @@
       <c r="B229" t="str">
         <v/>
       </c>
-      <c r="C229" s="22" t="str">
+      <c r="C229" s="21" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D229" s="6" t="str">
@@ -10822,7 +10814,7 @@
       <c r="B230" t="str">
         <v/>
       </c>
-      <c r="C230" s="22" t="str">
+      <c r="C230" s="21" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D230" t="str">
@@ -10887,7 +10879,7 @@
       <c r="B231" t="str">
         <v/>
       </c>
-      <c r="C231" s="22" t="str">
+      <c r="C231" s="21" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D231" s="6" t="str">
@@ -10952,7 +10944,7 @@
       <c r="B232" t="str">
         <v/>
       </c>
-      <c r="C232" s="20" t="str">
+      <c r="C232" s="19" t="str">
         <v>Future Version</v>
       </c>
       <c r="D232" t="str">
@@ -11017,7 +11009,7 @@
       <c r="B233" t="str">
         <v/>
       </c>
-      <c r="C233" s="20" t="str">
+      <c r="C233" s="19" t="str">
         <v>Future Version</v>
       </c>
       <c r="D233" s="6" t="str">
@@ -11091,10 +11083,10 @@
       <c r="E234" t="str">
         <v/>
       </c>
-      <c r="F234" s="25">
+      <c r="F234" s="24">
         <v>46061</v>
       </c>
-      <c r="G234" s="25">
+      <c r="G234" s="24">
         <v>46134</v>
       </c>
       <c r="H234" t="str">
@@ -11112,7 +11104,7 @@
       <c r="L234" t="str">
         <v/>
       </c>
-      <c r="M234" s="26">
+      <c r="M234" s="25">
         <v>1298</v>
       </c>
       <c r="N234" t="str">
@@ -11124,25 +11116,25 @@
       <c r="P234" t="str">
         <v/>
       </c>
-      <c r="Q234" s="27" t="str">
+      <c r="Q234" s="26" t="str">
         <v>2026-03-02 to 2026-03-23</v>
       </c>
       <c r="R234" t="str">
         <v/>
       </c>
-      <c r="S234" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T234" s="25">
+      <c r="S234" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T234" s="24">
         <v>46104</v>
       </c>
-      <c r="U234" s="25">
+      <c r="U234" s="24">
         <v>46104</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="236" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A236" s="33" t="str">
+      <c r="A236" s="32" t="str">
         <v>Program Milestones</v>
       </c>
     </row>
@@ -11747,10 +11739,10 @@
       <c r="E246" t="str">
         <v/>
       </c>
-      <c r="F246" s="25">
+      <c r="F246" s="24">
         <v>46048</v>
       </c>
-      <c r="G246" s="25">
+      <c r="G246" s="24">
         <v>46145</v>
       </c>
       <c r="H246" t="str">
@@ -11768,7 +11760,7 @@
       <c r="L246" t="str">
         <v/>
       </c>
-      <c r="M246" s="26">
+      <c r="M246" s="25">
         <v>0</v>
       </c>
       <c r="N246" t="str">
@@ -11780,25 +11772,25 @@
       <c r="P246" t="str">
         <v/>
       </c>
-      <c r="Q246" s="28" t="str">
+      <c r="Q246" s="27" t="str">
         <v/>
       </c>
       <c r="R246" t="str">
         <v/>
       </c>
-      <c r="S246" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T246" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U246" s="28" t="str">
+      <c r="S246" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T246" s="27" t="str">
+        <v/>
+      </c>
+      <c r="U246" s="27" t="str">
         <v/>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="248" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A248" s="29" t="str">
+      <c r="A248" s="28" t="str">
         <v>Dependencies</v>
       </c>
     </row>
@@ -11939,7 +11931,7 @@
       <c r="B251" t="str">
         <v/>
       </c>
-      <c r="C251" s="22" t="str">
+      <c r="C251" s="21" t="str">
         <v>Cancelled</v>
       </c>
       <c r="D251" t="str">
@@ -12078,10 +12070,10 @@
       <c r="E253" t="str">
         <v/>
       </c>
-      <c r="F253" s="28" t="str">
-        <v/>
-      </c>
-      <c r="G253" s="28" t="str">
+      <c r="F253" s="27" t="str">
+        <v/>
+      </c>
+      <c r="G253" s="27" t="str">
         <v/>
       </c>
       <c r="H253" t="str">
@@ -12099,7 +12091,7 @@
       <c r="L253" t="str">
         <v/>
       </c>
-      <c r="M253" s="26">
+      <c r="M253" s="25">
         <v>0</v>
       </c>
       <c r="N253" t="str">
@@ -12111,19 +12103,19 @@
       <c r="P253" t="str">
         <v/>
       </c>
-      <c r="Q253" s="28" t="str">
+      <c r="Q253" s="27" t="str">
         <v/>
       </c>
       <c r="R253" t="str">
         <v/>
       </c>
-      <c r="S253" s="28" t="str">
-        <v/>
-      </c>
-      <c r="T253" s="28" t="str">
-        <v/>
-      </c>
-      <c r="U253" s="28" t="str">
+      <c r="S253" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T253" s="27" t="str">
+        <v/>
+      </c>
+      <c r="U253" s="27" t="str">
         <v/>
       </c>
     </row>

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -93,17 +93,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00C875"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDF2F4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF9D50DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00C875"/>
       </patternFill>
     </fill>
     <fill>
@@ -793,28 +793,28 @@
         <v/>
       </c>
       <c r="B6" s="4" t="str">
-        <v>Balance Display</v>
+        <v>Export Transactions</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6" s="11" t="str">
-        <v>Done</v>
+      <c r="D6" s="5" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E6" s="6" t="str">
         <v/>
       </c>
       <c r="F6" s="6" t="str">
-        <v>V1(20.4)</v>
+        <v>V2(4.5)</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v/>
+      <c r="H6" s="8">
+        <v>46117</v>
+      </c>
+      <c r="I6" s="8">
+        <v>46126</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -828,21 +828,21 @@
         <v/>
       </c>
       <c r="B7" s="4" t="str">
-        <v>Transactions List FE</v>
+        <v>IBAN - Add Funds to Local Account (Account Info and launch Open Banking)</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" s="11" t="str">
-        <v>Done</v>
+        <v>Stuck</v>
       </c>
       <c r="E7" s="6" t="str">
         <v/>
       </c>
       <c r="F7" s="6" t="str">
-        <v>V1(20.4)</v>
-      </c>
-      <c r="G7" t="str">
+        <v>V3(18.5)</v>
+      </c>
+      <c r="G7" s="6" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
@@ -863,28 +863,28 @@
         <v/>
       </c>
       <c r="B8" s="4" t="str">
-        <v>Transactions List [BFF]- Amichai Kafka</v>
+        <v>Transactional push notifications + logic</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8" s="11" t="str">
-        <v>Done</v>
+      <c r="D8" s="12" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E8" s="6" t="str">
         <v/>
       </c>
       <c r="F8" s="6" t="str">
-        <v>V1(20.4)</v>
+        <v>V2(4.5)</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v/>
+      <c r="H8" s="8">
+        <v>46061</v>
+      </c>
+      <c r="I8" s="8">
+        <v>46061</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -898,12 +898,12 @@
         <v/>
       </c>
       <c r="B9" s="4" t="str">
-        <v>Account Details FE</v>
+        <v>Balance Display</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
-      <c r="D9" s="11" t="str">
+      <c r="D9" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E9" s="6" t="str">
@@ -915,11 +915,11 @@
       <c r="G9" t="str">
         <v/>
       </c>
-      <c r="H9" s="8">
-        <v>46064</v>
-      </c>
-      <c r="I9" s="8">
-        <v>46064</v>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -933,12 +933,12 @@
         <v/>
       </c>
       <c r="B10" s="4" t="str">
-        <v>Account Details [BFF]- Amichai Kafka</v>
+        <v>Transactions List FE</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
-      <c r="D10" s="11" t="str">
+      <c r="D10" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E10" s="6" t="str">
@@ -950,11 +950,11 @@
       <c r="G10" t="str">
         <v/>
       </c>
-      <c r="H10" s="8">
-        <v>46064</v>
-      </c>
-      <c r="I10" s="8">
-        <v>46064</v>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -968,12 +968,12 @@
         <v/>
       </c>
       <c r="B11" s="4" t="str">
-        <v>(Bank,Card,Internal) Transaction Types and Details</v>
+        <v>Transactions List [BFF]- Amichai Kafka</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
-      <c r="D11" s="11" t="str">
+      <c r="D11" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E11" s="6" t="str">
@@ -1003,28 +1003,28 @@
         <v/>
       </c>
       <c r="B12" s="4" t="str">
-        <v>Export Transactions</v>
+        <v>Account Details FE</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12" s="5" t="str">
-        <v>Dev - WIP</v>
+      <c r="D12" s="13" t="str">
+        <v>Done</v>
       </c>
       <c r="E12" s="6" t="str">
         <v/>
       </c>
       <c r="F12" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V1(20.4)</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" s="8">
-        <v>46117</v>
+        <v>46064</v>
       </c>
       <c r="I12" s="8">
-        <v>46126</v>
+        <v>46064</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -1038,28 +1038,28 @@
         <v/>
       </c>
       <c r="B13" s="4" t="str">
-        <v>IBAN - Add Funds to Local Account (Account Info and launch Open Banking)</v>
+        <v>Account Details [BFF]- Amichai Kafka</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13" s="12" t="str">
-        <v>Stuck</v>
+      <c r="D13" s="13" t="str">
+        <v>Done</v>
       </c>
       <c r="E13" s="6" t="str">
         <v/>
       </c>
       <c r="F13" s="6" t="str">
-        <v>V3(18.5)</v>
-      </c>
-      <c r="G13" s="6" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v/>
+        <v>V1(20.4)</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" s="8">
+        <v>46064</v>
+      </c>
+      <c r="I13" s="8">
+        <v>46064</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -1073,12 +1073,12 @@
         <v/>
       </c>
       <c r="B14" s="4" t="str">
-        <v>Move Funds touchpoint</v>
+        <v>(Bank,Card,Internal) Transaction Types and Details</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
-      <c r="D14" s="11" t="str">
+      <c r="D14" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E14" s="6" t="str">
@@ -1090,11 +1090,11 @@
       <c r="G14" t="str">
         <v/>
       </c>
-      <c r="H14" s="8">
-        <v>46061</v>
-      </c>
-      <c r="I14" s="8">
-        <v>46061</v>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1108,19 +1108,19 @@
         <v/>
       </c>
       <c r="B15" s="4" t="str">
-        <v>Transactional push notifications + logic</v>
+        <v>Move Funds touchpoint</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" s="13" t="str">
-        <v>Discovery</v>
+        <v>Done</v>
       </c>
       <c r="E15" s="6" t="str">
         <v/>
       </c>
       <c r="F15" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V1(20.4)</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1145,7 +1145,7 @@
       <c r="B16" t="str">
         <v/>
       </c>
-      <c r="C16" s="13" t="str">
+      <c r="C16" s="12" t="str">
         <v>In QA</v>
       </c>
       <c r="D16" t="str">
@@ -1248,7 +1248,7 @@
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18" s="11" t="str">
+      <c r="D18" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E18" s="6" t="str">
@@ -1283,7 +1283,7 @@
       <c r="C19" t="str">
         <v/>
       </c>
-      <c r="D19" s="11" t="str">
+      <c r="D19" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E19" s="6" t="str">
@@ -1315,7 +1315,7 @@
       <c r="B20" t="str">
         <v/>
       </c>
-      <c r="C20" s="13" t="str">
+      <c r="C20" s="12" t="str">
         <v>In QA</v>
       </c>
       <c r="D20" t="str">
@@ -1418,7 +1418,7 @@
       <c r="C22" t="str">
         <v/>
       </c>
-      <c r="D22" s="11" t="str">
+      <c r="D22" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E22" s="6" t="str">
@@ -1453,7 +1453,7 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23" s="11" t="str">
+      <c r="D23" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E23" s="6" t="str">
@@ -1488,7 +1488,7 @@
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24" s="11" t="str">
+      <c r="D24" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E24" s="6" t="str">
@@ -1590,7 +1590,7 @@
       <c r="B27" t="str">
         <v/>
       </c>
-      <c r="C27" s="11" t="str">
+      <c r="C27" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D27" t="str">
@@ -1933,7 +1933,7 @@
       <c r="C35" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D35" s="13" t="str">
+      <c r="D35" s="12" t="str">
         <v>Discovery</v>
       </c>
       <c r="E35" s="6" t="str">
@@ -1968,7 +1968,7 @@
       <c r="C36" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D36" s="13" t="str">
+      <c r="D36" s="12" t="str">
         <v>Discovery</v>
       </c>
       <c r="E36" s="6" t="str">
@@ -2003,7 +2003,7 @@
       <c r="C37" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D37" s="12" t="str">
+      <c r="D37" s="11" t="str">
         <v>Stuck</v>
       </c>
       <c r="E37" s="6" t="str">
@@ -2038,7 +2038,7 @@
       <c r="C38" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D38" s="13" t="str">
+      <c r="D38" s="12" t="str">
         <v>Discovery</v>
       </c>
       <c r="E38" s="6" t="str">
@@ -2073,7 +2073,7 @@
       <c r="C39" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D39" s="13" t="str">
+      <c r="D39" s="12" t="str">
         <v>Discovery</v>
       </c>
       <c r="E39" s="6" t="str">
@@ -2108,7 +2108,7 @@
       <c r="C40" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D40" s="13" t="str">
+      <c r="D40" s="12" t="str">
         <v>Discovery</v>
       </c>
       <c r="E40" s="6" t="str">
@@ -2143,7 +2143,7 @@
       <c r="C41" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D41" s="13" t="str">
+      <c r="D41" s="12" t="str">
         <v>Discovery</v>
       </c>
       <c r="E41" s="6" t="str">
@@ -2178,7 +2178,7 @@
       <c r="C42" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D42" s="13" t="str">
+      <c r="D42" s="12" t="str">
         <v>Discovery</v>
       </c>
       <c r="E42" s="6" t="str">
@@ -2458,7 +2458,7 @@
       <c r="C50" t="str">
         <v/>
       </c>
-      <c r="D50" s="13" t="str">
+      <c r="D50" s="12" t="str">
         <v>Discovery</v>
       </c>
       <c r="E50" s="6" t="str">
@@ -3143,7 +3143,7 @@
       <c r="C67" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D67" s="11" t="str">
+      <c r="D67" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E67" s="6" t="str">
@@ -3178,7 +3178,7 @@
       <c r="C68" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D68" s="11" t="str">
+      <c r="D68" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E68" s="6" t="str">
@@ -3213,7 +3213,7 @@
       <c r="C69" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D69" s="11" t="str">
+      <c r="D69" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E69" s="6" t="str">
@@ -3248,7 +3248,7 @@
       <c r="C70" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D70" s="11" t="str">
+      <c r="D70" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E70" s="6" t="str">
@@ -3525,7 +3525,7 @@
       <c r="B78" t="str">
         <v/>
       </c>
-      <c r="C78" s="13" t="str">
+      <c r="C78" s="12" t="str">
         <v>In QA</v>
       </c>
       <c r="D78" s="6" t="str">
@@ -3628,7 +3628,7 @@
       <c r="C80" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D80" s="11" t="str">
+      <c r="D80" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E80" s="6" t="str">
@@ -3663,7 +3663,7 @@
       <c r="C81" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D81" s="11" t="str">
+      <c r="D81" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E81" s="6" t="str">
@@ -3698,7 +3698,7 @@
       <c r="C82" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D82" s="11" t="str">
+      <c r="D82" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E82" s="6" t="str">
@@ -3733,7 +3733,7 @@
       <c r="C83" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D83" s="11" t="str">
+      <c r="D83" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E83" s="6" t="str">
@@ -3768,7 +3768,7 @@
       <c r="C84" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D84" s="11" t="str">
+      <c r="D84" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E84" s="6" t="str">
@@ -4458,7 +4458,7 @@
       <c r="C102" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D102" s="11" t="str">
+      <c r="D102" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E102" s="6" t="str">
@@ -4598,7 +4598,7 @@
       <c r="C106" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D106" s="11" t="str">
+      <c r="D106" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E106" s="6" t="str">
@@ -4773,7 +4773,7 @@
       <c r="C111" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D111" s="13" t="str">
+      <c r="D111" s="12" t="str">
         <v>Discovery</v>
       </c>
       <c r="E111" s="6" t="str">
@@ -5345,8 +5345,8 @@
       <c r="B124" t="str">
         <v/>
       </c>
-      <c r="C124" s="16" t="str">
-        <v>Deployment</v>
+      <c r="C124" s="13" t="str">
+        <v>Done</v>
       </c>
       <c r="D124" t="str">
         <v/>
@@ -5448,7 +5448,7 @@
       <c r="C126" s="6" t="str">
         <v>Hagit Zamir</v>
       </c>
-      <c r="D126" s="11" t="str">
+      <c r="D126" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E126" s="6" t="str">
@@ -5483,7 +5483,7 @@
       <c r="C127" t="str">
         <v/>
       </c>
-      <c r="D127" s="11" t="str">
+      <c r="D127" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E127" s="6" t="str">
@@ -5518,8 +5518,8 @@
       <c r="C128" t="str">
         <v/>
       </c>
-      <c r="D128" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D128" s="14" t="str">
+        <v>Handle by other team</v>
       </c>
       <c r="E128" s="6" t="str">
         <v/>
@@ -5553,8 +5553,8 @@
       <c r="C129" t="str">
         <v/>
       </c>
-      <c r="D129" s="17" t="str">
-        <v>Not Started</v>
+      <c r="D129" s="14" t="str">
+        <v>Handle by other team</v>
       </c>
       <c r="E129" s="6" t="str">
         <v/>
@@ -5588,8 +5588,8 @@
       <c r="C130" t="str">
         <v/>
       </c>
-      <c r="D130" s="17" t="str">
-        <v>Not Started</v>
+      <c r="D130" s="14" t="str">
+        <v>Handle by other team</v>
       </c>
       <c r="E130" s="6" t="str">
         <v/>
@@ -6161,7 +6161,7 @@
       <c r="B144" t="str">
         <v/>
       </c>
-      <c r="C144" s="11" t="str">
+      <c r="C144" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D144" t="str">
@@ -6421,7 +6421,7 @@
       <c r="B148" t="str">
         <v/>
       </c>
-      <c r="C148" s="11" t="str">
+      <c r="C148" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D148" t="str">
@@ -6486,7 +6486,7 @@
       <c r="B149" t="str">
         <v/>
       </c>
-      <c r="C149" s="11" t="str">
+      <c r="C149" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D149" t="str">
@@ -6551,7 +6551,7 @@
       <c r="B150" t="str">
         <v/>
       </c>
-      <c r="C150" s="11" t="str">
+      <c r="C150" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D150" t="str">
@@ -6616,7 +6616,7 @@
       <c r="B151" t="str">
         <v/>
       </c>
-      <c r="C151" s="11" t="str">
+      <c r="C151" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D151" t="str">
@@ -6681,7 +6681,7 @@
       <c r="B152" t="str">
         <v/>
       </c>
-      <c r="C152" s="11" t="str">
+      <c r="C152" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D152" t="str">
@@ -6746,7 +6746,7 @@
       <c r="B153" t="str">
         <v/>
       </c>
-      <c r="C153" s="11" t="str">
+      <c r="C153" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D153" t="str">
@@ -6811,7 +6811,7 @@
       <c r="B154" t="str">
         <v/>
       </c>
-      <c r="C154" s="11" t="str">
+      <c r="C154" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D154" t="str">
@@ -6876,7 +6876,7 @@
       <c r="B155" t="str">
         <v/>
       </c>
-      <c r="C155" s="11" t="str">
+      <c r="C155" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D155" t="str">
@@ -6941,7 +6941,7 @@
       <c r="B156" t="str">
         <v/>
       </c>
-      <c r="C156" s="11" t="str">
+      <c r="C156" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D156" t="str">
@@ -7006,7 +7006,7 @@
       <c r="B157" t="str">
         <v/>
       </c>
-      <c r="C157" s="11" t="str">
+      <c r="C157" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D157" t="str">
@@ -7071,7 +7071,7 @@
       <c r="B158" t="str">
         <v/>
       </c>
-      <c r="C158" s="11" t="str">
+      <c r="C158" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D158" s="6" t="str">
@@ -7136,7 +7136,7 @@
       <c r="B159" t="str">
         <v/>
       </c>
-      <c r="C159" s="11" t="str">
+      <c r="C159" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D159" t="str">
@@ -7201,7 +7201,7 @@
       <c r="B160" t="str">
         <v/>
       </c>
-      <c r="C160" s="11" t="str">
+      <c r="C160" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D160" t="str">
@@ -7266,7 +7266,7 @@
       <c r="B161" t="str">
         <v/>
       </c>
-      <c r="C161" s="11" t="str">
+      <c r="C161" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D161" t="str">
@@ -7331,7 +7331,7 @@
       <c r="B162" t="str">
         <v/>
       </c>
-      <c r="C162" s="11" t="str">
+      <c r="C162" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D162" t="str">
@@ -7396,7 +7396,7 @@
       <c r="B163" t="str">
         <v/>
       </c>
-      <c r="C163" s="11" t="str">
+      <c r="C163" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D163" t="str">
@@ -7461,7 +7461,7 @@
       <c r="B164" t="str">
         <v/>
       </c>
-      <c r="C164" s="11" t="str">
+      <c r="C164" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D164" t="str">
@@ -7526,7 +7526,7 @@
       <c r="B165" t="str">
         <v/>
       </c>
-      <c r="C165" s="11" t="str">
+      <c r="C165" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D165" t="str">
@@ -7727,7 +7727,7 @@
       <c r="B170" t="str">
         <v/>
       </c>
-      <c r="C170" s="11" t="str">
+      <c r="C170" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D170" s="6" t="str">
@@ -7830,7 +7830,7 @@
       <c r="C172" t="str">
         <v/>
       </c>
-      <c r="D172" s="11" t="str">
+      <c r="D172" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E172" s="6" t="str">
@@ -7865,7 +7865,7 @@
       <c r="C173" t="str">
         <v/>
       </c>
-      <c r="D173" s="11" t="str">
+      <c r="D173" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E173" s="6" t="str">
@@ -7900,7 +7900,7 @@
       <c r="C174" s="6" t="str">
         <v>Hagit Zamir</v>
       </c>
-      <c r="D174" s="11" t="str">
+      <c r="D174" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E174" s="6" t="str">
@@ -7935,7 +7935,7 @@
       <c r="C175" t="str">
         <v/>
       </c>
-      <c r="D175" s="11" t="str">
+      <c r="D175" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E175" s="6" t="str">
@@ -7970,7 +7970,7 @@
       <c r="C176" t="str">
         <v/>
       </c>
-      <c r="D176" s="11" t="str">
+      <c r="D176" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E176" s="6" t="str">
@@ -8005,7 +8005,7 @@
       <c r="C177" t="str">
         <v/>
       </c>
-      <c r="D177" s="11" t="str">
+      <c r="D177" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E177" s="6" t="str">
@@ -8040,7 +8040,7 @@
       <c r="C178" t="str">
         <v/>
       </c>
-      <c r="D178" s="11" t="str">
+      <c r="D178" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E178" s="6" t="str">
@@ -8072,7 +8072,7 @@
       <c r="B179" t="str">
         <v/>
       </c>
-      <c r="C179" s="11" t="str">
+      <c r="C179" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D179" s="6" t="str">
@@ -8137,7 +8137,7 @@
       <c r="B180" t="str">
         <v/>
       </c>
-      <c r="C180" s="11" t="str">
+      <c r="C180" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D180" s="6" t="str">
@@ -8240,7 +8240,7 @@
       <c r="C182" t="str">
         <v/>
       </c>
-      <c r="D182" s="11" t="str">
+      <c r="D182" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E182" s="6" t="str">
@@ -8275,7 +8275,7 @@
       <c r="C183" t="str">
         <v/>
       </c>
-      <c r="D183" s="11" t="str">
+      <c r="D183" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E183" s="6" t="str">
@@ -8310,7 +8310,7 @@
       <c r="C184" t="str">
         <v/>
       </c>
-      <c r="D184" s="11" t="str">
+      <c r="D184" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E184" s="6" t="str">
@@ -8345,7 +8345,7 @@
       <c r="C185" t="str">
         <v/>
       </c>
-      <c r="D185" s="11" t="str">
+      <c r="D185" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E185" s="6" t="str">
@@ -8380,7 +8380,7 @@
       <c r="C186" t="str">
         <v/>
       </c>
-      <c r="D186" s="11" t="str">
+      <c r="D186" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E186" s="6" t="str">
@@ -8415,7 +8415,7 @@
       <c r="C187" t="str">
         <v/>
       </c>
-      <c r="D187" s="11" t="str">
+      <c r="D187" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="E187" s="6" t="str">
@@ -8447,7 +8447,7 @@
       <c r="B188" t="str">
         <v/>
       </c>
-      <c r="C188" s="11" t="str">
+      <c r="C188" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D188" t="str">
@@ -8577,7 +8577,7 @@
       <c r="B190" t="str">
         <v/>
       </c>
-      <c r="C190" s="11" t="str">
+      <c r="C190" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D190" t="str">
@@ -8707,7 +8707,7 @@
       <c r="B192" t="str">
         <v/>
       </c>
-      <c r="C192" s="12" t="str">
+      <c r="C192" s="11" t="str">
         <v>Stuck</v>
       </c>
       <c r="D192" s="6" t="str">
@@ -8810,7 +8810,7 @@
       <c r="C194" t="str">
         <v/>
       </c>
-      <c r="D194" s="12" t="str">
+      <c r="D194" s="11" t="str">
         <v>Stuck</v>
       </c>
       <c r="E194" s="6" t="str">
@@ -8842,7 +8842,7 @@
       <c r="B195" t="str">
         <v/>
       </c>
-      <c r="C195" s="12" t="str">
+      <c r="C195" s="11" t="str">
         <v>Stuck</v>
       </c>
       <c r="D195" s="6" t="str">
@@ -8907,7 +8907,7 @@
       <c r="B196" t="str">
         <v/>
       </c>
-      <c r="C196" s="12" t="str">
+      <c r="C196" s="11" t="str">
         <v>Stuck</v>
       </c>
       <c r="D196" s="6" t="str">
@@ -11210,7 +11210,7 @@
       <c r="B238" t="str">
         <v/>
       </c>
-      <c r="C238" s="11" t="str">
+      <c r="C238" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D238" t="str">
@@ -11866,7 +11866,7 @@
       <c r="B250" t="str">
         <v/>
       </c>
-      <c r="C250" s="11" t="str">
+      <c r="C250" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D250" t="str">
@@ -11996,7 +11996,7 @@
       <c r="B252" t="str">
         <v/>
       </c>
-      <c r="C252" s="11" t="str">
+      <c r="C252" s="13" t="str">
         <v>Done</v>
       </c>
       <c r="D252" t="str">

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -797,7 +797,7 @@
         <v/>
       </c>
       <c r="F6" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V2(11.5)</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -832,7 +832,7 @@
         <v/>
       </c>
       <c r="F7" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G7" s="6" t="str">
         <v/>
@@ -867,7 +867,7 @@
         <v/>
       </c>
       <c r="F8" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V2(11.5)</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="F30" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V2(11.5)</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1792,7 +1792,7 @@
         <v/>
       </c>
       <c r="F31" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V2(11.5)</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1827,7 +1827,7 @@
         <v/>
       </c>
       <c r="F32" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V2(11.5)</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1862,7 +1862,7 @@
         <v/>
       </c>
       <c r="F33" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V2(11.5)</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="F34" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V2(11.5)</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1932,7 +1932,7 @@
         <v/>
       </c>
       <c r="F35" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1967,7 +1967,7 @@
         <v/>
       </c>
       <c r="F36" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2002,7 +2002,7 @@
         <v/>
       </c>
       <c r="F37" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2037,7 +2037,7 @@
         <v/>
       </c>
       <c r="F38" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2072,7 +2072,7 @@
         <v/>
       </c>
       <c r="F39" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2107,7 +2107,7 @@
         <v/>
       </c>
       <c r="F40" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2142,7 +2142,7 @@
         <v/>
       </c>
       <c r="F41" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2177,7 +2177,7 @@
         <v/>
       </c>
       <c r="F42" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2212,7 +2212,7 @@
         <v/>
       </c>
       <c r="F43" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2247,7 +2247,7 @@
         <v/>
       </c>
       <c r="F44" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2282,7 +2282,7 @@
         <v/>
       </c>
       <c r="F45" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2317,7 +2317,7 @@
         <v/>
       </c>
       <c r="F46" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3247,7 +3247,7 @@
         <v/>
       </c>
       <c r="F70" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V2(11.5)</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3282,7 +3282,7 @@
         <v/>
       </c>
       <c r="F71" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V2(11.5)</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3317,7 +3317,7 @@
         <v/>
       </c>
       <c r="F72" s="6" t="str">
-        <v>V2(4.5)</v>
+        <v>V2(11.5)</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3352,7 +3352,7 @@
         <v/>
       </c>
       <c r="F73" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3387,7 +3387,7 @@
         <v/>
       </c>
       <c r="F74" s="6" t="str">
-        <v>V3(18.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3422,7 +3422,7 @@
         <v/>
       </c>
       <c r="F75" s="6" t="str">
-        <v>V4(1.6)</v>
+        <v>V4(8.6)</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3457,7 +3457,7 @@
         <v/>
       </c>
       <c r="F76" s="6" t="str">
-        <v>V4(1.6)</v>
+        <v>V4(8.6)</v>
       </c>
       <c r="G76" t="str">
         <v/>

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -10922,7 +10922,7 @@
         <v>46134</v>
       </c>
       <c r="H232" s="6" t="str">
-        <v>V1(20.4)</v>
+        <v/>
       </c>
       <c r="I232" t="str">
         <v/>
@@ -11117,7 +11117,7 @@
         <v/>
       </c>
       <c r="H235" s="6" t="str">
-        <v>V4(8.6)</v>
+        <v/>
       </c>
       <c r="I235" t="str">
         <v/>

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -83,7 +83,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDAB3D"/>
+        <fgColor rgb="FF9D50DD"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,17 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00C875"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDF2F4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9D50DD"/>
+        <fgColor rgb="FF00C875"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,12 +108,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF007F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDAB3D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCAB641"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF007F"/>
+        <fgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
@@ -138,22 +143,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF333333"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBB3354"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF66CCFF"/>
+        <fgColor rgb="FFFF5AC4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF5AC4"/>
+        <fgColor rgb="FF66CCFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -232,6 +232,9 @@
     <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -245,7 +248,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -253,9 +256,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -688,7 +688,7 @@
         <v/>
       </c>
       <c r="C4" s="5" t="str">
-        <v>FE DEV WIP</v>
+        <v>In QA</v>
       </c>
       <c r="D4" s="6" t="str">
         <v>localAcctHome</v>
@@ -785,28 +785,28 @@
         <v/>
       </c>
       <c r="B6" s="4" t="str">
-        <v>Export Transactions</v>
+        <v>IBAN - Add Funds to Local Account (Account Info and launch Open Banking)</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6" s="11" t="str">
-        <v>Done</v>
+        <v>Stuck</v>
       </c>
       <c r="E6" s="6" t="str">
         <v/>
       </c>
       <c r="F6" s="6" t="str">
-        <v>V2(11.5)</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" s="8">
-        <v>46117</v>
-      </c>
-      <c r="I6" s="8">
-        <v>46126</v>
+        <v>V3(25.5)</v>
+      </c>
+      <c r="G6" s="6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -820,13 +820,13 @@
         <v/>
       </c>
       <c r="B7" s="4" t="str">
-        <v>IBAN - Add Funds to Local Account (Account Info and launch Open Banking)</v>
+        <v>Transactional push notifications + logic</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7" s="12" t="str">
-        <v>Stuck</v>
+      <c r="D7" s="5" t="str">
+        <v>Discovery</v>
       </c>
       <c r="E7" s="6" t="str">
         <v/>
@@ -834,14 +834,14 @@
       <c r="F7" s="6" t="str">
         <v>V3(25.5)</v>
       </c>
-      <c r="G7" s="6" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v/>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" s="8">
+        <v>46061</v>
+      </c>
+      <c r="I7" s="8">
+        <v>46061</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -855,28 +855,28 @@
         <v/>
       </c>
       <c r="B8" s="4" t="str">
-        <v>Transactional push notifications + logic</v>
+        <v>Balance Display</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D8" s="12" t="str">
+        <v>Done</v>
       </c>
       <c r="E8" s="6" t="str">
         <v/>
       </c>
       <c r="F8" s="6" t="str">
-        <v>V2(11.5)</v>
+        <v>V1(20.4)</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8" s="8">
-        <v>46061</v>
-      </c>
-      <c r="I8" s="8">
-        <v>46061</v>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -890,12 +890,12 @@
         <v/>
       </c>
       <c r="B9" s="4" t="str">
-        <v>Balance Display</v>
+        <v>Transactions List FE</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
-      <c r="D9" s="11" t="str">
+      <c r="D9" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E9" s="6" t="str">
@@ -925,28 +925,28 @@
         <v/>
       </c>
       <c r="B10" s="4" t="str">
-        <v>Transactions List FE</v>
+        <v>Export Transactions</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
-      <c r="D10" s="11" t="str">
+      <c r="D10" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E10" s="6" t="str">
         <v/>
       </c>
       <c r="F10" s="6" t="str">
-        <v>V1(20.4)</v>
+        <v>V2(11.5)</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v/>
+      <c r="H10" s="8">
+        <v>46117</v>
+      </c>
+      <c r="I10" s="8">
+        <v>46126</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -965,7 +965,7 @@
       <c r="C11" t="str">
         <v/>
       </c>
-      <c r="D11" s="11" t="str">
+      <c r="D11" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E11" s="6" t="str">
@@ -1000,7 +1000,7 @@
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12" s="11" t="str">
+      <c r="D12" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E12" s="6" t="str">
@@ -1035,7 +1035,7 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13" s="11" t="str">
+      <c r="D13" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E13" s="6" t="str">
@@ -1070,7 +1070,7 @@
       <c r="C14" t="str">
         <v/>
       </c>
-      <c r="D14" s="11" t="str">
+      <c r="D14" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E14" s="6" t="str">
@@ -1105,7 +1105,7 @@
       <c r="C15" t="str">
         <v/>
       </c>
-      <c r="D15" s="11" t="str">
+      <c r="D15" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E15" s="6" t="str">
@@ -1137,7 +1137,7 @@
       <c r="B16" t="str">
         <v/>
       </c>
-      <c r="C16" s="13" t="str">
+      <c r="C16" s="5" t="str">
         <v>In QA</v>
       </c>
       <c r="D16" t="str">
@@ -1240,7 +1240,7 @@
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18" s="11" t="str">
+      <c r="D18" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E18" s="6" t="str">
@@ -1275,7 +1275,7 @@
       <c r="C19" t="str">
         <v/>
       </c>
-      <c r="D19" s="11" t="str">
+      <c r="D19" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E19" s="6" t="str">
@@ -1307,7 +1307,7 @@
       <c r="B20" t="str">
         <v/>
       </c>
-      <c r="C20" s="13" t="str">
+      <c r="C20" s="5" t="str">
         <v>In QA</v>
       </c>
       <c r="D20" t="str">
@@ -1410,7 +1410,7 @@
       <c r="C22" t="str">
         <v/>
       </c>
-      <c r="D22" s="11" t="str">
+      <c r="D22" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E22" s="6" t="str">
@@ -1445,7 +1445,7 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23" s="11" t="str">
+      <c r="D23" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E23" s="6" t="str">
@@ -1480,7 +1480,7 @@
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24" s="11" t="str">
+      <c r="D24" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E24" s="6" t="str">
@@ -1510,12 +1510,12 @@
         <v/>
       </c>
       <c r="B25" s="4" t="str">
-        <v>Portfolio touchpoints - move funds- Roy- Ilan to check status</v>
+        <v>Portfolio touchpoints - move funds- Roy-Inbal  to check status</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
-      <c r="D25" s="14" t="str">
+      <c r="D25" s="13" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E25" s="6" t="str">
@@ -1545,19 +1545,19 @@
         <v/>
       </c>
       <c r="B26" s="4" t="str">
-        <v>Execution pop-up  Open &amp; close - move funds- Roy- Ilan to check status</v>
+        <v>Execution pop-up  Open &amp; close - move funds-</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
-      <c r="D26" s="12" t="str">
-        <v>Stuck</v>
+      <c r="D26" s="14" t="str">
+        <v>Groomed</v>
       </c>
       <c r="E26" s="6" t="str">
         <v/>
       </c>
-      <c r="F26" t="str">
-        <v/>
+      <c r="F26" s="6" t="str">
+        <v>V3(25.5)</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1582,7 +1582,7 @@
       <c r="B27" t="str">
         <v/>
       </c>
-      <c r="C27" s="11" t="str">
+      <c r="C27" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D27" t="str">
@@ -1647,7 +1647,7 @@
       <c r="B28" t="str">
         <v/>
       </c>
-      <c r="C28" s="5" t="str">
+      <c r="C28" s="15" t="str">
         <v>FE DEV WIP</v>
       </c>
       <c r="D28" s="6" t="str">
@@ -1750,7 +1750,7 @@
       <c r="C30" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D30" s="15" t="str">
+      <c r="D30" s="16" t="str">
         <v>QA</v>
       </c>
       <c r="E30" s="6" t="str">
@@ -1785,7 +1785,7 @@
       <c r="C31" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D31" s="15" t="str">
+      <c r="D31" s="16" t="str">
         <v>QA</v>
       </c>
       <c r="E31" s="6" t="str">
@@ -1820,7 +1820,7 @@
       <c r="C32" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D32" s="16" t="str">
+      <c r="D32" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E32" s="6" t="str">
@@ -1855,8 +1855,8 @@
       <c r="C33" s="6" t="str">
         <v>Noit Hoffman, Joanna Fajga</v>
       </c>
-      <c r="D33" s="16" t="str">
-        <v>Groomed</v>
+      <c r="D33" s="15" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E33" s="6" t="str">
         <v/>
@@ -1890,7 +1890,7 @@
       <c r="C34" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D34" s="15" t="str">
+      <c r="D34" s="16" t="str">
         <v>QA</v>
       </c>
       <c r="E34" s="6" t="str">
@@ -1925,8 +1925,8 @@
       <c r="C35" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D35" s="13" t="str">
-        <v>Discovery</v>
+      <c r="D35" s="17" t="str">
+        <v>Grooming</v>
       </c>
       <c r="E35" s="6" t="str">
         <v/>
@@ -1960,7 +1960,7 @@
       <c r="C36" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D36" s="13" t="str">
+      <c r="D36" s="5" t="str">
         <v>Discovery</v>
       </c>
       <c r="E36" s="6" t="str">
@@ -1995,7 +1995,7 @@
       <c r="C37" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D37" s="17" t="str">
+      <c r="D37" s="18" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E37" s="6" t="str">
@@ -2030,7 +2030,7 @@
       <c r="C38" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D38" s="17" t="str">
+      <c r="D38" s="18" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E38" s="6" t="str">
@@ -2065,7 +2065,7 @@
       <c r="C39" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D39" s="17" t="str">
+      <c r="D39" s="18" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E39" s="6" t="str">
@@ -2100,7 +2100,7 @@
       <c r="C40" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D40" s="17" t="str">
+      <c r="D40" s="18" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E40" s="6" t="str">
@@ -2135,7 +2135,7 @@
       <c r="C41" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D41" s="17" t="str">
+      <c r="D41" s="18" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E41" s="6" t="str">
@@ -2170,7 +2170,7 @@
       <c r="C42" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D42" s="17" t="str">
+      <c r="D42" s="18" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E42" s="6" t="str">
@@ -2205,7 +2205,7 @@
       <c r="C43" t="str">
         <v/>
       </c>
-      <c r="D43" s="5" t="str">
+      <c r="D43" s="15" t="str">
         <v>Dev - WIP</v>
       </c>
       <c r="E43" s="6" t="str">
@@ -2240,7 +2240,7 @@
       <c r="C44" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D44" s="16" t="str">
+      <c r="D44" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E44" s="6" t="str">
@@ -2275,7 +2275,7 @@
       <c r="C45" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D45" s="16" t="str">
+      <c r="D45" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E45" s="6" t="str">
@@ -2310,7 +2310,7 @@
       <c r="C46" t="str">
         <v/>
       </c>
-      <c r="D46" s="18" t="str">
+      <c r="D46" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E46" s="6" t="str">
@@ -2345,7 +2345,7 @@
       <c r="C47" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D47" s="19" t="str">
+      <c r="D47" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E47" s="6" t="str">
@@ -2380,7 +2380,7 @@
       <c r="C48" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D48" s="19" t="str">
+      <c r="D48" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E48" s="6" t="str">
@@ -2415,7 +2415,7 @@
       <c r="C49" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D49" s="19" t="str">
+      <c r="D49" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E49" s="6" t="str">
@@ -2450,14 +2450,14 @@
       <c r="C50" t="str">
         <v/>
       </c>
-      <c r="D50" s="13" t="str">
+      <c r="D50" s="5" t="str">
         <v>Discovery</v>
       </c>
       <c r="E50" s="6" t="str">
         <v/>
       </c>
-      <c r="F50" t="str">
-        <v/>
+      <c r="F50" s="6" t="str">
+        <v>V3(25.5)</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2482,7 +2482,7 @@
       <c r="B51" t="str">
         <v/>
       </c>
-      <c r="C51" s="5" t="str">
+      <c r="C51" s="15" t="str">
         <v>FE DEV WIP</v>
       </c>
       <c r="D51" t="str">
@@ -2585,7 +2585,7 @@
       <c r="C53" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D53" s="5" t="str">
+      <c r="D53" s="15" t="str">
         <v>Dev - WIP</v>
       </c>
       <c r="E53" s="6" t="str">
@@ -2620,7 +2620,7 @@
       <c r="C54" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D54" s="5" t="str">
+      <c r="D54" s="15" t="str">
         <v>Dev - WIP</v>
       </c>
       <c r="E54" s="6" t="str">
@@ -2655,7 +2655,7 @@
       <c r="C55" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D55" s="5" t="str">
+      <c r="D55" s="15" t="str">
         <v>Dev - WIP</v>
       </c>
       <c r="E55" s="6" t="str">
@@ -2690,7 +2690,7 @@
       <c r="C56" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D56" s="5" t="str">
+      <c r="D56" s="15" t="str">
         <v>Dev - WIP</v>
       </c>
       <c r="E56" s="6" t="str">
@@ -2725,7 +2725,7 @@
       <c r="C57" s="6" t="str">
         <v>Noit Hoffman</v>
       </c>
-      <c r="D57" s="5" t="str">
+      <c r="D57" s="15" t="str">
         <v>Dev - WIP</v>
       </c>
       <c r="E57" s="6" t="str">
@@ -2760,7 +2760,7 @@
       <c r="C58" t="str">
         <v/>
       </c>
-      <c r="D58" s="11" t="str">
+      <c r="D58" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E58" s="6" t="str">
@@ -2795,7 +2795,7 @@
       <c r="C59" t="str">
         <v/>
       </c>
-      <c r="D59" s="17" t="str">
+      <c r="D59" s="18" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E59" s="6" t="str">
@@ -2830,7 +2830,7 @@
       <c r="C60" t="str">
         <v/>
       </c>
-      <c r="D60" s="5" t="str">
+      <c r="D60" s="15" t="str">
         <v>Dev - WIP</v>
       </c>
       <c r="E60" s="6" t="str">
@@ -2862,7 +2862,7 @@
       <c r="B61" t="str">
         <v/>
       </c>
-      <c r="C61" s="15" t="str">
+      <c r="C61" s="16" t="str">
         <v>Grooming</v>
       </c>
       <c r="D61" s="6" t="str">
@@ -2878,7 +2878,7 @@
         <v/>
       </c>
       <c r="H61" s="6" t="str">
-        <v>V3(25.5)</v>
+        <v>V4(8.6)</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2965,7 +2965,7 @@
       <c r="C63" t="str">
         <v/>
       </c>
-      <c r="D63" s="20" t="str">
+      <c r="D63" s="17" t="str">
         <v>Grooming</v>
       </c>
       <c r="E63" s="6" t="str">
@@ -3000,7 +3000,7 @@
       <c r="C64" t="str">
         <v/>
       </c>
-      <c r="D64" s="20" t="str">
+      <c r="D64" s="17" t="str">
         <v>Grooming</v>
       </c>
       <c r="E64" s="6" t="str">
@@ -3035,7 +3035,7 @@
       <c r="C65" t="str">
         <v/>
       </c>
-      <c r="D65" s="20" t="str">
+      <c r="D65" s="17" t="str">
         <v>Grooming</v>
       </c>
       <c r="E65" s="6" t="str">
@@ -3067,7 +3067,7 @@
       <c r="B66" t="str">
         <v/>
       </c>
-      <c r="C66" s="5" t="str">
+      <c r="C66" s="15" t="str">
         <v>FE DEV WIP</v>
       </c>
       <c r="D66" s="6" t="str">
@@ -3170,7 +3170,7 @@
       <c r="C68" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D68" s="11" t="str">
+      <c r="D68" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E68" s="6" t="str">
@@ -3205,7 +3205,7 @@
       <c r="C69" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D69" s="11" t="str">
+      <c r="D69" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E69" s="6" t="str">
@@ -3240,7 +3240,7 @@
       <c r="C70" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D70" s="11" t="str">
+      <c r="D70" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E70" s="6" t="str">
@@ -3275,7 +3275,7 @@
       <c r="C71" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D71" s="11" t="str">
+      <c r="D71" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E71" s="6" t="str">
@@ -3310,7 +3310,7 @@
       <c r="C72" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D72" s="11" t="str">
+      <c r="D72" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E72" s="6" t="str">
@@ -3345,8 +3345,8 @@
       <c r="C73" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D73" s="16" t="str">
-        <v>Groomed</v>
+      <c r="D73" s="15" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E73" s="6" t="str">
         <v/>
@@ -3380,7 +3380,7 @@
       <c r="C74" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D74" s="16" t="str">
+      <c r="D74" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E74" s="6" t="str">
@@ -3415,7 +3415,7 @@
       <c r="C75" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D75" s="16" t="str">
+      <c r="D75" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E75" s="6" t="str">
@@ -3450,7 +3450,7 @@
       <c r="C76" s="6" t="str">
         <v>Nikolaus Kulier</v>
       </c>
-      <c r="D76" s="16" t="str">
+      <c r="D76" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E76" s="6" t="str">
@@ -3552,7 +3552,7 @@
       <c r="B79" t="str">
         <v/>
       </c>
-      <c r="C79" s="13" t="str">
+      <c r="C79" s="5" t="str">
         <v>In QA</v>
       </c>
       <c r="D79" s="6" t="str">
@@ -3655,7 +3655,7 @@
       <c r="C81" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D81" s="11" t="str">
+      <c r="D81" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E81" s="6" t="str">
@@ -3690,7 +3690,7 @@
       <c r="C82" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D82" s="11" t="str">
+      <c r="D82" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E82" s="6" t="str">
@@ -3725,7 +3725,7 @@
       <c r="C83" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D83" s="11" t="str">
+      <c r="D83" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E83" s="6" t="str">
@@ -3760,7 +3760,7 @@
       <c r="C84" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D84" s="11" t="str">
+      <c r="D84" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E84" s="6" t="str">
@@ -3795,7 +3795,7 @@
       <c r="C85" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D85" s="11" t="str">
+      <c r="D85" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E85" s="6" t="str">
@@ -3830,7 +3830,7 @@
       <c r="C86" t="str">
         <v/>
       </c>
-      <c r="D86" s="18" t="str">
+      <c r="D86" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E86" s="6" t="str">
@@ -3865,7 +3865,7 @@
       <c r="C87" t="str">
         <v/>
       </c>
-      <c r="D87" s="17" t="str">
+      <c r="D87" s="18" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E87" s="6" t="str">
@@ -3900,7 +3900,7 @@
       <c r="C88" t="str">
         <v/>
       </c>
-      <c r="D88" s="19" t="str">
+      <c r="D88" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E88" s="6" t="str">
@@ -3935,7 +3935,7 @@
       <c r="C89" t="str">
         <v/>
       </c>
-      <c r="D89" s="19" t="str">
+      <c r="D89" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E89" s="6" t="str">
@@ -3970,7 +3970,7 @@
       <c r="C90" t="str">
         <v/>
       </c>
-      <c r="D90" s="19" t="str">
+      <c r="D90" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E90" s="6" t="str">
@@ -4005,7 +4005,7 @@
       <c r="C91" t="str">
         <v/>
       </c>
-      <c r="D91" s="19" t="str">
+      <c r="D91" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E91" s="6" t="str">
@@ -4040,7 +4040,7 @@
       <c r="C92" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D92" s="19" t="str">
+      <c r="D92" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E92" s="6" t="str">
@@ -4075,7 +4075,7 @@
       <c r="C93" t="str">
         <v/>
       </c>
-      <c r="D93" s="14" t="str">
+      <c r="D93" s="13" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E93" s="6" t="str">
@@ -4110,7 +4110,7 @@
       <c r="C94" s="6" t="str">
         <v>Joanna Fajga</v>
       </c>
-      <c r="D94" s="19" t="str">
+      <c r="D94" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E94" s="6" t="str">
@@ -4142,7 +4142,7 @@
       <c r="B95" t="str">
         <v/>
       </c>
-      <c r="C95" s="15" t="str">
+      <c r="C95" s="16" t="str">
         <v>Grooming</v>
       </c>
       <c r="D95" s="6" t="str">
@@ -4158,7 +4158,7 @@
         <v>46134</v>
       </c>
       <c r="H95" s="6" t="str">
-        <v>V3(25.5)</v>
+        <v>V4(8.6)</v>
       </c>
       <c r="I95" s="6" t="str">
         <v>BFF</v>
@@ -4245,7 +4245,7 @@
       <c r="C97" t="str">
         <v/>
       </c>
-      <c r="D97" s="20" t="str">
+      <c r="D97" s="17" t="str">
         <v>Grooming</v>
       </c>
       <c r="E97" s="6" t="str">
@@ -4280,7 +4280,7 @@
       <c r="C98" t="str">
         <v/>
       </c>
-      <c r="D98" s="20" t="str">
+      <c r="D98" s="17" t="str">
         <v>Grooming</v>
       </c>
       <c r="E98" s="6" t="str">
@@ -4315,7 +4315,7 @@
       <c r="C99" t="str">
         <v/>
       </c>
-      <c r="D99" s="18" t="str">
+      <c r="D99" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E99" s="6" t="str">
@@ -4350,7 +4350,7 @@
       <c r="C100" t="str">
         <v/>
       </c>
-      <c r="D100" s="20" t="str">
+      <c r="D100" s="17" t="str">
         <v>Grooming</v>
       </c>
       <c r="E100" s="6" t="str">
@@ -4382,7 +4382,7 @@
       <c r="B101" t="str">
         <v/>
       </c>
-      <c r="C101" s="5" t="str">
+      <c r="C101" s="15" t="str">
         <v>FE DEV WIP</v>
       </c>
       <c r="D101" s="6" t="str">
@@ -4398,7 +4398,7 @@
         <v>46154</v>
       </c>
       <c r="H101" s="6" t="str">
-        <v>V2(11.5)</v>
+        <v>V3(25.5)</v>
       </c>
       <c r="I101" s="6" t="str">
         <v>Freeze Card and Card Status mgmt still requires Design</v>
@@ -4485,7 +4485,7 @@
       <c r="C103" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D103" s="11" t="str">
+      <c r="D103" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E103" s="6" t="str">
@@ -4520,8 +4520,8 @@
       <c r="C104" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D104" s="16" t="str">
-        <v>Groomed</v>
+      <c r="D104" s="15" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E104" s="6" t="str">
         <v/>
@@ -4555,7 +4555,7 @@
       <c r="C105" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D105" s="5" t="str">
+      <c r="D105" s="15" t="str">
         <v>Dev - WIP</v>
       </c>
       <c r="E105" s="6" t="str">
@@ -4590,7 +4590,7 @@
       <c r="C106" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D106" s="5" t="str">
+      <c r="D106" s="15" t="str">
         <v>Dev - WIP</v>
       </c>
       <c r="E106" s="6" t="str">
@@ -4625,7 +4625,7 @@
       <c r="C107" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D107" s="11" t="str">
+      <c r="D107" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E107" s="6" t="str">
@@ -4660,8 +4660,8 @@
       <c r="C108" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D108" s="16" t="str">
-        <v>Groomed</v>
+      <c r="D108" s="15" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E108" s="6" t="str">
         <v/>
@@ -4695,8 +4695,8 @@
       <c r="C109" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D109" s="16" t="str">
-        <v>Groomed</v>
+      <c r="D109" s="15" t="str">
+        <v>Dev - WIP</v>
       </c>
       <c r="E109" s="6" t="str">
         <v/>
@@ -4730,8 +4730,8 @@
       <c r="C110" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D110" s="16" t="str">
-        <v>Groomed</v>
+      <c r="D110" s="22" t="str">
+        <v>OnHold</v>
       </c>
       <c r="E110" s="6" t="str">
         <v/>
@@ -4765,7 +4765,7 @@
       <c r="C111" s="6" t="str">
         <v>Richard Whitehouse, Inbal Escholi</v>
       </c>
-      <c r="D111" s="16" t="str">
+      <c r="D111" s="14" t="str">
         <v>Groomed</v>
       </c>
       <c r="E111" s="6" t="str">
@@ -4800,7 +4800,7 @@
       <c r="C112" s="6" t="str">
         <v>Richard Whitehouse</v>
       </c>
-      <c r="D112" s="11" t="str">
+      <c r="D112" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E112" s="6" t="str">
@@ -4835,7 +4835,7 @@
       <c r="C113" s="6" t="str">
         <v>Richard Whitehouse</v>
       </c>
-      <c r="D113" s="17" t="str">
+      <c r="D113" s="18" t="str">
         <v>futureVersion</v>
       </c>
       <c r="E113" s="6" t="str">
@@ -4867,7 +4867,7 @@
       <c r="B114" t="str">
         <v/>
       </c>
-      <c r="C114" s="5" t="str">
+      <c r="C114" s="15" t="str">
         <v>FE DEV WIP</v>
       </c>
       <c r="D114" t="str">
@@ -4970,7 +4970,7 @@
       <c r="C116" t="str">
         <v/>
       </c>
-      <c r="D116" s="5" t="str">
+      <c r="D116" s="15" t="str">
         <v>Dev - WIP</v>
       </c>
       <c r="E116" s="6" t="str">
@@ -5005,7 +5005,7 @@
       <c r="C117" t="str">
         <v/>
       </c>
-      <c r="D117" s="5" t="str">
+      <c r="D117" s="15" t="str">
         <v>Dev - WIP</v>
       </c>
       <c r="E117" s="6" t="str">
@@ -5037,7 +5037,7 @@
       <c r="B118" t="str">
         <v/>
       </c>
-      <c r="C118" s="18" t="str">
+      <c r="C118" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="D118" s="6" t="str">
@@ -5102,7 +5102,7 @@
       <c r="B119" t="str">
         <v/>
       </c>
-      <c r="C119" s="17" t="str">
+      <c r="C119" s="18" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D119" t="str">
@@ -5205,7 +5205,7 @@
       <c r="C121" t="str">
         <v/>
       </c>
-      <c r="D121" s="14" t="str">
+      <c r="D121" s="13" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E121" s="6" t="str">
@@ -5240,7 +5240,7 @@
       <c r="C122" t="str">
         <v/>
       </c>
-      <c r="D122" s="14" t="str">
+      <c r="D122" s="13" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E122" s="6" t="str">
@@ -5275,7 +5275,7 @@
       <c r="C123" t="str">
         <v/>
       </c>
-      <c r="D123" s="19" t="str">
+      <c r="D123" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E123" s="6" t="str">
@@ -5302,12 +5302,12 @@
     </row>
     <row r="124" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="str">
-        <v>Crypto staking</v>
+        <v>Crypto staking - toggles</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
-      <c r="C124" s="14" t="str">
+      <c r="C124" s="13" t="str">
         <v>Discovery</v>
       </c>
       <c r="D124" t="str">
@@ -5323,7 +5323,7 @@
         <v>46141</v>
       </c>
       <c r="H124" s="6" t="str">
-        <v>V2(11.5)</v>
+        <v>V4(8.6)</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -5372,7 +5372,7 @@
       <c r="B125" t="str">
         <v/>
       </c>
-      <c r="C125" s="11" t="str">
+      <c r="C125" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D125" t="str">
@@ -5475,7 +5475,7 @@
       <c r="C127" s="6" t="str">
         <v>Hagit Zamir</v>
       </c>
-      <c r="D127" s="11" t="str">
+      <c r="D127" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E127" s="6" t="str">
@@ -5510,7 +5510,7 @@
       <c r="C128" t="str">
         <v/>
       </c>
-      <c r="D128" s="11" t="str">
+      <c r="D128" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E128" s="6" t="str">
@@ -5545,7 +5545,7 @@
       <c r="C129" t="str">
         <v/>
       </c>
-      <c r="D129" s="14" t="str">
+      <c r="D129" s="13" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E129" s="6" t="str">
@@ -5580,7 +5580,7 @@
       <c r="C130" t="str">
         <v/>
       </c>
-      <c r="D130" s="14" t="str">
+      <c r="D130" s="13" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E130" s="6" t="str">
@@ -5615,7 +5615,7 @@
       <c r="C131" t="str">
         <v/>
       </c>
-      <c r="D131" s="14" t="str">
+      <c r="D131" s="13" t="str">
         <v>Handle by other team</v>
       </c>
       <c r="E131" s="6" t="str">
@@ -5650,7 +5650,7 @@
       <c r="C132" s="6" t="str">
         <v>Eyal Boas</v>
       </c>
-      <c r="D132" s="19" t="str">
+      <c r="D132" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E132" s="6" t="str">
@@ -5685,7 +5685,7 @@
       <c r="C133" t="str">
         <v/>
       </c>
-      <c r="D133" s="19" t="str">
+      <c r="D133" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E133" s="6" t="str">
@@ -5720,7 +5720,7 @@
       <c r="C134" s="6" t="str">
         <v>Eyal Boas</v>
       </c>
-      <c r="D134" s="19" t="str">
+      <c r="D134" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E134" s="6" t="str">
@@ -5755,7 +5755,7 @@
       <c r="C135" t="str">
         <v/>
       </c>
-      <c r="D135" s="19" t="str">
+      <c r="D135" s="20" t="str">
         <v>Cancelled</v>
       </c>
       <c r="E135" s="6" t="str">
@@ -5787,7 +5787,7 @@
       <c r="B136" t="str">
         <v/>
       </c>
-      <c r="C136" s="15" t="str">
+      <c r="C136" s="16" t="str">
         <v>Grooming</v>
       </c>
       <c r="D136" t="str">
@@ -5890,7 +5890,7 @@
       <c r="C138" t="str">
         <v/>
       </c>
-      <c r="D138" s="20" t="str">
+      <c r="D138" s="17" t="str">
         <v>Grooming</v>
       </c>
       <c r="E138" s="6" t="str">
@@ -5922,7 +5922,7 @@
       <c r="B139" t="str">
         <v/>
       </c>
-      <c r="C139" s="14" t="str">
+      <c r="C139" s="13" t="str">
         <v>Discovery</v>
       </c>
       <c r="D139" s="6" t="str">
@@ -5987,7 +5987,7 @@
       <c r="B140" t="str">
         <v/>
       </c>
-      <c r="C140" s="14" t="str">
+      <c r="C140" s="13" t="str">
         <v>Discovery</v>
       </c>
       <c r="D140" t="str">
@@ -6002,8 +6002,8 @@
       <c r="G140" t="str">
         <v/>
       </c>
-      <c r="H140" t="str">
-        <v/>
+      <c r="H140" s="6" t="str">
+        <v>V3(25.5)</v>
       </c>
       <c r="I140" t="str">
         <v/>
@@ -6052,8 +6052,8 @@
       <c r="B141" t="str">
         <v/>
       </c>
-      <c r="C141" s="5" t="str">
-        <v>FE DEV WIP</v>
+      <c r="C141" s="21" t="str">
+        <v>Cancelled</v>
       </c>
       <c r="D141" t="str">
         <v/>
@@ -6126,10 +6126,10 @@
       <c r="E142" t="str">
         <v/>
       </c>
-      <c r="F142" s="22">
+      <c r="F142" s="23">
         <v>46061</v>
       </c>
-      <c r="G142" s="22">
+      <c r="G142" s="23">
         <v>46160</v>
       </c>
       <c r="H142" t="str">
@@ -6147,7 +6147,7 @@
       <c r="L142" t="str">
         <v/>
       </c>
-      <c r="M142" s="23">
+      <c r="M142" s="24">
         <v>32</v>
       </c>
       <c r="N142" t="str">
@@ -6159,25 +6159,25 @@
       <c r="P142" t="str">
         <v/>
       </c>
-      <c r="Q142" s="24" t="str">
+      <c r="Q142" s="25" t="str">
         <v>2026-02-02 to 2026-04-15</v>
       </c>
       <c r="R142" t="str">
         <v/>
       </c>
-      <c r="S142" s="25" t="str">
-        <v/>
-      </c>
-      <c r="T142" s="22">
+      <c r="S142" s="26" t="str">
+        <v/>
+      </c>
+      <c r="T142" s="23">
         <v>46058</v>
       </c>
-      <c r="U142" s="22">
+      <c r="U142" s="23">
         <v>46114</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="144" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="26" t="str">
+      <c r="A144" s="27" t="str">
         <v>In Focus</v>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       <c r="B146" t="str">
         <v/>
       </c>
-      <c r="C146" s="11" t="str">
+      <c r="C146" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D146" t="str">
@@ -6318,7 +6318,7 @@
       <c r="B147" t="str">
         <v/>
       </c>
-      <c r="C147" s="14" t="str">
+      <c r="C147" s="13" t="str">
         <v>Discovery</v>
       </c>
       <c r="D147" t="str">
@@ -6383,7 +6383,7 @@
       <c r="B148" t="str">
         <v/>
       </c>
-      <c r="C148" s="14" t="str">
+      <c r="C148" s="13" t="str">
         <v>Discovery</v>
       </c>
       <c r="D148" t="str">
@@ -6448,7 +6448,7 @@
       <c r="B149" t="str">
         <v/>
       </c>
-      <c r="C149" s="27" t="str">
+      <c r="C149" s="28" t="str">
         <v>Risk</v>
       </c>
       <c r="D149" t="str">
@@ -6513,7 +6513,7 @@
       <c r="B150" t="str">
         <v/>
       </c>
-      <c r="C150" s="11" t="str">
+      <c r="C150" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D150" t="str">
@@ -6578,7 +6578,7 @@
       <c r="B151" t="str">
         <v/>
       </c>
-      <c r="C151" s="11" t="str">
+      <c r="C151" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D151" t="str">
@@ -6643,7 +6643,7 @@
       <c r="B152" t="str">
         <v/>
       </c>
-      <c r="C152" s="11" t="str">
+      <c r="C152" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D152" t="str">
@@ -6708,7 +6708,7 @@
       <c r="B153" t="str">
         <v/>
       </c>
-      <c r="C153" s="11" t="str">
+      <c r="C153" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D153" t="str">
@@ -6773,7 +6773,7 @@
       <c r="B154" t="str">
         <v/>
       </c>
-      <c r="C154" s="11" t="str">
+      <c r="C154" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D154" t="str">
@@ -6838,7 +6838,7 @@
       <c r="B155" t="str">
         <v/>
       </c>
-      <c r="C155" s="11" t="str">
+      <c r="C155" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D155" t="str">
@@ -6903,7 +6903,7 @@
       <c r="B156" t="str">
         <v/>
       </c>
-      <c r="C156" s="11" t="str">
+      <c r="C156" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D156" t="str">
@@ -6968,7 +6968,7 @@
       <c r="B157" t="str">
         <v/>
       </c>
-      <c r="C157" s="11" t="str">
+      <c r="C157" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D157" t="str">
@@ -7033,7 +7033,7 @@
       <c r="B158" t="str">
         <v/>
       </c>
-      <c r="C158" s="11" t="str">
+      <c r="C158" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D158" t="str">
@@ -7098,7 +7098,7 @@
       <c r="B159" t="str">
         <v/>
       </c>
-      <c r="C159" s="11" t="str">
+      <c r="C159" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D159" t="str">
@@ -7163,7 +7163,7 @@
       <c r="B160" t="str">
         <v/>
       </c>
-      <c r="C160" s="11" t="str">
+      <c r="C160" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D160" s="6" t="str">
@@ -7228,7 +7228,7 @@
       <c r="B161" t="str">
         <v/>
       </c>
-      <c r="C161" s="11" t="str">
+      <c r="C161" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D161" t="str">
@@ -7293,7 +7293,7 @@
       <c r="B162" t="str">
         <v/>
       </c>
-      <c r="C162" s="11" t="str">
+      <c r="C162" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D162" t="str">
@@ -7358,7 +7358,7 @@
       <c r="B163" t="str">
         <v/>
       </c>
-      <c r="C163" s="11" t="str">
+      <c r="C163" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D163" t="str">
@@ -7423,7 +7423,7 @@
       <c r="B164" t="str">
         <v/>
       </c>
-      <c r="C164" s="11" t="str">
+      <c r="C164" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D164" t="str">
@@ -7488,7 +7488,7 @@
       <c r="B165" t="str">
         <v/>
       </c>
-      <c r="C165" s="11" t="str">
+      <c r="C165" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D165" t="str">
@@ -7553,7 +7553,7 @@
       <c r="B166" t="str">
         <v/>
       </c>
-      <c r="C166" s="11" t="str">
+      <c r="C166" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D166" t="str">
@@ -7618,7 +7618,7 @@
       <c r="B167" t="str">
         <v/>
       </c>
-      <c r="C167" s="11" t="str">
+      <c r="C167" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D167" t="str">
@@ -7692,10 +7692,10 @@
       <c r="E168" t="str">
         <v/>
       </c>
-      <c r="F168" s="22">
+      <c r="F168" s="23">
         <v>46054</v>
       </c>
-      <c r="G168" s="22">
+      <c r="G168" s="23">
         <v>46118</v>
       </c>
       <c r="H168" t="str">
@@ -7713,7 +7713,7 @@
       <c r="L168" t="str">
         <v/>
       </c>
-      <c r="M168" s="23">
+      <c r="M168" s="24">
         <v>0</v>
       </c>
       <c r="N168" t="str">
@@ -7725,25 +7725,25 @@
       <c r="P168" t="str">
         <v/>
       </c>
-      <c r="Q168" s="25" t="str">
+      <c r="Q168" s="26" t="str">
         <v/>
       </c>
       <c r="R168" t="str">
         <v/>
       </c>
-      <c r="S168" s="25" t="str">
-        <v/>
-      </c>
-      <c r="T168" s="25" t="str">
-        <v/>
-      </c>
-      <c r="U168" s="25" t="str">
+      <c r="S168" s="26" t="str">
+        <v/>
+      </c>
+      <c r="T168" s="26" t="str">
+        <v/>
+      </c>
+      <c r="U168" s="26" t="str">
         <v/>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="170" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="28" t="str">
+      <c r="A170" s="29" t="str">
         <v>MVP - API /BFF project</v>
       </c>
     </row>
@@ -7819,7 +7819,7 @@
       <c r="B172" t="str">
         <v/>
       </c>
-      <c r="C172" s="11" t="str">
+      <c r="C172" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D172" s="6" t="str">
@@ -7922,7 +7922,7 @@
       <c r="C174" t="str">
         <v/>
       </c>
-      <c r="D174" s="11" t="str">
+      <c r="D174" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E174" s="6" t="str">
@@ -7957,7 +7957,7 @@
       <c r="C175" t="str">
         <v/>
       </c>
-      <c r="D175" s="11" t="str">
+      <c r="D175" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E175" s="6" t="str">
@@ -7992,7 +7992,7 @@
       <c r="C176" s="6" t="str">
         <v>Hagit Zamir</v>
       </c>
-      <c r="D176" s="11" t="str">
+      <c r="D176" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E176" s="6" t="str">
@@ -8027,7 +8027,7 @@
       <c r="C177" t="str">
         <v/>
       </c>
-      <c r="D177" s="11" t="str">
+      <c r="D177" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E177" s="6" t="str">
@@ -8062,7 +8062,7 @@
       <c r="C178" t="str">
         <v/>
       </c>
-      <c r="D178" s="11" t="str">
+      <c r="D178" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E178" s="6" t="str">
@@ -8097,7 +8097,7 @@
       <c r="C179" t="str">
         <v/>
       </c>
-      <c r="D179" s="11" t="str">
+      <c r="D179" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E179" s="6" t="str">
@@ -8132,7 +8132,7 @@
       <c r="C180" t="str">
         <v/>
       </c>
-      <c r="D180" s="11" t="str">
+      <c r="D180" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E180" s="6" t="str">
@@ -8164,7 +8164,7 @@
       <c r="B181" t="str">
         <v/>
       </c>
-      <c r="C181" s="11" t="str">
+      <c r="C181" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D181" s="6" t="str">
@@ -8229,7 +8229,7 @@
       <c r="B182" t="str">
         <v/>
       </c>
-      <c r="C182" s="11" t="str">
+      <c r="C182" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D182" s="6" t="str">
@@ -8332,7 +8332,7 @@
       <c r="C184" t="str">
         <v/>
       </c>
-      <c r="D184" s="11" t="str">
+      <c r="D184" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E184" s="6" t="str">
@@ -8367,7 +8367,7 @@
       <c r="C185" t="str">
         <v/>
       </c>
-      <c r="D185" s="11" t="str">
+      <c r="D185" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E185" s="6" t="str">
@@ -8402,7 +8402,7 @@
       <c r="C186" t="str">
         <v/>
       </c>
-      <c r="D186" s="11" t="str">
+      <c r="D186" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E186" s="6" t="str">
@@ -8437,7 +8437,7 @@
       <c r="C187" t="str">
         <v/>
       </c>
-      <c r="D187" s="11" t="str">
+      <c r="D187" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E187" s="6" t="str">
@@ -8472,7 +8472,7 @@
       <c r="C188" t="str">
         <v/>
       </c>
-      <c r="D188" s="11" t="str">
+      <c r="D188" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E188" s="6" t="str">
@@ -8507,7 +8507,7 @@
       <c r="C189" t="str">
         <v/>
       </c>
-      <c r="D189" s="11" t="str">
+      <c r="D189" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="E189" s="6" t="str">
@@ -8539,7 +8539,7 @@
       <c r="B190" t="str">
         <v/>
       </c>
-      <c r="C190" s="11" t="str">
+      <c r="C190" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D190" t="str">
@@ -8604,7 +8604,7 @@
       <c r="B191" t="str">
         <v/>
       </c>
-      <c r="C191" s="18" t="str">
+      <c r="C191" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="D191" t="str">
@@ -8669,7 +8669,7 @@
       <c r="B192" t="str">
         <v/>
       </c>
-      <c r="C192" s="11" t="str">
+      <c r="C192" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D192" t="str">
@@ -8734,7 +8734,7 @@
       <c r="B193" t="str">
         <v/>
       </c>
-      <c r="C193" s="18" t="str">
+      <c r="C193" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="D193" s="6" t="str">
@@ -8799,7 +8799,7 @@
       <c r="B194" t="str">
         <v/>
       </c>
-      <c r="C194" s="12" t="str">
+      <c r="C194" s="11" t="str">
         <v>Stuck</v>
       </c>
       <c r="D194" s="6" t="str">
@@ -8902,7 +8902,7 @@
       <c r="C196" t="str">
         <v/>
       </c>
-      <c r="D196" s="12" t="str">
+      <c r="D196" s="11" t="str">
         <v>Stuck</v>
       </c>
       <c r="E196" s="6" t="str">
@@ -8934,7 +8934,7 @@
       <c r="B197" t="str">
         <v/>
       </c>
-      <c r="C197" s="12" t="str">
+      <c r="C197" s="11" t="str">
         <v>Stuck</v>
       </c>
       <c r="D197" s="6" t="str">
@@ -8999,7 +8999,7 @@
       <c r="B198" t="str">
         <v/>
       </c>
-      <c r="C198" s="12" t="str">
+      <c r="C198" s="11" t="str">
         <v>Stuck</v>
       </c>
       <c r="D198" s="6" t="str">
@@ -9064,7 +9064,7 @@
       <c r="B199" t="str">
         <v/>
       </c>
-      <c r="C199" s="18" t="str">
+      <c r="C199" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="D199" s="6" t="str">
@@ -9129,7 +9129,7 @@
       <c r="B200" t="str">
         <v/>
       </c>
-      <c r="C200" s="18" t="str">
+      <c r="C200" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="D200" s="6" t="str">
@@ -9194,7 +9194,7 @@
       <c r="B201" t="str">
         <v/>
       </c>
-      <c r="C201" s="14" t="str">
+      <c r="C201" s="13" t="str">
         <v>Discovery</v>
       </c>
       <c r="D201" t="str">
@@ -9259,7 +9259,7 @@
       <c r="B202" t="str">
         <v/>
       </c>
-      <c r="C202" s="14" t="str">
+      <c r="C202" s="13" t="str">
         <v>Discovery</v>
       </c>
       <c r="D202" t="str">
@@ -9454,7 +9454,7 @@
       <c r="B205" t="str">
         <v/>
       </c>
-      <c r="C205" s="17" t="str">
+      <c r="C205" s="18" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D205" s="6" t="str">
@@ -9528,10 +9528,10 @@
       <c r="E206" t="str">
         <v/>
       </c>
-      <c r="F206" s="22">
+      <c r="F206" s="23">
         <v>46036</v>
       </c>
-      <c r="G206" s="22">
+      <c r="G206" s="23">
         <v>46134</v>
       </c>
       <c r="H206" t="str">
@@ -9549,7 +9549,7 @@
       <c r="L206" t="str">
         <v/>
       </c>
-      <c r="M206" s="23">
+      <c r="M206" s="24">
         <v>9</v>
       </c>
       <c r="N206" t="str">
@@ -9561,25 +9561,25 @@
       <c r="P206" t="str">
         <v/>
       </c>
-      <c r="Q206" s="25" t="str">
+      <c r="Q206" s="26" t="str">
         <v/>
       </c>
       <c r="R206" t="str">
         <v/>
       </c>
-      <c r="S206" s="25" t="str">
-        <v/>
-      </c>
-      <c r="T206" s="25" t="str">
-        <v/>
-      </c>
-      <c r="U206" s="25" t="str">
+      <c r="S206" s="26" t="str">
+        <v/>
+      </c>
+      <c r="T206" s="26" t="str">
+        <v/>
+      </c>
+      <c r="U206" s="26" t="str">
         <v/>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="208" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A208" s="29" t="str">
+      <c r="A208" s="30" t="str">
         <v>Not in Money scope/Future versions</v>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       <c r="B210" t="str">
         <v/>
       </c>
-      <c r="C210" s="17" t="str">
+      <c r="C210" s="18" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D210" s="6" t="str">
@@ -9720,7 +9720,7 @@
       <c r="B211" t="str">
         <v/>
       </c>
-      <c r="C211" s="17" t="str">
+      <c r="C211" s="18" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D211" s="6" t="str">
@@ -9785,7 +9785,7 @@
       <c r="B212" t="str">
         <v/>
       </c>
-      <c r="C212" s="17" t="str">
+      <c r="C212" s="18" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D212" s="6" t="str">
@@ -9850,7 +9850,7 @@
       <c r="B213" t="str">
         <v/>
       </c>
-      <c r="C213" s="17" t="str">
+      <c r="C213" s="18" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D213" s="6" t="str">
@@ -9915,7 +9915,7 @@
       <c r="B214" t="str">
         <v/>
       </c>
-      <c r="C214" s="17" t="str">
+      <c r="C214" s="18" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D214" s="6" t="str">
@@ -9981,7 +9981,7 @@
       <c r="B215" t="str">
         <v/>
       </c>
-      <c r="C215" s="17" t="str">
+      <c r="C215" s="18" t="str">
         <v>Managed by other team</v>
       </c>
       <c r="D215" s="6" t="str">
@@ -10084,7 +10084,7 @@
       <c r="C217" t="str">
         <v/>
       </c>
-      <c r="D217" s="18" t="str">
+      <c r="D217" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E217" s="6" t="str">
@@ -10119,7 +10119,7 @@
       <c r="C218" t="str">
         <v/>
       </c>
-      <c r="D218" s="18" t="str">
+      <c r="D218" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E218" s="6" t="str">
@@ -10151,7 +10151,7 @@
       <c r="B219" t="str">
         <v/>
       </c>
-      <c r="C219" s="30" t="str">
+      <c r="C219" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D219" s="6" t="str">
@@ -10216,7 +10216,7 @@
       <c r="B220" t="str">
         <v/>
       </c>
-      <c r="C220" s="30" t="str">
+      <c r="C220" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D220" s="6" t="str">
@@ -10281,7 +10281,7 @@
       <c r="B221" t="str">
         <v/>
       </c>
-      <c r="C221" s="30" t="str">
+      <c r="C221" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D221" t="str">
@@ -10384,7 +10384,7 @@
       <c r="C223" t="str">
         <v/>
       </c>
-      <c r="D223" s="18" t="str">
+      <c r="D223" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E223" s="6" t="str">
@@ -10419,7 +10419,7 @@
       <c r="C224" t="str">
         <v/>
       </c>
-      <c r="D224" s="18" t="str">
+      <c r="D224" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="E224" s="6" t="str">
@@ -10451,7 +10451,7 @@
       <c r="B225" t="str">
         <v/>
       </c>
-      <c r="C225" s="30" t="str">
+      <c r="C225" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D225" s="6" t="str">
@@ -10516,7 +10516,7 @@
       <c r="B226" t="str">
         <v/>
       </c>
-      <c r="C226" s="30" t="str">
+      <c r="C226" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D226" s="6" t="str">
@@ -10581,7 +10581,7 @@
       <c r="B227" t="str">
         <v/>
       </c>
-      <c r="C227" s="30" t="str">
+      <c r="C227" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D227" t="str">
@@ -10646,7 +10646,7 @@
       <c r="B228" t="str">
         <v/>
       </c>
-      <c r="C228" s="30" t="str">
+      <c r="C228" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D228" t="str">
@@ -10711,7 +10711,7 @@
       <c r="B229" t="str">
         <v/>
       </c>
-      <c r="C229" s="30" t="str">
+      <c r="C229" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D229" s="6" t="str">
@@ -11036,7 +11036,7 @@
       <c r="B234" t="str">
         <v/>
       </c>
-      <c r="C234" s="30" t="str">
+      <c r="C234" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D234" t="str">
@@ -11101,7 +11101,7 @@
       <c r="B235" t="str">
         <v/>
       </c>
-      <c r="C235" s="30" t="str">
+      <c r="C235" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D235" s="6" t="str">
@@ -11175,10 +11175,10 @@
       <c r="E236" t="str">
         <v/>
       </c>
-      <c r="F236" s="22">
+      <c r="F236" s="23">
         <v>46061</v>
       </c>
-      <c r="G236" s="22">
+      <c r="G236" s="23">
         <v>46134</v>
       </c>
       <c r="H236" t="str">
@@ -11196,7 +11196,7 @@
       <c r="L236" t="str">
         <v/>
       </c>
-      <c r="M236" s="23">
+      <c r="M236" s="24">
         <v>1298</v>
       </c>
       <c r="N236" t="str">
@@ -11208,19 +11208,19 @@
       <c r="P236" t="str">
         <v/>
       </c>
-      <c r="Q236" s="24" t="str">
+      <c r="Q236" s="25" t="str">
         <v>2026-03-02 to 2026-03-23</v>
       </c>
       <c r="R236" t="str">
         <v/>
       </c>
-      <c r="S236" s="25" t="str">
-        <v/>
-      </c>
-      <c r="T236" s="22">
+      <c r="S236" s="26" t="str">
+        <v/>
+      </c>
+      <c r="T236" s="23">
         <v>46104</v>
       </c>
-      <c r="U236" s="22">
+      <c r="U236" s="23">
         <v>46104</v>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       <c r="B240" t="str">
         <v/>
       </c>
-      <c r="C240" s="11" t="str">
+      <c r="C240" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D240" t="str">
@@ -11367,7 +11367,7 @@
       <c r="B241" t="str">
         <v/>
       </c>
-      <c r="C241" s="5" t="str">
+      <c r="C241" s="15" t="str">
         <v>FE DEV WIP</v>
       </c>
       <c r="D241" t="str">
@@ -11432,7 +11432,7 @@
       <c r="B242" t="str">
         <v/>
       </c>
-      <c r="C242" s="5" t="str">
+      <c r="C242" s="15" t="str">
         <v>FE DEV WIP</v>
       </c>
       <c r="D242" t="str">
@@ -11497,7 +11497,7 @@
       <c r="B243" t="str">
         <v/>
       </c>
-      <c r="C243" s="18" t="str">
+      <c r="C243" s="19" t="str">
         <v>Not Started</v>
       </c>
       <c r="D243" t="str">
@@ -11562,7 +11562,7 @@
       <c r="B244" t="str">
         <v/>
       </c>
-      <c r="C244" s="16" t="str">
+      <c r="C244" s="14" t="str">
         <v>Deployment</v>
       </c>
       <c r="D244" t="str">
@@ -11627,7 +11627,7 @@
       <c r="B245" t="str">
         <v/>
       </c>
-      <c r="C245" s="5" t="str">
+      <c r="C245" s="15" t="str">
         <v>FE DEV WIP</v>
       </c>
       <c r="D245" t="str">
@@ -11692,7 +11692,7 @@
       <c r="B246" t="str">
         <v/>
       </c>
-      <c r="C246" s="5" t="str">
+      <c r="C246" s="15" t="str">
         <v>FE DEV WIP</v>
       </c>
       <c r="D246" t="str">
@@ -11757,7 +11757,7 @@
       <c r="B247" t="str">
         <v/>
       </c>
-      <c r="C247" s="14" t="str">
+      <c r="C247" s="13" t="str">
         <v>Discovery</v>
       </c>
       <c r="D247" t="str">
@@ -11831,10 +11831,10 @@
       <c r="E248" t="str">
         <v/>
       </c>
-      <c r="F248" s="22">
+      <c r="F248" s="23">
         <v>46048</v>
       </c>
-      <c r="G248" s="22">
+      <c r="G248" s="23">
         <v>46145</v>
       </c>
       <c r="H248" t="str">
@@ -11852,7 +11852,7 @@
       <c r="L248" t="str">
         <v/>
       </c>
-      <c r="M248" s="23">
+      <c r="M248" s="24">
         <v>0</v>
       </c>
       <c r="N248" t="str">
@@ -11864,25 +11864,25 @@
       <c r="P248" t="str">
         <v/>
       </c>
-      <c r="Q248" s="25" t="str">
+      <c r="Q248" s="26" t="str">
         <v/>
       </c>
       <c r="R248" t="str">
         <v/>
       </c>
-      <c r="S248" s="25" t="str">
-        <v/>
-      </c>
-      <c r="T248" s="25" t="str">
-        <v/>
-      </c>
-      <c r="U248" s="25" t="str">
+      <c r="S248" s="26" t="str">
+        <v/>
+      </c>
+      <c r="T248" s="26" t="str">
+        <v/>
+      </c>
+      <c r="U248" s="26" t="str">
         <v/>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="250" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A250" s="26" t="str">
+      <c r="A250" s="27" t="str">
         <v>Dependencies</v>
       </c>
     </row>
@@ -11958,7 +11958,7 @@
       <c r="B252" t="str">
         <v/>
       </c>
-      <c r="C252" s="11" t="str">
+      <c r="C252" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D252" t="str">
@@ -12088,7 +12088,7 @@
       <c r="B254" t="str">
         <v/>
       </c>
-      <c r="C254" s="11" t="str">
+      <c r="C254" s="12" t="str">
         <v>Done</v>
       </c>
       <c r="D254" t="str">
@@ -12162,10 +12162,10 @@
       <c r="E255" t="str">
         <v/>
       </c>
-      <c r="F255" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G255" s="25" t="str">
+      <c r="F255" s="26" t="str">
+        <v/>
+      </c>
+      <c r="G255" s="26" t="str">
         <v/>
       </c>
       <c r="H255" t="str">
@@ -12183,7 +12183,7 @@
       <c r="L255" t="str">
         <v/>
       </c>
-      <c r="M255" s="23">
+      <c r="M255" s="24">
         <v>0</v>
       </c>
       <c r="N255" t="str">
@@ -12195,19 +12195,19 @@
       <c r="P255" t="str">
         <v/>
       </c>
-      <c r="Q255" s="25" t="str">
+      <c r="Q255" s="26" t="str">
         <v/>
       </c>
       <c r="R255" t="str">
         <v/>
       </c>
-      <c r="S255" s="25" t="str">
-        <v/>
-      </c>
-      <c r="T255" s="25" t="str">
-        <v/>
-      </c>
-      <c r="U255" s="25" t="str">
+      <c r="S255" s="26" t="str">
+        <v/>
+      </c>
+      <c r="T255" s="26" t="str">
+        <v/>
+      </c>
+      <c r="U255" s="26" t="str">
         <v/>
       </c>
     </row>

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -3156,7 +3156,7 @@
         <v>46112</v>
       </c>
       <c r="H67" s="6" t="str">
-        <v>V2(11.5), V3(25.5), V1(20.4), V5(15.6), V4(8.6)</v>
+        <v>V2(11.5), V3(25.5), V1(20.4), V4(8.6)</v>
       </c>
       <c r="I67" t="str">
         <v/>

--- a/data/board-export.xlsx
+++ b/data/board-export.xlsx
@@ -148,17 +148,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF5AC4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF757575"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF66CCFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF5AC4"/>
       </patternFill>
     </fill>
   </fills>
@@ -240,6 +240,9 @@
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -253,7 +256,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -261,9 +264,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4180,8 +4180,8 @@
       <c r="B95" t="str">
         <v/>
       </c>
-      <c r="C95" s="12" t="str">
-        <v>Stuck</v>
+      <c r="C95" s="22" t="str">
+        <v>Future Version</v>
       </c>
       <c r="D95" s="6" t="str">
         <v>withdrawWizard</v>
@@ -5410,7 +5410,7 @@
       <c r="B125" t="str">
         <v/>
       </c>
-      <c r="C125" s="22" t="str">
+      <c r="C125" s="23" t="str">
         <v>Groomed</v>
       </c>
       <c r="D125" t="str">
@@ -5950,8 +5950,8 @@
       <c r="G134" t="str">
         <v/>
       </c>
-      <c r="H134" t="str">
-        <v/>
+      <c r="H134" s="6" t="str">
+        <v>V3(25.5)</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -6009,10 +6009,10 @@
       <c r="E135" t="str">
         <v/>
       </c>
-      <c r="F135" s="23">
+      <c r="F135" s="24">
         <v>46061</v>
       </c>
-      <c r="G135" s="23">
+      <c r="G135" s="24">
         <v>46160</v>
       </c>
       <c r="H135" t="str">
@@ -6030,7 +6030,7 @@
       <c r="L135" t="str">
         <v/>
       </c>
-      <c r="M135" s="24">
+      <c r="M135" s="25">
         <v>30</v>
       </c>
       <c r="N135" t="str">
@@ -6042,25 +6042,25 @@
       <c r="P135" t="str">
         <v/>
       </c>
-      <c r="Q135" s="25" t="str">
+      <c r="Q135" s="26" t="str">
         <v>2026-02-02 to 2026-04-15</v>
       </c>
       <c r="R135" t="str">
         <v/>
       </c>
-      <c r="S135" s="26" t="str">
-        <v/>
-      </c>
-      <c r="T135" s="23">
+      <c r="S135" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T135" s="24">
         <v>46058</v>
       </c>
-      <c r="U135" s="23">
+      <c r="U135" s="24">
         <v>46114</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="137" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="27" t="str">
+      <c r="A137" s="28" t="str">
         <v>In Focus</v>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       <c r="B142" t="str">
         <v/>
       </c>
-      <c r="C142" s="28" t="str">
+      <c r="C142" s="29" t="str">
         <v>Risk</v>
       </c>
       <c r="D142" t="str">
@@ -7640,10 +7640,10 @@
       <c r="E162" t="str">
         <v/>
       </c>
-      <c r="F162" s="23">
+      <c r="F162" s="24">
         <v>46054</v>
       </c>
-      <c r="G162" s="23">
+      <c r="G162" s="24">
         <v>46118</v>
       </c>
       <c r="H162" t="str">
@@ -7661,7 +7661,7 @@
       <c r="L162" t="str">
         <v/>
       </c>
-      <c r="M162" s="24">
+      <c r="M162" s="25">
         <v>0</v>
       </c>
       <c r="N162" t="str">
@@ -7673,25 +7673,25 @@
       <c r="P162" t="str">
         <v/>
       </c>
-      <c r="Q162" s="26" t="str">
+      <c r="Q162" s="27" t="str">
         <v/>
       </c>
       <c r="R162" t="str">
         <v/>
       </c>
-      <c r="S162" s="26" t="str">
-        <v/>
-      </c>
-      <c r="T162" s="26" t="str">
-        <v/>
-      </c>
-      <c r="U162" s="26" t="str">
+      <c r="S162" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T162" s="27" t="str">
+        <v/>
+      </c>
+      <c r="U162" s="27" t="str">
         <v/>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="164" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="29" t="str">
+      <c r="A164" s="30" t="str">
         <v>MVP - API /BFF project</v>
       </c>
     </row>
@@ -9891,10 +9891,10 @@
       <c r="E211" t="str">
         <v/>
       </c>
-      <c r="F211" s="23">
+      <c r="F211" s="24">
         <v>46036</v>
       </c>
-      <c r="G211" s="23">
+      <c r="G211" s="24">
         <v>46134</v>
       </c>
       <c r="H211" t="str">
@@ -9912,7 +9912,7 @@
       <c r="L211" t="str">
         <v/>
       </c>
-      <c r="M211" s="24">
+      <c r="M211" s="25">
         <v>11</v>
       </c>
       <c r="N211" t="str">
@@ -9924,25 +9924,25 @@
       <c r="P211" t="str">
         <v/>
       </c>
-      <c r="Q211" s="26" t="str">
+      <c r="Q211" s="27" t="str">
         <v/>
       </c>
       <c r="R211" t="str">
         <v/>
       </c>
-      <c r="S211" s="26" t="str">
-        <v/>
-      </c>
-      <c r="T211" s="26" t="str">
-        <v/>
-      </c>
-      <c r="U211" s="26" t="str">
+      <c r="S211" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T211" s="27" t="str">
+        <v/>
+      </c>
+      <c r="U211" s="27" t="str">
         <v/>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="213" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A213" s="30" t="str">
+      <c r="A213" s="31" t="str">
         <v>Not in Money scope/Future versions</v>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       <c r="B224" t="str">
         <v/>
       </c>
-      <c r="C224" s="31" t="str">
+      <c r="C224" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D224" s="6" t="str">
@@ -10579,7 +10579,7 @@
       <c r="B225" t="str">
         <v/>
       </c>
-      <c r="C225" s="31" t="str">
+      <c r="C225" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D225" s="6" t="str">
@@ -10644,7 +10644,7 @@
       <c r="B226" t="str">
         <v/>
       </c>
-      <c r="C226" s="31" t="str">
+      <c r="C226" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D226" t="str">
@@ -10814,7 +10814,7 @@
       <c r="B230" t="str">
         <v/>
       </c>
-      <c r="C230" s="31" t="str">
+      <c r="C230" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D230" s="6" t="str">
@@ -10879,7 +10879,7 @@
       <c r="B231" t="str">
         <v/>
       </c>
-      <c r="C231" s="31" t="str">
+      <c r="C231" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D231" s="6" t="str">
@@ -10944,7 +10944,7 @@
       <c r="B232" t="str">
         <v/>
       </c>
-      <c r="C232" s="31" t="str">
+      <c r="C232" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D232" t="str">
@@ -11009,7 +11009,7 @@
       <c r="B233" t="str">
         <v/>
       </c>
-      <c r="C233" s="31" t="str">
+      <c r="C233" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D233" t="str">
@@ -11074,7 +11074,7 @@
       <c r="B234" t="str">
         <v/>
       </c>
-      <c r="C234" s="31" t="str">
+      <c r="C234" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D234" s="6" t="str">
@@ -11399,7 +11399,7 @@
       <c r="B239" t="str">
         <v/>
       </c>
-      <c r="C239" s="31" t="str">
+      <c r="C239" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D239" t="str">
@@ -11464,7 +11464,7 @@
       <c r="B240" t="str">
         <v/>
       </c>
-      <c r="C240" s="31" t="str">
+      <c r="C240" s="22" t="str">
         <v>Future Version</v>
       </c>
       <c r="D240" s="6" t="str">
@@ -11538,10 +11538,10 @@
       <c r="E241" t="str">
         <v/>
       </c>
-      <c r="F241" s="23">
+      <c r="F241" s="24">
         <v>46061</v>
       </c>
-      <c r="G241" s="23">
+      <c r="G241" s="24">
         <v>46134</v>
       </c>
       <c r="H241" t="str">
@@ -11559,7 +11559,7 @@
       <c r="L241" t="str">
         <v/>
       </c>
-      <c r="M241" s="24">
+      <c r="M241" s="25">
         <v>1298</v>
       </c>
       <c r="N241" t="str">
@@ -11571,19 +11571,19 @@
       <c r="P241" t="str">
         <v/>
       </c>
-      <c r="Q241" s="25" t="str">
+      <c r="Q241" s="26" t="str">
         <v>2026-03-02 to 2026-03-23</v>
       </c>
       <c r="R241" t="str">
         <v/>
       </c>
-      <c r="S241" s="26" t="str">
-        <v/>
-      </c>
-      <c r="T241" s="23">
+      <c r="S241" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T241" s="24">
         <v>46104</v>
       </c>
-      <c r="U241" s="23">
+      <c r="U241" s="24">
         <v>46104</v>
       </c>
     </row>
@@ -12194,10 +12194,10 @@
       <c r="E253" t="str">
         <v/>
       </c>
-      <c r="F253" s="23">
+      <c r="F253" s="24">
         <v>46048</v>
       </c>
-      <c r="G253" s="23">
+      <c r="G253" s="24">
         <v>46145</v>
       </c>
       <c r="H253" t="str">
@@ -12215,7 +12215,7 @@
       <c r="L253" t="str">
         <v/>
       </c>
-      <c r="M253" s="24">
+      <c r="M253" s="25">
         <v>0</v>
       </c>
       <c r="N253" t="str">
@@ -12227,25 +12227,25 @@
       <c r="P253" t="str">
         <v/>
       </c>
-      <c r="Q253" s="26" t="str">
+      <c r="Q253" s="27" t="str">
         <v/>
       </c>
       <c r="R253" t="str">
         <v/>
       </c>
-      <c r="S253" s="26" t="str">
-        <v/>
-      </c>
-      <c r="T253" s="26" t="str">
-        <v/>
-      </c>
-      <c r="U253" s="26" t="str">
+      <c r="S253" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T253" s="27" t="str">
+        <v/>
+      </c>
+      <c r="U253" s="27" t="str">
         <v/>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="255" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A255" s="27" t="str">
+      <c r="A255" s="28" t="str">
         <v>Dependencies</v>
       </c>
     </row>
@@ -12525,10 +12525,10 @@
       <c r="E260" t="str">
         <v/>
       </c>
-      <c r="F260" s="26" t="str">
-        <v/>
-      </c>
-      <c r="G260" s="26" t="str">
+      <c r="F260" s="27" t="str">
+        <v/>
+      </c>
+      <c r="G260" s="27" t="str">
         <v/>
       </c>
       <c r="H260" t="str">
@@ -12546,7 +12546,7 @@
       <c r="L260" t="str">
         <v/>
       </c>
-      <c r="M260" s="24">
+      <c r="M260" s="25">
         <v>0</v>
       </c>
       <c r="N260" t="str">
@@ -12558,19 +12558,19 @@
       <c r="P260" t="str">
         <v/>
       </c>
-      <c r="Q260" s="26" t="str">
+      <c r="Q260" s="27" t="str">
         <v/>
       </c>
       <c r="R260" t="str">
         <v/>
       </c>
-      <c r="S260" s="26" t="str">
-        <v/>
-      </c>
-      <c r="T260" s="26" t="str">
-        <v/>
-      </c>
-      <c r="U260" s="26" t="str">
+      <c r="S260" s="27" t="str">
+        <v/>
+      </c>
+      <c r="T260" s="27" t="str">
+        <v/>
+      </c>
+      <c r="U260" s="27" t="str">
         <v/>
       </c>
     </row>
